--- a/2022_04_29 PWC Challenge 1 - Hotel Analytics/PWC Dashboard.xlsx
+++ b/2022_04_29 PWC Challenge 1 - Hotel Analytics/PWC Dashboard.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seoul\Dropbox\00 technical\github\kimep-data-science-lab\2022_04_29 PWC Challenge 1 - Hotel Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F2D73E-114D-45A7-AD50-BB2F95C8B32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20F72B8-DE5E-42A4-A84D-BD050A2A280F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AACBAEBD-F012-4269-A3B9-168C8D706687}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{AACBAEBD-F012-4269-A3B9-168C8D706687}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Validation for Sheet1" sheetId="3" r:id="rId2"/>
     <sheet name="Data for Sheet 1" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="45">
   <si>
     <t>Month</t>
   </si>
@@ -133,6 +134,48 @@
   </si>
   <si>
     <t>One Suite</t>
+  </si>
+  <si>
+    <t>P1Label</t>
+  </si>
+  <si>
+    <t>P2Label</t>
+  </si>
+  <si>
+    <t>P3Label</t>
+  </si>
+  <si>
+    <t>P2Count</t>
+  </si>
+  <si>
+    <t>P3Count</t>
+  </si>
+  <si>
+    <t>P1Count</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>Smell</t>
+  </si>
+  <si>
+    <t>Noise</t>
+  </si>
+  <si>
+    <t>Problem</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P3</t>
   </si>
 </sst>
 </file>
@@ -293,6 +336,9 @@
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -302,9 +348,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -479,40 +522,40 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1.068888888888889</c:v>
+                  <c:v>1.0811688311688312</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.97354497354497349</c:v>
+                  <c:v>1.1353305785123966</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0579710144927537</c:v>
+                  <c:v>1.0537190082644627</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0318930041152263</c:v>
+                  <c:v>1.0088383838383839</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.96825396825396826</c:v>
+                  <c:v>0.97443181818181823</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0648148148148149</c:v>
+                  <c:v>0.79242424242424248</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0622222222222222</c:v>
+                  <c:v>0.43039772727272729</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.93888888888888888</c:v>
+                  <c:v>0.37926136363636365</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.97839506172839508</c:v>
+                  <c:v>0.36969696969696969</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.99801587301587302</c:v>
+                  <c:v>0.25852272727272729</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.98472222222222228</c:v>
+                  <c:v>0.22727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.047979797979798</c:v>
+                  <c:v>0.18545454545454546</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -660,40 +703,40 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1.2992222222222223</c:v>
+                  <c:v>1.6474837662337662</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.92824808935920045</c:v>
+                  <c:v>1.4303891184573003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0468438003220613</c:v>
+                  <c:v>0.93027872305947168</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4516323731138545</c:v>
+                  <c:v>0.77790156466627058</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0551984126984126</c:v>
+                  <c:v>0.52562388591800357</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.86090534979423872</c:v>
+                  <c:v>0.61328282828282832</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0239012345679013</c:v>
+                  <c:v>9.8697916666666663E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.73932098765432097</c:v>
+                  <c:v>6.5364583333333337E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.83681069958847731</c:v>
+                  <c:v>9.0136660724896026E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0660163139329806</c:v>
+                  <c:v>3.7026515151515151E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.98617283950617285</c:v>
+                  <c:v>3.928872053872054E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.1762830323436384</c:v>
+                  <c:v>3.6942148760330577E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -841,40 +884,40 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1.3711728395061729</c:v>
+                  <c:v>1.6248308982683983</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.97817460317460314</c:v>
+                  <c:v>1.3619146005509641</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0215378421900161</c:v>
+                  <c:v>0.95186272524802595</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4414609053497942</c:v>
+                  <c:v>0.79917017587317318</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0694113756613757</c:v>
+                  <c:v>0.5418293363078639</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.83944187242798352</c:v>
+                  <c:v>0.66029040404040407</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0397222222222222</c:v>
+                  <c:v>0.10292376893939394</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.79558641975308642</c:v>
+                  <c:v>6.8714488636363633E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.83374485596707815</c:v>
+                  <c:v>8.3333333333333329E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.1372078924162257</c:v>
+                  <c:v>3.7109375E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.91543209876543208</c:v>
+                  <c:v>3.8457491582491579E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.1305970149253732</c:v>
+                  <c:v>3.8223140495867766E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9641,228 +9684,228 @@
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="2:5" ht="29" thickBot="1">
-      <c r="B3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
+      <c r="B3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
     </row>
     <row r="5" spans="2:5" ht="18.5">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="8" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="15.5">
-      <c r="B6" s="9">
+      <c r="B6" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M2,IF($B$3="King",'Data for Sheet 1'!M14,IF($B$3="Superior King",'Data for Sheet 1'!M26,IF($B$3="Executive",'Data for Sheet 1'!M38,IF($B$3="One Club",'Data for Sheet 1'!M50,'Data for Sheet 1'!M62)))))</f>
-        <v>1.068888888888889</v>
-      </c>
-      <c r="C6" s="9">
+        <v>1.0811688311688312</v>
+      </c>
+      <c r="C6" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N2,IF($B$3="King",'Data for Sheet 1'!N14,IF($B$3="Superior King",'Data for Sheet 1'!N26,IF($B$3="Executive",'Data for Sheet 1'!N38,IF($B$3="One Club",'Data for Sheet 1'!N50,'Data for Sheet 1'!N62)))))</f>
-        <v>1.2992222222222223</v>
-      </c>
-      <c r="D6" s="9">
+        <v>1.6474837662337662</v>
+      </c>
+      <c r="D6" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O2,IF($B$3="King",'Data for Sheet 1'!O14,IF($B$3="Superior King",'Data for Sheet 1'!O26,IF($B$3="Executive",'Data for Sheet 1'!O38,IF($B$3="One Club",'Data for Sheet 1'!O50,'Data for Sheet 1'!O62)))))</f>
-        <v>1.3711728395061729</v>
-      </c>
-      <c r="E6" s="10">
+        <v>1.6248308982683983</v>
+      </c>
+      <c r="E6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="15.5">
-      <c r="B7" s="9">
+      <c r="B7" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M3,IF($B$3="King",'Data for Sheet 1'!M15,IF($B$3="Superior King",'Data for Sheet 1'!M27,IF($B$3="Executive",'Data for Sheet 1'!M39,IF($B$3="One Club",'Data for Sheet 1'!M51,'Data for Sheet 1'!M63)))))</f>
-        <v>0.97354497354497349</v>
-      </c>
-      <c r="C7" s="9">
+        <v>1.1353305785123966</v>
+      </c>
+      <c r="C7" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N3,IF($B$3="King",'Data for Sheet 1'!N15,IF($B$3="Superior King",'Data for Sheet 1'!N27,IF($B$3="Executive",'Data for Sheet 1'!N39,IF($B$3="One Club",'Data for Sheet 1'!N51,'Data for Sheet 1'!N63)))))</f>
-        <v>0.92824808935920045</v>
-      </c>
-      <c r="D7" s="9">
+        <v>1.4303891184573003</v>
+      </c>
+      <c r="D7" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O3,IF($B$3="King",'Data for Sheet 1'!O15,IF($B$3="Superior King",'Data for Sheet 1'!O27,IF($B$3="Executive",'Data for Sheet 1'!O39,IF($B$3="One Club",'Data for Sheet 1'!O51,'Data for Sheet 1'!O63)))))</f>
-        <v>0.97817460317460314</v>
-      </c>
-      <c r="E7" s="10">
+        <v>1.3619146005509641</v>
+      </c>
+      <c r="E7" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="15.5">
-      <c r="B8" s="9">
+      <c r="B8" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M4,IF($B$3="King",'Data for Sheet 1'!M16,IF($B$3="Superior King",'Data for Sheet 1'!M28,IF($B$3="Executive",'Data for Sheet 1'!M40,IF($B$3="One Club",'Data for Sheet 1'!M52,'Data for Sheet 1'!M64)))))</f>
-        <v>1.0579710144927537</v>
-      </c>
-      <c r="C8" s="9">
+        <v>1.0537190082644627</v>
+      </c>
+      <c r="C8" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N4,IF($B$3="King",'Data for Sheet 1'!N16,IF($B$3="Superior King",'Data for Sheet 1'!N28,IF($B$3="Executive",'Data for Sheet 1'!N40,IF($B$3="One Club",'Data for Sheet 1'!N52,'Data for Sheet 1'!N64)))))</f>
-        <v>1.0468438003220613</v>
-      </c>
-      <c r="D8" s="9">
+        <v>0.93027872305947168</v>
+      </c>
+      <c r="D8" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O4,IF($B$3="King",'Data for Sheet 1'!O16,IF($B$3="Superior King",'Data for Sheet 1'!O28,IF($B$3="Executive",'Data for Sheet 1'!O40,IF($B$3="One Club",'Data for Sheet 1'!O52,'Data for Sheet 1'!O64)))))</f>
-        <v>1.0215378421900161</v>
-      </c>
-      <c r="E8" s="10">
+        <v>0.95186272524802595</v>
+      </c>
+      <c r="E8" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="15.5">
-      <c r="B9" s="9">
+      <c r="B9" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M5,IF($B$3="King",'Data for Sheet 1'!M17,IF($B$3="Superior King",'Data for Sheet 1'!M29,IF($B$3="Executive",'Data for Sheet 1'!M41,IF($B$3="One Club",'Data for Sheet 1'!M53,'Data for Sheet 1'!M65)))))</f>
-        <v>1.0318930041152263</v>
-      </c>
-      <c r="C9" s="9">
+        <v>1.0088383838383839</v>
+      </c>
+      <c r="C9" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N5,IF($B$3="King",'Data for Sheet 1'!N17,IF($B$3="Superior King",'Data for Sheet 1'!N29,IF($B$3="Executive",'Data for Sheet 1'!N41,IF($B$3="One Club",'Data for Sheet 1'!N53,'Data for Sheet 1'!N65)))))</f>
-        <v>1.4516323731138545</v>
-      </c>
-      <c r="D9" s="9">
+        <v>0.77790156466627058</v>
+      </c>
+      <c r="D9" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O5,IF($B$3="King",'Data for Sheet 1'!O17,IF($B$3="Superior King",'Data for Sheet 1'!O29,IF($B$3="Executive",'Data for Sheet 1'!O41,IF($B$3="One Club",'Data for Sheet 1'!O53,'Data for Sheet 1'!O65)))))</f>
-        <v>1.4414609053497942</v>
-      </c>
-      <c r="E9" s="10">
+        <v>0.79917017587317318</v>
+      </c>
+      <c r="E9" s="7">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="15.5">
-      <c r="B10" s="9">
+      <c r="B10" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M6,IF($B$3="King",'Data for Sheet 1'!M18,IF($B$3="Superior King",'Data for Sheet 1'!M30,IF($B$3="Executive",'Data for Sheet 1'!M42,IF($B$3="One Club",'Data for Sheet 1'!M54,'Data for Sheet 1'!M66)))))</f>
-        <v>0.96825396825396826</v>
-      </c>
-      <c r="C10" s="9">
+        <v>0.97443181818181823</v>
+      </c>
+      <c r="C10" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N6,IF($B$3="King",'Data for Sheet 1'!N18,IF($B$3="Superior King",'Data for Sheet 1'!N30,IF($B$3="Executive",'Data for Sheet 1'!N42,IF($B$3="One Club",'Data for Sheet 1'!N54,'Data for Sheet 1'!N66)))))</f>
-        <v>1.0551984126984126</v>
-      </c>
-      <c r="D10" s="9">
+        <v>0.52562388591800357</v>
+      </c>
+      <c r="D10" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O6,IF($B$3="King",'Data for Sheet 1'!O18,IF($B$3="Superior King",'Data for Sheet 1'!O30,IF($B$3="Executive",'Data for Sheet 1'!O42,IF($B$3="One Club",'Data for Sheet 1'!O54,'Data for Sheet 1'!O66)))))</f>
-        <v>1.0694113756613757</v>
-      </c>
-      <c r="E10" s="10">
+        <v>0.5418293363078639</v>
+      </c>
+      <c r="E10" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="15.5">
-      <c r="B11" s="9">
+      <c r="B11" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M7,IF($B$3="King",'Data for Sheet 1'!M19,IF($B$3="Superior King",'Data for Sheet 1'!M31,IF($B$3="Executive",'Data for Sheet 1'!M43,IF($B$3="One Club",'Data for Sheet 1'!M55,'Data for Sheet 1'!M67)))))</f>
-        <v>1.0648148148148149</v>
-      </c>
-      <c r="C11" s="9">
+        <v>0.79242424242424248</v>
+      </c>
+      <c r="C11" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N7,IF($B$3="King",'Data for Sheet 1'!N19,IF($B$3="Superior King",'Data for Sheet 1'!N31,IF($B$3="Executive",'Data for Sheet 1'!N43,IF($B$3="One Club",'Data for Sheet 1'!N55,'Data for Sheet 1'!N67)))))</f>
-        <v>0.86090534979423872</v>
-      </c>
-      <c r="D11" s="9">
+        <v>0.61328282828282832</v>
+      </c>
+      <c r="D11" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O7,IF($B$3="King",'Data for Sheet 1'!O19,IF($B$3="Superior King",'Data for Sheet 1'!O31,IF($B$3="Executive",'Data for Sheet 1'!O43,IF($B$3="One Club",'Data for Sheet 1'!O55,'Data for Sheet 1'!O67)))))</f>
-        <v>0.83944187242798352</v>
-      </c>
-      <c r="E11" s="10">
+        <v>0.66029040404040407</v>
+      </c>
+      <c r="E11" s="7">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="15.5">
-      <c r="B12" s="9">
+      <c r="B12" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M8,IF($B$3="King",'Data for Sheet 1'!M20,IF($B$3="Superior King",'Data for Sheet 1'!M32,IF($B$3="Executive",'Data for Sheet 1'!M44,IF($B$3="One Club",'Data for Sheet 1'!M56,'Data for Sheet 1'!M68)))))</f>
-        <v>1.0622222222222222</v>
-      </c>
-      <c r="C12" s="9">
+        <v>0.43039772727272729</v>
+      </c>
+      <c r="C12" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N8,IF($B$3="King",'Data for Sheet 1'!N20,IF($B$3="Superior King",'Data for Sheet 1'!N32,IF($B$3="Executive",'Data for Sheet 1'!N44,IF($B$3="One Club",'Data for Sheet 1'!N56,'Data for Sheet 1'!N68)))))</f>
-        <v>1.0239012345679013</v>
-      </c>
-      <c r="D12" s="9">
+        <v>9.8697916666666663E-2</v>
+      </c>
+      <c r="D12" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O8,IF($B$3="King",'Data for Sheet 1'!O20,IF($B$3="Superior King",'Data for Sheet 1'!O32,IF($B$3="Executive",'Data for Sheet 1'!O44,IF($B$3="One Club",'Data for Sheet 1'!O56,'Data for Sheet 1'!O68)))))</f>
-        <v>1.0397222222222222</v>
-      </c>
-      <c r="E12" s="10">
+        <v>0.10292376893939394</v>
+      </c>
+      <c r="E12" s="7">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="15.5">
-      <c r="B13" s="9">
+      <c r="B13" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M9,IF($B$3="King",'Data for Sheet 1'!M21,IF($B$3="Superior King",'Data for Sheet 1'!M33,IF($B$3="Executive",'Data for Sheet 1'!M45,IF($B$3="One Club",'Data for Sheet 1'!M57,'Data for Sheet 1'!M69)))))</f>
-        <v>0.93888888888888888</v>
-      </c>
-      <c r="C13" s="9">
+        <v>0.37926136363636365</v>
+      </c>
+      <c r="C13" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N9,IF($B$3="King",'Data for Sheet 1'!N21,IF($B$3="Superior King",'Data for Sheet 1'!N33,IF($B$3="Executive",'Data for Sheet 1'!N45,IF($B$3="One Club",'Data for Sheet 1'!N57,'Data for Sheet 1'!N69)))))</f>
-        <v>0.73932098765432097</v>
-      </c>
-      <c r="D13" s="9">
+        <v>6.5364583333333337E-2</v>
+      </c>
+      <c r="D13" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O9,IF($B$3="King",'Data for Sheet 1'!O21,IF($B$3="Superior King",'Data for Sheet 1'!O33,IF($B$3="Executive",'Data for Sheet 1'!O45,IF($B$3="One Club",'Data for Sheet 1'!O57,'Data for Sheet 1'!O69)))))</f>
-        <v>0.79558641975308642</v>
-      </c>
-      <c r="E13" s="10">
+        <v>6.8714488636363633E-2</v>
+      </c>
+      <c r="E13" s="7">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="15.5">
-      <c r="B14" s="9">
+      <c r="B14" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M10,IF($B$3="King",'Data for Sheet 1'!M22,IF($B$3="Superior King",'Data for Sheet 1'!M34,IF($B$3="Executive",'Data for Sheet 1'!M46,IF($B$3="One Club",'Data for Sheet 1'!M58,'Data for Sheet 1'!M70)))))</f>
-        <v>0.97839506172839508</v>
-      </c>
-      <c r="C14" s="9">
+        <v>0.36969696969696969</v>
+      </c>
+      <c r="C14" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N10,IF($B$3="King",'Data for Sheet 1'!N22,IF($B$3="Superior King",'Data for Sheet 1'!N34,IF($B$3="Executive",'Data for Sheet 1'!N46,IF($B$3="One Club",'Data for Sheet 1'!N58,'Data for Sheet 1'!N70)))))</f>
-        <v>0.83681069958847731</v>
-      </c>
-      <c r="D14" s="9">
+        <v>9.0136660724896026E-2</v>
+      </c>
+      <c r="D14" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O10,IF($B$3="King",'Data for Sheet 1'!O22,IF($B$3="Superior King",'Data for Sheet 1'!O34,IF($B$3="Executive",'Data for Sheet 1'!O46,IF($B$3="One Club",'Data for Sheet 1'!O58,'Data for Sheet 1'!O70)))))</f>
-        <v>0.83374485596707815</v>
-      </c>
-      <c r="E14" s="10">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="E14" s="7">
         <v>9</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="15.5">
-      <c r="B15" s="9">
+      <c r="B15" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M11,IF($B$3="King",'Data for Sheet 1'!M23,IF($B$3="Superior King",'Data for Sheet 1'!M35,IF($B$3="Executive",'Data for Sheet 1'!M47,IF($B$3="One Club",'Data for Sheet 1'!M59,'Data for Sheet 1'!M71)))))</f>
-        <v>0.99801587301587302</v>
-      </c>
-      <c r="C15" s="9">
+        <v>0.25852272727272729</v>
+      </c>
+      <c r="C15" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N11,IF($B$3="King",'Data for Sheet 1'!N23,IF($B$3="Superior King",'Data for Sheet 1'!N35,IF($B$3="Executive",'Data for Sheet 1'!N47,IF($B$3="One Club",'Data for Sheet 1'!N59,'Data for Sheet 1'!N71)))))</f>
-        <v>1.0660163139329806</v>
-      </c>
-      <c r="D15" s="9">
+        <v>3.7026515151515151E-2</v>
+      </c>
+      <c r="D15" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O11,IF($B$3="King",'Data for Sheet 1'!O23,IF($B$3="Superior King",'Data for Sheet 1'!O35,IF($B$3="Executive",'Data for Sheet 1'!O47,IF($B$3="One Club",'Data for Sheet 1'!O59,'Data for Sheet 1'!O71)))))</f>
-        <v>1.1372078924162257</v>
-      </c>
-      <c r="E15" s="10">
+        <v>3.7109375E-2</v>
+      </c>
+      <c r="E15" s="7">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="15.5">
-      <c r="B16" s="9">
+      <c r="B16" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M12,IF($B$3="King",'Data for Sheet 1'!M24,IF($B$3="Superior King",'Data for Sheet 1'!M36,IF($B$3="Executive",'Data for Sheet 1'!M48,IF($B$3="One Club",'Data for Sheet 1'!M60,'Data for Sheet 1'!M72)))))</f>
-        <v>0.98472222222222228</v>
-      </c>
-      <c r="C16" s="9">
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="C16" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N12,IF($B$3="King",'Data for Sheet 1'!N24,IF($B$3="Superior King",'Data for Sheet 1'!N36,IF($B$3="Executive",'Data for Sheet 1'!N48,IF($B$3="One Club",'Data for Sheet 1'!N60,'Data for Sheet 1'!N72)))))</f>
-        <v>0.98617283950617285</v>
-      </c>
-      <c r="D16" s="9">
+        <v>3.928872053872054E-2</v>
+      </c>
+      <c r="D16" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O12,IF($B$3="King",'Data for Sheet 1'!O24,IF($B$3="Superior King",'Data for Sheet 1'!O36,IF($B$3="Executive",'Data for Sheet 1'!O48,IF($B$3="One Club",'Data for Sheet 1'!O60,'Data for Sheet 1'!O72)))))</f>
-        <v>0.91543209876543208</v>
-      </c>
-      <c r="E16" s="10">
+        <v>3.8457491582491579E-2</v>
+      </c>
+      <c r="E16" s="7">
         <v>11</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="15.5">
-      <c r="B17" s="9">
+      <c r="B17" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M13,IF($B$3="King",'Data for Sheet 1'!M25,IF($B$3="Superior King",'Data for Sheet 1'!M37,IF($B$3="Executive",'Data for Sheet 1'!M49,IF($B$3="One Club",'Data for Sheet 1'!M61,'Data for Sheet 1'!M73)))))</f>
-        <v>1.047979797979798</v>
-      </c>
-      <c r="C17" s="9">
+        <v>0.18545454545454546</v>
+      </c>
+      <c r="C17" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N13,IF($B$3="King",'Data for Sheet 1'!N25,IF($B$3="Superior King",'Data for Sheet 1'!N37,IF($B$3="Executive",'Data for Sheet 1'!N49,IF($B$3="One Club",'Data for Sheet 1'!N61,'Data for Sheet 1'!N73)))))</f>
-        <v>1.1762830323436384</v>
-      </c>
-      <c r="D17" s="9">
+        <v>3.6942148760330577E-2</v>
+      </c>
+      <c r="D17" s="6">
         <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O13,IF($B$3="King",'Data for Sheet 1'!O25,IF($B$3="Superior King",'Data for Sheet 1'!O37,IF($B$3="Executive",'Data for Sheet 1'!O49,IF($B$3="One Club",'Data for Sheet 1'!O61,'Data for Sheet 1'!O73)))))</f>
-        <v>1.1305970149253732</v>
-      </c>
-      <c r="E17" s="10">
+        <v>3.8223140495867766E-2</v>
+      </c>
+      <c r="E17" s="7">
         <v>12</v>
       </c>
     </row>
@@ -13699,4 +13742,468 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6482E56F-AAD0-45DD-AED2-1DDF0978065A}">
+  <dimension ref="C4:O28"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="10" max="10" width="11.7265625" customWidth="1"/>
+    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:15">
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s">
+        <v>34</v>
+      </c>
+      <c r="O4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="3:15">
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="3:15">
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="3:15">
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="J7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="3:15">
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="J8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="3:15">
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="3:15">
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="J10" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="3:15">
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+      <c r="J11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="3:15">
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="J12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="3:15">
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>9</v>
+      </c>
+      <c r="J13" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="3:15">
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="J14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="3:15">
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15">
+        <v>11</v>
+      </c>
+      <c r="J15" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="3:15">
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16">
+        <v>12</v>
+      </c>
+      <c r="J16" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="3:12">
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" t="s">
+        <v>39</v>
+      </c>
+      <c r="L17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12">
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" t="s">
+        <v>39</v>
+      </c>
+      <c r="L18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12">
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="J19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K19" t="s">
+        <v>39</v>
+      </c>
+      <c r="L19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="3:12">
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="J20" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" t="s">
+        <v>39</v>
+      </c>
+      <c r="L20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12">
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="J21" t="s">
+        <v>38</v>
+      </c>
+      <c r="K21" t="s">
+        <v>39</v>
+      </c>
+      <c r="L21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12">
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+      <c r="J22" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" t="s">
+        <v>39</v>
+      </c>
+      <c r="L22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12">
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23">
+        <v>7</v>
+      </c>
+      <c r="J23" t="s">
+        <v>38</v>
+      </c>
+      <c r="K23" t="s">
+        <v>39</v>
+      </c>
+      <c r="L23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12">
+      <c r="C24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24">
+        <v>8</v>
+      </c>
+      <c r="J24" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" t="s">
+        <v>39</v>
+      </c>
+      <c r="L24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12">
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25">
+        <v>9</v>
+      </c>
+      <c r="J25" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" t="s">
+        <v>39</v>
+      </c>
+      <c r="L25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12">
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26">
+        <v>10</v>
+      </c>
+      <c r="J26" t="s">
+        <v>38</v>
+      </c>
+      <c r="K26" t="s">
+        <v>39</v>
+      </c>
+      <c r="L26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12">
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27">
+        <v>11</v>
+      </c>
+      <c r="J27" t="s">
+        <v>38</v>
+      </c>
+      <c r="K27" t="s">
+        <v>39</v>
+      </c>
+      <c r="L27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12">
+      <c r="C28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28">
+        <v>12</v>
+      </c>
+      <c r="J28" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" t="s">
+        <v>39</v>
+      </c>
+      <c r="L28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/2022_04_29 PWC Challenge 1 - Hotel Analytics/PWC Dashboard.xlsx
+++ b/2022_04_29 PWC Challenge 1 - Hotel Analytics/PWC Dashboard.xlsx
@@ -8,18 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seoul\Dropbox\00 technical\github\kimep-data-science-lab\2022_04_29 PWC Challenge 1 - Hotel Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20F72B8-DE5E-42A4-A84D-BD050A2A280F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C081C89-67B3-4252-A3CD-C644C6488322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{AACBAEBD-F012-4269-A3B9-168C8D706687}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="6" xr2:uid="{AACBAEBD-F012-4269-A3B9-168C8D706687}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Validation for Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="Data for Sheet 1" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
+    <sheet name="Introduction" sheetId="5" r:id="rId1"/>
+    <sheet name="Plan" sheetId="7" r:id="rId2"/>
+    <sheet name="Revenue Dash" sheetId="1" r:id="rId3"/>
+    <sheet name="Concerns" sheetId="8" r:id="rId4"/>
+    <sheet name="Concerns Dash" sheetId="6" r:id="rId5"/>
+    <sheet name="Revenue - Data" sheetId="2" r:id="rId6"/>
+    <sheet name="Concerns - Data" sheetId="4" r:id="rId7"/>
+    <sheet name="Validation" sheetId="3" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="93">
   <si>
     <t>Month</t>
   </si>
@@ -163,26 +167,173 @@
     <t>Noise</t>
   </si>
   <si>
-    <t>Problem</t>
-  </si>
-  <si>
     <t>Count</t>
   </si>
   <si>
-    <t>P1</t>
+    <t>Normal</t>
   </si>
   <si>
-    <t>P2</t>
+    <t>Club Deluxe, One Club, One Suite</t>
   </si>
   <si>
-    <t>P3</t>
+    <t>Executive, Superior</t>
+  </si>
+  <si>
+    <t>Food &amp; Bar - after March</t>
+  </si>
+  <si>
+    <t>Food - January thru June</t>
+  </si>
+  <si>
+    <t>Months &amp; Year</t>
+  </si>
+  <si>
+    <t>Revenue Types</t>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>Bar</t>
+  </si>
+  <si>
+    <t>Room Types</t>
+  </si>
+  <si>
+    <t>Concerns (11)</t>
+  </si>
+  <si>
+    <t>2019 revenue plan</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Club Deluxe King Room</t>
+  </si>
+  <si>
+    <t>Number of rooms</t>
+  </si>
+  <si>
+    <t>Sum of Revenue Total</t>
+  </si>
+  <si>
+    <t>Sum of Revenue Rooms</t>
+  </si>
+  <si>
+    <t>Sum of Revenue Food</t>
+  </si>
+  <si>
+    <t>Sum of Revenue Bar</t>
+  </si>
+  <si>
+    <t>Average of Occupancy</t>
+  </si>
+  <si>
+    <t>Average of ADR</t>
+  </si>
+  <si>
+    <t>Executive Suite</t>
+  </si>
+  <si>
+    <t>King Suite</t>
+  </si>
+  <si>
+    <t>One-Bedroom Club Room</t>
+  </si>
+  <si>
+    <t>One-Bedroom Suite</t>
+  </si>
+  <si>
+    <t>Superior King Room</t>
+  </si>
+  <si>
+    <t>Total Number of rooms</t>
+  </si>
+  <si>
+    <t>Total Sum of Revenue Total</t>
+  </si>
+  <si>
+    <t>Total Sum of Revenue Rooms</t>
+  </si>
+  <si>
+    <t>Total Sum of Revenue Food</t>
+  </si>
+  <si>
+    <t>Total Sum of Revenue Bar</t>
+  </si>
+  <si>
+    <t>Total Average of Occupancy</t>
+  </si>
+  <si>
+    <t>Total Average of ADR</t>
+  </si>
+  <si>
+    <t>Smells</t>
+  </si>
+  <si>
+    <t>Guests</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>blah blah blah</t>
+  </si>
+  <si>
+    <t>Concern Type</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,8 +388,52 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -263,8 +458,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -324,12 +531,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -348,6 +573,38 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -391,373 +648,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$5</c:f>
+              <c:f>'Revenue Dash'!$B$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Room Revenue</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$E$6:$E$17</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$B$6:$B$17</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1.0811688311688312</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.1353305785123966</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.0537190082644627</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.0088383838383839</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.97443181818181823</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.79242424242424248</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.43039772727272729</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.37926136363636365</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.36969696969696969</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.25852272727272729</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.22727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.18545454545454546</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-887F-4E2A-A864-C35B99865888}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Food Revenue</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="FFC000"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$E$6:$E$17</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$C$6:$C$17</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1.6474837662337662</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.4303891184573003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.93027872305947168</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.77790156466627058</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.52562388591800357</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.61328282828282832</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>9.8697916666666663E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>6.5364583333333337E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9.0136660724896026E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.7026515151515151E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>3.928872053872054E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>3.6942148760330577E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-887F-4E2A-A864-C35B99865888}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Bar Revenue</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -834,7 +729,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$E$6:$E$17</c:f>
+              <c:f>'Revenue Dash'!$E$6:$E$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -879,45 +774,407 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$6:$D$17</c:f>
+              <c:f>'Revenue Dash'!$B$6:$B$17</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1.6248308982683983</c:v>
+                  <c:v>0.95914127423822715</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.3619146005509641</c:v>
+                  <c:v>1.0639952153110048</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.95186272524802595</c:v>
+                  <c:v>1.0440503432494279</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.79917017587317318</c:v>
+                  <c:v>1.037828947368421</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5418293363078639</c:v>
+                  <c:v>1.0171624713958809</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.66029040404040407</c:v>
+                  <c:v>0.92690058479532167</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.10292376893939394</c:v>
+                  <c:v>0.98624401913875603</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.8714488636363633E-2</c:v>
+                  <c:v>0.99542334096109841</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.3333333333333329E-2</c:v>
+                  <c:v>1.0561403508771929</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.7109375E-2</c:v>
+                  <c:v>1.0427631578947369</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.8457491582491579E-2</c:v>
+                  <c:v>1.0007309941520468</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.8223140495867766E-2</c:v>
+                  <c:v>0.97488038277511957</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-887F-4E2A-A864-C35B99865888}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Revenue Dash'!$C$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Food Revenue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Revenue Dash'!$E$6:$E$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Revenue Dash'!$C$6:$C$17</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.78562634656817487</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1251860712387027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0278413424866515</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2092189608636976</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.92134600715836412</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.94291747888239119</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.78847687400318978</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.75115687770150008</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.77903733693207378</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.3246762740183793</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.85878817413905129</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.96106576601932636</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-887F-4E2A-A864-C35B99865888}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Revenue Dash'!$D$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Bar Revenue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Revenue Dash'!$E$6:$E$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Revenue Dash'!$D$6:$D$17</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.82094490612496152</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1200824029771399</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97504031666911006</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.162362792006755</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.88238528075062306</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.8464100064977258</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.81346358320042533</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.77571192473938466</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.73487404408457035</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.3357351712614871</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.88511208576998046</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0148868831321065</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -926,6 +1183,131 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-887F-4E2A-A864-C35B99865888}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Revenue Dash'!$J$6:$J$17</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2846-4184-9A68-CA9E7DD2AEA3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -952,7 +1334,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$E$5</c15:sqref>
+                          <c15:sqref>'Revenue Dash'!$E$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1041,7 +1423,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$E$6:$E$17</c15:sqref>
+                          <c15:sqref>'Revenue Dash'!$E$6:$E$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1092,7 +1474,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$E$6:$E$17</c15:sqref>
+                          <c15:sqref>'Revenue Dash'!$E$6:$E$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1268,9 +1650,7 @@
       <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
+        <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -1342,6 +1722,312 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Concerns!$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Concerns!$C$5:$C$10</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Smells</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Noise</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Temperature</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Guests</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Service</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>blah blah blah</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Concerns!$D$5:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-61C9-4D99-8764-46022B496168}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="597729336"/>
+        <c:axId val="597734136"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="597729336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="597734136"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="597734136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="597729336"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1456,7 +2142,7 @@
             <c:numRef>
               <c:f>[1]Merge!$M$2:$M$13</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.95798319327731096</c:v>
@@ -1534,7 +2220,7 @@
             <c:numRef>
               <c:f>[1]Merge!$N$2:$N$13</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.4710706504824152</c:v>
@@ -1612,7 +2298,7 @@
             <c:numRef>
               <c:f>[1]Merge!$O$2:$O$13</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.85154061624649857</c:v>
@@ -1744,7 +2430,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1776,520 +2462,6 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="452316504"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>King</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="9.9900481189851273E-2"/>
-          <c:y val="0.17634259259259263"/>
-          <c:w val="0.87232174103237092"/>
-          <c:h val="0.61498432487605714"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>[1]Merge!$M$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PercentRoom</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>[1]Merge!$M$14:$M$25</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1.0811688311688312</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.1353305785123966</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.0537190082644627</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.0088383838383839</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.97443181818181823</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.79242424242424248</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.43039772727272729</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.37926136363636365</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.36969696969696969</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.25852272727272729</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.22727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.18545454545454546</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2614-4993-9C03-9485410177EF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>[1]Merge!$N$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PercentFood</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>[1]Merge!$N$14:$N$25</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1.6474837662337662</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.4303891184573003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.93027872305947168</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.77790156466627058</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.52562388591800357</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.61328282828282832</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>9.8697916666666663E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>6.5364583333333337E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9.0136660724896026E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.7026515151515151E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>3.928872053872054E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>3.6942148760330577E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2614-4993-9C03-9485410177EF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>[1]Merge!$O$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PercentBar</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>[1]Merge!$O$14:$O$25</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1.6248308982683983</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.3619146005509641</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.95186272524802595</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.79917017587317318</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.5418293363078639</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.66029040404040407</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.10292376893939394</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>6.8714488636363633E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8.3333333333333329E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.7109375E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>3.8457491582491579E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>3.8223140495867766E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-2614-4993-9C03-9485410177EF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="547977288"/>
-        <c:axId val="547978272"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="547977288"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="547978272"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="547978272"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="547977288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2404,7 +2576,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>SuperiorKing</a:t>
+              <a:t>King</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2440,7 +2612,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.9900481189851273E-2"/>
+          <c:y val="0.17634259259259263"/>
+          <c:w val="0.87232174103237092"/>
+          <c:h val="0.61498432487605714"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -2472,45 +2654,45 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[1]Merge!$M$26:$M$37</c:f>
+              <c:f>[1]Merge!$M$14:$M$25</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.95914127423822715</c:v>
+                  <c:v>1.0811688311688312</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0639952153110048</c:v>
+                  <c:v>1.1353305785123966</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0440503432494279</c:v>
+                  <c:v>1.0537190082644627</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.037828947368421</c:v>
+                  <c:v>1.0088383838383839</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0171624713958809</c:v>
+                  <c:v>0.97443181818181823</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.92690058479532167</c:v>
+                  <c:v>0.79242424242424248</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.98624401913875603</c:v>
+                  <c:v>0.43039772727272729</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.99542334096109841</c:v>
+                  <c:v>0.37926136363636365</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0561403508771929</c:v>
+                  <c:v>0.36969696969696969</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0427631578947369</c:v>
+                  <c:v>0.25852272727272729</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0007309941520468</c:v>
+                  <c:v>0.22727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.97488038277511957</c:v>
+                  <c:v>0.18545454545454546</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2518,7 +2700,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E6DA-46DE-B99B-1852CA58D15B}"/>
+              <c16:uniqueId val="{00000000-2614-4993-9C03-9485410177EF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2550,45 +2732,45 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[1]Merge!$N$26:$N$37</c:f>
+              <c:f>[1]Merge!$N$14:$N$25</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.78562634656817487</c:v>
+                  <c:v>1.6474837662337662</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.1251860712387027</c:v>
+                  <c:v>1.4303891184573003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0278413424866515</c:v>
+                  <c:v>0.93027872305947168</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.2092189608636976</c:v>
+                  <c:v>0.77790156466627058</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.92134600715836412</c:v>
+                  <c:v>0.52562388591800357</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.94291747888239119</c:v>
+                  <c:v>0.61328282828282832</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.78847687400318978</c:v>
+                  <c:v>9.8697916666666663E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.75115687770150008</c:v>
+                  <c:v>6.5364583333333337E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.77903733693207378</c:v>
+                  <c:v>9.0136660724896026E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.3246762740183793</c:v>
+                  <c:v>3.7026515151515151E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.85878817413905129</c:v>
+                  <c:v>3.928872053872054E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.96106576601932636</c:v>
+                  <c:v>3.6942148760330577E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2596,7 +2778,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E6DA-46DE-B99B-1852CA58D15B}"/>
+              <c16:uniqueId val="{00000001-2614-4993-9C03-9485410177EF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2628,45 +2810,45 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[1]Merge!$O$26:$O$37</c:f>
+              <c:f>[1]Merge!$O$14:$O$25</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.82094490612496152</c:v>
+                  <c:v>1.6248308982683983</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.1200824029771399</c:v>
+                  <c:v>1.3619146005509641</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.97504031666911006</c:v>
+                  <c:v>0.95186272524802595</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.162362792006755</c:v>
+                  <c:v>0.79917017587317318</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.88238528075062306</c:v>
+                  <c:v>0.5418293363078639</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8464100064977258</c:v>
+                  <c:v>0.66029040404040407</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.81346358320042533</c:v>
+                  <c:v>0.10292376893939394</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.77571192473938466</c:v>
+                  <c:v>6.8714488636363633E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.73487404408457035</c:v>
+                  <c:v>8.3333333333333329E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.3357351712614871</c:v>
+                  <c:v>3.7109375E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.88511208576998046</c:v>
+                  <c:v>3.8457491582491579E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0148868831321065</c:v>
+                  <c:v>3.8223140495867766E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2674,7 +2856,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-E6DA-46DE-B99B-1852CA58D15B}"/>
+              <c16:uniqueId val="{00000002-2614-4993-9C03-9485410177EF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2687,11 +2869,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="452774736"/>
-        <c:axId val="452771456"/>
+        <c:axId val="547977288"/>
+        <c:axId val="547978272"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="452774736"/>
+        <c:axId val="547977288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2734,7 +2916,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452771456"/>
+        <c:crossAx val="547978272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2742,7 +2924,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="452771456"/>
+        <c:axId val="547978272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2762,7 +2944,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2793,7 +2975,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452774736"/>
+        <c:crossAx val="547977288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2908,7 +3090,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Executive</a:t>
+              <a:t>SuperiorKing</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2976,45 +3158,45 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[1]Merge!$M$38:$M$49</c:f>
+              <c:f>[1]Merge!$M$26:$M$37</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1.068888888888889</c:v>
+                  <c:v>0.95914127423822715</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.97354497354497349</c:v>
+                  <c:v>1.0639952153110048</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0579710144927537</c:v>
+                  <c:v>1.0440503432494279</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0318930041152263</c:v>
+                  <c:v>1.037828947368421</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.96825396825396826</c:v>
+                  <c:v>1.0171624713958809</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0648148148148149</c:v>
+                  <c:v>0.92690058479532167</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0622222222222222</c:v>
+                  <c:v>0.98624401913875603</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.93888888888888888</c:v>
+                  <c:v>0.99542334096109841</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.97839506172839508</c:v>
+                  <c:v>1.0561403508771929</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.99801587301587302</c:v>
+                  <c:v>1.0427631578947369</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.98472222222222228</c:v>
+                  <c:v>1.0007309941520468</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.047979797979798</c:v>
+                  <c:v>0.97488038277511957</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3022,7 +3204,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D1EB-4B8E-B993-31FB6E1CEAD4}"/>
+              <c16:uniqueId val="{00000000-E6DA-46DE-B99B-1852CA58D15B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3054,45 +3236,45 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[1]Merge!$N$38:$N$49</c:f>
+              <c:f>[1]Merge!$N$26:$N$37</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1.2992222222222223</c:v>
+                  <c:v>0.78562634656817487</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.92824808935920045</c:v>
+                  <c:v>1.1251860712387027</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0468438003220613</c:v>
+                  <c:v>1.0278413424866515</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4516323731138545</c:v>
+                  <c:v>1.2092189608636976</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0551984126984126</c:v>
+                  <c:v>0.92134600715836412</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.86090534979423872</c:v>
+                  <c:v>0.94291747888239119</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0239012345679013</c:v>
+                  <c:v>0.78847687400318978</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.73932098765432097</c:v>
+                  <c:v>0.75115687770150008</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.83681069958847731</c:v>
+                  <c:v>0.77903733693207378</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0660163139329806</c:v>
+                  <c:v>1.3246762740183793</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.98617283950617285</c:v>
+                  <c:v>0.85878817413905129</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.1762830323436384</c:v>
+                  <c:v>0.96106576601932636</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3100,7 +3282,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D1EB-4B8E-B993-31FB6E1CEAD4}"/>
+              <c16:uniqueId val="{00000001-E6DA-46DE-B99B-1852CA58D15B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3132,45 +3314,45 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[1]Merge!$O$38:$O$49</c:f>
+              <c:f>[1]Merge!$O$26:$O$37</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1.3711728395061729</c:v>
+                  <c:v>0.82094490612496152</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.97817460317460314</c:v>
+                  <c:v>1.1200824029771399</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0215378421900161</c:v>
+                  <c:v>0.97504031666911006</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4414609053497942</c:v>
+                  <c:v>1.162362792006755</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0694113756613757</c:v>
+                  <c:v>0.88238528075062306</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.83944187242798352</c:v>
+                  <c:v>0.8464100064977258</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0397222222222222</c:v>
+                  <c:v>0.81346358320042533</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.79558641975308642</c:v>
+                  <c:v>0.77571192473938466</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.83374485596707815</c:v>
+                  <c:v>0.73487404408457035</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.1372078924162257</c:v>
+                  <c:v>1.3357351712614871</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.91543209876543208</c:v>
+                  <c:v>0.88511208576998046</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.1305970149253732</c:v>
+                  <c:v>1.0148868831321065</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3178,7 +3360,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D1EB-4B8E-B993-31FB6E1CEAD4}"/>
+              <c16:uniqueId val="{00000002-E6DA-46DE-B99B-1852CA58D15B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3191,11 +3373,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="539138392"/>
-        <c:axId val="552761496"/>
+        <c:axId val="452774736"/>
+        <c:axId val="452771456"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="539138392"/>
+        <c:axId val="452774736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3238,7 +3420,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="552761496"/>
+        <c:crossAx val="452771456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3246,7 +3428,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="552761496"/>
+        <c:axId val="452771456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3266,7 +3448,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3297,7 +3479,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="539138392"/>
+        <c:crossAx val="452774736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3412,7 +3594,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>OneClub</a:t>
+              <a:t>Executive</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3480,45 +3662,45 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[1]Merge!$M$50:$M$61</c:f>
+              <c:f>[1]Merge!$M$38:$M$49</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1.0411764705882354</c:v>
+                  <c:v>1.068888888888889</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0176470588235293</c:v>
+                  <c:v>0.97354497354497349</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.87</c:v>
+                  <c:v>1.0579710144927537</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.79523809523809519</c:v>
+                  <c:v>1.0318930041152263</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.93913043478260871</c:v>
+                  <c:v>0.96825396825396826</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.93</c:v>
+                  <c:v>1.0648148148148149</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.1319999999999999</c:v>
+                  <c:v>1.0622222222222222</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0107142857142857</c:v>
+                  <c:v>0.93888888888888888</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.9285714285714286</c:v>
+                  <c:v>0.97839506172839508</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.92500000000000004</c:v>
+                  <c:v>0.99801587301587302</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.76</c:v>
+                  <c:v>0.98472222222222228</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.85624999999999996</c:v>
+                  <c:v>1.047979797979798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3526,7 +3708,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9DD1-4204-B9DC-25FB9620AAA2}"/>
+              <c16:uniqueId val="{00000000-D1EB-4B8E-B993-31FB6E1CEAD4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3558,45 +3740,45 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[1]Merge!$N$50:$N$61</c:f>
+              <c:f>[1]Merge!$N$38:$N$49</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.46202614379084966</c:v>
+                  <c:v>1.2992222222222223</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.34316993464052287</c:v>
+                  <c:v>0.92824808935920045</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.24977564102564104</c:v>
+                  <c:v>1.0468438003220613</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.21666666666666667</c:v>
+                  <c:v>1.4516323731138545</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.16950947603121516</c:v>
+                  <c:v>1.0551984126984126</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.10038888888888889</c:v>
+                  <c:v>0.86090534979423872</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.5257777777777777</c:v>
+                  <c:v>1.0239012345679013</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.1243452380952381</c:v>
+                  <c:v>0.73932098765432097</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.8662698412698413</c:v>
+                  <c:v>0.83681069958847731</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.62561111111111112</c:v>
+                  <c:v>1.0660163139329806</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.48385185185185187</c:v>
+                  <c:v>0.98617283950617285</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.55869047619047618</c:v>
+                  <c:v>1.1762830323436384</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3604,7 +3786,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9DD1-4204-B9DC-25FB9620AAA2}"/>
+              <c16:uniqueId val="{00000001-D1EB-4B8E-B993-31FB6E1CEAD4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3636,45 +3818,45 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[1]Merge!$O$50:$O$61</c:f>
+              <c:f>[1]Merge!$O$38:$O$49</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.81903594771241828</c:v>
+                  <c:v>1.3711728395061729</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.89468954248366017</c:v>
+                  <c:v>0.97817460317460314</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.68830128205128205</c:v>
+                  <c:v>1.0215378421900161</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.65396946564885494</c:v>
+                  <c:v>1.4414609053497942</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.79108013937282229</c:v>
+                  <c:v>1.0694113756613757</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.89701388888888889</c:v>
+                  <c:v>0.83944187242798352</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.2549444444444444</c:v>
+                  <c:v>1.0397222222222222</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.1268353174603174</c:v>
+                  <c:v>0.79558641975308642</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.94687022900763362</c:v>
+                  <c:v>0.83374485596707815</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.60180555555555559</c:v>
+                  <c:v>1.1372078924162257</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.51148148148148154</c:v>
+                  <c:v>0.91543209876543208</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.56175595238095233</c:v>
+                  <c:v>1.1305970149253732</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3682,7 +3864,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-9DD1-4204-B9DC-25FB9620AAA2}"/>
+              <c16:uniqueId val="{00000002-D1EB-4B8E-B993-31FB6E1CEAD4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3695,11 +3877,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="555230072"/>
-        <c:axId val="555228104"/>
+        <c:axId val="539138392"/>
+        <c:axId val="552761496"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="555230072"/>
+        <c:axId val="539138392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3742,7 +3924,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="555228104"/>
+        <c:crossAx val="552761496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3750,7 +3932,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="555228104"/>
+        <c:axId val="552761496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3770,7 +3952,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3801,7 +3983,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="555230072"/>
+        <c:crossAx val="539138392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3916,6 +4098,510 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
+              <a:t>OneClub</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]Merge!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PercentRoom</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]Merge!$M$50:$M$61</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1.0411764705882354</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0176470588235293</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.79523809523809519</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.93913043478260871</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1319999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0107142857142857</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.9285714285714286</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.92500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.85624999999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9DD1-4204-B9DC-25FB9620AAA2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]Merge!$N$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PercentFood</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]Merge!$N$50:$N$61</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.46202614379084966</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.34316993464052287</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.24977564102564104</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.21666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.16950947603121516</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.10038888888888889</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.5257777777777777</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1243452380952381</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8662698412698413</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.62561111111111112</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.48385185185185187</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.55869047619047618</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9DD1-4204-B9DC-25FB9620AAA2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]Merge!$O$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PercentBar</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]Merge!$O$50:$O$61</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.81903594771241828</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.89468954248366017</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.68830128205128205</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.65396946564885494</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.79108013937282229</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.89701388888888889</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.2549444444444444</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1268353174603174</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.94687022900763362</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.60180555555555559</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.51148148148148154</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.56175595238095233</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9DD1-4204-B9DC-25FB9620AAA2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="555230072"/>
+        <c:axId val="555228104"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="555230072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="555228104"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="555228104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="555230072"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>OneSuite</a:t>
             </a:r>
           </a:p>
@@ -3986,7 +4672,7 @@
             <c:numRef>
               <c:f>[1]Merge!$M$62:$M$73</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.96875</c:v>
@@ -4064,7 +4750,7 @@
             <c:numRef>
               <c:f>[1]Merge!$N$62:$N$73</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.4055121527777778</c:v>
@@ -4142,7 +4828,7 @@
             <c:numRef>
               <c:f>[1]Merge!$O$62:$O$73</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.79166666666666663</c:v>
@@ -4274,7 +4960,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4662,6 +5348,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -5179,7 +5905,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -5287,11 +6013,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -5302,11 +6023,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -5338,9 +6054,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8274,20 +8987,602 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>50801</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>151442</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>254133</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Luxury Hotels Almaty: InterContinental Almaty">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC31EB7B-011A-2F29-65A3-D8C2408689EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="660401" y="335592"/>
+          <a:ext cx="6908932" cy="3461708"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
+      <xdr:colOff>336550</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:rowOff>44450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>273050</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8315,7 +9610,48 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>495299</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E796AEA7-1D8A-2D0C-0691-1EBB63D27364}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -9665,8 +11001,2446 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BCF4362-FBA8-48F8-85F0-F3780936CF85}">
+  <dimension ref="C6:I12"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="6" spans="3:9">
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9">
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9">
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9">
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9">
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9">
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9">
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63BE1CC1-D986-4D23-869E-6D72B1F14DF2}">
+  <dimension ref="B1:O58"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="1.7265625" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="14" width="8.90625" customWidth="1"/>
+    <col min="15" max="15" width="8.90625" style="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" s="13" customFormat="1" ht="19.899999999999999" customHeight="1">
+      <c r="B1" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15">
+      <c r="B3" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N3" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="O3" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15">
+      <c r="B4" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+    </row>
+    <row r="5" spans="2:15">
+      <c r="B5" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5">
+        <v>28</v>
+      </c>
+      <c r="D5">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>28</v>
+      </c>
+      <c r="F5">
+        <v>28</v>
+      </c>
+      <c r="G5">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>28</v>
+      </c>
+      <c r="I5">
+        <v>28</v>
+      </c>
+      <c r="J5">
+        <v>28</v>
+      </c>
+      <c r="K5">
+        <v>28</v>
+      </c>
+      <c r="L5">
+        <v>28</v>
+      </c>
+      <c r="M5">
+        <v>28</v>
+      </c>
+      <c r="N5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15">
+      <c r="B6" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="2">
+        <v>304164</v>
+      </c>
+      <c r="D6" s="2">
+        <v>357840</v>
+      </c>
+      <c r="E6" s="2">
+        <v>445312</v>
+      </c>
+      <c r="F6" s="2">
+        <v>365792</v>
+      </c>
+      <c r="G6" s="2">
+        <v>397600</v>
+      </c>
+      <c r="H6" s="2">
+        <v>322056</v>
+      </c>
+      <c r="I6" s="2">
+        <v>500976</v>
+      </c>
+      <c r="J6" s="2">
+        <v>500976</v>
+      </c>
+      <c r="K6" s="2">
+        <v>333984</v>
+      </c>
+      <c r="L6" s="2">
+        <v>411516</v>
+      </c>
+      <c r="M6" s="2">
+        <v>357840</v>
+      </c>
+      <c r="N6" s="2">
+        <v>370160</v>
+      </c>
+      <c r="O6" s="19">
+        <v>4668216</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15">
+      <c r="B7" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="2">
+        <v>214200</v>
+      </c>
+      <c r="D7" s="2">
+        <v>252000</v>
+      </c>
+      <c r="E7" s="2">
+        <v>313600</v>
+      </c>
+      <c r="F7" s="2">
+        <v>257600</v>
+      </c>
+      <c r="G7" s="2">
+        <v>280000</v>
+      </c>
+      <c r="H7" s="2">
+        <v>226800</v>
+      </c>
+      <c r="I7" s="2">
+        <v>352800</v>
+      </c>
+      <c r="J7" s="2">
+        <v>352800</v>
+      </c>
+      <c r="K7" s="2">
+        <v>235200</v>
+      </c>
+      <c r="L7" s="2">
+        <v>289800</v>
+      </c>
+      <c r="M7" s="2">
+        <v>252000</v>
+      </c>
+      <c r="N7" s="2">
+        <v>260680</v>
+      </c>
+      <c r="O7" s="19">
+        <v>3287480</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="B8" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="2">
+        <v>64260</v>
+      </c>
+      <c r="D8" s="2">
+        <v>75600</v>
+      </c>
+      <c r="E8" s="2">
+        <v>94080</v>
+      </c>
+      <c r="F8" s="2">
+        <v>77280</v>
+      </c>
+      <c r="G8" s="2">
+        <v>84000</v>
+      </c>
+      <c r="H8" s="2">
+        <v>68040</v>
+      </c>
+      <c r="I8" s="2">
+        <v>105840</v>
+      </c>
+      <c r="J8" s="2">
+        <v>105840</v>
+      </c>
+      <c r="K8" s="2">
+        <v>70560</v>
+      </c>
+      <c r="L8" s="2">
+        <v>86940</v>
+      </c>
+      <c r="M8" s="2">
+        <v>75600</v>
+      </c>
+      <c r="N8" s="2">
+        <v>78204</v>
+      </c>
+      <c r="O8" s="19">
+        <v>986244</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="B9" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="2">
+        <v>25704</v>
+      </c>
+      <c r="D9" s="2">
+        <v>30240</v>
+      </c>
+      <c r="E9" s="2">
+        <v>37632</v>
+      </c>
+      <c r="F9" s="2">
+        <v>30912</v>
+      </c>
+      <c r="G9" s="2">
+        <v>33600</v>
+      </c>
+      <c r="H9" s="2">
+        <v>27216</v>
+      </c>
+      <c r="I9" s="2">
+        <v>42336</v>
+      </c>
+      <c r="J9" s="2">
+        <v>42336</v>
+      </c>
+      <c r="K9" s="2">
+        <v>28224</v>
+      </c>
+      <c r="L9" s="2">
+        <v>34776</v>
+      </c>
+      <c r="M9" s="2">
+        <v>30240</v>
+      </c>
+      <c r="N9" s="2">
+        <v>31276</v>
+      </c>
+      <c r="O9" s="19">
+        <v>394492</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" s="23" customFormat="1">
+      <c r="B10" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="21">
+        <v>31</v>
+      </c>
+      <c r="D10" s="21">
+        <v>28</v>
+      </c>
+      <c r="E10" s="21">
+        <v>31</v>
+      </c>
+      <c r="F10" s="21">
+        <v>30</v>
+      </c>
+      <c r="G10" s="21">
+        <v>31</v>
+      </c>
+      <c r="H10" s="21">
+        <v>30</v>
+      </c>
+      <c r="I10" s="21">
+        <v>31</v>
+      </c>
+      <c r="J10" s="21">
+        <v>31</v>
+      </c>
+      <c r="K10" s="21">
+        <v>30</v>
+      </c>
+      <c r="L10" s="21">
+        <v>31</v>
+      </c>
+      <c r="M10" s="21">
+        <v>30</v>
+      </c>
+      <c r="N10" s="21">
+        <v>31</v>
+      </c>
+      <c r="O10" s="22"/>
+    </row>
+    <row r="11" spans="2:15" s="23" customFormat="1">
+      <c r="B11" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="21">
+        <f>C6/C10/C5</f>
+        <v>350.41935483870969</v>
+      </c>
+      <c r="D11" s="21">
+        <f t="shared" ref="D11:N11" si="0">D6/D10/D5</f>
+        <v>456.42857142857144</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="0"/>
+        <v>513.0322580645161</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="0"/>
+        <v>435.4666666666667</v>
+      </c>
+      <c r="G11" s="21">
+        <f t="shared" si="0"/>
+        <v>458.06451612903226</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="0"/>
+        <v>383.40000000000003</v>
+      </c>
+      <c r="I11" s="21">
+        <f t="shared" si="0"/>
+        <v>577.16129032258061</v>
+      </c>
+      <c r="J11" s="21">
+        <f t="shared" si="0"/>
+        <v>577.16129032258061</v>
+      </c>
+      <c r="K11" s="21">
+        <f t="shared" si="0"/>
+        <v>397.59999999999997</v>
+      </c>
+      <c r="L11" s="21">
+        <f t="shared" si="0"/>
+        <v>474.09677419354836</v>
+      </c>
+      <c r="M11" s="21">
+        <f t="shared" si="0"/>
+        <v>426</v>
+      </c>
+      <c r="N11" s="21">
+        <f t="shared" si="0"/>
+        <v>426.45161290322579</v>
+      </c>
+      <c r="O11" s="22"/>
+    </row>
+    <row r="12" spans="2:15">
+      <c r="B12" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+    </row>
+    <row r="13" spans="2:15">
+      <c r="B13" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13">
+        <v>36</v>
+      </c>
+      <c r="D13">
+        <v>36</v>
+      </c>
+      <c r="E13">
+        <v>36</v>
+      </c>
+      <c r="F13">
+        <v>36</v>
+      </c>
+      <c r="G13">
+        <v>36</v>
+      </c>
+      <c r="H13">
+        <v>36</v>
+      </c>
+      <c r="I13">
+        <v>36</v>
+      </c>
+      <c r="J13">
+        <v>36</v>
+      </c>
+      <c r="K13">
+        <v>36</v>
+      </c>
+      <c r="L13">
+        <v>36</v>
+      </c>
+      <c r="M13">
+        <v>36</v>
+      </c>
+      <c r="N13">
+        <v>36</v>
+      </c>
+      <c r="O13" s="13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15">
+      <c r="B14" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="2">
+        <v>383400</v>
+      </c>
+      <c r="D14" s="2">
+        <v>322056</v>
+      </c>
+      <c r="E14" s="2">
+        <v>293940</v>
+      </c>
+      <c r="F14" s="2">
+        <v>345060</v>
+      </c>
+      <c r="G14" s="2">
+        <v>357840</v>
+      </c>
+      <c r="H14" s="2">
+        <v>184032</v>
+      </c>
+      <c r="I14" s="2">
+        <v>383400</v>
+      </c>
+      <c r="J14" s="2">
+        <v>383400</v>
+      </c>
+      <c r="K14" s="2">
+        <v>230040</v>
+      </c>
+      <c r="L14" s="2">
+        <v>429408</v>
+      </c>
+      <c r="M14" s="2">
+        <v>306720</v>
+      </c>
+      <c r="N14" s="2">
+        <v>371124</v>
+      </c>
+      <c r="O14" s="19">
+        <v>3990420</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15">
+      <c r="B15" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="2">
+        <v>270000</v>
+      </c>
+      <c r="D15" s="2">
+        <v>226800</v>
+      </c>
+      <c r="E15" s="2">
+        <v>207000</v>
+      </c>
+      <c r="F15" s="2">
+        <v>243000</v>
+      </c>
+      <c r="G15" s="2">
+        <v>252000</v>
+      </c>
+      <c r="H15" s="2">
+        <v>129600</v>
+      </c>
+      <c r="I15" s="2">
+        <v>270000</v>
+      </c>
+      <c r="J15" s="2">
+        <v>270000</v>
+      </c>
+      <c r="K15" s="2">
+        <v>162000</v>
+      </c>
+      <c r="L15" s="2">
+        <v>302400</v>
+      </c>
+      <c r="M15" s="2">
+        <v>216000</v>
+      </c>
+      <c r="N15" s="2">
+        <v>261360</v>
+      </c>
+      <c r="O15" s="19">
+        <v>2810160</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15">
+      <c r="B16" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="2">
+        <v>81000</v>
+      </c>
+      <c r="D16" s="2">
+        <v>68040</v>
+      </c>
+      <c r="E16" s="2">
+        <v>62100</v>
+      </c>
+      <c r="F16" s="2">
+        <v>72900</v>
+      </c>
+      <c r="G16" s="2">
+        <v>75600</v>
+      </c>
+      <c r="H16" s="2">
+        <v>38880</v>
+      </c>
+      <c r="I16" s="2">
+        <v>81000</v>
+      </c>
+      <c r="J16" s="2">
+        <v>81000</v>
+      </c>
+      <c r="K16" s="2">
+        <v>48600</v>
+      </c>
+      <c r="L16" s="2">
+        <v>90720</v>
+      </c>
+      <c r="M16" s="2">
+        <v>64800</v>
+      </c>
+      <c r="N16" s="2">
+        <v>78408</v>
+      </c>
+      <c r="O16" s="19">
+        <v>843048</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15">
+      <c r="B17" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="2">
+        <v>32400</v>
+      </c>
+      <c r="D17" s="2">
+        <v>27216</v>
+      </c>
+      <c r="E17" s="2">
+        <v>24840</v>
+      </c>
+      <c r="F17" s="2">
+        <v>29160</v>
+      </c>
+      <c r="G17" s="2">
+        <v>30240</v>
+      </c>
+      <c r="H17" s="2">
+        <v>15552</v>
+      </c>
+      <c r="I17" s="2">
+        <v>32400</v>
+      </c>
+      <c r="J17" s="2">
+        <v>32400</v>
+      </c>
+      <c r="K17" s="2">
+        <v>19440</v>
+      </c>
+      <c r="L17" s="2">
+        <v>36288</v>
+      </c>
+      <c r="M17" s="2">
+        <v>25920</v>
+      </c>
+      <c r="N17" s="2">
+        <v>31356</v>
+      </c>
+      <c r="O17" s="19">
+        <v>337212</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" s="23" customFormat="1">
+      <c r="B18" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="21">
+        <v>31</v>
+      </c>
+      <c r="D18" s="21">
+        <v>28</v>
+      </c>
+      <c r="E18" s="21">
+        <v>31</v>
+      </c>
+      <c r="F18" s="21">
+        <v>30</v>
+      </c>
+      <c r="G18" s="21">
+        <v>31</v>
+      </c>
+      <c r="H18" s="21">
+        <v>30</v>
+      </c>
+      <c r="I18" s="21">
+        <v>31</v>
+      </c>
+      <c r="J18" s="21">
+        <v>31</v>
+      </c>
+      <c r="K18" s="21">
+        <v>30</v>
+      </c>
+      <c r="L18" s="21">
+        <v>31</v>
+      </c>
+      <c r="M18" s="21">
+        <v>30</v>
+      </c>
+      <c r="N18" s="21">
+        <v>31</v>
+      </c>
+      <c r="O18" s="22"/>
+    </row>
+    <row r="19" spans="2:15" s="23" customFormat="1">
+      <c r="B19" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="21">
+        <f>C14/C18/C13</f>
+        <v>343.54838709677421</v>
+      </c>
+      <c r="D19" s="21">
+        <f t="shared" ref="D19:N19" si="1">D14/D18/D13</f>
+        <v>319.5</v>
+      </c>
+      <c r="E19" s="21">
+        <f t="shared" si="1"/>
+        <v>263.38709677419354</v>
+      </c>
+      <c r="F19" s="21">
+        <f t="shared" si="1"/>
+        <v>319.5</v>
+      </c>
+      <c r="G19" s="21">
+        <f t="shared" si="1"/>
+        <v>320.64516129032262</v>
+      </c>
+      <c r="H19" s="21">
+        <f t="shared" si="1"/>
+        <v>170.39999999999998</v>
+      </c>
+      <c r="I19" s="21">
+        <f t="shared" si="1"/>
+        <v>343.54838709677421</v>
+      </c>
+      <c r="J19" s="21">
+        <f t="shared" si="1"/>
+        <v>343.54838709677421</v>
+      </c>
+      <c r="K19" s="21">
+        <f t="shared" si="1"/>
+        <v>213</v>
+      </c>
+      <c r="L19" s="21">
+        <f t="shared" si="1"/>
+        <v>384.77419354838707</v>
+      </c>
+      <c r="M19" s="21">
+        <f t="shared" si="1"/>
+        <v>284</v>
+      </c>
+      <c r="N19" s="21">
+        <f t="shared" si="1"/>
+        <v>332.54838709677421</v>
+      </c>
+      <c r="O19" s="22"/>
+    </row>
+    <row r="20" spans="2:15">
+      <c r="B20" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+    </row>
+    <row r="21" spans="2:15">
+      <c r="B21" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21">
+        <v>44</v>
+      </c>
+      <c r="D21">
+        <v>44</v>
+      </c>
+      <c r="E21">
+        <v>44</v>
+      </c>
+      <c r="F21">
+        <v>44</v>
+      </c>
+      <c r="G21">
+        <v>44</v>
+      </c>
+      <c r="H21">
+        <v>44</v>
+      </c>
+      <c r="I21">
+        <v>44</v>
+      </c>
+      <c r="J21">
+        <v>44</v>
+      </c>
+      <c r="K21">
+        <v>44</v>
+      </c>
+      <c r="L21">
+        <v>44</v>
+      </c>
+      <c r="M21">
+        <v>44</v>
+      </c>
+      <c r="N21">
+        <v>44</v>
+      </c>
+      <c r="O21" s="13">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="B22" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="2">
+        <v>349888</v>
+      </c>
+      <c r="D22" s="2">
+        <v>274912</v>
+      </c>
+      <c r="E22" s="2">
+        <v>233684</v>
+      </c>
+      <c r="F22" s="2">
+        <v>191180</v>
+      </c>
+      <c r="G22" s="2">
+        <v>169928</v>
+      </c>
+      <c r="H22" s="2">
+        <v>187440</v>
+      </c>
+      <c r="I22" s="2">
+        <v>199936</v>
+      </c>
+      <c r="J22" s="2">
+        <v>199936</v>
+      </c>
+      <c r="K22" s="2">
+        <v>159324</v>
+      </c>
+      <c r="L22" s="2">
+        <v>199936</v>
+      </c>
+      <c r="M22" s="2">
+        <v>224928</v>
+      </c>
+      <c r="N22" s="2">
+        <v>343640</v>
+      </c>
+      <c r="O22" s="19">
+        <v>2734732</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15">
+      <c r="B23" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="2">
+        <v>246400</v>
+      </c>
+      <c r="D23" s="2">
+        <v>193600</v>
+      </c>
+      <c r="E23" s="2">
+        <v>164560</v>
+      </c>
+      <c r="F23" s="2">
+        <v>134640</v>
+      </c>
+      <c r="G23" s="2">
+        <v>119680</v>
+      </c>
+      <c r="H23" s="2">
+        <v>132000</v>
+      </c>
+      <c r="I23" s="2">
+        <v>140800</v>
+      </c>
+      <c r="J23" s="2">
+        <v>140800</v>
+      </c>
+      <c r="K23" s="2">
+        <v>112200</v>
+      </c>
+      <c r="L23" s="2">
+        <v>140800</v>
+      </c>
+      <c r="M23" s="2">
+        <v>158400</v>
+      </c>
+      <c r="N23" s="2">
+        <v>242000</v>
+      </c>
+      <c r="O23" s="19">
+        <v>1925880</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15">
+      <c r="B24" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="2">
+        <v>73920</v>
+      </c>
+      <c r="D24" s="2">
+        <v>58080</v>
+      </c>
+      <c r="E24" s="2">
+        <v>49368</v>
+      </c>
+      <c r="F24" s="2">
+        <v>40392</v>
+      </c>
+      <c r="G24" s="2">
+        <v>35904</v>
+      </c>
+      <c r="H24" s="2">
+        <v>39600</v>
+      </c>
+      <c r="I24" s="2">
+        <v>42240</v>
+      </c>
+      <c r="J24" s="2">
+        <v>42240</v>
+      </c>
+      <c r="K24" s="2">
+        <v>33660</v>
+      </c>
+      <c r="L24" s="2">
+        <v>42240</v>
+      </c>
+      <c r="M24" s="2">
+        <v>47520</v>
+      </c>
+      <c r="N24" s="2">
+        <v>72600</v>
+      </c>
+      <c r="O24" s="19">
+        <v>577764</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15">
+      <c r="B25" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="2">
+        <v>29568</v>
+      </c>
+      <c r="D25" s="2">
+        <v>23232</v>
+      </c>
+      <c r="E25" s="2">
+        <v>19756</v>
+      </c>
+      <c r="F25" s="2">
+        <v>16148</v>
+      </c>
+      <c r="G25" s="2">
+        <v>14344</v>
+      </c>
+      <c r="H25" s="2">
+        <v>15840</v>
+      </c>
+      <c r="I25" s="2">
+        <v>16896</v>
+      </c>
+      <c r="J25" s="2">
+        <v>16896</v>
+      </c>
+      <c r="K25" s="2">
+        <v>13464</v>
+      </c>
+      <c r="L25" s="2">
+        <v>16896</v>
+      </c>
+      <c r="M25" s="2">
+        <v>19008</v>
+      </c>
+      <c r="N25" s="2">
+        <v>29040</v>
+      </c>
+      <c r="O25" s="19">
+        <v>231088</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" s="23" customFormat="1">
+      <c r="B26" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="21">
+        <v>31</v>
+      </c>
+      <c r="D26" s="21">
+        <v>28</v>
+      </c>
+      <c r="E26" s="21">
+        <v>31</v>
+      </c>
+      <c r="F26" s="21">
+        <v>30</v>
+      </c>
+      <c r="G26" s="21">
+        <v>31</v>
+      </c>
+      <c r="H26" s="21">
+        <v>30</v>
+      </c>
+      <c r="I26" s="21">
+        <v>31</v>
+      </c>
+      <c r="J26" s="21">
+        <v>31</v>
+      </c>
+      <c r="K26" s="21">
+        <v>30</v>
+      </c>
+      <c r="L26" s="21">
+        <v>31</v>
+      </c>
+      <c r="M26" s="21">
+        <v>30</v>
+      </c>
+      <c r="N26" s="21">
+        <v>31</v>
+      </c>
+      <c r="O26" s="22"/>
+    </row>
+    <row r="27" spans="2:15" s="23" customFormat="1">
+      <c r="B27" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="21">
+        <f>C22/C26/C21</f>
+        <v>256.51612903225805</v>
+      </c>
+      <c r="D27" s="21">
+        <f t="shared" ref="D27:N27" si="2">D22/D26/D21</f>
+        <v>223.14285714285714</v>
+      </c>
+      <c r="E27" s="21">
+        <f t="shared" si="2"/>
+        <v>171.32258064516128</v>
+      </c>
+      <c r="F27" s="21">
+        <f t="shared" si="2"/>
+        <v>144.83333333333334</v>
+      </c>
+      <c r="G27" s="21">
+        <f t="shared" si="2"/>
+        <v>124.58064516129033</v>
+      </c>
+      <c r="H27" s="21">
+        <f t="shared" si="2"/>
+        <v>142</v>
+      </c>
+      <c r="I27" s="21">
+        <f t="shared" si="2"/>
+        <v>146.58064516129033</v>
+      </c>
+      <c r="J27" s="21">
+        <f t="shared" si="2"/>
+        <v>146.58064516129033</v>
+      </c>
+      <c r="K27" s="21">
+        <f t="shared" si="2"/>
+        <v>120.7</v>
+      </c>
+      <c r="L27" s="21">
+        <f t="shared" si="2"/>
+        <v>146.58064516129033</v>
+      </c>
+      <c r="M27" s="21">
+        <f t="shared" si="2"/>
+        <v>170.4</v>
+      </c>
+      <c r="N27" s="21">
+        <f t="shared" si="2"/>
+        <v>251.93548387096777</v>
+      </c>
+      <c r="O27" s="22"/>
+    </row>
+    <row r="28" spans="2:15">
+      <c r="B28" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="B29" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29">
+        <v>10</v>
+      </c>
+      <c r="D29">
+        <v>10</v>
+      </c>
+      <c r="E29">
+        <v>10</v>
+      </c>
+      <c r="F29">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>10</v>
+      </c>
+      <c r="H29">
+        <v>10</v>
+      </c>
+      <c r="I29">
+        <v>10</v>
+      </c>
+      <c r="J29">
+        <v>10</v>
+      </c>
+      <c r="K29">
+        <v>10</v>
+      </c>
+      <c r="L29">
+        <v>10</v>
+      </c>
+      <c r="M29">
+        <v>10</v>
+      </c>
+      <c r="N29">
+        <v>10</v>
+      </c>
+      <c r="O29" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15">
+      <c r="B30" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="2">
+        <v>144840</v>
+      </c>
+      <c r="D30" s="2">
+        <v>144840</v>
+      </c>
+      <c r="E30" s="2">
+        <v>147680</v>
+      </c>
+      <c r="F30" s="2">
+        <v>155060</v>
+      </c>
+      <c r="G30" s="2">
+        <v>169830</v>
+      </c>
+      <c r="H30" s="2">
+        <v>170400</v>
+      </c>
+      <c r="I30" s="2">
+        <v>213000</v>
+      </c>
+      <c r="J30" s="2">
+        <v>238560</v>
+      </c>
+      <c r="K30" s="2">
+        <v>155060</v>
+      </c>
+      <c r="L30" s="2">
+        <v>170400</v>
+      </c>
+      <c r="M30" s="2">
+        <v>127800</v>
+      </c>
+      <c r="N30" s="2">
+        <v>159040</v>
+      </c>
+      <c r="O30" s="19">
+        <v>1996510</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15">
+      <c r="B31" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="2">
+        <v>102000</v>
+      </c>
+      <c r="D31" s="2">
+        <v>102000</v>
+      </c>
+      <c r="E31" s="2">
+        <v>104000</v>
+      </c>
+      <c r="F31" s="2">
+        <v>109200</v>
+      </c>
+      <c r="G31" s="2">
+        <v>119600</v>
+      </c>
+      <c r="H31" s="2">
+        <v>120000</v>
+      </c>
+      <c r="I31" s="2">
+        <v>150000</v>
+      </c>
+      <c r="J31" s="2">
+        <v>168000</v>
+      </c>
+      <c r="K31" s="2">
+        <v>109200</v>
+      </c>
+      <c r="L31" s="2">
+        <v>120000</v>
+      </c>
+      <c r="M31" s="2">
+        <v>90000</v>
+      </c>
+      <c r="N31" s="2">
+        <v>112000</v>
+      </c>
+      <c r="O31" s="19">
+        <v>1406000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15">
+      <c r="B32" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="2">
+        <v>30600</v>
+      </c>
+      <c r="D32" s="2">
+        <v>30600</v>
+      </c>
+      <c r="E32" s="2">
+        <v>31200</v>
+      </c>
+      <c r="F32" s="2">
+        <v>32760</v>
+      </c>
+      <c r="G32" s="2">
+        <v>35880</v>
+      </c>
+      <c r="H32" s="2">
+        <v>36000</v>
+      </c>
+      <c r="I32" s="2">
+        <v>45000</v>
+      </c>
+      <c r="J32" s="2">
+        <v>50400</v>
+      </c>
+      <c r="K32" s="2">
+        <v>32760</v>
+      </c>
+      <c r="L32" s="2">
+        <v>36000</v>
+      </c>
+      <c r="M32" s="2">
+        <v>27000</v>
+      </c>
+      <c r="N32" s="2">
+        <v>33600</v>
+      </c>
+      <c r="O32" s="19">
+        <v>421800</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15">
+      <c r="B33" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="2">
+        <v>12240</v>
+      </c>
+      <c r="D33" s="2">
+        <v>12240</v>
+      </c>
+      <c r="E33" s="2">
+        <v>12480</v>
+      </c>
+      <c r="F33" s="2">
+        <v>13100</v>
+      </c>
+      <c r="G33" s="2">
+        <v>14350</v>
+      </c>
+      <c r="H33" s="2">
+        <v>14400</v>
+      </c>
+      <c r="I33" s="2">
+        <v>18000</v>
+      </c>
+      <c r="J33" s="2">
+        <v>20160</v>
+      </c>
+      <c r="K33" s="2">
+        <v>13100</v>
+      </c>
+      <c r="L33" s="2">
+        <v>14400</v>
+      </c>
+      <c r="M33" s="2">
+        <v>10800</v>
+      </c>
+      <c r="N33" s="2">
+        <v>13440</v>
+      </c>
+      <c r="O33" s="19">
+        <v>168710</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" s="23" customFormat="1">
+      <c r="B34" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="21">
+        <v>31</v>
+      </c>
+      <c r="D34" s="21">
+        <v>28</v>
+      </c>
+      <c r="E34" s="21">
+        <v>31</v>
+      </c>
+      <c r="F34" s="21">
+        <v>30</v>
+      </c>
+      <c r="G34" s="21">
+        <v>31</v>
+      </c>
+      <c r="H34" s="21">
+        <v>30</v>
+      </c>
+      <c r="I34" s="21">
+        <v>31</v>
+      </c>
+      <c r="J34" s="21">
+        <v>31</v>
+      </c>
+      <c r="K34" s="21">
+        <v>30</v>
+      </c>
+      <c r="L34" s="21">
+        <v>31</v>
+      </c>
+      <c r="M34" s="21">
+        <v>30</v>
+      </c>
+      <c r="N34" s="21">
+        <v>31</v>
+      </c>
+      <c r="O34" s="22"/>
+    </row>
+    <row r="35" spans="2:15" s="23" customFormat="1">
+      <c r="B35" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="21">
+        <f>C30/C34/C29</f>
+        <v>467.22580645161287</v>
+      </c>
+      <c r="D35" s="21">
+        <f t="shared" ref="D35:N35" si="3">D30/D34/D29</f>
+        <v>517.28571428571433</v>
+      </c>
+      <c r="E35" s="21">
+        <f t="shared" si="3"/>
+        <v>476.38709677419354</v>
+      </c>
+      <c r="F35" s="21">
+        <f t="shared" si="3"/>
+        <v>516.86666666666667</v>
+      </c>
+      <c r="G35" s="21">
+        <f t="shared" si="3"/>
+        <v>547.83870967741927</v>
+      </c>
+      <c r="H35" s="21">
+        <f t="shared" si="3"/>
+        <v>568</v>
+      </c>
+      <c r="I35" s="21">
+        <f t="shared" si="3"/>
+        <v>687.09677419354841</v>
+      </c>
+      <c r="J35" s="21">
+        <f t="shared" si="3"/>
+        <v>769.54838709677415</v>
+      </c>
+      <c r="K35" s="21">
+        <f t="shared" si="3"/>
+        <v>516.86666666666667</v>
+      </c>
+      <c r="L35" s="21">
+        <f t="shared" si="3"/>
+        <v>549.67741935483878</v>
+      </c>
+      <c r="M35" s="21">
+        <f t="shared" si="3"/>
+        <v>426</v>
+      </c>
+      <c r="N35" s="21">
+        <f t="shared" si="3"/>
+        <v>513.0322580645161</v>
+      </c>
+      <c r="O35" s="22"/>
+    </row>
+    <row r="36" spans="2:15">
+      <c r="B36" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="16"/>
+    </row>
+    <row r="37" spans="2:15">
+      <c r="B37" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37">
+        <v>6</v>
+      </c>
+      <c r="D37">
+        <v>6</v>
+      </c>
+      <c r="E37">
+        <v>6</v>
+      </c>
+      <c r="F37">
+        <v>6</v>
+      </c>
+      <c r="G37">
+        <v>6</v>
+      </c>
+      <c r="H37">
+        <v>6</v>
+      </c>
+      <c r="I37">
+        <v>6</v>
+      </c>
+      <c r="J37">
+        <v>6</v>
+      </c>
+      <c r="K37">
+        <v>6</v>
+      </c>
+      <c r="L37">
+        <v>6</v>
+      </c>
+      <c r="M37">
+        <v>6</v>
+      </c>
+      <c r="N37">
+        <v>6</v>
+      </c>
+      <c r="O37" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15">
+      <c r="B38" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="2">
+        <v>109056</v>
+      </c>
+      <c r="D38" s="2">
+        <v>95424</v>
+      </c>
+      <c r="E38" s="2">
+        <v>95424</v>
+      </c>
+      <c r="F38" s="2">
+        <v>89460</v>
+      </c>
+      <c r="G38" s="2">
+        <v>149100</v>
+      </c>
+      <c r="H38" s="2">
+        <v>122688</v>
+      </c>
+      <c r="I38" s="2">
+        <v>170400</v>
+      </c>
+      <c r="J38" s="2">
+        <v>170400</v>
+      </c>
+      <c r="K38" s="2">
+        <v>143136</v>
+      </c>
+      <c r="L38" s="2">
+        <v>149952</v>
+      </c>
+      <c r="M38" s="2">
+        <v>122688</v>
+      </c>
+      <c r="N38" s="2">
+        <v>145692</v>
+      </c>
+      <c r="O38" s="19">
+        <v>1563420</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15">
+      <c r="B39" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="2">
+        <v>76800</v>
+      </c>
+      <c r="D39" s="2">
+        <v>67200</v>
+      </c>
+      <c r="E39" s="2">
+        <v>67200</v>
+      </c>
+      <c r="F39" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G39" s="2">
+        <v>105000</v>
+      </c>
+      <c r="H39" s="2">
+        <v>86400</v>
+      </c>
+      <c r="I39" s="2">
+        <v>120000</v>
+      </c>
+      <c r="J39" s="2">
+        <v>120000</v>
+      </c>
+      <c r="K39" s="2">
+        <v>100800</v>
+      </c>
+      <c r="L39" s="2">
+        <v>105600</v>
+      </c>
+      <c r="M39" s="2">
+        <v>86400</v>
+      </c>
+      <c r="N39" s="2">
+        <v>102600</v>
+      </c>
+      <c r="O39" s="19">
+        <v>1101000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15">
+      <c r="B40" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="2">
+        <v>23040</v>
+      </c>
+      <c r="D40" s="2">
+        <v>20160</v>
+      </c>
+      <c r="E40" s="2">
+        <v>20160</v>
+      </c>
+      <c r="F40" s="2">
+        <v>18900</v>
+      </c>
+      <c r="G40" s="2">
+        <v>31500</v>
+      </c>
+      <c r="H40" s="2">
+        <v>25920</v>
+      </c>
+      <c r="I40" s="2">
+        <v>36000</v>
+      </c>
+      <c r="J40" s="2">
+        <v>36000</v>
+      </c>
+      <c r="K40" s="2">
+        <v>30240</v>
+      </c>
+      <c r="L40" s="2">
+        <v>31680</v>
+      </c>
+      <c r="M40" s="2">
+        <v>25920</v>
+      </c>
+      <c r="N40" s="2">
+        <v>30780</v>
+      </c>
+      <c r="O40" s="19">
+        <v>330300</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15">
+      <c r="B41" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="2">
+        <v>9216</v>
+      </c>
+      <c r="D41" s="2">
+        <v>8064</v>
+      </c>
+      <c r="E41" s="2">
+        <v>8064</v>
+      </c>
+      <c r="F41" s="2">
+        <v>7560</v>
+      </c>
+      <c r="G41" s="2">
+        <v>12600</v>
+      </c>
+      <c r="H41" s="2">
+        <v>10368</v>
+      </c>
+      <c r="I41" s="2">
+        <v>14400</v>
+      </c>
+      <c r="J41" s="2">
+        <v>14400</v>
+      </c>
+      <c r="K41" s="2">
+        <v>12096</v>
+      </c>
+      <c r="L41" s="2">
+        <v>12672</v>
+      </c>
+      <c r="M41" s="2">
+        <v>10368</v>
+      </c>
+      <c r="N41" s="2">
+        <v>12312</v>
+      </c>
+      <c r="O41" s="19">
+        <v>132120</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" s="23" customFormat="1">
+      <c r="B42" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" s="21">
+        <v>31</v>
+      </c>
+      <c r="D42" s="21">
+        <v>28</v>
+      </c>
+      <c r="E42" s="21">
+        <v>31</v>
+      </c>
+      <c r="F42" s="21">
+        <v>30</v>
+      </c>
+      <c r="G42" s="21">
+        <v>31</v>
+      </c>
+      <c r="H42" s="21">
+        <v>30</v>
+      </c>
+      <c r="I42" s="21">
+        <v>31</v>
+      </c>
+      <c r="J42" s="21">
+        <v>31</v>
+      </c>
+      <c r="K42" s="21">
+        <v>30</v>
+      </c>
+      <c r="L42" s="21">
+        <v>31</v>
+      </c>
+      <c r="M42" s="21">
+        <v>30</v>
+      </c>
+      <c r="N42" s="21">
+        <v>31</v>
+      </c>
+      <c r="O42" s="22"/>
+    </row>
+    <row r="43" spans="2:15" s="23" customFormat="1">
+      <c r="B43" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="21">
+        <f>C38/C42/C37</f>
+        <v>586.32258064516134</v>
+      </c>
+      <c r="D43" s="21">
+        <f t="shared" ref="D43:N43" si="4">D38/D42/D37</f>
+        <v>568</v>
+      </c>
+      <c r="E43" s="21">
+        <f t="shared" si="4"/>
+        <v>513.0322580645161</v>
+      </c>
+      <c r="F43" s="21">
+        <f t="shared" si="4"/>
+        <v>497</v>
+      </c>
+      <c r="G43" s="21">
+        <f t="shared" si="4"/>
+        <v>801.61290322580646</v>
+      </c>
+      <c r="H43" s="21">
+        <f t="shared" si="4"/>
+        <v>681.6</v>
+      </c>
+      <c r="I43" s="21">
+        <f t="shared" si="4"/>
+        <v>916.12903225806451</v>
+      </c>
+      <c r="J43" s="21">
+        <f t="shared" si="4"/>
+        <v>916.12903225806451</v>
+      </c>
+      <c r="K43" s="21">
+        <f t="shared" si="4"/>
+        <v>795.19999999999993</v>
+      </c>
+      <c r="L43" s="21">
+        <f t="shared" si="4"/>
+        <v>806.19354838709671</v>
+      </c>
+      <c r="M43" s="21">
+        <f t="shared" si="4"/>
+        <v>681.6</v>
+      </c>
+      <c r="N43" s="21">
+        <f t="shared" si="4"/>
+        <v>783.29032258064524</v>
+      </c>
+      <c r="O43" s="22"/>
+    </row>
+    <row r="44" spans="2:15">
+      <c r="B44" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="16"/>
+      <c r="O44" s="16"/>
+    </row>
+    <row r="45" spans="2:15">
+      <c r="B45" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45">
+        <v>76</v>
+      </c>
+      <c r="D45">
+        <v>76</v>
+      </c>
+      <c r="E45">
+        <v>76</v>
+      </c>
+      <c r="F45">
+        <v>76</v>
+      </c>
+      <c r="G45">
+        <v>76</v>
+      </c>
+      <c r="H45">
+        <v>76</v>
+      </c>
+      <c r="I45">
+        <v>76</v>
+      </c>
+      <c r="J45">
+        <v>76</v>
+      </c>
+      <c r="K45">
+        <v>76</v>
+      </c>
+      <c r="L45">
+        <v>76</v>
+      </c>
+      <c r="M45">
+        <v>76</v>
+      </c>
+      <c r="N45">
+        <v>76</v>
+      </c>
+      <c r="O45" s="13">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15">
+      <c r="B46" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="2">
+        <v>307572</v>
+      </c>
+      <c r="D46" s="2">
+        <v>356136</v>
+      </c>
+      <c r="E46" s="2">
+        <v>322696</v>
+      </c>
+      <c r="F46" s="2">
+        <v>336680</v>
+      </c>
+      <c r="G46" s="2">
+        <v>322696</v>
+      </c>
+      <c r="H46" s="2">
+        <v>291384</v>
+      </c>
+      <c r="I46" s="2">
+        <v>356136</v>
+      </c>
+      <c r="J46" s="2">
+        <v>372324</v>
+      </c>
+      <c r="K46" s="2">
+        <v>210444</v>
+      </c>
+      <c r="L46" s="2">
+        <v>453264</v>
+      </c>
+      <c r="M46" s="2">
+        <v>291384</v>
+      </c>
+      <c r="N46" s="2">
+        <v>403636</v>
+      </c>
+      <c r="O46" s="19">
+        <v>4024352</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15">
+      <c r="B47" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="2">
+        <v>216600</v>
+      </c>
+      <c r="D47" s="2">
+        <v>250800</v>
+      </c>
+      <c r="E47" s="2">
+        <v>227240</v>
+      </c>
+      <c r="F47" s="2">
+        <v>237120</v>
+      </c>
+      <c r="G47" s="2">
+        <v>227240</v>
+      </c>
+      <c r="H47" s="2">
+        <v>205200</v>
+      </c>
+      <c r="I47" s="2">
+        <v>250800</v>
+      </c>
+      <c r="J47" s="2">
+        <v>262200</v>
+      </c>
+      <c r="K47" s="2">
+        <v>148200</v>
+      </c>
+      <c r="L47" s="2">
+        <v>319200</v>
+      </c>
+      <c r="M47" s="2">
+        <v>205200</v>
+      </c>
+      <c r="N47" s="2">
+        <v>284240</v>
+      </c>
+      <c r="O47" s="19">
+        <v>2834040</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15">
+      <c r="B48" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="2">
+        <v>64980</v>
+      </c>
+      <c r="D48" s="2">
+        <v>75240</v>
+      </c>
+      <c r="E48" s="2">
+        <v>68172</v>
+      </c>
+      <c r="F48" s="2">
+        <v>71136</v>
+      </c>
+      <c r="G48" s="2">
+        <v>68172</v>
+      </c>
+      <c r="H48" s="2">
+        <v>61560</v>
+      </c>
+      <c r="I48" s="2">
+        <v>75240</v>
+      </c>
+      <c r="J48" s="2">
+        <v>78660</v>
+      </c>
+      <c r="K48" s="2">
+        <v>44460</v>
+      </c>
+      <c r="L48" s="2">
+        <v>95760</v>
+      </c>
+      <c r="M48" s="2">
+        <v>61560</v>
+      </c>
+      <c r="N48" s="2">
+        <v>85272</v>
+      </c>
+      <c r="O48" s="19">
+        <v>850212</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15">
+      <c r="B49" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="2">
+        <v>25992</v>
+      </c>
+      <c r="D49" s="2">
+        <v>30096</v>
+      </c>
+      <c r="E49" s="2">
+        <v>27284</v>
+      </c>
+      <c r="F49" s="2">
+        <v>28424</v>
+      </c>
+      <c r="G49" s="2">
+        <v>27284</v>
+      </c>
+      <c r="H49" s="2">
+        <v>24624</v>
+      </c>
+      <c r="I49" s="2">
+        <v>30096</v>
+      </c>
+      <c r="J49" s="2">
+        <v>31464</v>
+      </c>
+      <c r="K49" s="2">
+        <v>17784</v>
+      </c>
+      <c r="L49" s="2">
+        <v>38304</v>
+      </c>
+      <c r="M49" s="2">
+        <v>24624</v>
+      </c>
+      <c r="N49" s="2">
+        <v>34124</v>
+      </c>
+      <c r="O49" s="19">
+        <v>340100</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15" s="23" customFormat="1">
+      <c r="B50" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" s="21">
+        <v>31</v>
+      </c>
+      <c r="D50" s="21">
+        <v>28</v>
+      </c>
+      <c r="E50" s="21">
+        <v>31</v>
+      </c>
+      <c r="F50" s="21">
+        <v>30</v>
+      </c>
+      <c r="G50" s="21">
+        <v>31</v>
+      </c>
+      <c r="H50" s="21">
+        <v>30</v>
+      </c>
+      <c r="I50" s="21">
+        <v>31</v>
+      </c>
+      <c r="J50" s="21">
+        <v>31</v>
+      </c>
+      <c r="K50" s="21">
+        <v>30</v>
+      </c>
+      <c r="L50" s="21">
+        <v>31</v>
+      </c>
+      <c r="M50" s="21">
+        <v>30</v>
+      </c>
+      <c r="N50" s="21">
+        <v>31</v>
+      </c>
+      <c r="O50" s="22"/>
+    </row>
+    <row r="51" spans="2:15" s="23" customFormat="1">
+      <c r="B51" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" s="21">
+        <f>C46/C50/C45</f>
+        <v>130.54838709677421</v>
+      </c>
+      <c r="D51" s="21">
+        <f t="shared" ref="D51:N51" si="5">D46/D50/D45</f>
+        <v>167.35714285714286</v>
+      </c>
+      <c r="E51" s="21">
+        <f t="shared" si="5"/>
+        <v>136.96774193548387</v>
+      </c>
+      <c r="F51" s="21">
+        <f t="shared" si="5"/>
+        <v>147.66666666666666</v>
+      </c>
+      <c r="G51" s="21">
+        <f t="shared" si="5"/>
+        <v>136.96774193548387</v>
+      </c>
+      <c r="H51" s="21">
+        <f t="shared" si="5"/>
+        <v>127.8</v>
+      </c>
+      <c r="I51" s="21">
+        <f t="shared" si="5"/>
+        <v>151.16129032258064</v>
+      </c>
+      <c r="J51" s="21">
+        <f t="shared" si="5"/>
+        <v>158.03225806451613</v>
+      </c>
+      <c r="K51" s="21">
+        <f t="shared" si="5"/>
+        <v>92.3</v>
+      </c>
+      <c r="L51" s="21">
+        <f t="shared" si="5"/>
+        <v>192.38709677419357</v>
+      </c>
+      <c r="M51" s="21">
+        <f t="shared" si="5"/>
+        <v>127.8</v>
+      </c>
+      <c r="N51" s="21">
+        <f t="shared" si="5"/>
+        <v>171.32258064516128</v>
+      </c>
+      <c r="O51" s="22"/>
+    </row>
+    <row r="52" spans="2:15">
+      <c r="B52" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" s="25">
+        <v>200</v>
+      </c>
+      <c r="D52" s="25">
+        <v>200</v>
+      </c>
+      <c r="E52" s="25">
+        <v>200</v>
+      </c>
+      <c r="F52" s="25">
+        <v>200</v>
+      </c>
+      <c r="G52" s="25">
+        <v>200</v>
+      </c>
+      <c r="H52" s="25">
+        <v>200</v>
+      </c>
+      <c r="I52" s="25">
+        <v>200</v>
+      </c>
+      <c r="J52" s="25">
+        <v>200</v>
+      </c>
+      <c r="K52" s="25">
+        <v>200</v>
+      </c>
+      <c r="L52" s="25">
+        <v>200</v>
+      </c>
+      <c r="M52" s="25">
+        <v>200</v>
+      </c>
+      <c r="N52" s="25">
+        <v>200</v>
+      </c>
+      <c r="O52" s="25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15">
+      <c r="B53" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C53" s="19">
+        <v>1598920</v>
+      </c>
+      <c r="D53" s="19">
+        <v>1551208</v>
+      </c>
+      <c r="E53" s="19">
+        <v>1538736</v>
+      </c>
+      <c r="F53" s="19">
+        <v>1483232</v>
+      </c>
+      <c r="G53" s="19">
+        <v>1566994</v>
+      </c>
+      <c r="H53" s="19">
+        <v>1278000</v>
+      </c>
+      <c r="I53" s="19">
+        <v>1823848</v>
+      </c>
+      <c r="J53" s="19">
+        <v>1865596</v>
+      </c>
+      <c r="K53" s="19">
+        <v>1231988</v>
+      </c>
+      <c r="L53" s="19">
+        <v>1814476</v>
+      </c>
+      <c r="M53" s="19">
+        <v>1431360</v>
+      </c>
+      <c r="N53" s="19">
+        <v>1793292</v>
+      </c>
+      <c r="O53" s="19">
+        <v>18977650</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15">
+      <c r="B54" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" s="19">
+        <v>1126000</v>
+      </c>
+      <c r="D54" s="19">
+        <v>1092400</v>
+      </c>
+      <c r="E54" s="19">
+        <v>1083600</v>
+      </c>
+      <c r="F54" s="19">
+        <v>1044560</v>
+      </c>
+      <c r="G54" s="19">
+        <v>1103520</v>
+      </c>
+      <c r="H54" s="19">
+        <v>900000</v>
+      </c>
+      <c r="I54" s="19">
+        <v>1284400</v>
+      </c>
+      <c r="J54" s="19">
+        <v>1313800</v>
+      </c>
+      <c r="K54" s="19">
+        <v>867600</v>
+      </c>
+      <c r="L54" s="19">
+        <v>1277800</v>
+      </c>
+      <c r="M54" s="19">
+        <v>1008000</v>
+      </c>
+      <c r="N54" s="19">
+        <v>1262880</v>
+      </c>
+      <c r="O54" s="19">
+        <v>13364560</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15">
+      <c r="B55" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="19">
+        <v>337800</v>
+      </c>
+      <c r="D55" s="19">
+        <v>327720</v>
+      </c>
+      <c r="E55" s="19">
+        <v>325080</v>
+      </c>
+      <c r="F55" s="19">
+        <v>313368</v>
+      </c>
+      <c r="G55" s="19">
+        <v>331056</v>
+      </c>
+      <c r="H55" s="19">
+        <v>270000</v>
+      </c>
+      <c r="I55" s="19">
+        <v>385320</v>
+      </c>
+      <c r="J55" s="19">
+        <v>394140</v>
+      </c>
+      <c r="K55" s="19">
+        <v>260280</v>
+      </c>
+      <c r="L55" s="19">
+        <v>383340</v>
+      </c>
+      <c r="M55" s="19">
+        <v>302400</v>
+      </c>
+      <c r="N55" s="19">
+        <v>378864</v>
+      </c>
+      <c r="O55" s="19">
+        <v>4009368</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15">
+      <c r="B56" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C56" s="19">
+        <v>135120</v>
+      </c>
+      <c r="D56" s="19">
+        <v>131088</v>
+      </c>
+      <c r="E56" s="19">
+        <v>130056</v>
+      </c>
+      <c r="F56" s="19">
+        <v>125304</v>
+      </c>
+      <c r="G56" s="19">
+        <v>132418</v>
+      </c>
+      <c r="H56" s="19">
+        <v>108000</v>
+      </c>
+      <c r="I56" s="19">
+        <v>154128</v>
+      </c>
+      <c r="J56" s="19">
+        <v>157656</v>
+      </c>
+      <c r="K56" s="19">
+        <v>104108</v>
+      </c>
+      <c r="L56" s="19">
+        <v>153336</v>
+      </c>
+      <c r="M56" s="19">
+        <v>120960</v>
+      </c>
+      <c r="N56" s="19">
+        <v>151548</v>
+      </c>
+      <c r="O56" s="19">
+        <v>1603722</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15">
+      <c r="B57" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C57" s="27">
+        <v>31</v>
+      </c>
+      <c r="D57" s="27">
+        <v>28</v>
+      </c>
+      <c r="E57" s="27">
+        <v>31</v>
+      </c>
+      <c r="F57" s="27">
+        <v>30</v>
+      </c>
+      <c r="G57" s="27">
+        <v>31</v>
+      </c>
+      <c r="H57" s="27">
+        <v>30</v>
+      </c>
+      <c r="I57" s="27">
+        <v>31</v>
+      </c>
+      <c r="J57" s="27">
+        <v>31</v>
+      </c>
+      <c r="K57" s="27">
+        <v>30</v>
+      </c>
+      <c r="L57" s="27">
+        <v>31</v>
+      </c>
+      <c r="M57" s="27">
+        <v>30</v>
+      </c>
+      <c r="N57" s="27">
+        <v>31</v>
+      </c>
+      <c r="O57" s="27">
+        <v>30.416666666666668</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" ht="15" thickBot="1">
+      <c r="B58" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C58" s="29">
+        <v>386.24</v>
+      </c>
+      <c r="D58" s="29">
+        <v>386.24</v>
+      </c>
+      <c r="E58" s="29">
+        <v>333.42130434782661</v>
+      </c>
+      <c r="F58" s="29">
+        <v>333.40626984127101</v>
+      </c>
+      <c r="G58" s="29">
+        <v>333.41336956521803</v>
+      </c>
+      <c r="H58" s="29">
+        <v>386.24</v>
+      </c>
+      <c r="I58" s="29">
+        <v>386.24</v>
+      </c>
+      <c r="J58" s="29">
+        <v>386.24</v>
+      </c>
+      <c r="K58" s="29">
+        <v>333.4150476190477</v>
+      </c>
+      <c r="L58" s="29">
+        <v>386.24</v>
+      </c>
+      <c r="M58" s="29">
+        <v>386.24</v>
+      </c>
+      <c r="N58" s="29">
+        <v>430.26034449760687</v>
+      </c>
+      <c r="O58" s="29">
+        <v>372.29969465591421</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73523379-831F-41E0-B5B2-536D4959CE04}">
-  <dimension ref="B2:E17"/>
+  <dimension ref="B2:J22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="4.6328125" customWidth="1"/>
@@ -9675,7 +13449,7 @@
     <col min="7" max="7" width="17.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="16" thickBot="1">
+    <row r="2" spans="2:10" ht="16" thickBot="1">
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
@@ -9683,15 +13457,15 @@
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="2:5" ht="29" thickBot="1">
+    <row r="3" spans="2:10" ht="29" thickBot="1">
       <c r="B3" s="9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
     </row>
-    <row r="5" spans="2:5" ht="18.5">
+    <row r="5" spans="2:10" ht="18.5">
       <c r="B5" s="8" t="s">
         <v>1</v>
       </c>
@@ -9704,209 +13478,270 @@
       <c r="E5" s="8" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" ht="15.5">
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="2:10" ht="15.5">
       <c r="B6" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M2,IF($B$3="King",'Data for Sheet 1'!M14,IF($B$3="Superior King",'Data for Sheet 1'!M26,IF($B$3="Executive",'Data for Sheet 1'!M38,IF($B$3="One Club",'Data for Sheet 1'!M50,'Data for Sheet 1'!M62)))))</f>
-        <v>1.0811688311688312</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M2,IF($B$3="King",'Revenue - Data'!M14,IF($B$3="Superior King",'Revenue - Data'!M26,IF($B$3="Executive",'Revenue - Data'!M38,IF($B$3="One Club",'Revenue - Data'!M50,'Revenue - Data'!M62)))))</f>
+        <v>0.95914127423822715</v>
       </c>
       <c r="C6" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N2,IF($B$3="King",'Data for Sheet 1'!N14,IF($B$3="Superior King",'Data for Sheet 1'!N26,IF($B$3="Executive",'Data for Sheet 1'!N38,IF($B$3="One Club",'Data for Sheet 1'!N50,'Data for Sheet 1'!N62)))))</f>
-        <v>1.6474837662337662</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N2,IF($B$3="King",'Revenue - Data'!N14,IF($B$3="Superior King",'Revenue - Data'!N26,IF($B$3="Executive",'Revenue - Data'!N38,IF($B$3="One Club",'Revenue - Data'!N50,'Revenue - Data'!N62)))))</f>
+        <v>0.78562634656817487</v>
       </c>
       <c r="D6" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O2,IF($B$3="King",'Data for Sheet 1'!O14,IF($B$3="Superior King",'Data for Sheet 1'!O26,IF($B$3="Executive",'Data for Sheet 1'!O38,IF($B$3="One Club",'Data for Sheet 1'!O50,'Data for Sheet 1'!O62)))))</f>
-        <v>1.6248308982683983</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O2,IF($B$3="King",'Revenue - Data'!O14,IF($B$3="Superior King",'Revenue - Data'!O26,IF($B$3="Executive",'Revenue - Data'!O38,IF($B$3="One Club",'Revenue - Data'!O50,'Revenue - Data'!O62)))))</f>
+        <v>0.82094490612496152</v>
       </c>
       <c r="E6" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" ht="15.5">
+      <c r="J6" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="15.5">
       <c r="B7" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M3,IF($B$3="King",'Data for Sheet 1'!M15,IF($B$3="Superior King",'Data for Sheet 1'!M27,IF($B$3="Executive",'Data for Sheet 1'!M39,IF($B$3="One Club",'Data for Sheet 1'!M51,'Data for Sheet 1'!M63)))))</f>
-        <v>1.1353305785123966</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M3,IF($B$3="King",'Revenue - Data'!M15,IF($B$3="Superior King",'Revenue - Data'!M27,IF($B$3="Executive",'Revenue - Data'!M39,IF($B$3="One Club",'Revenue - Data'!M51,'Revenue - Data'!M63)))))</f>
+        <v>1.0639952153110048</v>
       </c>
       <c r="C7" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N3,IF($B$3="King",'Data for Sheet 1'!N15,IF($B$3="Superior King",'Data for Sheet 1'!N27,IF($B$3="Executive",'Data for Sheet 1'!N39,IF($B$3="One Club",'Data for Sheet 1'!N51,'Data for Sheet 1'!N63)))))</f>
-        <v>1.4303891184573003</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N3,IF($B$3="King",'Revenue - Data'!N15,IF($B$3="Superior King",'Revenue - Data'!N27,IF($B$3="Executive",'Revenue - Data'!N39,IF($B$3="One Club",'Revenue - Data'!N51,'Revenue - Data'!N63)))))</f>
+        <v>1.1251860712387027</v>
       </c>
       <c r="D7" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O3,IF($B$3="King",'Data for Sheet 1'!O15,IF($B$3="Superior King",'Data for Sheet 1'!O27,IF($B$3="Executive",'Data for Sheet 1'!O39,IF($B$3="One Club",'Data for Sheet 1'!O51,'Data for Sheet 1'!O63)))))</f>
-        <v>1.3619146005509641</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O3,IF($B$3="King",'Revenue - Data'!O15,IF($B$3="Superior King",'Revenue - Data'!O27,IF($B$3="Executive",'Revenue - Data'!O39,IF($B$3="One Club",'Revenue - Data'!O51,'Revenue - Data'!O63)))))</f>
+        <v>1.1200824029771399</v>
       </c>
       <c r="E7" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" ht="15.5">
+      <c r="J7" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="15.5">
       <c r="B8" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M4,IF($B$3="King",'Data for Sheet 1'!M16,IF($B$3="Superior King",'Data for Sheet 1'!M28,IF($B$3="Executive",'Data for Sheet 1'!M40,IF($B$3="One Club",'Data for Sheet 1'!M52,'Data for Sheet 1'!M64)))))</f>
-        <v>1.0537190082644627</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M4,IF($B$3="King",'Revenue - Data'!M16,IF($B$3="Superior King",'Revenue - Data'!M28,IF($B$3="Executive",'Revenue - Data'!M40,IF($B$3="One Club",'Revenue - Data'!M52,'Revenue - Data'!M64)))))</f>
+        <v>1.0440503432494279</v>
       </c>
       <c r="C8" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N4,IF($B$3="King",'Data for Sheet 1'!N16,IF($B$3="Superior King",'Data for Sheet 1'!N28,IF($B$3="Executive",'Data for Sheet 1'!N40,IF($B$3="One Club",'Data for Sheet 1'!N52,'Data for Sheet 1'!N64)))))</f>
-        <v>0.93027872305947168</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N4,IF($B$3="King",'Revenue - Data'!N16,IF($B$3="Superior King",'Revenue - Data'!N28,IF($B$3="Executive",'Revenue - Data'!N40,IF($B$3="One Club",'Revenue - Data'!N52,'Revenue - Data'!N64)))))</f>
+        <v>1.0278413424866515</v>
       </c>
       <c r="D8" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O4,IF($B$3="King",'Data for Sheet 1'!O16,IF($B$3="Superior King",'Data for Sheet 1'!O28,IF($B$3="Executive",'Data for Sheet 1'!O40,IF($B$3="One Club",'Data for Sheet 1'!O52,'Data for Sheet 1'!O64)))))</f>
-        <v>0.95186272524802595</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O4,IF($B$3="King",'Revenue - Data'!O16,IF($B$3="Superior King",'Revenue - Data'!O28,IF($B$3="Executive",'Revenue - Data'!O40,IF($B$3="One Club",'Revenue - Data'!O52,'Revenue - Data'!O64)))))</f>
+        <v>0.97504031666911006</v>
       </c>
       <c r="E8" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" ht="15.5">
+      <c r="J8" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="15.5">
       <c r="B9" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M5,IF($B$3="King",'Data for Sheet 1'!M17,IF($B$3="Superior King",'Data for Sheet 1'!M29,IF($B$3="Executive",'Data for Sheet 1'!M41,IF($B$3="One Club",'Data for Sheet 1'!M53,'Data for Sheet 1'!M65)))))</f>
-        <v>1.0088383838383839</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M5,IF($B$3="King",'Revenue - Data'!M17,IF($B$3="Superior King",'Revenue - Data'!M29,IF($B$3="Executive",'Revenue - Data'!M41,IF($B$3="One Club",'Revenue - Data'!M53,'Revenue - Data'!M65)))))</f>
+        <v>1.037828947368421</v>
       </c>
       <c r="C9" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N5,IF($B$3="King",'Data for Sheet 1'!N17,IF($B$3="Superior King",'Data for Sheet 1'!N29,IF($B$3="Executive",'Data for Sheet 1'!N41,IF($B$3="One Club",'Data for Sheet 1'!N53,'Data for Sheet 1'!N65)))))</f>
-        <v>0.77790156466627058</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N5,IF($B$3="King",'Revenue - Data'!N17,IF($B$3="Superior King",'Revenue - Data'!N29,IF($B$3="Executive",'Revenue - Data'!N41,IF($B$3="One Club",'Revenue - Data'!N53,'Revenue - Data'!N65)))))</f>
+        <v>1.2092189608636976</v>
       </c>
       <c r="D9" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O5,IF($B$3="King",'Data for Sheet 1'!O17,IF($B$3="Superior King",'Data for Sheet 1'!O29,IF($B$3="Executive",'Data for Sheet 1'!O41,IF($B$3="One Club",'Data for Sheet 1'!O53,'Data for Sheet 1'!O65)))))</f>
-        <v>0.79917017587317318</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O5,IF($B$3="King",'Revenue - Data'!O17,IF($B$3="Superior King",'Revenue - Data'!O29,IF($B$3="Executive",'Revenue - Data'!O41,IF($B$3="One Club",'Revenue - Data'!O53,'Revenue - Data'!O65)))))</f>
+        <v>1.162362792006755</v>
       </c>
       <c r="E9" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" ht="15.5">
+      <c r="J9" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="15.5">
       <c r="B10" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M6,IF($B$3="King",'Data for Sheet 1'!M18,IF($B$3="Superior King",'Data for Sheet 1'!M30,IF($B$3="Executive",'Data for Sheet 1'!M42,IF($B$3="One Club",'Data for Sheet 1'!M54,'Data for Sheet 1'!M66)))))</f>
-        <v>0.97443181818181823</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M6,IF($B$3="King",'Revenue - Data'!M18,IF($B$3="Superior King",'Revenue - Data'!M30,IF($B$3="Executive",'Revenue - Data'!M42,IF($B$3="One Club",'Revenue - Data'!M54,'Revenue - Data'!M66)))))</f>
+        <v>1.0171624713958809</v>
       </c>
       <c r="C10" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N6,IF($B$3="King",'Data for Sheet 1'!N18,IF($B$3="Superior King",'Data for Sheet 1'!N30,IF($B$3="Executive",'Data for Sheet 1'!N42,IF($B$3="One Club",'Data for Sheet 1'!N54,'Data for Sheet 1'!N66)))))</f>
-        <v>0.52562388591800357</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N6,IF($B$3="King",'Revenue - Data'!N18,IF($B$3="Superior King",'Revenue - Data'!N30,IF($B$3="Executive",'Revenue - Data'!N42,IF($B$3="One Club",'Revenue - Data'!N54,'Revenue - Data'!N66)))))</f>
+        <v>0.92134600715836412</v>
       </c>
       <c r="D10" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O6,IF($B$3="King",'Data for Sheet 1'!O18,IF($B$3="Superior King",'Data for Sheet 1'!O30,IF($B$3="Executive",'Data for Sheet 1'!O42,IF($B$3="One Club",'Data for Sheet 1'!O54,'Data for Sheet 1'!O66)))))</f>
-        <v>0.5418293363078639</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O6,IF($B$3="King",'Revenue - Data'!O18,IF($B$3="Superior King",'Revenue - Data'!O30,IF($B$3="Executive",'Revenue - Data'!O42,IF($B$3="One Club",'Revenue - Data'!O54,'Revenue - Data'!O66)))))</f>
+        <v>0.88238528075062306</v>
       </c>
       <c r="E10" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" ht="15.5">
+      <c r="J10" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="15.5">
       <c r="B11" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M7,IF($B$3="King",'Data for Sheet 1'!M19,IF($B$3="Superior King",'Data for Sheet 1'!M31,IF($B$3="Executive",'Data for Sheet 1'!M43,IF($B$3="One Club",'Data for Sheet 1'!M55,'Data for Sheet 1'!M67)))))</f>
-        <v>0.79242424242424248</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M7,IF($B$3="King",'Revenue - Data'!M19,IF($B$3="Superior King",'Revenue - Data'!M31,IF($B$3="Executive",'Revenue - Data'!M43,IF($B$3="One Club",'Revenue - Data'!M55,'Revenue - Data'!M67)))))</f>
+        <v>0.92690058479532167</v>
       </c>
       <c r="C11" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N7,IF($B$3="King",'Data for Sheet 1'!N19,IF($B$3="Superior King",'Data for Sheet 1'!N31,IF($B$3="Executive",'Data for Sheet 1'!N43,IF($B$3="One Club",'Data for Sheet 1'!N55,'Data for Sheet 1'!N67)))))</f>
-        <v>0.61328282828282832</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N7,IF($B$3="King",'Revenue - Data'!N19,IF($B$3="Superior King",'Revenue - Data'!N31,IF($B$3="Executive",'Revenue - Data'!N43,IF($B$3="One Club",'Revenue - Data'!N55,'Revenue - Data'!N67)))))</f>
+        <v>0.94291747888239119</v>
       </c>
       <c r="D11" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O7,IF($B$3="King",'Data for Sheet 1'!O19,IF($B$3="Superior King",'Data for Sheet 1'!O31,IF($B$3="Executive",'Data for Sheet 1'!O43,IF($B$3="One Club",'Data for Sheet 1'!O55,'Data for Sheet 1'!O67)))))</f>
-        <v>0.66029040404040407</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O7,IF($B$3="King",'Revenue - Data'!O19,IF($B$3="Superior King",'Revenue - Data'!O31,IF($B$3="Executive",'Revenue - Data'!O43,IF($B$3="One Club",'Revenue - Data'!O55,'Revenue - Data'!O67)))))</f>
+        <v>0.8464100064977258</v>
       </c>
       <c r="E11" s="7">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" ht="15.5">
+      <c r="J11" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="15.5">
       <c r="B12" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M8,IF($B$3="King",'Data for Sheet 1'!M20,IF($B$3="Superior King",'Data for Sheet 1'!M32,IF($B$3="Executive",'Data for Sheet 1'!M44,IF($B$3="One Club",'Data for Sheet 1'!M56,'Data for Sheet 1'!M68)))))</f>
-        <v>0.43039772727272729</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M8,IF($B$3="King",'Revenue - Data'!M20,IF($B$3="Superior King",'Revenue - Data'!M32,IF($B$3="Executive",'Revenue - Data'!M44,IF($B$3="One Club",'Revenue - Data'!M56,'Revenue - Data'!M68)))))</f>
+        <v>0.98624401913875603</v>
       </c>
       <c r="C12" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N8,IF($B$3="King",'Data for Sheet 1'!N20,IF($B$3="Superior King",'Data for Sheet 1'!N32,IF($B$3="Executive",'Data for Sheet 1'!N44,IF($B$3="One Club",'Data for Sheet 1'!N56,'Data for Sheet 1'!N68)))))</f>
-        <v>9.8697916666666663E-2</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N8,IF($B$3="King",'Revenue - Data'!N20,IF($B$3="Superior King",'Revenue - Data'!N32,IF($B$3="Executive",'Revenue - Data'!N44,IF($B$3="One Club",'Revenue - Data'!N56,'Revenue - Data'!N68)))))</f>
+        <v>0.78847687400318978</v>
       </c>
       <c r="D12" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O8,IF($B$3="King",'Data for Sheet 1'!O20,IF($B$3="Superior King",'Data for Sheet 1'!O32,IF($B$3="Executive",'Data for Sheet 1'!O44,IF($B$3="One Club",'Data for Sheet 1'!O56,'Data for Sheet 1'!O68)))))</f>
-        <v>0.10292376893939394</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O8,IF($B$3="King",'Revenue - Data'!O20,IF($B$3="Superior King",'Revenue - Data'!O32,IF($B$3="Executive",'Revenue - Data'!O44,IF($B$3="One Club",'Revenue - Data'!O56,'Revenue - Data'!O68)))))</f>
+        <v>0.81346358320042533</v>
       </c>
       <c r="E12" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" ht="15.5">
+      <c r="J12" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="15.5">
       <c r="B13" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M9,IF($B$3="King",'Data for Sheet 1'!M21,IF($B$3="Superior King",'Data for Sheet 1'!M33,IF($B$3="Executive",'Data for Sheet 1'!M45,IF($B$3="One Club",'Data for Sheet 1'!M57,'Data for Sheet 1'!M69)))))</f>
-        <v>0.37926136363636365</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M9,IF($B$3="King",'Revenue - Data'!M21,IF($B$3="Superior King",'Revenue - Data'!M33,IF($B$3="Executive",'Revenue - Data'!M45,IF($B$3="One Club",'Revenue - Data'!M57,'Revenue - Data'!M69)))))</f>
+        <v>0.99542334096109841</v>
       </c>
       <c r="C13" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N9,IF($B$3="King",'Data for Sheet 1'!N21,IF($B$3="Superior King",'Data for Sheet 1'!N33,IF($B$3="Executive",'Data for Sheet 1'!N45,IF($B$3="One Club",'Data for Sheet 1'!N57,'Data for Sheet 1'!N69)))))</f>
-        <v>6.5364583333333337E-2</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N9,IF($B$3="King",'Revenue - Data'!N21,IF($B$3="Superior King",'Revenue - Data'!N33,IF($B$3="Executive",'Revenue - Data'!N45,IF($B$3="One Club",'Revenue - Data'!N57,'Revenue - Data'!N69)))))</f>
+        <v>0.75115687770150008</v>
       </c>
       <c r="D13" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O9,IF($B$3="King",'Data for Sheet 1'!O21,IF($B$3="Superior King",'Data for Sheet 1'!O33,IF($B$3="Executive",'Data for Sheet 1'!O45,IF($B$3="One Club",'Data for Sheet 1'!O57,'Data for Sheet 1'!O69)))))</f>
-        <v>6.8714488636363633E-2</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O9,IF($B$3="King",'Revenue - Data'!O21,IF($B$3="Superior King",'Revenue - Data'!O33,IF($B$3="Executive",'Revenue - Data'!O45,IF($B$3="One Club",'Revenue - Data'!O57,'Revenue - Data'!O69)))))</f>
+        <v>0.77571192473938466</v>
       </c>
       <c r="E13" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" ht="15.5">
+      <c r="J13" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="15.5">
       <c r="B14" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M10,IF($B$3="King",'Data for Sheet 1'!M22,IF($B$3="Superior King",'Data for Sheet 1'!M34,IF($B$3="Executive",'Data for Sheet 1'!M46,IF($B$3="One Club",'Data for Sheet 1'!M58,'Data for Sheet 1'!M70)))))</f>
-        <v>0.36969696969696969</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M10,IF($B$3="King",'Revenue - Data'!M22,IF($B$3="Superior King",'Revenue - Data'!M34,IF($B$3="Executive",'Revenue - Data'!M46,IF($B$3="One Club",'Revenue - Data'!M58,'Revenue - Data'!M70)))))</f>
+        <v>1.0561403508771929</v>
       </c>
       <c r="C14" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N10,IF($B$3="King",'Data for Sheet 1'!N22,IF($B$3="Superior King",'Data for Sheet 1'!N34,IF($B$3="Executive",'Data for Sheet 1'!N46,IF($B$3="One Club",'Data for Sheet 1'!N58,'Data for Sheet 1'!N70)))))</f>
-        <v>9.0136660724896026E-2</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N10,IF($B$3="King",'Revenue - Data'!N22,IF($B$3="Superior King",'Revenue - Data'!N34,IF($B$3="Executive",'Revenue - Data'!N46,IF($B$3="One Club",'Revenue - Data'!N58,'Revenue - Data'!N70)))))</f>
+        <v>0.77903733693207378</v>
       </c>
       <c r="D14" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O10,IF($B$3="King",'Data for Sheet 1'!O22,IF($B$3="Superior King",'Data for Sheet 1'!O34,IF($B$3="Executive",'Data for Sheet 1'!O46,IF($B$3="One Club",'Data for Sheet 1'!O58,'Data for Sheet 1'!O70)))))</f>
-        <v>8.3333333333333329E-2</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O10,IF($B$3="King",'Revenue - Data'!O22,IF($B$3="Superior King",'Revenue - Data'!O34,IF($B$3="Executive",'Revenue - Data'!O46,IF($B$3="One Club",'Revenue - Data'!O58,'Revenue - Data'!O70)))))</f>
+        <v>0.73487404408457035</v>
       </c>
       <c r="E14" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" ht="15.5">
+      <c r="J14" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="15.5">
       <c r="B15" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M11,IF($B$3="King",'Data for Sheet 1'!M23,IF($B$3="Superior King",'Data for Sheet 1'!M35,IF($B$3="Executive",'Data for Sheet 1'!M47,IF($B$3="One Club",'Data for Sheet 1'!M59,'Data for Sheet 1'!M71)))))</f>
-        <v>0.25852272727272729</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M11,IF($B$3="King",'Revenue - Data'!M23,IF($B$3="Superior King",'Revenue - Data'!M35,IF($B$3="Executive",'Revenue - Data'!M47,IF($B$3="One Club",'Revenue - Data'!M59,'Revenue - Data'!M71)))))</f>
+        <v>1.0427631578947369</v>
       </c>
       <c r="C15" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N11,IF($B$3="King",'Data for Sheet 1'!N23,IF($B$3="Superior King",'Data for Sheet 1'!N35,IF($B$3="Executive",'Data for Sheet 1'!N47,IF($B$3="One Club",'Data for Sheet 1'!N59,'Data for Sheet 1'!N71)))))</f>
-        <v>3.7026515151515151E-2</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N11,IF($B$3="King",'Revenue - Data'!N23,IF($B$3="Superior King",'Revenue - Data'!N35,IF($B$3="Executive",'Revenue - Data'!N47,IF($B$3="One Club",'Revenue - Data'!N59,'Revenue - Data'!N71)))))</f>
+        <v>1.3246762740183793</v>
       </c>
       <c r="D15" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O11,IF($B$3="King",'Data for Sheet 1'!O23,IF($B$3="Superior King",'Data for Sheet 1'!O35,IF($B$3="Executive",'Data for Sheet 1'!O47,IF($B$3="One Club",'Data for Sheet 1'!O59,'Data for Sheet 1'!O71)))))</f>
-        <v>3.7109375E-2</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O11,IF($B$3="King",'Revenue - Data'!O23,IF($B$3="Superior King",'Revenue - Data'!O35,IF($B$3="Executive",'Revenue - Data'!O47,IF($B$3="One Club",'Revenue - Data'!O59,'Revenue - Data'!O71)))))</f>
+        <v>1.3357351712614871</v>
       </c>
       <c r="E15" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" ht="15.5">
+      <c r="J15" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="15.5">
       <c r="B16" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M12,IF($B$3="King",'Data for Sheet 1'!M24,IF($B$3="Superior King",'Data for Sheet 1'!M36,IF($B$3="Executive",'Data for Sheet 1'!M48,IF($B$3="One Club",'Data for Sheet 1'!M60,'Data for Sheet 1'!M72)))))</f>
-        <v>0.22727272727272727</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M12,IF($B$3="King",'Revenue - Data'!M24,IF($B$3="Superior King",'Revenue - Data'!M36,IF($B$3="Executive",'Revenue - Data'!M48,IF($B$3="One Club",'Revenue - Data'!M60,'Revenue - Data'!M72)))))</f>
+        <v>1.0007309941520468</v>
       </c>
       <c r="C16" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N12,IF($B$3="King",'Data for Sheet 1'!N24,IF($B$3="Superior King",'Data for Sheet 1'!N36,IF($B$3="Executive",'Data for Sheet 1'!N48,IF($B$3="One Club",'Data for Sheet 1'!N60,'Data for Sheet 1'!N72)))))</f>
-        <v>3.928872053872054E-2</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N12,IF($B$3="King",'Revenue - Data'!N24,IF($B$3="Superior King",'Revenue - Data'!N36,IF($B$3="Executive",'Revenue - Data'!N48,IF($B$3="One Club",'Revenue - Data'!N60,'Revenue - Data'!N72)))))</f>
+        <v>0.85878817413905129</v>
       </c>
       <c r="D16" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O12,IF($B$3="King",'Data for Sheet 1'!O24,IF($B$3="Superior King",'Data for Sheet 1'!O36,IF($B$3="Executive",'Data for Sheet 1'!O48,IF($B$3="One Club",'Data for Sheet 1'!O60,'Data for Sheet 1'!O72)))))</f>
-        <v>3.8457491582491579E-2</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O12,IF($B$3="King",'Revenue - Data'!O24,IF($B$3="Superior King",'Revenue - Data'!O36,IF($B$3="Executive",'Revenue - Data'!O48,IF($B$3="One Club",'Revenue - Data'!O60,'Revenue - Data'!O72)))))</f>
+        <v>0.88511208576998046</v>
       </c>
       <c r="E16" s="7">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" ht="15.5">
+      <c r="J16" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="15.5">
       <c r="B17" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!M13,IF($B$3="King",'Data for Sheet 1'!M25,IF($B$3="Superior King",'Data for Sheet 1'!M37,IF($B$3="Executive",'Data for Sheet 1'!M49,IF($B$3="One Club",'Data for Sheet 1'!M61,'Data for Sheet 1'!M73)))))</f>
-        <v>0.18545454545454546</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M13,IF($B$3="King",'Revenue - Data'!M25,IF($B$3="Superior King",'Revenue - Data'!M37,IF($B$3="Executive",'Revenue - Data'!M49,IF($B$3="One Club",'Revenue - Data'!M61,'Revenue - Data'!M73)))))</f>
+        <v>0.97488038277511957</v>
       </c>
       <c r="C17" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!N13,IF($B$3="King",'Data for Sheet 1'!N25,IF($B$3="Superior King",'Data for Sheet 1'!N37,IF($B$3="Executive",'Data for Sheet 1'!N49,IF($B$3="One Club",'Data for Sheet 1'!N61,'Data for Sheet 1'!N73)))))</f>
-        <v>3.6942148760330577E-2</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N13,IF($B$3="King",'Revenue - Data'!N25,IF($B$3="Superior King",'Revenue - Data'!N37,IF($B$3="Executive",'Revenue - Data'!N49,IF($B$3="One Club",'Revenue - Data'!N61,'Revenue - Data'!N73)))))</f>
+        <v>0.96106576601932636</v>
       </c>
       <c r="D17" s="6">
-        <f>IF($B$3="Club Deluxe",'Data for Sheet 1'!O13,IF($B$3="King",'Data for Sheet 1'!O25,IF($B$3="Superior King",'Data for Sheet 1'!O37,IF($B$3="Executive",'Data for Sheet 1'!O49,IF($B$3="One Club",'Data for Sheet 1'!O61,'Data for Sheet 1'!O73)))))</f>
-        <v>3.8223140495867766E-2</v>
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O13,IF($B$3="King",'Revenue - Data'!O25,IF($B$3="Superior King",'Revenue - Data'!O37,IF($B$3="Executive",'Revenue - Data'!O49,IF($B$3="One Club",'Revenue - Data'!O61,'Revenue - Data'!O73)))))</f>
+        <v>1.0148868831321065</v>
       </c>
       <c r="E17" s="7">
         <v>12</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -9921,7 +13756,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1EB5C39D-600B-4A14-8FC2-FC88ED3829FC}">
           <x14:formula1>
-            <xm:f>'Validation for Sheet1'!$B$3:$B$8</xm:f>
+            <xm:f>Validation!$B$3:$B$8</xm:f>
           </x14:formula1>
           <xm:sqref>B3</xm:sqref>
         </x14:dataValidation>
@@ -9931,47 +13766,83 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B47D7F0-07B4-4A35-A454-668FBC6C9FFD}">
-  <dimension ref="B3:B8"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2617BFCE-6B72-4CE3-BC83-1F4D7ED9EB31}">
+  <dimension ref="C4:D10"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="3" spans="2:2">
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2">
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2">
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2">
-      <c r="B8" t="s">
-        <v>30</v>
+    <row r="4" spans="3:4">
+      <c r="C4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4">
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4">
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4">
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4">
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4">
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4">
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA41081-7588-469A-AFDA-DD303C470471}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A11F2F3-4F7B-405C-912E-D34822220CD1}">
   <dimension ref="A1:S73"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -13744,463 +17615,509 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6482E56F-AAD0-45DD-AED2-1DDF0978065A}">
-  <dimension ref="C4:O28"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="10" max="10" width="11.7265625" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" customWidth="1"/>
+    <col min="5" max="5" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:15">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
       <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="3:15">
       <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="D5">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14">
         <v>1</v>
       </c>
-      <c r="J5" t="s">
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" t="s">
         <v>37</v>
       </c>
-      <c r="K5" t="s">
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
         <v>38</v>
       </c>
-      <c r="L5" t="s">
+      <c r="D15" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="6" spans="3:15">
-      <c r="C6" t="s">
+      <c r="E15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B47D7F0-07B4-4A35-A454-668FBC6C9FFD}">
+  <dimension ref="A3:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="31.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="D6">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="J6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="3:15">
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7">
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="J7" t="s">
-        <v>37</v>
-      </c>
-      <c r="K7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="3:15">
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="J8" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="3:15">
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9">
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="J9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="3:15">
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10">
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="J10" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="3:15">
-      <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11">
-        <v>7</v>
-      </c>
-      <c r="J11" t="s">
-        <v>37</v>
-      </c>
-      <c r="K11" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="3:15">
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12">
-        <v>8</v>
-      </c>
-      <c r="J12" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="3:15">
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13">
-        <v>9</v>
-      </c>
-      <c r="J13" t="s">
-        <v>37</v>
-      </c>
-      <c r="K13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="3:15">
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14">
-        <v>10</v>
-      </c>
-      <c r="J14" t="s">
-        <v>37</v>
-      </c>
-      <c r="K14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="3:15">
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15">
-        <v>11</v>
-      </c>
-      <c r="J15" t="s">
-        <v>37</v>
-      </c>
-      <c r="K15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="3:15">
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16">
-        <v>12</v>
-      </c>
-      <c r="J16" t="s">
-        <v>37</v>
-      </c>
-      <c r="K16" t="s">
-        <v>38</v>
-      </c>
-      <c r="L16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="3:12">
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="J17" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" t="s">
-        <v>39</v>
-      </c>
-      <c r="L17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="3:12">
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="J18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" t="s">
-        <v>39</v>
-      </c>
-      <c r="L18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="3:12">
-      <c r="C19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="J19" t="s">
-        <v>38</v>
-      </c>
-      <c r="K19" t="s">
-        <v>39</v>
-      </c>
-      <c r="L19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="3:12">
-      <c r="C20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20">
-        <v>4</v>
-      </c>
-      <c r="J20" t="s">
-        <v>38</v>
-      </c>
-      <c r="K20" t="s">
-        <v>39</v>
-      </c>
-      <c r="L20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="3:12">
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21">
-        <v>5</v>
-      </c>
-      <c r="J21" t="s">
-        <v>38</v>
-      </c>
-      <c r="K21" t="s">
-        <v>39</v>
-      </c>
-      <c r="L21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="3:12">
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22">
-        <v>6</v>
-      </c>
-      <c r="J22" t="s">
-        <v>38</v>
-      </c>
-      <c r="K22" t="s">
-        <v>39</v>
-      </c>
-      <c r="L22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="3:12">
-      <c r="C23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23">
-        <v>7</v>
-      </c>
-      <c r="J23" t="s">
-        <v>38</v>
-      </c>
-      <c r="K23" t="s">
-        <v>39</v>
-      </c>
-      <c r="L23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="3:12">
-      <c r="C24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24">
-        <v>8</v>
-      </c>
-      <c r="J24" t="s">
-        <v>38</v>
-      </c>
-      <c r="K24" t="s">
-        <v>39</v>
-      </c>
-      <c r="L24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="3:12">
-      <c r="C25" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25">
-        <v>9</v>
-      </c>
-      <c r="J25" t="s">
-        <v>38</v>
-      </c>
-      <c r="K25" t="s">
-        <v>39</v>
-      </c>
-      <c r="L25" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="3:12">
-      <c r="C26" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26">
-        <v>10</v>
-      </c>
-      <c r="J26" t="s">
-        <v>38</v>
-      </c>
-      <c r="K26" t="s">
-        <v>39</v>
-      </c>
-      <c r="L26" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="3:12">
-      <c r="C27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27">
-        <v>11</v>
-      </c>
-      <c r="J27" t="s">
-        <v>38</v>
-      </c>
-      <c r="K27" t="s">
-        <v>39</v>
-      </c>
-      <c r="L27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="3:12">
-      <c r="C28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28">
-        <v>12</v>
-      </c>
-      <c r="J28" t="s">
-        <v>38</v>
-      </c>
-      <c r="K28" t="s">
-        <v>39</v>
-      </c>
-      <c r="L28" t="s">
-        <v>37</v>
+      <c r="B8" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/2022_04_29 PWC Challenge 1 - Hotel Analytics/PWC Dashboard.xlsx
+++ b/2022_04_29 PWC Challenge 1 - Hotel Analytics/PWC Dashboard.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seoul\Dropbox\00 technical\github\kimep-data-science-lab\2022_04_29 PWC Challenge 1 - Hotel Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C081C89-67B3-4252-A3CD-C644C6488322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09DEA4F-BF38-49D2-8237-A73EF4413C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="6" xr2:uid="{AACBAEBD-F012-4269-A3B9-168C8D706687}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AACBAEBD-F012-4269-A3B9-168C8D706687}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="5" r:id="rId1"/>
-    <sheet name="Plan" sheetId="7" r:id="rId2"/>
+    <sheet name="Revenue" sheetId="7" r:id="rId2"/>
     <sheet name="Revenue Dash" sheetId="1" r:id="rId3"/>
     <sheet name="Concerns" sheetId="8" r:id="rId4"/>
     <sheet name="Concerns Dash" sheetId="6" r:id="rId5"/>
     <sheet name="Revenue - Data" sheetId="2" r:id="rId6"/>
-    <sheet name="Concerns - Data" sheetId="4" r:id="rId7"/>
-    <sheet name="Validation" sheetId="3" r:id="rId8"/>
+    <sheet name="Concerns barplot Data" sheetId="4" r:id="rId7"/>
+    <sheet name="Concerns dash data" sheetId="9" r:id="rId8"/>
+    <sheet name="Validation" sheetId="3" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="86">
   <si>
     <t>Month</t>
   </si>
@@ -140,28 +141,7 @@
     <t>One Suite</t>
   </si>
   <si>
-    <t>P1Label</t>
-  </si>
-  <si>
-    <t>P2Label</t>
-  </si>
-  <si>
-    <t>P3Label</t>
-  </si>
-  <si>
-    <t>P2Count</t>
-  </si>
-  <si>
-    <t>P3Count</t>
-  </si>
-  <si>
-    <t>P1Count</t>
-  </si>
-  <si>
     <t>Temperature</t>
-  </si>
-  <si>
-    <t>Smell</t>
   </si>
   <si>
     <t>Noise</t>
@@ -564,15 +544,6 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -605,6 +576,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -779,40 +759,40 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.95914127423822715</c:v>
+                  <c:v>0.96875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0639952153110048</c:v>
+                  <c:v>1.0119047619047619</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0440503432494279</c:v>
+                  <c:v>0.89583333333333337</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.037828947368421</c:v>
+                  <c:v>0.68888888888888888</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0171624713958809</c:v>
+                  <c:v>0.95333333333333337</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.92690058479532167</c:v>
+                  <c:v>0.87037037037037035</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.98624401913875603</c:v>
+                  <c:v>0.94</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.99542334096109841</c:v>
+                  <c:v>1.1933333333333334</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0561403508771929</c:v>
+                  <c:v>0.92361111111111116</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0427631578947369</c:v>
+                  <c:v>0.93181818181818177</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0007309941520468</c:v>
+                  <c:v>0.9907407407407407</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.97488038277511957</c:v>
+                  <c:v>0.86842105263157898</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -960,40 +940,40 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.78562634656817487</c:v>
+                  <c:v>0.4055121527777778</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.1251860712387027</c:v>
+                  <c:v>0.29181547619047621</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0278413424866515</c:v>
+                  <c:v>0.21289682539682539</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.2092189608636976</c:v>
+                  <c:v>0.11037037037037037</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.92134600715836412</c:v>
+                  <c:v>0.18450793650793651</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.94291747888239119</c:v>
+                  <c:v>8.4104938271604937E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.78847687400318978</c:v>
+                  <c:v>0.88180555555555551</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.75115687770150008</c:v>
+                  <c:v>1.4589722222222221</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.77903733693207378</c:v>
+                  <c:v>1.0264219576719578</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.3246762740183793</c:v>
+                  <c:v>0.67572601010101008</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.85878817413905129</c:v>
+                  <c:v>1.0784336419753087</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.96106576601932636</c:v>
+                  <c:v>0.68479532163742685</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1141,40 +1121,40 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.82094490612496152</c:v>
+                  <c:v>0.79166666666666663</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.1200824029771399</c:v>
+                  <c:v>0.52802579365079361</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.97504031666911006</c:v>
+                  <c:v>0.54389880952380953</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.162362792006755</c:v>
+                  <c:v>0.31732804232804235</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.88238528075062306</c:v>
+                  <c:v>0.96047619047619048</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8464100064977258</c:v>
+                  <c:v>0.59924768518518523</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.81346358320042533</c:v>
+                  <c:v>0.86236111111111113</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.77571192473938466</c:v>
+                  <c:v>1.153125</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.73487404408457035</c:v>
+                  <c:v>0.85945767195767198</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.3357351712614871</c:v>
+                  <c:v>0.77541035353535348</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.88511208576998046</c:v>
+                  <c:v>0.99807098765432101</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0148868831321065</c:v>
+                  <c:v>0.70175438596491224</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2142,7 +2122,7 @@
             <c:numRef>
               <c:f>[1]Merge!$M$2:$M$13</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.95798319327731096</c:v>
@@ -2220,7 +2200,7 @@
             <c:numRef>
               <c:f>[1]Merge!$N$2:$N$13</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.4710706504824152</c:v>
@@ -2298,7 +2278,7 @@
             <c:numRef>
               <c:f>[1]Merge!$O$2:$O$13</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.85154061624649857</c:v>
@@ -2430,7 +2410,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2656,7 +2636,7 @@
             <c:numRef>
               <c:f>[1]Merge!$M$14:$M$25</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1.0811688311688312</c:v>
@@ -2734,7 +2714,7 @@
             <c:numRef>
               <c:f>[1]Merge!$N$14:$N$25</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1.6474837662337662</c:v>
@@ -2812,7 +2792,7 @@
             <c:numRef>
               <c:f>[1]Merge!$O$14:$O$25</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1.6248308982683983</c:v>
@@ -2944,7 +2924,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3160,7 +3140,7 @@
             <c:numRef>
               <c:f>[1]Merge!$M$26:$M$37</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.95914127423822715</c:v>
@@ -3238,7 +3218,7 @@
             <c:numRef>
               <c:f>[1]Merge!$N$26:$N$37</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.78562634656817487</c:v>
@@ -3316,7 +3296,7 @@
             <c:numRef>
               <c:f>[1]Merge!$O$26:$O$37</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.82094490612496152</c:v>
@@ -3448,7 +3428,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3664,7 +3644,7 @@
             <c:numRef>
               <c:f>[1]Merge!$M$38:$M$49</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1.068888888888889</c:v>
@@ -3742,7 +3722,7 @@
             <c:numRef>
               <c:f>[1]Merge!$N$38:$N$49</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1.2992222222222223</c:v>
@@ -3820,7 +3800,7 @@
             <c:numRef>
               <c:f>[1]Merge!$O$38:$O$49</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1.3711728395061729</c:v>
@@ -3952,7 +3932,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4168,7 +4148,7 @@
             <c:numRef>
               <c:f>[1]Merge!$M$50:$M$61</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1.0411764705882354</c:v>
@@ -4246,7 +4226,7 @@
             <c:numRef>
               <c:f>[1]Merge!$N$50:$N$61</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.46202614379084966</c:v>
@@ -4324,7 +4304,7 @@
             <c:numRef>
               <c:f>[1]Merge!$O$50:$O$61</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.81903594771241828</c:v>
@@ -4456,7 +4436,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4672,7 +4652,7 @@
             <c:numRef>
               <c:f>[1]Merge!$M$62:$M$73</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.96875</c:v>
@@ -4750,7 +4730,7 @@
             <c:numRef>
               <c:f>[1]Merge!$N$62:$N$73</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.4055121527777778</c:v>
@@ -4828,7 +4808,7 @@
             <c:numRef>
               <c:f>[1]Merge!$O$62:$O$73</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0.79166666666666663</c:v>
@@ -4960,7 +4940,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -9507,16 +9487,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>50801</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>127001</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>151442</xdr:rowOff>
+      <xdr:rowOff>126042</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>254133</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>330333</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -9546,7 +9526,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="660401" y="335592"/>
+          <a:off x="1346201" y="310192"/>
           <a:ext cx="6908932" cy="3461708"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -11007,16 +10987,16 @@
   <sheetData>
     <row r="6" spans="3:9">
       <c r="C6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="3:9">
@@ -11024,7 +11004,7 @@
         <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="3:9">
@@ -11032,7 +11012,7 @@
         <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="3:9">
@@ -11040,7 +11020,7 @@
         <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="3:9">
@@ -11072,79 +11052,79 @@
     <col min="1" max="1" width="1.7265625" customWidth="1"/>
     <col min="2" max="2" width="26.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="14" width="8.90625" customWidth="1"/>
-    <col min="15" max="15" width="8.90625" style="13" customWidth="1"/>
+    <col min="15" max="15" width="8.90625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" s="13" customFormat="1" ht="19.899999999999999" customHeight="1">
-      <c r="B1" s="12" t="s">
-        <v>53</v>
+    <row r="1" spans="2:15" s="10" customFormat="1" ht="19.899999999999999" customHeight="1">
+      <c r="B1" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="2:15">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="J3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="K3" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="L3" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="M3" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="N3" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="O3" s="11" t="s">
         <v>60</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="M3" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="N3" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="O3" s="14" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="4" spans="2:15">
-      <c r="B4" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
+      <c r="B4" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
     </row>
     <row r="5" spans="2:15">
-      <c r="B5" s="17" t="s">
-        <v>69</v>
+      <c r="B5" s="14" t="s">
+        <v>62</v>
       </c>
       <c r="C5">
         <v>28</v>
@@ -11184,8 +11164,8 @@
       </c>
     </row>
     <row r="6" spans="2:15">
-      <c r="B6" s="18" t="s">
-        <v>70</v>
+      <c r="B6" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="C6" s="2">
         <v>304164</v>
@@ -11223,13 +11203,13 @@
       <c r="N6" s="2">
         <v>370160</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="16">
         <v>4668216</v>
       </c>
     </row>
     <row r="7" spans="2:15">
-      <c r="B7" s="18" t="s">
-        <v>71</v>
+      <c r="B7" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="C7" s="2">
         <v>214200</v>
@@ -11267,13 +11247,13 @@
       <c r="N7" s="2">
         <v>260680</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="16">
         <v>3287480</v>
       </c>
     </row>
     <row r="8" spans="2:15">
-      <c r="B8" s="18" t="s">
-        <v>72</v>
+      <c r="B8" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="C8" s="2">
         <v>64260</v>
@@ -11311,13 +11291,13 @@
       <c r="N8" s="2">
         <v>78204</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="16">
         <v>986244</v>
       </c>
     </row>
     <row r="9" spans="2:15">
-      <c r="B9" s="18" t="s">
-        <v>73</v>
+      <c r="B9" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="C9" s="2">
         <v>25704</v>
@@ -11355,127 +11335,127 @@
       <c r="N9" s="2">
         <v>31276</v>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="16">
         <v>394492</v>
       </c>
     </row>
-    <row r="10" spans="2:15" s="23" customFormat="1">
-      <c r="B10" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="21">
+    <row r="10" spans="2:15" s="20" customFormat="1">
+      <c r="B10" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="18">
         <v>31</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="18">
         <v>28</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="18">
         <v>31</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="18">
         <v>30</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="18">
         <v>31</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="18">
         <v>30</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="18">
         <v>31</v>
       </c>
-      <c r="J10" s="21">
+      <c r="J10" s="18">
         <v>31</v>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="18">
         <v>30</v>
       </c>
-      <c r="L10" s="21">
+      <c r="L10" s="18">
         <v>31</v>
       </c>
-      <c r="M10" s="21">
+      <c r="M10" s="18">
         <v>30</v>
       </c>
-      <c r="N10" s="21">
+      <c r="N10" s="18">
         <v>31</v>
       </c>
-      <c r="O10" s="22"/>
+      <c r="O10" s="19"/>
     </row>
-    <row r="11" spans="2:15" s="23" customFormat="1">
-      <c r="B11" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="21">
+    <row r="11" spans="2:15" s="20" customFormat="1">
+      <c r="B11" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="18">
         <f>C6/C10/C5</f>
         <v>350.41935483870969</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="18">
         <f t="shared" ref="D11:N11" si="0">D6/D10/D5</f>
         <v>456.42857142857144</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="18">
         <f t="shared" si="0"/>
         <v>513.0322580645161</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="18">
         <f t="shared" si="0"/>
         <v>435.4666666666667</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="18">
         <f t="shared" si="0"/>
         <v>458.06451612903226</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="18">
         <f t="shared" si="0"/>
         <v>383.40000000000003</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="18">
         <f t="shared" si="0"/>
         <v>577.16129032258061</v>
       </c>
-      <c r="J11" s="21">
+      <c r="J11" s="18">
         <f t="shared" si="0"/>
         <v>577.16129032258061</v>
       </c>
-      <c r="K11" s="21">
+      <c r="K11" s="18">
         <f t="shared" si="0"/>
         <v>397.59999999999997</v>
       </c>
-      <c r="L11" s="21">
+      <c r="L11" s="18">
         <f t="shared" si="0"/>
         <v>474.09677419354836</v>
       </c>
-      <c r="M11" s="21">
+      <c r="M11" s="18">
         <f t="shared" si="0"/>
         <v>426</v>
       </c>
-      <c r="N11" s="21">
+      <c r="N11" s="18">
         <f t="shared" si="0"/>
         <v>426.45161290322579</v>
       </c>
-      <c r="O11" s="22"/>
+      <c r="O11" s="19"/>
     </row>
     <row r="12" spans="2:15">
-      <c r="B12" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
+      <c r="B12" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
     </row>
     <row r="13" spans="2:15">
-      <c r="B13" s="17" t="s">
-        <v>69</v>
+      <c r="B13" s="14" t="s">
+        <v>62</v>
       </c>
       <c r="C13">
         <v>36</v>
@@ -11513,13 +11493,13 @@
       <c r="N13">
         <v>36</v>
       </c>
-      <c r="O13" s="13">
+      <c r="O13" s="10">
         <v>36</v>
       </c>
     </row>
     <row r="14" spans="2:15">
-      <c r="B14" s="18" t="s">
-        <v>70</v>
+      <c r="B14" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="C14" s="2">
         <v>383400</v>
@@ -11557,13 +11537,13 @@
       <c r="N14" s="2">
         <v>371124</v>
       </c>
-      <c r="O14" s="19">
+      <c r="O14" s="16">
         <v>3990420</v>
       </c>
     </row>
     <row r="15" spans="2:15">
-      <c r="B15" s="18" t="s">
-        <v>71</v>
+      <c r="B15" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="C15" s="2">
         <v>270000</v>
@@ -11601,13 +11581,13 @@
       <c r="N15" s="2">
         <v>261360</v>
       </c>
-      <c r="O15" s="19">
+      <c r="O15" s="16">
         <v>2810160</v>
       </c>
     </row>
     <row r="16" spans="2:15">
-      <c r="B16" s="18" t="s">
-        <v>72</v>
+      <c r="B16" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="C16" s="2">
         <v>81000</v>
@@ -11645,13 +11625,13 @@
       <c r="N16" s="2">
         <v>78408</v>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="16">
         <v>843048</v>
       </c>
     </row>
     <row r="17" spans="2:15">
-      <c r="B17" s="18" t="s">
-        <v>73</v>
+      <c r="B17" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="C17" s="2">
         <v>32400</v>
@@ -11689,127 +11669,127 @@
       <c r="N17" s="2">
         <v>31356</v>
       </c>
-      <c r="O17" s="19">
+      <c r="O17" s="16">
         <v>337212</v>
       </c>
     </row>
-    <row r="18" spans="2:15" s="23" customFormat="1">
-      <c r="B18" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="21">
+    <row r="18" spans="2:15" s="20" customFormat="1">
+      <c r="B18" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="18">
         <v>31</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="18">
         <v>28</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="18">
         <v>31</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="18">
         <v>30</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="18">
         <v>31</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="18">
         <v>30</v>
       </c>
-      <c r="I18" s="21">
+      <c r="I18" s="18">
         <v>31</v>
       </c>
-      <c r="J18" s="21">
+      <c r="J18" s="18">
         <v>31</v>
       </c>
-      <c r="K18" s="21">
+      <c r="K18" s="18">
         <v>30</v>
       </c>
-      <c r="L18" s="21">
+      <c r="L18" s="18">
         <v>31</v>
       </c>
-      <c r="M18" s="21">
+      <c r="M18" s="18">
         <v>30</v>
       </c>
-      <c r="N18" s="21">
+      <c r="N18" s="18">
         <v>31</v>
       </c>
-      <c r="O18" s="22"/>
+      <c r="O18" s="19"/>
     </row>
-    <row r="19" spans="2:15" s="23" customFormat="1">
-      <c r="B19" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="21">
+    <row r="19" spans="2:15" s="20" customFormat="1">
+      <c r="B19" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="18">
         <f>C14/C18/C13</f>
         <v>343.54838709677421</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="18">
         <f t="shared" ref="D19:N19" si="1">D14/D18/D13</f>
         <v>319.5</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="18">
         <f t="shared" si="1"/>
         <v>263.38709677419354</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="18">
         <f t="shared" si="1"/>
         <v>319.5</v>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="18">
         <f t="shared" si="1"/>
         <v>320.64516129032262</v>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="18">
         <f t="shared" si="1"/>
         <v>170.39999999999998</v>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="18">
         <f t="shared" si="1"/>
         <v>343.54838709677421</v>
       </c>
-      <c r="J19" s="21">
+      <c r="J19" s="18">
         <f t="shared" si="1"/>
         <v>343.54838709677421</v>
       </c>
-      <c r="K19" s="21">
+      <c r="K19" s="18">
         <f t="shared" si="1"/>
         <v>213</v>
       </c>
-      <c r="L19" s="21">
+      <c r="L19" s="18">
         <f t="shared" si="1"/>
         <v>384.77419354838707</v>
       </c>
-      <c r="M19" s="21">
+      <c r="M19" s="18">
         <f t="shared" si="1"/>
         <v>284</v>
       </c>
-      <c r="N19" s="21">
+      <c r="N19" s="18">
         <f t="shared" si="1"/>
         <v>332.54838709677421</v>
       </c>
-      <c r="O19" s="22"/>
+      <c r="O19" s="19"/>
     </row>
     <row r="20" spans="2:15">
-      <c r="B20" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
+      <c r="B20" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
     </row>
     <row r="21" spans="2:15">
-      <c r="B21" s="17" t="s">
-        <v>69</v>
+      <c r="B21" s="14" t="s">
+        <v>62</v>
       </c>
       <c r="C21">
         <v>44</v>
@@ -11847,13 +11827,13 @@
       <c r="N21">
         <v>44</v>
       </c>
-      <c r="O21" s="13">
+      <c r="O21" s="10">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="2:15">
-      <c r="B22" s="18" t="s">
-        <v>70</v>
+      <c r="B22" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="C22" s="2">
         <v>349888</v>
@@ -11891,13 +11871,13 @@
       <c r="N22" s="2">
         <v>343640</v>
       </c>
-      <c r="O22" s="19">
+      <c r="O22" s="16">
         <v>2734732</v>
       </c>
     </row>
     <row r="23" spans="2:15">
-      <c r="B23" s="18" t="s">
-        <v>71</v>
+      <c r="B23" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="C23" s="2">
         <v>246400</v>
@@ -11935,13 +11915,13 @@
       <c r="N23" s="2">
         <v>242000</v>
       </c>
-      <c r="O23" s="19">
+      <c r="O23" s="16">
         <v>1925880</v>
       </c>
     </row>
     <row r="24" spans="2:15">
-      <c r="B24" s="18" t="s">
-        <v>72</v>
+      <c r="B24" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="C24" s="2">
         <v>73920</v>
@@ -11979,13 +11959,13 @@
       <c r="N24" s="2">
         <v>72600</v>
       </c>
-      <c r="O24" s="19">
+      <c r="O24" s="16">
         <v>577764</v>
       </c>
     </row>
     <row r="25" spans="2:15">
-      <c r="B25" s="18" t="s">
-        <v>73</v>
+      <c r="B25" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="C25" s="2">
         <v>29568</v>
@@ -12023,127 +12003,127 @@
       <c r="N25" s="2">
         <v>29040</v>
       </c>
-      <c r="O25" s="19">
+      <c r="O25" s="16">
         <v>231088</v>
       </c>
     </row>
-    <row r="26" spans="2:15" s="23" customFormat="1">
-      <c r="B26" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="21">
+    <row r="26" spans="2:15" s="20" customFormat="1">
+      <c r="B26" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="18">
         <v>31</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="18">
         <v>28</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="18">
         <v>31</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="18">
         <v>30</v>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="18">
         <v>31</v>
       </c>
-      <c r="H26" s="21">
+      <c r="H26" s="18">
         <v>30</v>
       </c>
-      <c r="I26" s="21">
+      <c r="I26" s="18">
         <v>31</v>
       </c>
-      <c r="J26" s="21">
+      <c r="J26" s="18">
         <v>31</v>
       </c>
-      <c r="K26" s="21">
+      <c r="K26" s="18">
         <v>30</v>
       </c>
-      <c r="L26" s="21">
+      <c r="L26" s="18">
         <v>31</v>
       </c>
-      <c r="M26" s="21">
+      <c r="M26" s="18">
         <v>30</v>
       </c>
-      <c r="N26" s="21">
+      <c r="N26" s="18">
         <v>31</v>
       </c>
-      <c r="O26" s="22"/>
+      <c r="O26" s="19"/>
     </row>
-    <row r="27" spans="2:15" s="23" customFormat="1">
-      <c r="B27" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="21">
+    <row r="27" spans="2:15" s="20" customFormat="1">
+      <c r="B27" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="18">
         <f>C22/C26/C21</f>
         <v>256.51612903225805</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="18">
         <f t="shared" ref="D27:N27" si="2">D22/D26/D21</f>
         <v>223.14285714285714</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="18">
         <f t="shared" si="2"/>
         <v>171.32258064516128</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="18">
         <f t="shared" si="2"/>
         <v>144.83333333333334</v>
       </c>
-      <c r="G27" s="21">
+      <c r="G27" s="18">
         <f t="shared" si="2"/>
         <v>124.58064516129033</v>
       </c>
-      <c r="H27" s="21">
+      <c r="H27" s="18">
         <f t="shared" si="2"/>
         <v>142</v>
       </c>
-      <c r="I27" s="21">
+      <c r="I27" s="18">
         <f t="shared" si="2"/>
         <v>146.58064516129033</v>
       </c>
-      <c r="J27" s="21">
+      <c r="J27" s="18">
         <f t="shared" si="2"/>
         <v>146.58064516129033</v>
       </c>
-      <c r="K27" s="21">
+      <c r="K27" s="18">
         <f t="shared" si="2"/>
         <v>120.7</v>
       </c>
-      <c r="L27" s="21">
+      <c r="L27" s="18">
         <f t="shared" si="2"/>
         <v>146.58064516129033</v>
       </c>
-      <c r="M27" s="21">
+      <c r="M27" s="18">
         <f t="shared" si="2"/>
         <v>170.4</v>
       </c>
-      <c r="N27" s="21">
+      <c r="N27" s="18">
         <f t="shared" si="2"/>
         <v>251.93548387096777</v>
       </c>
-      <c r="O27" s="22"/>
+      <c r="O27" s="19"/>
     </row>
     <row r="28" spans="2:15">
-      <c r="B28" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
+      <c r="B28" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
     </row>
     <row r="29" spans="2:15">
-      <c r="B29" s="17" t="s">
-        <v>69</v>
+      <c r="B29" s="14" t="s">
+        <v>62</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -12181,13 +12161,13 @@
       <c r="N29">
         <v>10</v>
       </c>
-      <c r="O29" s="13">
+      <c r="O29" s="10">
         <v>10</v>
       </c>
     </row>
     <row r="30" spans="2:15">
-      <c r="B30" s="18" t="s">
-        <v>70</v>
+      <c r="B30" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="C30" s="2">
         <v>144840</v>
@@ -12225,13 +12205,13 @@
       <c r="N30" s="2">
         <v>159040</v>
       </c>
-      <c r="O30" s="19">
+      <c r="O30" s="16">
         <v>1996510</v>
       </c>
     </row>
     <row r="31" spans="2:15">
-      <c r="B31" s="18" t="s">
-        <v>71</v>
+      <c r="B31" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="C31" s="2">
         <v>102000</v>
@@ -12269,13 +12249,13 @@
       <c r="N31" s="2">
         <v>112000</v>
       </c>
-      <c r="O31" s="19">
+      <c r="O31" s="16">
         <v>1406000</v>
       </c>
     </row>
     <row r="32" spans="2:15">
-      <c r="B32" s="18" t="s">
-        <v>72</v>
+      <c r="B32" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="C32" s="2">
         <v>30600</v>
@@ -12313,13 +12293,13 @@
       <c r="N32" s="2">
         <v>33600</v>
       </c>
-      <c r="O32" s="19">
+      <c r="O32" s="16">
         <v>421800</v>
       </c>
     </row>
     <row r="33" spans="2:15">
-      <c r="B33" s="18" t="s">
-        <v>73</v>
+      <c r="B33" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="C33" s="2">
         <v>12240</v>
@@ -12357,127 +12337,127 @@
       <c r="N33" s="2">
         <v>13440</v>
       </c>
-      <c r="O33" s="19">
+      <c r="O33" s="16">
         <v>168710</v>
       </c>
     </row>
-    <row r="34" spans="2:15" s="23" customFormat="1">
-      <c r="B34" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="21">
+    <row r="34" spans="2:15" s="20" customFormat="1">
+      <c r="B34" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="18">
         <v>31</v>
       </c>
-      <c r="D34" s="21">
+      <c r="D34" s="18">
         <v>28</v>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="18">
         <v>31</v>
       </c>
-      <c r="F34" s="21">
+      <c r="F34" s="18">
         <v>30</v>
       </c>
-      <c r="G34" s="21">
+      <c r="G34" s="18">
         <v>31</v>
       </c>
-      <c r="H34" s="21">
+      <c r="H34" s="18">
         <v>30</v>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="18">
         <v>31</v>
       </c>
-      <c r="J34" s="21">
+      <c r="J34" s="18">
         <v>31</v>
       </c>
-      <c r="K34" s="21">
+      <c r="K34" s="18">
         <v>30</v>
       </c>
-      <c r="L34" s="21">
+      <c r="L34" s="18">
         <v>31</v>
       </c>
-      <c r="M34" s="21">
+      <c r="M34" s="18">
         <v>30</v>
       </c>
-      <c r="N34" s="21">
+      <c r="N34" s="18">
         <v>31</v>
       </c>
-      <c r="O34" s="22"/>
+      <c r="O34" s="19"/>
     </row>
-    <row r="35" spans="2:15" s="23" customFormat="1">
-      <c r="B35" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" s="21">
+    <row r="35" spans="2:15" s="20" customFormat="1">
+      <c r="B35" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="18">
         <f>C30/C34/C29</f>
         <v>467.22580645161287</v>
       </c>
-      <c r="D35" s="21">
+      <c r="D35" s="18">
         <f t="shared" ref="D35:N35" si="3">D30/D34/D29</f>
         <v>517.28571428571433</v>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="18">
         <f t="shared" si="3"/>
         <v>476.38709677419354</v>
       </c>
-      <c r="F35" s="21">
+      <c r="F35" s="18">
         <f t="shared" si="3"/>
         <v>516.86666666666667</v>
       </c>
-      <c r="G35" s="21">
+      <c r="G35" s="18">
         <f t="shared" si="3"/>
         <v>547.83870967741927</v>
       </c>
-      <c r="H35" s="21">
+      <c r="H35" s="18">
         <f t="shared" si="3"/>
         <v>568</v>
       </c>
-      <c r="I35" s="21">
+      <c r="I35" s="18">
         <f t="shared" si="3"/>
         <v>687.09677419354841</v>
       </c>
-      <c r="J35" s="21">
+      <c r="J35" s="18">
         <f t="shared" si="3"/>
         <v>769.54838709677415</v>
       </c>
-      <c r="K35" s="21">
+      <c r="K35" s="18">
         <f t="shared" si="3"/>
         <v>516.86666666666667</v>
       </c>
-      <c r="L35" s="21">
+      <c r="L35" s="18">
         <f t="shared" si="3"/>
         <v>549.67741935483878</v>
       </c>
-      <c r="M35" s="21">
+      <c r="M35" s="18">
         <f t="shared" si="3"/>
         <v>426</v>
       </c>
-      <c r="N35" s="21">
+      <c r="N35" s="18">
         <f t="shared" si="3"/>
         <v>513.0322580645161</v>
       </c>
-      <c r="O35" s="22"/>
+      <c r="O35" s="19"/>
     </row>
     <row r="36" spans="2:15">
-      <c r="B36" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
+      <c r="B36" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
     </row>
     <row r="37" spans="2:15">
-      <c r="B37" s="17" t="s">
-        <v>69</v>
+      <c r="B37" s="14" t="s">
+        <v>62</v>
       </c>
       <c r="C37">
         <v>6</v>
@@ -12515,13 +12495,13 @@
       <c r="N37">
         <v>6</v>
       </c>
-      <c r="O37" s="13">
+      <c r="O37" s="10">
         <v>6</v>
       </c>
     </row>
     <row r="38" spans="2:15">
-      <c r="B38" s="18" t="s">
-        <v>70</v>
+      <c r="B38" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="C38" s="2">
         <v>109056</v>
@@ -12559,13 +12539,13 @@
       <c r="N38" s="2">
         <v>145692</v>
       </c>
-      <c r="O38" s="19">
+      <c r="O38" s="16">
         <v>1563420</v>
       </c>
     </row>
     <row r="39" spans="2:15">
-      <c r="B39" s="18" t="s">
-        <v>71</v>
+      <c r="B39" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="C39" s="2">
         <v>76800</v>
@@ -12603,13 +12583,13 @@
       <c r="N39" s="2">
         <v>102600</v>
       </c>
-      <c r="O39" s="19">
+      <c r="O39" s="16">
         <v>1101000</v>
       </c>
     </row>
     <row r="40" spans="2:15">
-      <c r="B40" s="18" t="s">
-        <v>72</v>
+      <c r="B40" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="C40" s="2">
         <v>23040</v>
@@ -12647,13 +12627,13 @@
       <c r="N40" s="2">
         <v>30780</v>
       </c>
-      <c r="O40" s="19">
+      <c r="O40" s="16">
         <v>330300</v>
       </c>
     </row>
     <row r="41" spans="2:15">
-      <c r="B41" s="18" t="s">
-        <v>73</v>
+      <c r="B41" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="C41" s="2">
         <v>9216</v>
@@ -12691,127 +12671,127 @@
       <c r="N41" s="2">
         <v>12312</v>
       </c>
-      <c r="O41" s="19">
+      <c r="O41" s="16">
         <v>132120</v>
       </c>
     </row>
-    <row r="42" spans="2:15" s="23" customFormat="1">
-      <c r="B42" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" s="21">
+    <row r="42" spans="2:15" s="20" customFormat="1">
+      <c r="B42" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" s="18">
         <v>31</v>
       </c>
-      <c r="D42" s="21">
+      <c r="D42" s="18">
         <v>28</v>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="18">
         <v>31</v>
       </c>
-      <c r="F42" s="21">
+      <c r="F42" s="18">
         <v>30</v>
       </c>
-      <c r="G42" s="21">
+      <c r="G42" s="18">
         <v>31</v>
       </c>
-      <c r="H42" s="21">
+      <c r="H42" s="18">
         <v>30</v>
       </c>
-      <c r="I42" s="21">
+      <c r="I42" s="18">
         <v>31</v>
       </c>
-      <c r="J42" s="21">
+      <c r="J42" s="18">
         <v>31</v>
       </c>
-      <c r="K42" s="21">
+      <c r="K42" s="18">
         <v>30</v>
       </c>
-      <c r="L42" s="21">
+      <c r="L42" s="18">
         <v>31</v>
       </c>
-      <c r="M42" s="21">
+      <c r="M42" s="18">
         <v>30</v>
       </c>
-      <c r="N42" s="21">
+      <c r="N42" s="18">
         <v>31</v>
       </c>
-      <c r="O42" s="22"/>
+      <c r="O42" s="19"/>
     </row>
-    <row r="43" spans="2:15" s="23" customFormat="1">
-      <c r="B43" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C43" s="21">
+    <row r="43" spans="2:15" s="20" customFormat="1">
+      <c r="B43" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="18">
         <f>C38/C42/C37</f>
         <v>586.32258064516134</v>
       </c>
-      <c r="D43" s="21">
+      <c r="D43" s="18">
         <f t="shared" ref="D43:N43" si="4">D38/D42/D37</f>
         <v>568</v>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="18">
         <f t="shared" si="4"/>
         <v>513.0322580645161</v>
       </c>
-      <c r="F43" s="21">
+      <c r="F43" s="18">
         <f t="shared" si="4"/>
         <v>497</v>
       </c>
-      <c r="G43" s="21">
+      <c r="G43" s="18">
         <f t="shared" si="4"/>
         <v>801.61290322580646</v>
       </c>
-      <c r="H43" s="21">
+      <c r="H43" s="18">
         <f t="shared" si="4"/>
         <v>681.6</v>
       </c>
-      <c r="I43" s="21">
+      <c r="I43" s="18">
         <f t="shared" si="4"/>
         <v>916.12903225806451</v>
       </c>
-      <c r="J43" s="21">
+      <c r="J43" s="18">
         <f t="shared" si="4"/>
         <v>916.12903225806451</v>
       </c>
-      <c r="K43" s="21">
+      <c r="K43" s="18">
         <f t="shared" si="4"/>
         <v>795.19999999999993</v>
       </c>
-      <c r="L43" s="21">
+      <c r="L43" s="18">
         <f t="shared" si="4"/>
         <v>806.19354838709671</v>
       </c>
-      <c r="M43" s="21">
+      <c r="M43" s="18">
         <f t="shared" si="4"/>
         <v>681.6</v>
       </c>
-      <c r="N43" s="21">
+      <c r="N43" s="18">
         <f t="shared" si="4"/>
         <v>783.29032258064524</v>
       </c>
-      <c r="O43" s="22"/>
+      <c r="O43" s="19"/>
     </row>
     <row r="44" spans="2:15">
-      <c r="B44" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="16"/>
-      <c r="O44" s="16"/>
+      <c r="B44" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13"/>
     </row>
     <row r="45" spans="2:15">
-      <c r="B45" s="17" t="s">
-        <v>69</v>
+      <c r="B45" s="14" t="s">
+        <v>62</v>
       </c>
       <c r="C45">
         <v>76</v>
@@ -12849,13 +12829,13 @@
       <c r="N45">
         <v>76</v>
       </c>
-      <c r="O45" s="13">
+      <c r="O45" s="10">
         <v>76</v>
       </c>
     </row>
     <row r="46" spans="2:15">
-      <c r="B46" s="18" t="s">
-        <v>70</v>
+      <c r="B46" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="C46" s="2">
         <v>307572</v>
@@ -12893,13 +12873,13 @@
       <c r="N46" s="2">
         <v>403636</v>
       </c>
-      <c r="O46" s="19">
+      <c r="O46" s="16">
         <v>4024352</v>
       </c>
     </row>
     <row r="47" spans="2:15">
-      <c r="B47" s="18" t="s">
-        <v>71</v>
+      <c r="B47" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="C47" s="2">
         <v>216600</v>
@@ -12937,13 +12917,13 @@
       <c r="N47" s="2">
         <v>284240</v>
       </c>
-      <c r="O47" s="19">
+      <c r="O47" s="16">
         <v>2834040</v>
       </c>
     </row>
     <row r="48" spans="2:15">
-      <c r="B48" s="18" t="s">
-        <v>72</v>
+      <c r="B48" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="C48" s="2">
         <v>64980</v>
@@ -12981,13 +12961,13 @@
       <c r="N48" s="2">
         <v>85272</v>
       </c>
-      <c r="O48" s="19">
+      <c r="O48" s="16">
         <v>850212</v>
       </c>
     </row>
     <row r="49" spans="2:15">
-      <c r="B49" s="18" t="s">
-        <v>73</v>
+      <c r="B49" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="C49" s="2">
         <v>25992</v>
@@ -13025,411 +13005,411 @@
       <c r="N49" s="2">
         <v>34124</v>
       </c>
-      <c r="O49" s="19">
+      <c r="O49" s="16">
         <v>340100</v>
       </c>
     </row>
-    <row r="50" spans="2:15" s="23" customFormat="1">
-      <c r="B50" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C50" s="21">
+    <row r="50" spans="2:15" s="20" customFormat="1">
+      <c r="B50" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="18">
         <v>31</v>
       </c>
-      <c r="D50" s="21">
+      <c r="D50" s="18">
         <v>28</v>
       </c>
-      <c r="E50" s="21">
+      <c r="E50" s="18">
         <v>31</v>
       </c>
-      <c r="F50" s="21">
+      <c r="F50" s="18">
         <v>30</v>
       </c>
-      <c r="G50" s="21">
+      <c r="G50" s="18">
         <v>31</v>
       </c>
-      <c r="H50" s="21">
+      <c r="H50" s="18">
         <v>30</v>
       </c>
-      <c r="I50" s="21">
+      <c r="I50" s="18">
         <v>31</v>
       </c>
-      <c r="J50" s="21">
+      <c r="J50" s="18">
         <v>31</v>
       </c>
-      <c r="K50" s="21">
+      <c r="K50" s="18">
         <v>30</v>
       </c>
-      <c r="L50" s="21">
+      <c r="L50" s="18">
         <v>31</v>
       </c>
-      <c r="M50" s="21">
+      <c r="M50" s="18">
         <v>30</v>
       </c>
-      <c r="N50" s="21">
+      <c r="N50" s="18">
         <v>31</v>
       </c>
-      <c r="O50" s="22"/>
+      <c r="O50" s="19"/>
     </row>
-    <row r="51" spans="2:15" s="23" customFormat="1">
-      <c r="B51" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C51" s="21">
+    <row r="51" spans="2:15" s="20" customFormat="1">
+      <c r="B51" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" s="18">
         <f>C46/C50/C45</f>
         <v>130.54838709677421</v>
       </c>
-      <c r="D51" s="21">
+      <c r="D51" s="18">
         <f t="shared" ref="D51:N51" si="5">D46/D50/D45</f>
         <v>167.35714285714286</v>
       </c>
-      <c r="E51" s="21">
+      <c r="E51" s="18">
         <f t="shared" si="5"/>
         <v>136.96774193548387</v>
       </c>
-      <c r="F51" s="21">
+      <c r="F51" s="18">
         <f t="shared" si="5"/>
         <v>147.66666666666666</v>
       </c>
-      <c r="G51" s="21">
+      <c r="G51" s="18">
         <f t="shared" si="5"/>
         <v>136.96774193548387</v>
       </c>
-      <c r="H51" s="21">
+      <c r="H51" s="18">
         <f t="shared" si="5"/>
         <v>127.8</v>
       </c>
-      <c r="I51" s="21">
+      <c r="I51" s="18">
         <f t="shared" si="5"/>
         <v>151.16129032258064</v>
       </c>
-      <c r="J51" s="21">
+      <c r="J51" s="18">
         <f t="shared" si="5"/>
         <v>158.03225806451613</v>
       </c>
-      <c r="K51" s="21">
+      <c r="K51" s="18">
         <f t="shared" si="5"/>
         <v>92.3</v>
       </c>
-      <c r="L51" s="21">
+      <c r="L51" s="18">
         <f t="shared" si="5"/>
         <v>192.38709677419357</v>
       </c>
-      <c r="M51" s="21">
+      <c r="M51" s="18">
         <f t="shared" si="5"/>
         <v>127.8</v>
       </c>
-      <c r="N51" s="21">
+      <c r="N51" s="18">
         <f t="shared" si="5"/>
         <v>171.32258064516128</v>
       </c>
-      <c r="O51" s="22"/>
+      <c r="O51" s="19"/>
     </row>
     <row r="52" spans="2:15">
-      <c r="B52" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C52" s="25">
+      <c r="B52" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" s="22">
         <v>200</v>
       </c>
-      <c r="D52" s="25">
+      <c r="D52" s="22">
         <v>200</v>
       </c>
-      <c r="E52" s="25">
+      <c r="E52" s="22">
         <v>200</v>
       </c>
-      <c r="F52" s="25">
+      <c r="F52" s="22">
         <v>200</v>
       </c>
-      <c r="G52" s="25">
+      <c r="G52" s="22">
         <v>200</v>
       </c>
-      <c r="H52" s="25">
+      <c r="H52" s="22">
         <v>200</v>
       </c>
-      <c r="I52" s="25">
+      <c r="I52" s="22">
         <v>200</v>
       </c>
-      <c r="J52" s="25">
+      <c r="J52" s="22">
         <v>200</v>
       </c>
-      <c r="K52" s="25">
+      <c r="K52" s="22">
         <v>200</v>
       </c>
-      <c r="L52" s="25">
+      <c r="L52" s="22">
         <v>200</v>
       </c>
-      <c r="M52" s="25">
+      <c r="M52" s="22">
         <v>200</v>
       </c>
-      <c r="N52" s="25">
+      <c r="N52" s="22">
         <v>200</v>
       </c>
-      <c r="O52" s="25">
+      <c r="O52" s="22">
         <v>200</v>
       </c>
     </row>
     <row r="53" spans="2:15">
-      <c r="B53" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C53" s="19">
+      <c r="B53" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="16">
         <v>1598920</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="16">
         <v>1551208</v>
       </c>
-      <c r="E53" s="19">
+      <c r="E53" s="16">
         <v>1538736</v>
       </c>
-      <c r="F53" s="19">
+      <c r="F53" s="16">
         <v>1483232</v>
       </c>
-      <c r="G53" s="19">
+      <c r="G53" s="16">
         <v>1566994</v>
       </c>
-      <c r="H53" s="19">
+      <c r="H53" s="16">
         <v>1278000</v>
       </c>
-      <c r="I53" s="19">
+      <c r="I53" s="16">
         <v>1823848</v>
       </c>
-      <c r="J53" s="19">
+      <c r="J53" s="16">
         <v>1865596</v>
       </c>
-      <c r="K53" s="19">
+      <c r="K53" s="16">
         <v>1231988</v>
       </c>
-      <c r="L53" s="19">
+      <c r="L53" s="16">
         <v>1814476</v>
       </c>
-      <c r="M53" s="19">
+      <c r="M53" s="16">
         <v>1431360</v>
       </c>
-      <c r="N53" s="19">
+      <c r="N53" s="16">
         <v>1793292</v>
       </c>
-      <c r="O53" s="19">
+      <c r="O53" s="16">
         <v>18977650</v>
       </c>
     </row>
     <row r="54" spans="2:15">
-      <c r="B54" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C54" s="19">
+      <c r="B54" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" s="16">
         <v>1126000</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="16">
         <v>1092400</v>
       </c>
-      <c r="E54" s="19">
+      <c r="E54" s="16">
         <v>1083600</v>
       </c>
-      <c r="F54" s="19">
+      <c r="F54" s="16">
         <v>1044560</v>
       </c>
-      <c r="G54" s="19">
+      <c r="G54" s="16">
         <v>1103520</v>
       </c>
-      <c r="H54" s="19">
+      <c r="H54" s="16">
         <v>900000</v>
       </c>
-      <c r="I54" s="19">
+      <c r="I54" s="16">
         <v>1284400</v>
       </c>
-      <c r="J54" s="19">
+      <c r="J54" s="16">
         <v>1313800</v>
       </c>
-      <c r="K54" s="19">
+      <c r="K54" s="16">
         <v>867600</v>
       </c>
-      <c r="L54" s="19">
+      <c r="L54" s="16">
         <v>1277800</v>
       </c>
-      <c r="M54" s="19">
+      <c r="M54" s="16">
         <v>1008000</v>
       </c>
-      <c r="N54" s="19">
+      <c r="N54" s="16">
         <v>1262880</v>
       </c>
-      <c r="O54" s="19">
+      <c r="O54" s="16">
         <v>13364560</v>
       </c>
     </row>
     <row r="55" spans="2:15">
-      <c r="B55" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C55" s="19">
+      <c r="B55" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C55" s="16">
         <v>337800</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="16">
         <v>327720</v>
       </c>
-      <c r="E55" s="19">
+      <c r="E55" s="16">
         <v>325080</v>
       </c>
-      <c r="F55" s="19">
+      <c r="F55" s="16">
         <v>313368</v>
       </c>
-      <c r="G55" s="19">
+      <c r="G55" s="16">
         <v>331056</v>
       </c>
-      <c r="H55" s="19">
+      <c r="H55" s="16">
         <v>270000</v>
       </c>
-      <c r="I55" s="19">
+      <c r="I55" s="16">
         <v>385320</v>
       </c>
-      <c r="J55" s="19">
+      <c r="J55" s="16">
         <v>394140</v>
       </c>
-      <c r="K55" s="19">
+      <c r="K55" s="16">
         <v>260280</v>
       </c>
-      <c r="L55" s="19">
+      <c r="L55" s="16">
         <v>383340</v>
       </c>
-      <c r="M55" s="19">
+      <c r="M55" s="16">
         <v>302400</v>
       </c>
-      <c r="N55" s="19">
+      <c r="N55" s="16">
         <v>378864</v>
       </c>
-      <c r="O55" s="19">
+      <c r="O55" s="16">
         <v>4009368</v>
       </c>
     </row>
     <row r="56" spans="2:15">
-      <c r="B56" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="C56" s="19">
+      <c r="B56" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C56" s="16">
         <v>135120</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="16">
         <v>131088</v>
       </c>
-      <c r="E56" s="19">
+      <c r="E56" s="16">
         <v>130056</v>
       </c>
-      <c r="F56" s="19">
+      <c r="F56" s="16">
         <v>125304</v>
       </c>
-      <c r="G56" s="19">
+      <c r="G56" s="16">
         <v>132418</v>
       </c>
-      <c r="H56" s="19">
+      <c r="H56" s="16">
         <v>108000</v>
       </c>
-      <c r="I56" s="19">
+      <c r="I56" s="16">
         <v>154128</v>
       </c>
-      <c r="J56" s="19">
+      <c r="J56" s="16">
         <v>157656</v>
       </c>
-      <c r="K56" s="19">
+      <c r="K56" s="16">
         <v>104108</v>
       </c>
-      <c r="L56" s="19">
+      <c r="L56" s="16">
         <v>153336</v>
       </c>
-      <c r="M56" s="19">
+      <c r="M56" s="16">
         <v>120960</v>
       </c>
-      <c r="N56" s="19">
+      <c r="N56" s="16">
         <v>151548</v>
       </c>
-      <c r="O56" s="19">
+      <c r="O56" s="16">
         <v>1603722</v>
       </c>
     </row>
     <row r="57" spans="2:15">
-      <c r="B57" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C57" s="27">
+      <c r="B57" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57" s="24">
         <v>31</v>
       </c>
-      <c r="D57" s="27">
+      <c r="D57" s="24">
         <v>28</v>
       </c>
-      <c r="E57" s="27">
+      <c r="E57" s="24">
         <v>31</v>
       </c>
-      <c r="F57" s="27">
+      <c r="F57" s="24">
         <v>30</v>
       </c>
-      <c r="G57" s="27">
+      <c r="G57" s="24">
         <v>31</v>
       </c>
-      <c r="H57" s="27">
+      <c r="H57" s="24">
         <v>30</v>
       </c>
-      <c r="I57" s="27">
+      <c r="I57" s="24">
         <v>31</v>
       </c>
-      <c r="J57" s="27">
+      <c r="J57" s="24">
         <v>31</v>
       </c>
-      <c r="K57" s="27">
+      <c r="K57" s="24">
         <v>30</v>
       </c>
-      <c r="L57" s="27">
+      <c r="L57" s="24">
         <v>31</v>
       </c>
-      <c r="M57" s="27">
+      <c r="M57" s="24">
         <v>30</v>
       </c>
-      <c r="N57" s="27">
+      <c r="N57" s="24">
         <v>31</v>
       </c>
-      <c r="O57" s="27">
+      <c r="O57" s="24">
         <v>30.416666666666668</v>
       </c>
     </row>
     <row r="58" spans="2:15" ht="15" thickBot="1">
-      <c r="B58" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C58" s="29">
+      <c r="B58" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C58" s="26">
         <v>386.24</v>
       </c>
-      <c r="D58" s="29">
+      <c r="D58" s="26">
         <v>386.24</v>
       </c>
-      <c r="E58" s="29">
+      <c r="E58" s="26">
         <v>333.42130434782661</v>
       </c>
-      <c r="F58" s="29">
+      <c r="F58" s="26">
         <v>333.40626984127101</v>
       </c>
-      <c r="G58" s="29">
+      <c r="G58" s="26">
         <v>333.41336956521803</v>
       </c>
-      <c r="H58" s="29">
+      <c r="H58" s="26">
         <v>386.24</v>
       </c>
-      <c r="I58" s="29">
+      <c r="I58" s="26">
         <v>386.24</v>
       </c>
-      <c r="J58" s="29">
+      <c r="J58" s="26">
         <v>386.24</v>
       </c>
-      <c r="K58" s="29">
+      <c r="K58" s="26">
         <v>333.4150476190477</v>
       </c>
-      <c r="L58" s="29">
+      <c r="L58" s="26">
         <v>386.24</v>
       </c>
-      <c r="M58" s="29">
+      <c r="M58" s="26">
         <v>386.24</v>
       </c>
-      <c r="N58" s="29">
+      <c r="N58" s="26">
         <v>430.26034449760687</v>
       </c>
-      <c r="O58" s="29">
+      <c r="O58" s="26">
         <v>372.29969465591421</v>
       </c>
     </row>
@@ -13458,12 +13438,12 @@
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="2:10" ht="29" thickBot="1">
-      <c r="B3" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="11"/>
+      <c r="B3" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="29"/>
     </row>
     <row r="5" spans="2:10" ht="18.5">
       <c r="B5" s="8" t="s">
@@ -13483,15 +13463,15 @@
     <row r="6" spans="2:10" ht="15.5">
       <c r="B6" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M2,IF($B$3="King",'Revenue - Data'!M14,IF($B$3="Superior King",'Revenue - Data'!M26,IF($B$3="Executive",'Revenue - Data'!M38,IF($B$3="One Club",'Revenue - Data'!M50,'Revenue - Data'!M62)))))</f>
-        <v>0.95914127423822715</v>
+        <v>0.96875</v>
       </c>
       <c r="C6" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N2,IF($B$3="King",'Revenue - Data'!N14,IF($B$3="Superior King",'Revenue - Data'!N26,IF($B$3="Executive",'Revenue - Data'!N38,IF($B$3="One Club",'Revenue - Data'!N50,'Revenue - Data'!N62)))))</f>
-        <v>0.78562634656817487</v>
+        <v>0.4055121527777778</v>
       </c>
       <c r="D6" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O2,IF($B$3="King",'Revenue - Data'!O14,IF($B$3="Superior King",'Revenue - Data'!O26,IF($B$3="Executive",'Revenue - Data'!O38,IF($B$3="One Club",'Revenue - Data'!O50,'Revenue - Data'!O62)))))</f>
-        <v>0.82094490612496152</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="E6" s="7">
         <v>1</v>
@@ -13503,15 +13483,15 @@
     <row r="7" spans="2:10" ht="15.5">
       <c r="B7" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M3,IF($B$3="King",'Revenue - Data'!M15,IF($B$3="Superior King",'Revenue - Data'!M27,IF($B$3="Executive",'Revenue - Data'!M39,IF($B$3="One Club",'Revenue - Data'!M51,'Revenue - Data'!M63)))))</f>
-        <v>1.0639952153110048</v>
+        <v>1.0119047619047619</v>
       </c>
       <c r="C7" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N3,IF($B$3="King",'Revenue - Data'!N15,IF($B$3="Superior King",'Revenue - Data'!N27,IF($B$3="Executive",'Revenue - Data'!N39,IF($B$3="One Club",'Revenue - Data'!N51,'Revenue - Data'!N63)))))</f>
-        <v>1.1251860712387027</v>
+        <v>0.29181547619047621</v>
       </c>
       <c r="D7" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O3,IF($B$3="King",'Revenue - Data'!O15,IF($B$3="Superior King",'Revenue - Data'!O27,IF($B$3="Executive",'Revenue - Data'!O39,IF($B$3="One Club",'Revenue - Data'!O51,'Revenue - Data'!O63)))))</f>
-        <v>1.1200824029771399</v>
+        <v>0.52802579365079361</v>
       </c>
       <c r="E7" s="7">
         <v>2</v>
@@ -13523,15 +13503,15 @@
     <row r="8" spans="2:10" ht="15.5">
       <c r="B8" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M4,IF($B$3="King",'Revenue - Data'!M16,IF($B$3="Superior King",'Revenue - Data'!M28,IF($B$3="Executive",'Revenue - Data'!M40,IF($B$3="One Club",'Revenue - Data'!M52,'Revenue - Data'!M64)))))</f>
-        <v>1.0440503432494279</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C8" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N4,IF($B$3="King",'Revenue - Data'!N16,IF($B$3="Superior King",'Revenue - Data'!N28,IF($B$3="Executive",'Revenue - Data'!N40,IF($B$3="One Club",'Revenue - Data'!N52,'Revenue - Data'!N64)))))</f>
-        <v>1.0278413424866515</v>
+        <v>0.21289682539682539</v>
       </c>
       <c r="D8" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O4,IF($B$3="King",'Revenue - Data'!O16,IF($B$3="Superior King",'Revenue - Data'!O28,IF($B$3="Executive",'Revenue - Data'!O40,IF($B$3="One Club",'Revenue - Data'!O52,'Revenue - Data'!O64)))))</f>
-        <v>0.97504031666911006</v>
+        <v>0.54389880952380953</v>
       </c>
       <c r="E8" s="7">
         <v>3</v>
@@ -13543,15 +13523,15 @@
     <row r="9" spans="2:10" ht="15.5">
       <c r="B9" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M5,IF($B$3="King",'Revenue - Data'!M17,IF($B$3="Superior King",'Revenue - Data'!M29,IF($B$3="Executive",'Revenue - Data'!M41,IF($B$3="One Club",'Revenue - Data'!M53,'Revenue - Data'!M65)))))</f>
-        <v>1.037828947368421</v>
+        <v>0.68888888888888888</v>
       </c>
       <c r="C9" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N5,IF($B$3="King",'Revenue - Data'!N17,IF($B$3="Superior King",'Revenue - Data'!N29,IF($B$3="Executive",'Revenue - Data'!N41,IF($B$3="One Club",'Revenue - Data'!N53,'Revenue - Data'!N65)))))</f>
-        <v>1.2092189608636976</v>
+        <v>0.11037037037037037</v>
       </c>
       <c r="D9" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O5,IF($B$3="King",'Revenue - Data'!O17,IF($B$3="Superior King",'Revenue - Data'!O29,IF($B$3="Executive",'Revenue - Data'!O41,IF($B$3="One Club",'Revenue - Data'!O53,'Revenue - Data'!O65)))))</f>
-        <v>1.162362792006755</v>
+        <v>0.31732804232804235</v>
       </c>
       <c r="E9" s="7">
         <v>4</v>
@@ -13563,15 +13543,15 @@
     <row r="10" spans="2:10" ht="15.5">
       <c r="B10" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M6,IF($B$3="King",'Revenue - Data'!M18,IF($B$3="Superior King",'Revenue - Data'!M30,IF($B$3="Executive",'Revenue - Data'!M42,IF($B$3="One Club",'Revenue - Data'!M54,'Revenue - Data'!M66)))))</f>
-        <v>1.0171624713958809</v>
+        <v>0.95333333333333337</v>
       </c>
       <c r="C10" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N6,IF($B$3="King",'Revenue - Data'!N18,IF($B$3="Superior King",'Revenue - Data'!N30,IF($B$3="Executive",'Revenue - Data'!N42,IF($B$3="One Club",'Revenue - Data'!N54,'Revenue - Data'!N66)))))</f>
-        <v>0.92134600715836412</v>
+        <v>0.18450793650793651</v>
       </c>
       <c r="D10" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O6,IF($B$3="King",'Revenue - Data'!O18,IF($B$3="Superior King",'Revenue - Data'!O30,IF($B$3="Executive",'Revenue - Data'!O42,IF($B$3="One Club",'Revenue - Data'!O54,'Revenue - Data'!O66)))))</f>
-        <v>0.88238528075062306</v>
+        <v>0.96047619047619048</v>
       </c>
       <c r="E10" s="7">
         <v>5</v>
@@ -13583,15 +13563,15 @@
     <row r="11" spans="2:10" ht="15.5">
       <c r="B11" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M7,IF($B$3="King",'Revenue - Data'!M19,IF($B$3="Superior King",'Revenue - Data'!M31,IF($B$3="Executive",'Revenue - Data'!M43,IF($B$3="One Club",'Revenue - Data'!M55,'Revenue - Data'!M67)))))</f>
-        <v>0.92690058479532167</v>
+        <v>0.87037037037037035</v>
       </c>
       <c r="C11" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N7,IF($B$3="King",'Revenue - Data'!N19,IF($B$3="Superior King",'Revenue - Data'!N31,IF($B$3="Executive",'Revenue - Data'!N43,IF($B$3="One Club",'Revenue - Data'!N55,'Revenue - Data'!N67)))))</f>
-        <v>0.94291747888239119</v>
+        <v>8.4104938271604937E-2</v>
       </c>
       <c r="D11" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O7,IF($B$3="King",'Revenue - Data'!O19,IF($B$3="Superior King",'Revenue - Data'!O31,IF($B$3="Executive",'Revenue - Data'!O43,IF($B$3="One Club",'Revenue - Data'!O55,'Revenue - Data'!O67)))))</f>
-        <v>0.8464100064977258</v>
+        <v>0.59924768518518523</v>
       </c>
       <c r="E11" s="7">
         <v>6</v>
@@ -13603,15 +13583,15 @@
     <row r="12" spans="2:10" ht="15.5">
       <c r="B12" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M8,IF($B$3="King",'Revenue - Data'!M20,IF($B$3="Superior King",'Revenue - Data'!M32,IF($B$3="Executive",'Revenue - Data'!M44,IF($B$3="One Club",'Revenue - Data'!M56,'Revenue - Data'!M68)))))</f>
-        <v>0.98624401913875603</v>
+        <v>0.94</v>
       </c>
       <c r="C12" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N8,IF($B$3="King",'Revenue - Data'!N20,IF($B$3="Superior King",'Revenue - Data'!N32,IF($B$3="Executive",'Revenue - Data'!N44,IF($B$3="One Club",'Revenue - Data'!N56,'Revenue - Data'!N68)))))</f>
-        <v>0.78847687400318978</v>
+        <v>0.88180555555555551</v>
       </c>
       <c r="D12" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O8,IF($B$3="King",'Revenue - Data'!O20,IF($B$3="Superior King",'Revenue - Data'!O32,IF($B$3="Executive",'Revenue - Data'!O44,IF($B$3="One Club",'Revenue - Data'!O56,'Revenue - Data'!O68)))))</f>
-        <v>0.81346358320042533</v>
+        <v>0.86236111111111113</v>
       </c>
       <c r="E12" s="7">
         <v>7</v>
@@ -13623,15 +13603,15 @@
     <row r="13" spans="2:10" ht="15.5">
       <c r="B13" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M9,IF($B$3="King",'Revenue - Data'!M21,IF($B$3="Superior King",'Revenue - Data'!M33,IF($B$3="Executive",'Revenue - Data'!M45,IF($B$3="One Club",'Revenue - Data'!M57,'Revenue - Data'!M69)))))</f>
-        <v>0.99542334096109841</v>
+        <v>1.1933333333333334</v>
       </c>
       <c r="C13" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N9,IF($B$3="King",'Revenue - Data'!N21,IF($B$3="Superior King",'Revenue - Data'!N33,IF($B$3="Executive",'Revenue - Data'!N45,IF($B$3="One Club",'Revenue - Data'!N57,'Revenue - Data'!N69)))))</f>
-        <v>0.75115687770150008</v>
+        <v>1.4589722222222221</v>
       </c>
       <c r="D13" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O9,IF($B$3="King",'Revenue - Data'!O21,IF($B$3="Superior King",'Revenue - Data'!O33,IF($B$3="Executive",'Revenue - Data'!O45,IF($B$3="One Club",'Revenue - Data'!O57,'Revenue - Data'!O69)))))</f>
-        <v>0.77571192473938466</v>
+        <v>1.153125</v>
       </c>
       <c r="E13" s="7">
         <v>8</v>
@@ -13643,15 +13623,15 @@
     <row r="14" spans="2:10" ht="15.5">
       <c r="B14" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M10,IF($B$3="King",'Revenue - Data'!M22,IF($B$3="Superior King",'Revenue - Data'!M34,IF($B$3="Executive",'Revenue - Data'!M46,IF($B$3="One Club",'Revenue - Data'!M58,'Revenue - Data'!M70)))))</f>
-        <v>1.0561403508771929</v>
+        <v>0.92361111111111116</v>
       </c>
       <c r="C14" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N10,IF($B$3="King",'Revenue - Data'!N22,IF($B$3="Superior King",'Revenue - Data'!N34,IF($B$3="Executive",'Revenue - Data'!N46,IF($B$3="One Club",'Revenue - Data'!N58,'Revenue - Data'!N70)))))</f>
-        <v>0.77903733693207378</v>
+        <v>1.0264219576719578</v>
       </c>
       <c r="D14" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O10,IF($B$3="King",'Revenue - Data'!O22,IF($B$3="Superior King",'Revenue - Data'!O34,IF($B$3="Executive",'Revenue - Data'!O46,IF($B$3="One Club",'Revenue - Data'!O58,'Revenue - Data'!O70)))))</f>
-        <v>0.73487404408457035</v>
+        <v>0.85945767195767198</v>
       </c>
       <c r="E14" s="7">
         <v>9</v>
@@ -13663,15 +13643,15 @@
     <row r="15" spans="2:10" ht="15.5">
       <c r="B15" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M11,IF($B$3="King",'Revenue - Data'!M23,IF($B$3="Superior King",'Revenue - Data'!M35,IF($B$3="Executive",'Revenue - Data'!M47,IF($B$3="One Club",'Revenue - Data'!M59,'Revenue - Data'!M71)))))</f>
-        <v>1.0427631578947369</v>
+        <v>0.93181818181818177</v>
       </c>
       <c r="C15" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N11,IF($B$3="King",'Revenue - Data'!N23,IF($B$3="Superior King",'Revenue - Data'!N35,IF($B$3="Executive",'Revenue - Data'!N47,IF($B$3="One Club",'Revenue - Data'!N59,'Revenue - Data'!N71)))))</f>
-        <v>1.3246762740183793</v>
+        <v>0.67572601010101008</v>
       </c>
       <c r="D15" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O11,IF($B$3="King",'Revenue - Data'!O23,IF($B$3="Superior King",'Revenue - Data'!O35,IF($B$3="Executive",'Revenue - Data'!O47,IF($B$3="One Club",'Revenue - Data'!O59,'Revenue - Data'!O71)))))</f>
-        <v>1.3357351712614871</v>
+        <v>0.77541035353535348</v>
       </c>
       <c r="E15" s="7">
         <v>10</v>
@@ -13683,15 +13663,15 @@
     <row r="16" spans="2:10" ht="15.5">
       <c r="B16" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M12,IF($B$3="King",'Revenue - Data'!M24,IF($B$3="Superior King",'Revenue - Data'!M36,IF($B$3="Executive",'Revenue - Data'!M48,IF($B$3="One Club",'Revenue - Data'!M60,'Revenue - Data'!M72)))))</f>
-        <v>1.0007309941520468</v>
+        <v>0.9907407407407407</v>
       </c>
       <c r="C16" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N12,IF($B$3="King",'Revenue - Data'!N24,IF($B$3="Superior King",'Revenue - Data'!N36,IF($B$3="Executive",'Revenue - Data'!N48,IF($B$3="One Club",'Revenue - Data'!N60,'Revenue - Data'!N72)))))</f>
-        <v>0.85878817413905129</v>
+        <v>1.0784336419753087</v>
       </c>
       <c r="D16" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O12,IF($B$3="King",'Revenue - Data'!O24,IF($B$3="Superior King",'Revenue - Data'!O36,IF($B$3="Executive",'Revenue - Data'!O48,IF($B$3="One Club",'Revenue - Data'!O60,'Revenue - Data'!O72)))))</f>
-        <v>0.88511208576998046</v>
+        <v>0.99807098765432101</v>
       </c>
       <c r="E16" s="7">
         <v>11</v>
@@ -13703,15 +13683,15 @@
     <row r="17" spans="2:10" ht="15.5">
       <c r="B17" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M13,IF($B$3="King",'Revenue - Data'!M25,IF($B$3="Superior King",'Revenue - Data'!M37,IF($B$3="Executive",'Revenue - Data'!M49,IF($B$3="One Club",'Revenue - Data'!M61,'Revenue - Data'!M73)))))</f>
-        <v>0.97488038277511957</v>
+        <v>0.86842105263157898</v>
       </c>
       <c r="C17" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N13,IF($B$3="King",'Revenue - Data'!N25,IF($B$3="Superior King",'Revenue - Data'!N37,IF($B$3="Executive",'Revenue - Data'!N49,IF($B$3="One Club",'Revenue - Data'!N61,'Revenue - Data'!N73)))))</f>
-        <v>0.96106576601932636</v>
+        <v>0.68479532163742685</v>
       </c>
       <c r="D17" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O13,IF($B$3="King",'Revenue - Data'!O25,IF($B$3="Superior King",'Revenue - Data'!O37,IF($B$3="Executive",'Revenue - Data'!O49,IF($B$3="One Club",'Revenue - Data'!O61,'Revenue - Data'!O73)))))</f>
-        <v>1.0148868831321065</v>
+        <v>0.70175438596491224</v>
       </c>
       <c r="E17" s="7">
         <v>12</v>
@@ -13722,26 +13702,26 @@
     </row>
     <row r="20" spans="2:10">
       <c r="B20" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="2:10">
       <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" t="s">
         <v>22</v>
-      </c>
-      <c r="D21" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="22" spans="2:10">
       <c r="B22" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -13773,15 +13753,15 @@
   <sheetData>
     <row r="4" spans="3:4">
       <c r="C4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="3:4">
       <c r="C5" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -13789,7 +13769,7 @@
     </row>
     <row r="6" spans="3:4">
       <c r="C6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>90</v>
@@ -13797,7 +13777,7 @@
     </row>
     <row r="7" spans="3:4">
       <c r="C7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>80</v>
@@ -13805,7 +13785,7 @@
     </row>
     <row r="8" spans="3:4">
       <c r="C8" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D8">
         <v>70</v>
@@ -13813,7 +13793,7 @@
     </row>
     <row r="9" spans="3:4">
       <c r="C9" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -13821,7 +13801,7 @@
     </row>
     <row r="10" spans="3:4">
       <c r="C10" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D10">
         <v>50</v>
@@ -17617,454 +17597,28 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6482E56F-AAD0-45DD-AED2-1DDF0978065A}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="3" max="3" width="11.7265625" customWidth="1"/>
     <col min="5" max="5" width="12.6328125" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17">
-        <v>4</v>
-      </c>
-      <c r="C17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18">
-        <v>5</v>
-      </c>
-      <c r="C18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19">
-        <v>6</v>
-      </c>
-      <c r="C19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20">
-        <v>7</v>
-      </c>
-      <c r="C20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23">
-        <v>10</v>
-      </c>
-      <c r="C23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24">
-        <v>11</v>
-      </c>
-      <c r="C24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25">
-        <v>12</v>
-      </c>
-      <c r="C25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{292D24D9-B7AF-4404-B87D-6D3347D4D37D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B47D7F0-07B4-4A35-A454-668FBC6C9FFD}">
   <dimension ref="A3:B8"/>
   <sheetFormatPr defaultRowHeight="14.5"/>

--- a/2022_04_29 PWC Challenge 1 - Hotel Analytics/PWC Dashboard.xlsx
+++ b/2022_04_29 PWC Challenge 1 - Hotel Analytics/PWC Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seoul\Dropbox\00 technical\github\kimep-data-science-lab\2022_04_29 PWC Challenge 1 - Hotel Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09DEA4F-BF38-49D2-8237-A73EF4413C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40FDD92-024C-418D-B95D-3C5F09D10D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AACBAEBD-F012-4269-A3B9-168C8D706687}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="4" activeTab="7" xr2:uid="{AACBAEBD-F012-4269-A3B9-168C8D706687}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="5" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="102">
   <si>
     <t>Month</t>
   </si>
@@ -305,6 +305,54 @@
   <si>
     <t>Concern Type</t>
   </si>
+  <si>
+    <t>Room type</t>
+  </si>
+  <si>
+    <t>Concern description</t>
+  </si>
+  <si>
+    <t>Doesn’t match the website/brochure</t>
+  </si>
+  <si>
+    <t>Faulty electronics</t>
+  </si>
+  <si>
+    <t>Low-quality food</t>
+  </si>
+  <si>
+    <t>Noisy neighbors</t>
+  </si>
+  <si>
+    <t>Slow Wi-Fi</t>
+  </si>
+  <si>
+    <t>No hot water</t>
+  </si>
+  <si>
+    <t>Dirty rooms</t>
+  </si>
+  <si>
+    <t>Bad smells</t>
+  </si>
+  <si>
+    <t>Issues with staff</t>
+  </si>
+  <si>
+    <t>Temperature of their room</t>
+  </si>
+  <si>
+    <t>Rodents, roaches, &amp; other unwanted guests</t>
+  </si>
+  <si>
+    <t>Concerns</t>
+  </si>
+  <si>
+    <t>Count_x</t>
+  </si>
+  <si>
+    <t>Count_y</t>
+  </si>
 </sst>
 </file>
 
@@ -313,7 +361,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -411,6 +459,11 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -534,7 +587,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -576,6 +629,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2021,6 +2077,1104 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Revenue Dash'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Room Revenue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Revenue Dash'!$E$6:$E$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Revenue Dash'!$B$6:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.96875</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0119047619047619</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.89583333333333337</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.68888888888888888</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.95333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.87037037037037035</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1933333333333334</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.92361111111111116</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.93181818181818177</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.9907407407407407</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.86842105263157898</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0600-42E3-ADDF-5AF8218284DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Revenue Dash'!$C$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Food Revenue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Revenue Dash'!$E$6:$E$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Revenue Dash'!$C$6:$C$17</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.4055121527777778</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.29181547619047621</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.21289682539682539</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11037037037037037</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.18450793650793651</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.4104938271604937E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.88180555555555551</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.4589722222222221</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.0264219576719578</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.67572601010101008</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0784336419753087</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.68479532163742685</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0600-42E3-ADDF-5AF8218284DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Revenue Dash'!$D$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Bar Revenue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Revenue Dash'!$E$6:$E$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Revenue Dash'!$D$6:$D$17</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.79166666666666663</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.52802579365079361</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.54389880952380953</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.31732804232804235</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.96047619047619048</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.59924768518518523</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.86236111111111113</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.153125</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.85945767195767198</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.77541035353535348</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.99807098765432101</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.70175438596491224</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0600-42E3-ADDF-5AF8218284DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Revenue Dash'!$J$6:$J$17</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0600-42E3-ADDF-5AF8218284DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="589614264"/>
+        <c:axId val="589614904"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Revenue Dash'!$E$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Month</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent6">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="ctr"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Revenue Dash'!$E$6:$E$17</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="12"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Revenue Dash'!$E$6:$E$17</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="12"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000004-0600-42E3-ADDF-5AF8218284DB}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="589614264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="589614904"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="589614904"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="589614264"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
@@ -2521,7 +3675,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3035,7 +4189,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3539,7 +4693,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4043,7 +5197,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4547,7 +5701,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5129,13 +6283,10 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -5368,6 +6519,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -8968,6 +10159,522 @@
 </file>
 
 <file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -9632,6 +11339,49 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>336550</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A982CA32-023A-40E5-8CBB-9DAC946D9F57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -13438,12 +15188,12 @@
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="2:10" ht="29" thickBot="1">
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
     </row>
     <row r="5" spans="2:10" ht="18.5">
       <c r="B5" s="8" t="s">
@@ -13815,10 +15565,328 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA41081-7588-469A-AFDA-DD303C470471}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:J22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="4.6328125" customWidth="1"/>
+    <col min="2" max="4" width="17.54296875" customWidth="1"/>
+    <col min="5" max="5" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="17.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" ht="16" thickBot="1">
+      <c r="B2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="2:10" ht="29" thickBot="1">
+      <c r="B3" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="5" spans="2:10" ht="18.5">
+      <c r="B5" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="2:10" ht="15.5">
+      <c r="B6" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M2,IF($B$3="King",'Revenue - Data'!M14,IF($B$3="Superior King",'Revenue - Data'!M26,IF($B$3="Executive",'Revenue - Data'!M38,IF($B$3="One Club",'Revenue - Data'!M50,'Revenue - Data'!M62)))))</f>
+        <v>0.96875</v>
+      </c>
+      <c r="C6" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N2,IF($B$3="King",'Revenue - Data'!N14,IF($B$3="Superior King",'Revenue - Data'!N26,IF($B$3="Executive",'Revenue - Data'!N38,IF($B$3="One Club",'Revenue - Data'!N50,'Revenue - Data'!N62)))))</f>
+        <v>0.4055121527777778</v>
+      </c>
+      <c r="D6" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O2,IF($B$3="King",'Revenue - Data'!O14,IF($B$3="Superior King",'Revenue - Data'!O26,IF($B$3="Executive",'Revenue - Data'!O38,IF($B$3="One Club",'Revenue - Data'!O50,'Revenue - Data'!O62)))))</f>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="15.5">
+      <c r="B7" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M3,IF($B$3="King",'Revenue - Data'!M15,IF($B$3="Superior King",'Revenue - Data'!M27,IF($B$3="Executive",'Revenue - Data'!M39,IF($B$3="One Club",'Revenue - Data'!M51,'Revenue - Data'!M63)))))</f>
+        <v>1.0119047619047619</v>
+      </c>
+      <c r="C7" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N3,IF($B$3="King",'Revenue - Data'!N15,IF($B$3="Superior King",'Revenue - Data'!N27,IF($B$3="Executive",'Revenue - Data'!N39,IF($B$3="One Club",'Revenue - Data'!N51,'Revenue - Data'!N63)))))</f>
+        <v>0.29181547619047621</v>
+      </c>
+      <c r="D7" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O3,IF($B$3="King",'Revenue - Data'!O15,IF($B$3="Superior King",'Revenue - Data'!O27,IF($B$3="Executive",'Revenue - Data'!O39,IF($B$3="One Club",'Revenue - Data'!O51,'Revenue - Data'!O63)))))</f>
+        <v>0.52802579365079361</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="15.5">
+      <c r="B8" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M4,IF($B$3="King",'Revenue - Data'!M16,IF($B$3="Superior King",'Revenue - Data'!M28,IF($B$3="Executive",'Revenue - Data'!M40,IF($B$3="One Club",'Revenue - Data'!M52,'Revenue - Data'!M64)))))</f>
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C8" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N4,IF($B$3="King",'Revenue - Data'!N16,IF($B$3="Superior King",'Revenue - Data'!N28,IF($B$3="Executive",'Revenue - Data'!N40,IF($B$3="One Club",'Revenue - Data'!N52,'Revenue - Data'!N64)))))</f>
+        <v>0.21289682539682539</v>
+      </c>
+      <c r="D8" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O4,IF($B$3="King",'Revenue - Data'!O16,IF($B$3="Superior King",'Revenue - Data'!O28,IF($B$3="Executive",'Revenue - Data'!O40,IF($B$3="One Club",'Revenue - Data'!O52,'Revenue - Data'!O64)))))</f>
+        <v>0.54389880952380953</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="15.5">
+      <c r="B9" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M5,IF($B$3="King",'Revenue - Data'!M17,IF($B$3="Superior King",'Revenue - Data'!M29,IF($B$3="Executive",'Revenue - Data'!M41,IF($B$3="One Club",'Revenue - Data'!M53,'Revenue - Data'!M65)))))</f>
+        <v>0.68888888888888888</v>
+      </c>
+      <c r="C9" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N5,IF($B$3="King",'Revenue - Data'!N17,IF($B$3="Superior King",'Revenue - Data'!N29,IF($B$3="Executive",'Revenue - Data'!N41,IF($B$3="One Club",'Revenue - Data'!N53,'Revenue - Data'!N65)))))</f>
+        <v>0.11037037037037037</v>
+      </c>
+      <c r="D9" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O5,IF($B$3="King",'Revenue - Data'!O17,IF($B$3="Superior King",'Revenue - Data'!O29,IF($B$3="Executive",'Revenue - Data'!O41,IF($B$3="One Club",'Revenue - Data'!O53,'Revenue - Data'!O65)))))</f>
+        <v>0.31732804232804235</v>
+      </c>
+      <c r="E9" s="7">
+        <v>4</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="15.5">
+      <c r="B10" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M6,IF($B$3="King",'Revenue - Data'!M18,IF($B$3="Superior King",'Revenue - Data'!M30,IF($B$3="Executive",'Revenue - Data'!M42,IF($B$3="One Club",'Revenue - Data'!M54,'Revenue - Data'!M66)))))</f>
+        <v>0.95333333333333337</v>
+      </c>
+      <c r="C10" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N6,IF($B$3="King",'Revenue - Data'!N18,IF($B$3="Superior King",'Revenue - Data'!N30,IF($B$3="Executive",'Revenue - Data'!N42,IF($B$3="One Club",'Revenue - Data'!N54,'Revenue - Data'!N66)))))</f>
+        <v>0.18450793650793651</v>
+      </c>
+      <c r="D10" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O6,IF($B$3="King",'Revenue - Data'!O18,IF($B$3="Superior King",'Revenue - Data'!O30,IF($B$3="Executive",'Revenue - Data'!O42,IF($B$3="One Club",'Revenue - Data'!O54,'Revenue - Data'!O66)))))</f>
+        <v>0.96047619047619048</v>
+      </c>
+      <c r="E10" s="7">
+        <v>5</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="15.5">
+      <c r="B11" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M7,IF($B$3="King",'Revenue - Data'!M19,IF($B$3="Superior King",'Revenue - Data'!M31,IF($B$3="Executive",'Revenue - Data'!M43,IF($B$3="One Club",'Revenue - Data'!M55,'Revenue - Data'!M67)))))</f>
+        <v>0.87037037037037035</v>
+      </c>
+      <c r="C11" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N7,IF($B$3="King",'Revenue - Data'!N19,IF($B$3="Superior King",'Revenue - Data'!N31,IF($B$3="Executive",'Revenue - Data'!N43,IF($B$3="One Club",'Revenue - Data'!N55,'Revenue - Data'!N67)))))</f>
+        <v>8.4104938271604937E-2</v>
+      </c>
+      <c r="D11" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O7,IF($B$3="King",'Revenue - Data'!O19,IF($B$3="Superior King",'Revenue - Data'!O31,IF($B$3="Executive",'Revenue - Data'!O43,IF($B$3="One Club",'Revenue - Data'!O55,'Revenue - Data'!O67)))))</f>
+        <v>0.59924768518518523</v>
+      </c>
+      <c r="E11" s="7">
+        <v>6</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="15.5">
+      <c r="B12" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M8,IF($B$3="King",'Revenue - Data'!M20,IF($B$3="Superior King",'Revenue - Data'!M32,IF($B$3="Executive",'Revenue - Data'!M44,IF($B$3="One Club",'Revenue - Data'!M56,'Revenue - Data'!M68)))))</f>
+        <v>0.94</v>
+      </c>
+      <c r="C12" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N8,IF($B$3="King",'Revenue - Data'!N20,IF($B$3="Superior King",'Revenue - Data'!N32,IF($B$3="Executive",'Revenue - Data'!N44,IF($B$3="One Club",'Revenue - Data'!N56,'Revenue - Data'!N68)))))</f>
+        <v>0.88180555555555551</v>
+      </c>
+      <c r="D12" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O8,IF($B$3="King",'Revenue - Data'!O20,IF($B$3="Superior King",'Revenue - Data'!O32,IF($B$3="Executive",'Revenue - Data'!O44,IF($B$3="One Club",'Revenue - Data'!O56,'Revenue - Data'!O68)))))</f>
+        <v>0.86236111111111113</v>
+      </c>
+      <c r="E12" s="7">
+        <v>7</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="15.5">
+      <c r="B13" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M9,IF($B$3="King",'Revenue - Data'!M21,IF($B$3="Superior King",'Revenue - Data'!M33,IF($B$3="Executive",'Revenue - Data'!M45,IF($B$3="One Club",'Revenue - Data'!M57,'Revenue - Data'!M69)))))</f>
+        <v>1.1933333333333334</v>
+      </c>
+      <c r="C13" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N9,IF($B$3="King",'Revenue - Data'!N21,IF($B$3="Superior King",'Revenue - Data'!N33,IF($B$3="Executive",'Revenue - Data'!N45,IF($B$3="One Club",'Revenue - Data'!N57,'Revenue - Data'!N69)))))</f>
+        <v>1.4589722222222221</v>
+      </c>
+      <c r="D13" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O9,IF($B$3="King",'Revenue - Data'!O21,IF($B$3="Superior King",'Revenue - Data'!O33,IF($B$3="Executive",'Revenue - Data'!O45,IF($B$3="One Club",'Revenue - Data'!O57,'Revenue - Data'!O69)))))</f>
+        <v>1.153125</v>
+      </c>
+      <c r="E13" s="7">
+        <v>8</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="15.5">
+      <c r="B14" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M10,IF($B$3="King",'Revenue - Data'!M22,IF($B$3="Superior King",'Revenue - Data'!M34,IF($B$3="Executive",'Revenue - Data'!M46,IF($B$3="One Club",'Revenue - Data'!M58,'Revenue - Data'!M70)))))</f>
+        <v>0.92361111111111116</v>
+      </c>
+      <c r="C14" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N10,IF($B$3="King",'Revenue - Data'!N22,IF($B$3="Superior King",'Revenue - Data'!N34,IF($B$3="Executive",'Revenue - Data'!N46,IF($B$3="One Club",'Revenue - Data'!N58,'Revenue - Data'!N70)))))</f>
+        <v>1.0264219576719578</v>
+      </c>
+      <c r="D14" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O10,IF($B$3="King",'Revenue - Data'!O22,IF($B$3="Superior King",'Revenue - Data'!O34,IF($B$3="Executive",'Revenue - Data'!O46,IF($B$3="One Club",'Revenue - Data'!O58,'Revenue - Data'!O70)))))</f>
+        <v>0.85945767195767198</v>
+      </c>
+      <c r="E14" s="7">
+        <v>9</v>
+      </c>
+      <c r="J14" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="15.5">
+      <c r="B15" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M11,IF($B$3="King",'Revenue - Data'!M23,IF($B$3="Superior King",'Revenue - Data'!M35,IF($B$3="Executive",'Revenue - Data'!M47,IF($B$3="One Club",'Revenue - Data'!M59,'Revenue - Data'!M71)))))</f>
+        <v>0.93181818181818177</v>
+      </c>
+      <c r="C15" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N11,IF($B$3="King",'Revenue - Data'!N23,IF($B$3="Superior King",'Revenue - Data'!N35,IF($B$3="Executive",'Revenue - Data'!N47,IF($B$3="One Club",'Revenue - Data'!N59,'Revenue - Data'!N71)))))</f>
+        <v>0.67572601010101008</v>
+      </c>
+      <c r="D15" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O11,IF($B$3="King",'Revenue - Data'!O23,IF($B$3="Superior King",'Revenue - Data'!O35,IF($B$3="Executive",'Revenue - Data'!O47,IF($B$3="One Club",'Revenue - Data'!O59,'Revenue - Data'!O71)))))</f>
+        <v>0.77541035353535348</v>
+      </c>
+      <c r="E15" s="7">
+        <v>10</v>
+      </c>
+      <c r="J15" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="15.5">
+      <c r="B16" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M12,IF($B$3="King",'Revenue - Data'!M24,IF($B$3="Superior King",'Revenue - Data'!M36,IF($B$3="Executive",'Revenue - Data'!M48,IF($B$3="One Club",'Revenue - Data'!M60,'Revenue - Data'!M72)))))</f>
+        <v>0.9907407407407407</v>
+      </c>
+      <c r="C16" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N12,IF($B$3="King",'Revenue - Data'!N24,IF($B$3="Superior King",'Revenue - Data'!N36,IF($B$3="Executive",'Revenue - Data'!N48,IF($B$3="One Club",'Revenue - Data'!N60,'Revenue - Data'!N72)))))</f>
+        <v>1.0784336419753087</v>
+      </c>
+      <c r="D16" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O12,IF($B$3="King",'Revenue - Data'!O24,IF($B$3="Superior King",'Revenue - Data'!O36,IF($B$3="Executive",'Revenue - Data'!O48,IF($B$3="One Club",'Revenue - Data'!O60,'Revenue - Data'!O72)))))</f>
+        <v>0.99807098765432101</v>
+      </c>
+      <c r="E16" s="7">
+        <v>11</v>
+      </c>
+      <c r="J16" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="15.5">
+      <c r="B17" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M13,IF($B$3="King",'Revenue - Data'!M25,IF($B$3="Superior King",'Revenue - Data'!M37,IF($B$3="Executive",'Revenue - Data'!M49,IF($B$3="One Club",'Revenue - Data'!M61,'Revenue - Data'!M73)))))</f>
+        <v>0.86842105263157898</v>
+      </c>
+      <c r="C17" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N13,IF($B$3="King",'Revenue - Data'!N25,IF($B$3="Superior King",'Revenue - Data'!N37,IF($B$3="Executive",'Revenue - Data'!N49,IF($B$3="One Club",'Revenue - Data'!N61,'Revenue - Data'!N73)))))</f>
+        <v>0.68479532163742685</v>
+      </c>
+      <c r="D17" s="6">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O13,IF($B$3="King",'Revenue - Data'!O25,IF($B$3="Superior King",'Revenue - Data'!O37,IF($B$3="Executive",'Revenue - Data'!O49,IF($B$3="One Club",'Revenue - Data'!O61,'Revenue - Data'!O73)))))</f>
+        <v>0.70175438596491224</v>
+      </c>
+      <c r="E17" s="7">
+        <v>12</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:E3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2DA1212D-44AD-4199-B927-6CE5D9DD7CAF}">
+          <x14:formula1>
+            <xm:f>Validation!$B$3:$B$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>B3</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -17597,23 +19665,3811 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6482E56F-AAD0-45DD-AED2-1DDF0978065A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" customWidth="1"/>
-    <col min="5" max="5" width="12.6328125" customWidth="1"/>
+    <col min="1" max="2" width="23" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{292D24D9-B7AF-4404-B87D-6D3347D4D37D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E217"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="5" width="21.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16">
+        <v>9</v>
+      </c>
+      <c r="E16">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17">
+        <v>7</v>
+      </c>
+      <c r="E17">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22">
+        <v>7</v>
+      </c>
+      <c r="E22">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26">
+        <v>13</v>
+      </c>
+      <c r="E26">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27">
+        <v>13</v>
+      </c>
+      <c r="E27">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28">
+        <v>12</v>
+      </c>
+      <c r="E28">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29">
+        <v>5</v>
+      </c>
+      <c r="E29">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38">
+        <v>6</v>
+      </c>
+      <c r="E38">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>88</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+      <c r="E39">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40">
+        <v>5</v>
+      </c>
+      <c r="E40">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42">
+        <v>5</v>
+      </c>
+      <c r="C42" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42">
+        <v>7</v>
+      </c>
+      <c r="E42">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>88</v>
+      </c>
+      <c r="D44">
+        <v>6</v>
+      </c>
+      <c r="E44">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>88</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>69</v>
+      </c>
+      <c r="B47">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48">
+        <v>11</v>
+      </c>
+      <c r="C48" t="s">
+        <v>88</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>89</v>
+      </c>
+      <c r="D50">
+        <v>6</v>
+      </c>
+      <c r="E50">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52">
+        <v>3</v>
+      </c>
+      <c r="C52" t="s">
+        <v>89</v>
+      </c>
+      <c r="D52">
+        <v>10</v>
+      </c>
+      <c r="E52">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>89</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54">
+        <v>5</v>
+      </c>
+      <c r="C54" t="s">
+        <v>89</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+      <c r="E54">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55">
+        <v>6</v>
+      </c>
+      <c r="C55" t="s">
+        <v>89</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>89</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57">
+        <v>8</v>
+      </c>
+      <c r="C57" t="s">
+        <v>89</v>
+      </c>
+      <c r="D57">
+        <v>5</v>
+      </c>
+      <c r="E57">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58">
+        <v>9</v>
+      </c>
+      <c r="C58" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>89</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+      <c r="E59">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>89</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61">
+        <v>12</v>
+      </c>
+      <c r="C61" t="s">
+        <v>89</v>
+      </c>
+      <c r="D61">
+        <v>6</v>
+      </c>
+      <c r="E61">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>91</v>
+      </c>
+      <c r="D62">
+        <v>5</v>
+      </c>
+      <c r="E62">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>91</v>
+      </c>
+      <c r="D63">
+        <v>7</v>
+      </c>
+      <c r="E63">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="E64">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>91</v>
+      </c>
+      <c r="D65">
+        <v>5</v>
+      </c>
+      <c r="E65">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>91</v>
+      </c>
+      <c r="D66">
+        <v>6</v>
+      </c>
+      <c r="E66">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>91</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>91</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>91</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>91</v>
+      </c>
+      <c r="D70">
+        <v>3</v>
+      </c>
+      <c r="E70">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>91</v>
+      </c>
+      <c r="D71">
+        <v>4</v>
+      </c>
+      <c r="E71">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>69</v>
+      </c>
+      <c r="B72">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>91</v>
+      </c>
+      <c r="D72">
+        <v>5</v>
+      </c>
+      <c r="E72">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>69</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>91</v>
+      </c>
+      <c r="D73">
+        <v>2</v>
+      </c>
+      <c r="E73">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
+        <v>95</v>
+      </c>
+      <c r="D74">
+        <v>11</v>
+      </c>
+      <c r="E74">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75" t="s">
+        <v>95</v>
+      </c>
+      <c r="D75">
+        <v>8</v>
+      </c>
+      <c r="E75">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>70</v>
+      </c>
+      <c r="B76">
+        <v>3</v>
+      </c>
+      <c r="C76" t="s">
+        <v>95</v>
+      </c>
+      <c r="D76">
+        <v>2</v>
+      </c>
+      <c r="E76">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>70</v>
+      </c>
+      <c r="B77">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
+        <v>95</v>
+      </c>
+      <c r="D77">
+        <v>3</v>
+      </c>
+      <c r="E77">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>70</v>
+      </c>
+      <c r="B78">
+        <v>5</v>
+      </c>
+      <c r="C78" t="s">
+        <v>95</v>
+      </c>
+      <c r="D78">
+        <v>5</v>
+      </c>
+      <c r="E78">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>70</v>
+      </c>
+      <c r="B79">
+        <v>6</v>
+      </c>
+      <c r="C79" t="s">
+        <v>95</v>
+      </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
+      <c r="E79">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>70</v>
+      </c>
+      <c r="B80">
+        <v>7</v>
+      </c>
+      <c r="C80" t="s">
+        <v>95</v>
+      </c>
+      <c r="D80">
+        <v>5</v>
+      </c>
+      <c r="E80">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>70</v>
+      </c>
+      <c r="B81">
+        <v>8</v>
+      </c>
+      <c r="C81" t="s">
+        <v>95</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+      <c r="E81">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>70</v>
+      </c>
+      <c r="B82">
+        <v>9</v>
+      </c>
+      <c r="C82" t="s">
+        <v>95</v>
+      </c>
+      <c r="D82">
+        <v>5</v>
+      </c>
+      <c r="E82">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>70</v>
+      </c>
+      <c r="B83">
+        <v>10</v>
+      </c>
+      <c r="C83" t="s">
+        <v>95</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>70</v>
+      </c>
+      <c r="B84">
+        <v>11</v>
+      </c>
+      <c r="C84" t="s">
+        <v>95</v>
+      </c>
+      <c r="D84">
+        <v>3</v>
+      </c>
+      <c r="E84">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>70</v>
+      </c>
+      <c r="B85">
+        <v>12</v>
+      </c>
+      <c r="C85" t="s">
+        <v>95</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>70</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
+        <v>91</v>
+      </c>
+      <c r="D86">
+        <v>17</v>
+      </c>
+      <c r="E86">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>70</v>
+      </c>
+      <c r="B87">
+        <v>2</v>
+      </c>
+      <c r="C87" t="s">
+        <v>91</v>
+      </c>
+      <c r="D87">
+        <v>13</v>
+      </c>
+      <c r="E87">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>70</v>
+      </c>
+      <c r="B88">
+        <v>3</v>
+      </c>
+      <c r="C88" t="s">
+        <v>91</v>
+      </c>
+      <c r="D88">
+        <v>14</v>
+      </c>
+      <c r="E88">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>70</v>
+      </c>
+      <c r="B89">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>91</v>
+      </c>
+      <c r="D89">
+        <v>8</v>
+      </c>
+      <c r="E89">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>70</v>
+      </c>
+      <c r="B90">
+        <v>5</v>
+      </c>
+      <c r="C90" t="s">
+        <v>91</v>
+      </c>
+      <c r="D90">
+        <v>3</v>
+      </c>
+      <c r="E90">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>70</v>
+      </c>
+      <c r="B91">
+        <v>6</v>
+      </c>
+      <c r="C91" t="s">
+        <v>91</v>
+      </c>
+      <c r="D91">
+        <v>3</v>
+      </c>
+      <c r="E91">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>70</v>
+      </c>
+      <c r="B92">
+        <v>7</v>
+      </c>
+      <c r="C92" t="s">
+        <v>91</v>
+      </c>
+      <c r="D92">
+        <v>6</v>
+      </c>
+      <c r="E92">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>70</v>
+      </c>
+      <c r="B93">
+        <v>8</v>
+      </c>
+      <c r="C93" t="s">
+        <v>91</v>
+      </c>
+      <c r="D93">
+        <v>8</v>
+      </c>
+      <c r="E93">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>70</v>
+      </c>
+      <c r="B94">
+        <v>9</v>
+      </c>
+      <c r="C94" t="s">
+        <v>91</v>
+      </c>
+      <c r="D94">
+        <v>8</v>
+      </c>
+      <c r="E94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>70</v>
+      </c>
+      <c r="B95">
+        <v>10</v>
+      </c>
+      <c r="C95" t="s">
+        <v>91</v>
+      </c>
+      <c r="D95">
+        <v>3</v>
+      </c>
+      <c r="E95">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>70</v>
+      </c>
+      <c r="B96">
+        <v>11</v>
+      </c>
+      <c r="C96" t="s">
+        <v>91</v>
+      </c>
+      <c r="D96">
+        <v>5</v>
+      </c>
+      <c r="E96">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>70</v>
+      </c>
+      <c r="B97">
+        <v>12</v>
+      </c>
+      <c r="C97" t="s">
+        <v>91</v>
+      </c>
+      <c r="D97">
+        <v>5</v>
+      </c>
+      <c r="E97">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>70</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>97</v>
+      </c>
+      <c r="D98">
+        <v>4</v>
+      </c>
+      <c r="E98">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>70</v>
+      </c>
+      <c r="B99">
+        <v>2</v>
+      </c>
+      <c r="C99" t="s">
+        <v>97</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+      <c r="E99">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>70</v>
+      </c>
+      <c r="B100">
+        <v>3</v>
+      </c>
+      <c r="C100" t="s">
+        <v>97</v>
+      </c>
+      <c r="D100">
+        <v>4</v>
+      </c>
+      <c r="E100">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>70</v>
+      </c>
+      <c r="B101">
+        <v>4</v>
+      </c>
+      <c r="C101" t="s">
+        <v>97</v>
+      </c>
+      <c r="D101">
+        <v>2</v>
+      </c>
+      <c r="E101">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>70</v>
+      </c>
+      <c r="B102">
+        <v>5</v>
+      </c>
+      <c r="C102" t="s">
+        <v>97</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>70</v>
+      </c>
+      <c r="B103">
+        <v>6</v>
+      </c>
+      <c r="C103" t="s">
+        <v>97</v>
+      </c>
+      <c r="D103">
+        <v>2</v>
+      </c>
+      <c r="E103">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>70</v>
+      </c>
+      <c r="B104">
+        <v>7</v>
+      </c>
+      <c r="C104" t="s">
+        <v>97</v>
+      </c>
+      <c r="D104">
+        <v>56</v>
+      </c>
+      <c r="E104">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>70</v>
+      </c>
+      <c r="B105">
+        <v>8</v>
+      </c>
+      <c r="C105" t="s">
+        <v>97</v>
+      </c>
+      <c r="D105">
+        <v>71</v>
+      </c>
+      <c r="E105">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>70</v>
+      </c>
+      <c r="B106">
+        <v>9</v>
+      </c>
+      <c r="C106" t="s">
+        <v>97</v>
+      </c>
+      <c r="D106">
+        <v>97</v>
+      </c>
+      <c r="E106">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>70</v>
+      </c>
+      <c r="B107">
+        <v>10</v>
+      </c>
+      <c r="C107" t="s">
+        <v>97</v>
+      </c>
+      <c r="D107">
+        <v>50</v>
+      </c>
+      <c r="E107">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>70</v>
+      </c>
+      <c r="B108">
+        <v>11</v>
+      </c>
+      <c r="C108" t="s">
+        <v>97</v>
+      </c>
+      <c r="D108">
+        <v>52</v>
+      </c>
+      <c r="E108">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>70</v>
+      </c>
+      <c r="B109">
+        <v>12</v>
+      </c>
+      <c r="C109" t="s">
+        <v>97</v>
+      </c>
+      <c r="D109">
+        <v>54</v>
+      </c>
+      <c r="E109">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>71</v>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
+        <v>88</v>
+      </c>
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>71</v>
+      </c>
+      <c r="B111">
+        <v>2</v>
+      </c>
+      <c r="C111" t="s">
+        <v>88</v>
+      </c>
+      <c r="D111">
+        <v>5</v>
+      </c>
+      <c r="E111">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>71</v>
+      </c>
+      <c r="B112">
+        <v>3</v>
+      </c>
+      <c r="C112" t="s">
+        <v>88</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>71</v>
+      </c>
+      <c r="B113">
+        <v>4</v>
+      </c>
+      <c r="C113" t="s">
+        <v>88</v>
+      </c>
+      <c r="D113">
+        <v>2</v>
+      </c>
+      <c r="E113">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>71</v>
+      </c>
+      <c r="B114">
+        <v>5</v>
+      </c>
+      <c r="C114" t="s">
+        <v>88</v>
+      </c>
+      <c r="D114">
+        <v>4</v>
+      </c>
+      <c r="E114">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>71</v>
+      </c>
+      <c r="B115">
+        <v>6</v>
+      </c>
+      <c r="C115" t="s">
+        <v>88</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+      <c r="E115">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>71</v>
+      </c>
+      <c r="B116">
+        <v>7</v>
+      </c>
+      <c r="C116" t="s">
+        <v>88</v>
+      </c>
+      <c r="D116">
+        <v>6</v>
+      </c>
+      <c r="E116">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
+        <v>71</v>
+      </c>
+      <c r="B117">
+        <v>8</v>
+      </c>
+      <c r="C117" t="s">
+        <v>88</v>
+      </c>
+      <c r="D117">
+        <v>5</v>
+      </c>
+      <c r="E117">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
+        <v>71</v>
+      </c>
+      <c r="B118">
+        <v>9</v>
+      </c>
+      <c r="C118" t="s">
+        <v>88</v>
+      </c>
+      <c r="D118">
+        <v>1</v>
+      </c>
+      <c r="E118">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
+        <v>71</v>
+      </c>
+      <c r="B119">
+        <v>10</v>
+      </c>
+      <c r="C119" t="s">
+        <v>88</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
+      </c>
+      <c r="E119">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
+        <v>71</v>
+      </c>
+      <c r="B120">
+        <v>11</v>
+      </c>
+      <c r="C120" t="s">
+        <v>88</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="E120">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
+        <v>71</v>
+      </c>
+      <c r="B121">
+        <v>12</v>
+      </c>
+      <c r="C121" t="s">
+        <v>88</v>
+      </c>
+      <c r="D121">
+        <v>4</v>
+      </c>
+      <c r="E121">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" t="s">
+        <v>71</v>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122" t="s">
+        <v>89</v>
+      </c>
+      <c r="D122">
+        <v>2</v>
+      </c>
+      <c r="E122">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" t="s">
+        <v>71</v>
+      </c>
+      <c r="B123">
+        <v>2</v>
+      </c>
+      <c r="C123" t="s">
+        <v>89</v>
+      </c>
+      <c r="D123">
+        <v>1</v>
+      </c>
+      <c r="E123">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" t="s">
+        <v>71</v>
+      </c>
+      <c r="B124">
+        <v>3</v>
+      </c>
+      <c r="C124" t="s">
+        <v>89</v>
+      </c>
+      <c r="D124">
+        <v>3</v>
+      </c>
+      <c r="E124">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" t="s">
+        <v>71</v>
+      </c>
+      <c r="B125">
+        <v>4</v>
+      </c>
+      <c r="C125" t="s">
+        <v>89</v>
+      </c>
+      <c r="D125">
+        <v>3</v>
+      </c>
+      <c r="E125">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" t="s">
+        <v>71</v>
+      </c>
+      <c r="B126">
+        <v>5</v>
+      </c>
+      <c r="C126" t="s">
+        <v>89</v>
+      </c>
+      <c r="D126">
+        <v>3</v>
+      </c>
+      <c r="E126">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" t="s">
+        <v>71</v>
+      </c>
+      <c r="B127">
+        <v>6</v>
+      </c>
+      <c r="C127" t="s">
+        <v>89</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" t="s">
+        <v>71</v>
+      </c>
+      <c r="B128">
+        <v>7</v>
+      </c>
+      <c r="C128" t="s">
+        <v>89</v>
+      </c>
+      <c r="D128">
+        <v>1</v>
+      </c>
+      <c r="E128">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" t="s">
+        <v>71</v>
+      </c>
+      <c r="B129">
+        <v>8</v>
+      </c>
+      <c r="C129" t="s">
+        <v>89</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="E129">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" t="s">
+        <v>71</v>
+      </c>
+      <c r="B130">
+        <v>9</v>
+      </c>
+      <c r="C130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="E130">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" t="s">
+        <v>71</v>
+      </c>
+      <c r="B131">
+        <v>10</v>
+      </c>
+      <c r="C131" t="s">
+        <v>89</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="E131">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" t="s">
+        <v>71</v>
+      </c>
+      <c r="B132">
+        <v>11</v>
+      </c>
+      <c r="C132" t="s">
+        <v>89</v>
+      </c>
+      <c r="D132">
+        <v>2</v>
+      </c>
+      <c r="E132">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" t="s">
+        <v>71</v>
+      </c>
+      <c r="B133">
+        <v>12</v>
+      </c>
+      <c r="C133" t="s">
+        <v>89</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" t="s">
+        <v>71</v>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134" t="s">
+        <v>90</v>
+      </c>
+      <c r="D134">
+        <v>6</v>
+      </c>
+      <c r="E134">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" t="s">
+        <v>71</v>
+      </c>
+      <c r="B135">
+        <v>2</v>
+      </c>
+      <c r="C135" t="s">
+        <v>90</v>
+      </c>
+      <c r="D135">
+        <v>3</v>
+      </c>
+      <c r="E135">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" t="s">
+        <v>71</v>
+      </c>
+      <c r="B136">
+        <v>3</v>
+      </c>
+      <c r="C136" t="s">
+        <v>90</v>
+      </c>
+      <c r="D136">
+        <v>3</v>
+      </c>
+      <c r="E136">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" t="s">
+        <v>71</v>
+      </c>
+      <c r="B137">
+        <v>4</v>
+      </c>
+      <c r="C137" t="s">
+        <v>90</v>
+      </c>
+      <c r="D137">
+        <v>2</v>
+      </c>
+      <c r="E137">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" t="s">
+        <v>71</v>
+      </c>
+      <c r="B138">
+        <v>5</v>
+      </c>
+      <c r="C138" t="s">
+        <v>90</v>
+      </c>
+      <c r="D138">
+        <v>3</v>
+      </c>
+      <c r="E138">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" t="s">
+        <v>71</v>
+      </c>
+      <c r="B139">
+        <v>6</v>
+      </c>
+      <c r="C139" t="s">
+        <v>90</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" t="s">
+        <v>71</v>
+      </c>
+      <c r="B140">
+        <v>7</v>
+      </c>
+      <c r="C140" t="s">
+        <v>90</v>
+      </c>
+      <c r="D140">
+        <v>1</v>
+      </c>
+      <c r="E140">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" t="s">
+        <v>71</v>
+      </c>
+      <c r="B141">
+        <v>8</v>
+      </c>
+      <c r="C141" t="s">
+        <v>90</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" t="s">
+        <v>71</v>
+      </c>
+      <c r="B142">
+        <v>9</v>
+      </c>
+      <c r="C142" t="s">
+        <v>90</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" t="s">
+        <v>71</v>
+      </c>
+      <c r="B143">
+        <v>10</v>
+      </c>
+      <c r="C143" t="s">
+        <v>90</v>
+      </c>
+      <c r="D143">
+        <v>2</v>
+      </c>
+      <c r="E143">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" t="s">
+        <v>71</v>
+      </c>
+      <c r="B144">
+        <v>11</v>
+      </c>
+      <c r="C144" t="s">
+        <v>90</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="E144">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" t="s">
+        <v>71</v>
+      </c>
+      <c r="B145">
+        <v>12</v>
+      </c>
+      <c r="C145" t="s">
+        <v>90</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" t="s">
+        <v>72</v>
+      </c>
+      <c r="B146">
+        <v>1</v>
+      </c>
+      <c r="C146" t="s">
+        <v>88</v>
+      </c>
+      <c r="D146">
+        <v>2</v>
+      </c>
+      <c r="E146">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" t="s">
+        <v>72</v>
+      </c>
+      <c r="B147">
+        <v>2</v>
+      </c>
+      <c r="C147" t="s">
+        <v>88</v>
+      </c>
+      <c r="D147">
+        <v>3</v>
+      </c>
+      <c r="E147">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" t="s">
+        <v>72</v>
+      </c>
+      <c r="B148">
+        <v>3</v>
+      </c>
+      <c r="C148" t="s">
+        <v>88</v>
+      </c>
+      <c r="D148">
+        <v>1</v>
+      </c>
+      <c r="E148">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" t="s">
+        <v>72</v>
+      </c>
+      <c r="B149">
+        <v>4</v>
+      </c>
+      <c r="C149" t="s">
+        <v>88</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" t="s">
+        <v>72</v>
+      </c>
+      <c r="B150">
+        <v>5</v>
+      </c>
+      <c r="C150" t="s">
+        <v>88</v>
+      </c>
+      <c r="D150">
+        <v>2</v>
+      </c>
+      <c r="E150">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" t="s">
+        <v>72</v>
+      </c>
+      <c r="B151">
+        <v>6</v>
+      </c>
+      <c r="C151" t="s">
+        <v>88</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="E151">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" t="s">
+        <v>72</v>
+      </c>
+      <c r="B152">
+        <v>7</v>
+      </c>
+      <c r="C152" t="s">
+        <v>88</v>
+      </c>
+      <c r="D152">
+        <v>1</v>
+      </c>
+      <c r="E152">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" t="s">
+        <v>72</v>
+      </c>
+      <c r="B153">
+        <v>8</v>
+      </c>
+      <c r="C153" t="s">
+        <v>88</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="E153">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" t="s">
+        <v>72</v>
+      </c>
+      <c r="B154">
+        <v>9</v>
+      </c>
+      <c r="C154" t="s">
+        <v>88</v>
+      </c>
+      <c r="D154">
+        <v>3</v>
+      </c>
+      <c r="E154">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" t="s">
+        <v>72</v>
+      </c>
+      <c r="B155">
+        <v>10</v>
+      </c>
+      <c r="C155" t="s">
+        <v>88</v>
+      </c>
+      <c r="D155">
+        <v>2</v>
+      </c>
+      <c r="E155">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" t="s">
+        <v>72</v>
+      </c>
+      <c r="B156">
+        <v>11</v>
+      </c>
+      <c r="C156" t="s">
+        <v>88</v>
+      </c>
+      <c r="D156">
+        <v>3</v>
+      </c>
+      <c r="E156">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" t="s">
+        <v>72</v>
+      </c>
+      <c r="B157">
+        <v>12</v>
+      </c>
+      <c r="C157" t="s">
+        <v>88</v>
+      </c>
+      <c r="D157">
+        <v>3</v>
+      </c>
+      <c r="E157">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" t="s">
+        <v>72</v>
+      </c>
+      <c r="B158">
+        <v>1</v>
+      </c>
+      <c r="C158" t="s">
+        <v>89</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+      <c r="E158">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B159">
+        <v>2</v>
+      </c>
+      <c r="C159" t="s">
+        <v>89</v>
+      </c>
+      <c r="D159">
+        <v>2</v>
+      </c>
+      <c r="E159">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" t="s">
+        <v>72</v>
+      </c>
+      <c r="B160">
+        <v>3</v>
+      </c>
+      <c r="C160" t="s">
+        <v>89</v>
+      </c>
+      <c r="D160">
+        <v>3</v>
+      </c>
+      <c r="E160">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" t="s">
+        <v>72</v>
+      </c>
+      <c r="B161">
+        <v>4</v>
+      </c>
+      <c r="C161" t="s">
+        <v>89</v>
+      </c>
+      <c r="D161">
+        <v>2</v>
+      </c>
+      <c r="E161">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" t="s">
+        <v>72</v>
+      </c>
+      <c r="B162">
+        <v>5</v>
+      </c>
+      <c r="C162" t="s">
+        <v>89</v>
+      </c>
+      <c r="D162">
+        <v>6</v>
+      </c>
+      <c r="E162">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" t="s">
+        <v>72</v>
+      </c>
+      <c r="B163">
+        <v>6</v>
+      </c>
+      <c r="C163" t="s">
+        <v>89</v>
+      </c>
+      <c r="D163">
+        <v>2</v>
+      </c>
+      <c r="E163">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" t="s">
+        <v>72</v>
+      </c>
+      <c r="B164">
+        <v>7</v>
+      </c>
+      <c r="C164" t="s">
+        <v>89</v>
+      </c>
+      <c r="D164">
+        <v>1</v>
+      </c>
+      <c r="E164">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" t="s">
+        <v>72</v>
+      </c>
+      <c r="B165">
+        <v>8</v>
+      </c>
+      <c r="C165" t="s">
+        <v>89</v>
+      </c>
+      <c r="D165">
+        <v>4</v>
+      </c>
+      <c r="E165">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" t="s">
+        <v>72</v>
+      </c>
+      <c r="B166">
+        <v>9</v>
+      </c>
+      <c r="C166" t="s">
+        <v>89</v>
+      </c>
+      <c r="D166">
+        <v>2</v>
+      </c>
+      <c r="E166">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" t="s">
+        <v>72</v>
+      </c>
+      <c r="B167">
+        <v>10</v>
+      </c>
+      <c r="C167" t="s">
+        <v>89</v>
+      </c>
+      <c r="D167">
+        <v>4</v>
+      </c>
+      <c r="E167">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" t="s">
+        <v>72</v>
+      </c>
+      <c r="B168">
+        <v>11</v>
+      </c>
+      <c r="C168" t="s">
+        <v>89</v>
+      </c>
+      <c r="D168">
+        <v>3</v>
+      </c>
+      <c r="E168">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" t="s">
+        <v>72</v>
+      </c>
+      <c r="B169">
+        <v>12</v>
+      </c>
+      <c r="C169" t="s">
+        <v>89</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="E169">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" t="s">
+        <v>72</v>
+      </c>
+      <c r="B170">
+        <v>1</v>
+      </c>
+      <c r="C170" t="s">
+        <v>90</v>
+      </c>
+      <c r="D170">
+        <v>6</v>
+      </c>
+      <c r="E170">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" t="s">
+        <v>72</v>
+      </c>
+      <c r="B171">
+        <v>2</v>
+      </c>
+      <c r="C171" t="s">
+        <v>90</v>
+      </c>
+      <c r="D171">
+        <v>8</v>
+      </c>
+      <c r="E171">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" t="s">
+        <v>72</v>
+      </c>
+      <c r="B172">
+        <v>3</v>
+      </c>
+      <c r="C172" t="s">
+        <v>90</v>
+      </c>
+      <c r="D172">
+        <v>5</v>
+      </c>
+      <c r="E172">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" t="s">
+        <v>72</v>
+      </c>
+      <c r="B173">
+        <v>4</v>
+      </c>
+      <c r="C173" t="s">
+        <v>90</v>
+      </c>
+      <c r="D173">
+        <v>4</v>
+      </c>
+      <c r="E173">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" t="s">
+        <v>72</v>
+      </c>
+      <c r="B174">
+        <v>5</v>
+      </c>
+      <c r="C174" t="s">
+        <v>90</v>
+      </c>
+      <c r="D174">
+        <v>7</v>
+      </c>
+      <c r="E174">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" t="s">
+        <v>72</v>
+      </c>
+      <c r="B175">
+        <v>6</v>
+      </c>
+      <c r="C175" t="s">
+        <v>90</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" t="s">
+        <v>72</v>
+      </c>
+      <c r="B176">
+        <v>7</v>
+      </c>
+      <c r="C176" t="s">
+        <v>90</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="E176">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" t="s">
+        <v>72</v>
+      </c>
+      <c r="B177">
+        <v>8</v>
+      </c>
+      <c r="C177" t="s">
+        <v>90</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="E177">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" t="s">
+        <v>72</v>
+      </c>
+      <c r="B178">
+        <v>9</v>
+      </c>
+      <c r="C178" t="s">
+        <v>90</v>
+      </c>
+      <c r="D178">
+        <v>1</v>
+      </c>
+      <c r="E178">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" t="s">
+        <v>72</v>
+      </c>
+      <c r="B179">
+        <v>10</v>
+      </c>
+      <c r="C179" t="s">
+        <v>90</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="E179">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" t="s">
+        <v>72</v>
+      </c>
+      <c r="B180">
+        <v>11</v>
+      </c>
+      <c r="C180" t="s">
+        <v>90</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="E180">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" t="s">
+        <v>72</v>
+      </c>
+      <c r="B181">
+        <v>12</v>
+      </c>
+      <c r="C181" t="s">
+        <v>90</v>
+      </c>
+      <c r="D181">
+        <v>1</v>
+      </c>
+      <c r="E181">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" t="s">
+        <v>73</v>
+      </c>
+      <c r="B182">
+        <v>1</v>
+      </c>
+      <c r="C182" t="s">
+        <v>95</v>
+      </c>
+      <c r="D182">
+        <v>23</v>
+      </c>
+      <c r="E182">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" t="s">
+        <v>73</v>
+      </c>
+      <c r="B183">
+        <v>2</v>
+      </c>
+      <c r="C183" t="s">
+        <v>95</v>
+      </c>
+      <c r="D183">
+        <v>19</v>
+      </c>
+      <c r="E183">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" t="s">
+        <v>73</v>
+      </c>
+      <c r="B184">
+        <v>3</v>
+      </c>
+      <c r="C184" t="s">
+        <v>95</v>
+      </c>
+      <c r="D184">
+        <v>7</v>
+      </c>
+      <c r="E184">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" t="s">
+        <v>73</v>
+      </c>
+      <c r="B185">
+        <v>4</v>
+      </c>
+      <c r="C185" t="s">
+        <v>95</v>
+      </c>
+      <c r="D185">
+        <v>11</v>
+      </c>
+      <c r="E185">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" t="s">
+        <v>73</v>
+      </c>
+      <c r="B186">
+        <v>5</v>
+      </c>
+      <c r="C186" t="s">
+        <v>95</v>
+      </c>
+      <c r="D186">
+        <v>11</v>
+      </c>
+      <c r="E186">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" t="s">
+        <v>73</v>
+      </c>
+      <c r="B187">
+        <v>6</v>
+      </c>
+      <c r="C187" t="s">
+        <v>95</v>
+      </c>
+      <c r="D187">
+        <v>12</v>
+      </c>
+      <c r="E187">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" t="s">
+        <v>73</v>
+      </c>
+      <c r="B188">
+        <v>7</v>
+      </c>
+      <c r="C188" t="s">
+        <v>95</v>
+      </c>
+      <c r="D188">
+        <v>8</v>
+      </c>
+      <c r="E188">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" t="s">
+        <v>73</v>
+      </c>
+      <c r="B189">
+        <v>8</v>
+      </c>
+      <c r="C189" t="s">
+        <v>95</v>
+      </c>
+      <c r="D189">
+        <v>10</v>
+      </c>
+      <c r="E189">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" t="s">
+        <v>73</v>
+      </c>
+      <c r="B190">
+        <v>9</v>
+      </c>
+      <c r="C190" t="s">
+        <v>95</v>
+      </c>
+      <c r="D190">
+        <v>11</v>
+      </c>
+      <c r="E190">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" t="s">
+        <v>73</v>
+      </c>
+      <c r="B191">
+        <v>10</v>
+      </c>
+      <c r="C191" t="s">
+        <v>95</v>
+      </c>
+      <c r="D191">
+        <v>37</v>
+      </c>
+      <c r="E191">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" t="s">
+        <v>73</v>
+      </c>
+      <c r="B192">
+        <v>11</v>
+      </c>
+      <c r="C192" t="s">
+        <v>95</v>
+      </c>
+      <c r="D192">
+        <v>5</v>
+      </c>
+      <c r="E192">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" t="s">
+        <v>73</v>
+      </c>
+      <c r="B193">
+        <v>12</v>
+      </c>
+      <c r="C193" t="s">
+        <v>95</v>
+      </c>
+      <c r="D193">
+        <v>13</v>
+      </c>
+      <c r="E193">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" t="s">
+        <v>73</v>
+      </c>
+      <c r="B194">
+        <v>1</v>
+      </c>
+      <c r="C194" t="s">
+        <v>89</v>
+      </c>
+      <c r="D194">
+        <v>6</v>
+      </c>
+      <c r="E194">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" t="s">
+        <v>73</v>
+      </c>
+      <c r="B195">
+        <v>2</v>
+      </c>
+      <c r="C195" t="s">
+        <v>89</v>
+      </c>
+      <c r="D195">
+        <v>5</v>
+      </c>
+      <c r="E195">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" t="s">
+        <v>73</v>
+      </c>
+      <c r="B196">
+        <v>3</v>
+      </c>
+      <c r="C196" t="s">
+        <v>89</v>
+      </c>
+      <c r="D196">
+        <v>11</v>
+      </c>
+      <c r="E196">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" t="s">
+        <v>73</v>
+      </c>
+      <c r="B197">
+        <v>4</v>
+      </c>
+      <c r="C197" t="s">
+        <v>89</v>
+      </c>
+      <c r="D197">
+        <v>8</v>
+      </c>
+      <c r="E197">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" t="s">
+        <v>73</v>
+      </c>
+      <c r="B198">
+        <v>5</v>
+      </c>
+      <c r="C198" t="s">
+        <v>89</v>
+      </c>
+      <c r="D198">
+        <v>11</v>
+      </c>
+      <c r="E198">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" t="s">
+        <v>73</v>
+      </c>
+      <c r="B199">
+        <v>6</v>
+      </c>
+      <c r="C199" t="s">
+        <v>89</v>
+      </c>
+      <c r="D199">
+        <v>3</v>
+      </c>
+      <c r="E199">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" t="s">
+        <v>73</v>
+      </c>
+      <c r="B200">
+        <v>7</v>
+      </c>
+      <c r="C200" t="s">
+        <v>89</v>
+      </c>
+      <c r="D200">
+        <v>3</v>
+      </c>
+      <c r="E200">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" t="s">
+        <v>73</v>
+      </c>
+      <c r="B201">
+        <v>8</v>
+      </c>
+      <c r="C201" t="s">
+        <v>89</v>
+      </c>
+      <c r="D201">
+        <v>6</v>
+      </c>
+      <c r="E201">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" t="s">
+        <v>73</v>
+      </c>
+      <c r="B202">
+        <v>9</v>
+      </c>
+      <c r="C202" t="s">
+        <v>89</v>
+      </c>
+      <c r="D202">
+        <v>2</v>
+      </c>
+      <c r="E202">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" t="s">
+        <v>73</v>
+      </c>
+      <c r="B203">
+        <v>10</v>
+      </c>
+      <c r="C203" t="s">
+        <v>89</v>
+      </c>
+      <c r="D203">
+        <v>19</v>
+      </c>
+      <c r="E203">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" t="s">
+        <v>73</v>
+      </c>
+      <c r="B204">
+        <v>11</v>
+      </c>
+      <c r="C204" t="s">
+        <v>89</v>
+      </c>
+      <c r="D204">
+        <v>7</v>
+      </c>
+      <c r="E204">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" t="s">
+        <v>73</v>
+      </c>
+      <c r="B205">
+        <v>12</v>
+      </c>
+      <c r="C205" t="s">
+        <v>89</v>
+      </c>
+      <c r="D205">
+        <v>8</v>
+      </c>
+      <c r="E205">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" t="s">
+        <v>73</v>
+      </c>
+      <c r="B206">
+        <v>1</v>
+      </c>
+      <c r="C206" t="s">
+        <v>91</v>
+      </c>
+      <c r="D206">
+        <v>16</v>
+      </c>
+      <c r="E206">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" t="s">
+        <v>73</v>
+      </c>
+      <c r="B207">
+        <v>2</v>
+      </c>
+      <c r="C207" t="s">
+        <v>91</v>
+      </c>
+      <c r="D207">
+        <v>34</v>
+      </c>
+      <c r="E207">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" t="s">
+        <v>73</v>
+      </c>
+      <c r="B208">
+        <v>3</v>
+      </c>
+      <c r="C208" t="s">
+        <v>91</v>
+      </c>
+      <c r="D208">
+        <v>12</v>
+      </c>
+      <c r="E208">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" t="s">
+        <v>73</v>
+      </c>
+      <c r="B209">
+        <v>4</v>
+      </c>
+      <c r="C209" t="s">
+        <v>91</v>
+      </c>
+      <c r="D209">
+        <v>28</v>
+      </c>
+      <c r="E209">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" t="s">
+        <v>73</v>
+      </c>
+      <c r="B210">
+        <v>5</v>
+      </c>
+      <c r="C210" t="s">
+        <v>91</v>
+      </c>
+      <c r="D210">
+        <v>16</v>
+      </c>
+      <c r="E210">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" t="s">
+        <v>73</v>
+      </c>
+      <c r="B211">
+        <v>6</v>
+      </c>
+      <c r="C211" t="s">
+        <v>91</v>
+      </c>
+      <c r="D211">
+        <v>9</v>
+      </c>
+      <c r="E211">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" t="s">
+        <v>73</v>
+      </c>
+      <c r="B212">
+        <v>7</v>
+      </c>
+      <c r="C212" t="s">
+        <v>91</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" t="s">
+        <v>73</v>
+      </c>
+      <c r="B213">
+        <v>8</v>
+      </c>
+      <c r="C213" t="s">
+        <v>91</v>
+      </c>
+      <c r="D213">
+        <v>21</v>
+      </c>
+      <c r="E213">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" t="s">
+        <v>73</v>
+      </c>
+      <c r="B214">
+        <v>9</v>
+      </c>
+      <c r="C214" t="s">
+        <v>91</v>
+      </c>
+      <c r="D214">
+        <v>5</v>
+      </c>
+      <c r="E214">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" t="s">
+        <v>73</v>
+      </c>
+      <c r="B215">
+        <v>10</v>
+      </c>
+      <c r="C215" t="s">
+        <v>91</v>
+      </c>
+      <c r="D215">
+        <v>23</v>
+      </c>
+      <c r="E215">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" t="s">
+        <v>73</v>
+      </c>
+      <c r="B216">
+        <v>11</v>
+      </c>
+      <c r="C216" t="s">
+        <v>91</v>
+      </c>
+      <c r="D216">
+        <v>6</v>
+      </c>
+      <c r="E216">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" t="s">
+        <v>73</v>
+      </c>
+      <c r="B217">
+        <v>12</v>
+      </c>
+      <c r="C217" t="s">
+        <v>91</v>
+      </c>
+      <c r="D217">
+        <v>23</v>
+      </c>
+      <c r="E217">
+        <v>212</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/2022_04_29 PWC Challenge 1 - Hotel Analytics/PWC Dashboard.xlsx
+++ b/2022_04_29 PWC Challenge 1 - Hotel Analytics/PWC Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seoul\Dropbox\00 technical\github\kimep-data-science-lab\2022_04_29 PWC Challenge 1 - Hotel Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40FDD92-024C-418D-B95D-3C5F09D10D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF621287-69B4-4783-8982-5553D9A1A387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="4" activeTab="7" xr2:uid="{AACBAEBD-F012-4269-A3B9-168C8D706687}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="4" activeTab="6" xr2:uid="{AACBAEBD-F012-4269-A3B9-168C8D706687}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="5" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="Concerns" sheetId="8" r:id="rId4"/>
     <sheet name="Concerns Dash" sheetId="6" r:id="rId5"/>
     <sheet name="Revenue - Data" sheetId="2" r:id="rId6"/>
-    <sheet name="Concerns barplot Data" sheetId="4" r:id="rId7"/>
-    <sheet name="Concerns dash data" sheetId="9" r:id="rId8"/>
+    <sheet name="Concerns dash data" sheetId="9" r:id="rId7"/>
+    <sheet name="Concerns barplot Data" sheetId="4" r:id="rId8"/>
     <sheet name="Validation" sheetId="3" r:id="rId9"/>
   </sheets>
   <externalReferences>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="102">
   <si>
     <t>Month</t>
   </si>
@@ -15584,21 +15584,24 @@
     </row>
     <row r="3" spans="2:10" ht="29" thickBot="1">
       <c r="B3" s="28" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C3" s="29"/>
       <c r="D3" s="29"/>
       <c r="E3" s="30"/>
     </row>
     <row r="5" spans="2:10" ht="18.5">
-      <c r="B5" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>3</v>
+      <c r="B5" s="6" t="str">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!C2,IF($B$3="King",'Revenue - Data'!M13,IF($B$3="Superior King",'Revenue - Data'!M25,IF($B$3="Executive",'Revenue - Data'!M37,IF($B$3="One Club",'Revenue - Data'!M49,'Revenue - Data'!M61)))))</f>
+        <v>Faulty electronics</v>
+      </c>
+      <c r="C5" s="6" t="str">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N1,IF($B$3="King",'Revenue - Data'!N13,IF($B$3="Superior King",'Revenue - Data'!N25,IF($B$3="Executive",'Revenue - Data'!N37,IF($B$3="One Club",'Revenue - Data'!N49,'Revenue - Data'!N61)))))</f>
+        <v>PercentFood</v>
+      </c>
+      <c r="D5" s="6" t="str">
+        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O1,IF($B$3="King",'Revenue - Data'!O13,IF($B$3="Superior King",'Revenue - Data'!O25,IF($B$3="Executive",'Revenue - Data'!O37,IF($B$3="One Club",'Revenue - Data'!O49,'Revenue - Data'!O61)))))</f>
+        <v>PercentBar</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>0</v>
@@ -15608,15 +15611,15 @@
     <row r="6" spans="2:10" ht="15.5">
       <c r="B6" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M2,IF($B$3="King",'Revenue - Data'!M14,IF($B$3="Superior King",'Revenue - Data'!M26,IF($B$3="Executive",'Revenue - Data'!M38,IF($B$3="One Club",'Revenue - Data'!M50,'Revenue - Data'!M62)))))</f>
-        <v>0.96875</v>
+        <v>0.95798319327731096</v>
       </c>
       <c r="C6" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N2,IF($B$3="King",'Revenue - Data'!N14,IF($B$3="Superior King",'Revenue - Data'!N26,IF($B$3="Executive",'Revenue - Data'!N38,IF($B$3="One Club",'Revenue - Data'!N50,'Revenue - Data'!N62)))))</f>
-        <v>0.4055121527777778</v>
+        <v>0.4710706504824152</v>
       </c>
       <c r="D6" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O2,IF($B$3="King",'Revenue - Data'!O14,IF($B$3="Superior King",'Revenue - Data'!O26,IF($B$3="Executive",'Revenue - Data'!O38,IF($B$3="One Club",'Revenue - Data'!O50,'Revenue - Data'!O62)))))</f>
-        <v>0.79166666666666663</v>
+        <v>0.85154061624649857</v>
       </c>
       <c r="E6" s="7">
         <v>1</v>
@@ -15628,15 +15631,15 @@
     <row r="7" spans="2:10" ht="15.5">
       <c r="B7" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M3,IF($B$3="King",'Revenue - Data'!M15,IF($B$3="Superior King",'Revenue - Data'!M27,IF($B$3="Executive",'Revenue - Data'!M39,IF($B$3="One Club",'Revenue - Data'!M51,'Revenue - Data'!M63)))))</f>
-        <v>1.0119047619047619</v>
+        <v>0.9732142857142857</v>
       </c>
       <c r="C7" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N3,IF($B$3="King",'Revenue - Data'!N15,IF($B$3="Superior King",'Revenue - Data'!N27,IF($B$3="Executive",'Revenue - Data'!N39,IF($B$3="One Club",'Revenue - Data'!N51,'Revenue - Data'!N63)))))</f>
-        <v>0.29181547619047621</v>
+        <v>0.42544973544973547</v>
       </c>
       <c r="D7" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O3,IF($B$3="King",'Revenue - Data'!O15,IF($B$3="Superior King",'Revenue - Data'!O27,IF($B$3="Executive",'Revenue - Data'!O39,IF($B$3="One Club",'Revenue - Data'!O51,'Revenue - Data'!O63)))))</f>
-        <v>0.52802579365079361</v>
+        <v>0.86908068783068781</v>
       </c>
       <c r="E7" s="7">
         <v>2</v>
@@ -15648,15 +15651,15 @@
     <row r="8" spans="2:10" ht="15.5">
       <c r="B8" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M4,IF($B$3="King",'Revenue - Data'!M16,IF($B$3="Superior King",'Revenue - Data'!M28,IF($B$3="Executive",'Revenue - Data'!M40,IF($B$3="One Club",'Revenue - Data'!M52,'Revenue - Data'!M64)))))</f>
-        <v>0.89583333333333337</v>
+        <v>0.92729591836734693</v>
       </c>
       <c r="C8" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N4,IF($B$3="King",'Revenue - Data'!N16,IF($B$3="Superior King",'Revenue - Data'!N28,IF($B$3="Executive",'Revenue - Data'!N40,IF($B$3="One Club",'Revenue - Data'!N52,'Revenue - Data'!N64)))))</f>
-        <v>0.21289682539682539</v>
+        <v>0.43664965986394561</v>
       </c>
       <c r="D8" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O4,IF($B$3="King",'Revenue - Data'!O16,IF($B$3="Superior King",'Revenue - Data'!O28,IF($B$3="Executive",'Revenue - Data'!O40,IF($B$3="One Club",'Revenue - Data'!O52,'Revenue - Data'!O64)))))</f>
-        <v>0.54389880952380953</v>
+        <v>1.0997555272108843</v>
       </c>
       <c r="E8" s="7">
         <v>3</v>
@@ -15668,15 +15671,15 @@
     <row r="9" spans="2:10" ht="15.5">
       <c r="B9" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M5,IF($B$3="King",'Revenue - Data'!M17,IF($B$3="Superior King",'Revenue - Data'!M29,IF($B$3="Executive",'Revenue - Data'!M41,IF($B$3="One Club",'Revenue - Data'!M53,'Revenue - Data'!M65)))))</f>
-        <v>0.68888888888888888</v>
+        <v>0.99068322981366463</v>
       </c>
       <c r="C9" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N5,IF($B$3="King",'Revenue - Data'!N17,IF($B$3="Superior King",'Revenue - Data'!N29,IF($B$3="Executive",'Revenue - Data'!N41,IF($B$3="One Club",'Revenue - Data'!N53,'Revenue - Data'!N65)))))</f>
-        <v>0.11037037037037037</v>
+        <v>0.32637163561076604</v>
       </c>
       <c r="D9" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O5,IF($B$3="King",'Revenue - Data'!O17,IF($B$3="Superior King",'Revenue - Data'!O29,IF($B$3="Executive",'Revenue - Data'!O41,IF($B$3="One Club",'Revenue - Data'!O53,'Revenue - Data'!O65)))))</f>
-        <v>0.31732804232804235</v>
+        <v>1.132214026915114</v>
       </c>
       <c r="E9" s="7">
         <v>4</v>
@@ -15688,15 +15691,15 @@
     <row r="10" spans="2:10" ht="15.5">
       <c r="B10" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M6,IF($B$3="King",'Revenue - Data'!M18,IF($B$3="Superior King",'Revenue - Data'!M30,IF($B$3="Executive",'Revenue - Data'!M42,IF($B$3="One Club",'Revenue - Data'!M54,'Revenue - Data'!M66)))))</f>
-        <v>0.95333333333333337</v>
+        <v>1.0285714285714285</v>
       </c>
       <c r="C10" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N6,IF($B$3="King",'Revenue - Data'!N18,IF($B$3="Superior King",'Revenue - Data'!N30,IF($B$3="Executive",'Revenue - Data'!N42,IF($B$3="One Club",'Revenue - Data'!N54,'Revenue - Data'!N66)))))</f>
-        <v>0.18450793650793651</v>
+        <v>0.19396428571428573</v>
       </c>
       <c r="D10" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O6,IF($B$3="King",'Revenue - Data'!O18,IF($B$3="Superior King",'Revenue - Data'!O30,IF($B$3="Executive",'Revenue - Data'!O42,IF($B$3="One Club",'Revenue - Data'!O54,'Revenue - Data'!O66)))))</f>
-        <v>0.96047619047619048</v>
+        <v>0.93348214285714282</v>
       </c>
       <c r="E10" s="7">
         <v>5</v>
@@ -15708,15 +15711,15 @@
     <row r="11" spans="2:10" ht="15.5">
       <c r="B11" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M7,IF($B$3="King",'Revenue - Data'!M19,IF($B$3="Superior King",'Revenue - Data'!M31,IF($B$3="Executive",'Revenue - Data'!M43,IF($B$3="One Club",'Revenue - Data'!M55,'Revenue - Data'!M67)))))</f>
-        <v>0.87037037037037035</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="C11" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N7,IF($B$3="King",'Revenue - Data'!N19,IF($B$3="Superior King",'Revenue - Data'!N31,IF($B$3="Executive",'Revenue - Data'!N43,IF($B$3="One Club",'Revenue - Data'!N55,'Revenue - Data'!N67)))))</f>
-        <v>8.4104938271604937E-2</v>
+        <v>9.9029982363315699E-2</v>
       </c>
       <c r="D11" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O7,IF($B$3="King",'Revenue - Data'!O19,IF($B$3="Superior King",'Revenue - Data'!O31,IF($B$3="Executive",'Revenue - Data'!O43,IF($B$3="One Club",'Revenue - Data'!O55,'Revenue - Data'!O67)))))</f>
-        <v>0.59924768518518523</v>
+        <v>0.79574514991181655</v>
       </c>
       <c r="E11" s="7">
         <v>6</v>
@@ -15728,15 +15731,15 @@
     <row r="12" spans="2:10" ht="15.5">
       <c r="B12" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M8,IF($B$3="King",'Revenue - Data'!M20,IF($B$3="Superior King",'Revenue - Data'!M32,IF($B$3="Executive",'Revenue - Data'!M44,IF($B$3="One Club",'Revenue - Data'!M56,'Revenue - Data'!M68)))))</f>
-        <v>0.94</v>
+        <v>1.0012755102040816</v>
       </c>
       <c r="C12" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N8,IF($B$3="King",'Revenue - Data'!N20,IF($B$3="Superior King",'Revenue - Data'!N32,IF($B$3="Executive",'Revenue - Data'!N44,IF($B$3="One Club",'Revenue - Data'!N56,'Revenue - Data'!N68)))))</f>
-        <v>0.88180555555555551</v>
+        <v>1.1167044595616025</v>
       </c>
       <c r="D12" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O8,IF($B$3="King",'Revenue - Data'!O20,IF($B$3="Superior King",'Revenue - Data'!O32,IF($B$3="Executive",'Revenue - Data'!O44,IF($B$3="One Club",'Revenue - Data'!O56,'Revenue - Data'!O68)))))</f>
-        <v>0.86236111111111113</v>
+        <v>1.1552343159486016</v>
       </c>
       <c r="E12" s="7">
         <v>7</v>
@@ -15748,15 +15751,15 @@
     <row r="13" spans="2:10" ht="15.5">
       <c r="B13" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M9,IF($B$3="King",'Revenue - Data'!M21,IF($B$3="Superior King",'Revenue - Data'!M33,IF($B$3="Executive",'Revenue - Data'!M45,IF($B$3="One Club",'Revenue - Data'!M57,'Revenue - Data'!M69)))))</f>
-        <v>1.1933333333333334</v>
+        <v>1.0127551020408163</v>
       </c>
       <c r="C13" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N9,IF($B$3="King",'Revenue - Data'!N21,IF($B$3="Superior King",'Revenue - Data'!N33,IF($B$3="Executive",'Revenue - Data'!N45,IF($B$3="One Club",'Revenue - Data'!N57,'Revenue - Data'!N69)))))</f>
-        <v>1.4589722222222221</v>
+        <v>1.0267668178382463</v>
       </c>
       <c r="D13" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O9,IF($B$3="King",'Revenue - Data'!O21,IF($B$3="Superior King",'Revenue - Data'!O33,IF($B$3="Executive",'Revenue - Data'!O45,IF($B$3="One Club",'Revenue - Data'!O57,'Revenue - Data'!O69)))))</f>
-        <v>1.153125</v>
+        <v>1.0101568405139834</v>
       </c>
       <c r="E13" s="7">
         <v>8</v>
@@ -15768,15 +15771,15 @@
     <row r="14" spans="2:10" ht="15.5">
       <c r="B14" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M10,IF($B$3="King",'Revenue - Data'!M22,IF($B$3="Superior King",'Revenue - Data'!M34,IF($B$3="Executive",'Revenue - Data'!M46,IF($B$3="One Club",'Revenue - Data'!M58,'Revenue - Data'!M70)))))</f>
-        <v>0.92361111111111116</v>
+        <v>0.96768707482993199</v>
       </c>
       <c r="C14" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N10,IF($B$3="King",'Revenue - Data'!N22,IF($B$3="Superior King",'Revenue - Data'!N34,IF($B$3="Executive",'Revenue - Data'!N46,IF($B$3="One Club",'Revenue - Data'!N58,'Revenue - Data'!N70)))))</f>
-        <v>1.0264219576719578</v>
+        <v>0.99092970521541945</v>
       </c>
       <c r="D14" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O10,IF($B$3="King",'Revenue - Data'!O22,IF($B$3="Superior King",'Revenue - Data'!O34,IF($B$3="Executive",'Revenue - Data'!O46,IF($B$3="One Club",'Revenue - Data'!O58,'Revenue - Data'!O70)))))</f>
-        <v>0.85945767195767198</v>
+        <v>0.87673611111111116</v>
       </c>
       <c r="E14" s="7">
         <v>9</v>
@@ -15788,15 +15791,15 @@
     <row r="15" spans="2:10" ht="15.5">
       <c r="B15" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M11,IF($B$3="King",'Revenue - Data'!M23,IF($B$3="Superior King",'Revenue - Data'!M35,IF($B$3="Executive",'Revenue - Data'!M47,IF($B$3="One Club",'Revenue - Data'!M59,'Revenue - Data'!M71)))))</f>
-        <v>0.93181818181818177</v>
+        <v>0.98913043478260865</v>
       </c>
       <c r="C15" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N11,IF($B$3="King",'Revenue - Data'!N23,IF($B$3="Superior King",'Revenue - Data'!N35,IF($B$3="Executive",'Revenue - Data'!N47,IF($B$3="One Club",'Revenue - Data'!N59,'Revenue - Data'!N71)))))</f>
-        <v>0.67572601010101008</v>
+        <v>0.99608925695882222</v>
       </c>
       <c r="D15" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O11,IF($B$3="King",'Revenue - Data'!O23,IF($B$3="Superior King",'Revenue - Data'!O35,IF($B$3="Executive",'Revenue - Data'!O47,IF($B$3="One Club",'Revenue - Data'!O59,'Revenue - Data'!O71)))))</f>
-        <v>0.77541035353535348</v>
+        <v>0.9511732229123534</v>
       </c>
       <c r="E15" s="7">
         <v>10</v>
@@ -15808,15 +15811,15 @@
     <row r="16" spans="2:10" ht="15.5">
       <c r="B16" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M12,IF($B$3="King",'Revenue - Data'!M24,IF($B$3="Superior King",'Revenue - Data'!M36,IF($B$3="Executive",'Revenue - Data'!M48,IF($B$3="One Club",'Revenue - Data'!M60,'Revenue - Data'!M72)))))</f>
-        <v>0.9907407407407407</v>
+        <v>1</v>
       </c>
       <c r="C16" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N12,IF($B$3="King",'Revenue - Data'!N24,IF($B$3="Superior King",'Revenue - Data'!N36,IF($B$3="Executive",'Revenue - Data'!N48,IF($B$3="One Club",'Revenue - Data'!N60,'Revenue - Data'!N72)))))</f>
-        <v>1.0784336419753087</v>
+        <v>0.96484126984126983</v>
       </c>
       <c r="D16" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O12,IF($B$3="King",'Revenue - Data'!O24,IF($B$3="Superior King",'Revenue - Data'!O36,IF($B$3="Executive",'Revenue - Data'!O48,IF($B$3="One Club",'Revenue - Data'!O60,'Revenue - Data'!O72)))))</f>
-        <v>0.99807098765432101</v>
+        <v>0.92685185185185182</v>
       </c>
       <c r="E16" s="7">
         <v>11</v>
@@ -15828,15 +15831,15 @@
     <row r="17" spans="2:10" ht="15.5">
       <c r="B17" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M13,IF($B$3="King",'Revenue - Data'!M25,IF($B$3="Superior King",'Revenue - Data'!M37,IF($B$3="Executive",'Revenue - Data'!M49,IF($B$3="One Club",'Revenue - Data'!M61,'Revenue - Data'!M73)))))</f>
-        <v>0.86842105263157898</v>
+        <v>0.95676691729323304</v>
       </c>
       <c r="C17" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N13,IF($B$3="King",'Revenue - Data'!N25,IF($B$3="Superior King",'Revenue - Data'!N37,IF($B$3="Executive",'Revenue - Data'!N49,IF($B$3="One Club",'Revenue - Data'!N61,'Revenue - Data'!N73)))))</f>
-        <v>0.68479532163742685</v>
+        <v>0.78618740729374459</v>
       </c>
       <c r="D17" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O13,IF($B$3="King",'Revenue - Data'!O25,IF($B$3="Superior King",'Revenue - Data'!O37,IF($B$3="Executive",'Revenue - Data'!O49,IF($B$3="One Club",'Revenue - Data'!O61,'Revenue - Data'!O73)))))</f>
-        <v>0.70175438596491224</v>
+        <v>0.80911881314746126</v>
       </c>
       <c r="E17" s="7">
         <v>12</v>
@@ -19664,6 +19667,3714 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{292D24D9-B7AF-4404-B87D-6D3347D4D37D}">
+  <dimension ref="A1:E217"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="5" width="21.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4">
+        <v>13</v>
+      </c>
+      <c r="E4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10">
+        <v>12</v>
+      </c>
+      <c r="E10">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+      <c r="E11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21">
+        <v>7</v>
+      </c>
+      <c r="E21">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26">
+        <v>7</v>
+      </c>
+      <c r="E26">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30">
+        <v>6</v>
+      </c>
+      <c r="E30">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33">
+        <v>11</v>
+      </c>
+      <c r="C33" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36">
+        <v>5</v>
+      </c>
+      <c r="E36">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38">
+        <v>6</v>
+      </c>
+      <c r="E38">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40">
+        <v>6</v>
+      </c>
+      <c r="E40">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42">
+        <v>7</v>
+      </c>
+      <c r="E42">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
+      </c>
+      <c r="C44" t="s">
+        <v>88</v>
+      </c>
+      <c r="D44">
+        <v>5</v>
+      </c>
+      <c r="E44">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45">
+        <v>3</v>
+      </c>
+      <c r="C45" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46">
+        <v>3</v>
+      </c>
+      <c r="C46" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46">
+        <v>10</v>
+      </c>
+      <c r="E46">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>69</v>
+      </c>
+      <c r="B47">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="E47">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>91</v>
+      </c>
+      <c r="D48">
+        <v>5</v>
+      </c>
+      <c r="E48">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>89</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50">
+        <v>7</v>
+      </c>
+      <c r="E50">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51">
+        <v>6</v>
+      </c>
+      <c r="E51">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52">
+        <v>5</v>
+      </c>
+      <c r="C52" t="s">
+        <v>89</v>
+      </c>
+      <c r="D52">
+        <v>2</v>
+      </c>
+      <c r="E52">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53">
+        <v>6</v>
+      </c>
+      <c r="C53" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53">
+        <v>2</v>
+      </c>
+      <c r="E53">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55">
+        <v>6</v>
+      </c>
+      <c r="C55" t="s">
+        <v>89</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>88</v>
+      </c>
+      <c r="D56">
+        <v>6</v>
+      </c>
+      <c r="E56">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s">
+        <v>91</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58">
+        <v>2</v>
+      </c>
+      <c r="E58">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>88</v>
+      </c>
+      <c r="D59">
+        <v>3</v>
+      </c>
+      <c r="E59">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60">
+        <v>8</v>
+      </c>
+      <c r="C60" t="s">
+        <v>91</v>
+      </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61">
+        <v>8</v>
+      </c>
+      <c r="C61" t="s">
+        <v>89</v>
+      </c>
+      <c r="D61">
+        <v>5</v>
+      </c>
+      <c r="E61">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63">
+        <v>9</v>
+      </c>
+      <c r="C63" t="s">
+        <v>91</v>
+      </c>
+      <c r="D63">
+        <v>3</v>
+      </c>
+      <c r="E63">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64">
+        <v>9</v>
+      </c>
+      <c r="C64" t="s">
+        <v>89</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s">
+        <v>88</v>
+      </c>
+      <c r="D65">
+        <v>4</v>
+      </c>
+      <c r="E65">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66">
+        <v>10</v>
+      </c>
+      <c r="C66" t="s">
+        <v>91</v>
+      </c>
+      <c r="D66">
+        <v>4</v>
+      </c>
+      <c r="E66">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67">
+        <v>10</v>
+      </c>
+      <c r="C67" t="s">
+        <v>89</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+      <c r="E67">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68">
+        <v>11</v>
+      </c>
+      <c r="C68" t="s">
+        <v>88</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69">
+        <v>11</v>
+      </c>
+      <c r="C69" t="s">
+        <v>91</v>
+      </c>
+      <c r="D69">
+        <v>5</v>
+      </c>
+      <c r="E69">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>89</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <v>12</v>
+      </c>
+      <c r="C71" t="s">
+        <v>88</v>
+      </c>
+      <c r="D71">
+        <v>3</v>
+      </c>
+      <c r="E71">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>69</v>
+      </c>
+      <c r="B72">
+        <v>12</v>
+      </c>
+      <c r="C72" t="s">
+        <v>91</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+      <c r="E72">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>69</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>89</v>
+      </c>
+      <c r="D73">
+        <v>6</v>
+      </c>
+      <c r="E73">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
+        <v>97</v>
+      </c>
+      <c r="D74">
+        <v>4</v>
+      </c>
+      <c r="E74">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
+        <v>91</v>
+      </c>
+      <c r="D75">
+        <v>17</v>
+      </c>
+      <c r="E75">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>70</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>95</v>
+      </c>
+      <c r="D76">
+        <v>11</v>
+      </c>
+      <c r="E76">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>70</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77" t="s">
+        <v>97</v>
+      </c>
+      <c r="D77">
+        <v>2</v>
+      </c>
+      <c r="E77">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>70</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>91</v>
+      </c>
+      <c r="D78">
+        <v>13</v>
+      </c>
+      <c r="E78">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>70</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79" t="s">
+        <v>95</v>
+      </c>
+      <c r="D79">
+        <v>8</v>
+      </c>
+      <c r="E79">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>70</v>
+      </c>
+      <c r="B80">
+        <v>3</v>
+      </c>
+      <c r="C80" t="s">
+        <v>97</v>
+      </c>
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>70</v>
+      </c>
+      <c r="B81">
+        <v>3</v>
+      </c>
+      <c r="C81" t="s">
+        <v>91</v>
+      </c>
+      <c r="D81">
+        <v>14</v>
+      </c>
+      <c r="E81">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>70</v>
+      </c>
+      <c r="B82">
+        <v>3</v>
+      </c>
+      <c r="C82" t="s">
+        <v>95</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+      <c r="E82">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>70</v>
+      </c>
+      <c r="B83">
+        <v>4</v>
+      </c>
+      <c r="C83" t="s">
+        <v>97</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+      <c r="E83">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>70</v>
+      </c>
+      <c r="B84">
+        <v>4</v>
+      </c>
+      <c r="C84" t="s">
+        <v>91</v>
+      </c>
+      <c r="D84">
+        <v>8</v>
+      </c>
+      <c r="E84">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>70</v>
+      </c>
+      <c r="B85">
+        <v>4</v>
+      </c>
+      <c r="C85" t="s">
+        <v>95</v>
+      </c>
+      <c r="D85">
+        <v>3</v>
+      </c>
+      <c r="E85">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>70</v>
+      </c>
+      <c r="B86">
+        <v>5</v>
+      </c>
+      <c r="C86" t="s">
+        <v>97</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>70</v>
+      </c>
+      <c r="B87">
+        <v>5</v>
+      </c>
+      <c r="C87" t="s">
+        <v>91</v>
+      </c>
+      <c r="D87">
+        <v>3</v>
+      </c>
+      <c r="E87">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>70</v>
+      </c>
+      <c r="B88">
+        <v>5</v>
+      </c>
+      <c r="C88" t="s">
+        <v>95</v>
+      </c>
+      <c r="D88">
+        <v>5</v>
+      </c>
+      <c r="E88">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>70</v>
+      </c>
+      <c r="B89">
+        <v>6</v>
+      </c>
+      <c r="C89" t="s">
+        <v>97</v>
+      </c>
+      <c r="D89">
+        <v>2</v>
+      </c>
+      <c r="E89">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>70</v>
+      </c>
+      <c r="B90">
+        <v>6</v>
+      </c>
+      <c r="C90" t="s">
+        <v>91</v>
+      </c>
+      <c r="D90">
+        <v>3</v>
+      </c>
+      <c r="E90">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>70</v>
+      </c>
+      <c r="B91">
+        <v>6</v>
+      </c>
+      <c r="C91" t="s">
+        <v>95</v>
+      </c>
+      <c r="D91">
+        <v>2</v>
+      </c>
+      <c r="E91">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>70</v>
+      </c>
+      <c r="B92">
+        <v>7</v>
+      </c>
+      <c r="C92" t="s">
+        <v>97</v>
+      </c>
+      <c r="D92">
+        <v>56</v>
+      </c>
+      <c r="E92">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>70</v>
+      </c>
+      <c r="B93">
+        <v>7</v>
+      </c>
+      <c r="C93" t="s">
+        <v>91</v>
+      </c>
+      <c r="D93">
+        <v>6</v>
+      </c>
+      <c r="E93">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>70</v>
+      </c>
+      <c r="B94">
+        <v>7</v>
+      </c>
+      <c r="C94" t="s">
+        <v>95</v>
+      </c>
+      <c r="D94">
+        <v>5</v>
+      </c>
+      <c r="E94">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>70</v>
+      </c>
+      <c r="B95">
+        <v>8</v>
+      </c>
+      <c r="C95" t="s">
+        <v>97</v>
+      </c>
+      <c r="D95">
+        <v>71</v>
+      </c>
+      <c r="E95">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>70</v>
+      </c>
+      <c r="B96">
+        <v>8</v>
+      </c>
+      <c r="C96" t="s">
+        <v>91</v>
+      </c>
+      <c r="D96">
+        <v>8</v>
+      </c>
+      <c r="E96">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>70</v>
+      </c>
+      <c r="B97">
+        <v>8</v>
+      </c>
+      <c r="C97" t="s">
+        <v>95</v>
+      </c>
+      <c r="D97">
+        <v>2</v>
+      </c>
+      <c r="E97">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>70</v>
+      </c>
+      <c r="B98">
+        <v>9</v>
+      </c>
+      <c r="C98" t="s">
+        <v>97</v>
+      </c>
+      <c r="D98">
+        <v>97</v>
+      </c>
+      <c r="E98">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>70</v>
+      </c>
+      <c r="B99">
+        <v>9</v>
+      </c>
+      <c r="C99" t="s">
+        <v>91</v>
+      </c>
+      <c r="D99">
+        <v>8</v>
+      </c>
+      <c r="E99">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>70</v>
+      </c>
+      <c r="B100">
+        <v>9</v>
+      </c>
+      <c r="C100" t="s">
+        <v>95</v>
+      </c>
+      <c r="D100">
+        <v>5</v>
+      </c>
+      <c r="E100">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>70</v>
+      </c>
+      <c r="B101">
+        <v>10</v>
+      </c>
+      <c r="C101" t="s">
+        <v>97</v>
+      </c>
+      <c r="D101">
+        <v>50</v>
+      </c>
+      <c r="E101">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>70</v>
+      </c>
+      <c r="B102">
+        <v>10</v>
+      </c>
+      <c r="C102" t="s">
+        <v>91</v>
+      </c>
+      <c r="D102">
+        <v>3</v>
+      </c>
+      <c r="E102">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>70</v>
+      </c>
+      <c r="B103">
+        <v>10</v>
+      </c>
+      <c r="C103" t="s">
+        <v>95</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>70</v>
+      </c>
+      <c r="B104">
+        <v>11</v>
+      </c>
+      <c r="C104" t="s">
+        <v>97</v>
+      </c>
+      <c r="D104">
+        <v>52</v>
+      </c>
+      <c r="E104">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>70</v>
+      </c>
+      <c r="B105">
+        <v>11</v>
+      </c>
+      <c r="C105" t="s">
+        <v>91</v>
+      </c>
+      <c r="D105">
+        <v>5</v>
+      </c>
+      <c r="E105">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>70</v>
+      </c>
+      <c r="B106">
+        <v>11</v>
+      </c>
+      <c r="C106" t="s">
+        <v>95</v>
+      </c>
+      <c r="D106">
+        <v>3</v>
+      </c>
+      <c r="E106">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>70</v>
+      </c>
+      <c r="B107">
+        <v>12</v>
+      </c>
+      <c r="C107" t="s">
+        <v>97</v>
+      </c>
+      <c r="D107">
+        <v>54</v>
+      </c>
+      <c r="E107">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>70</v>
+      </c>
+      <c r="B108">
+        <v>12</v>
+      </c>
+      <c r="C108" t="s">
+        <v>91</v>
+      </c>
+      <c r="D108">
+        <v>5</v>
+      </c>
+      <c r="E108">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>70</v>
+      </c>
+      <c r="B109">
+        <v>12</v>
+      </c>
+      <c r="C109" t="s">
+        <v>95</v>
+      </c>
+      <c r="D109">
+        <v>1</v>
+      </c>
+      <c r="E109">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>71</v>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
+        <v>88</v>
+      </c>
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>71</v>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111" t="s">
+        <v>90</v>
+      </c>
+      <c r="D111">
+        <v>6</v>
+      </c>
+      <c r="E111">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>71</v>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112" t="s">
+        <v>89</v>
+      </c>
+      <c r="D112">
+        <v>2</v>
+      </c>
+      <c r="E112">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>71</v>
+      </c>
+      <c r="B113">
+        <v>2</v>
+      </c>
+      <c r="C113" t="s">
+        <v>88</v>
+      </c>
+      <c r="D113">
+        <v>5</v>
+      </c>
+      <c r="E113">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>71</v>
+      </c>
+      <c r="B114">
+        <v>2</v>
+      </c>
+      <c r="C114" t="s">
+        <v>90</v>
+      </c>
+      <c r="D114">
+        <v>3</v>
+      </c>
+      <c r="E114">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>71</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+      <c r="C115" t="s">
+        <v>89</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+      <c r="E115">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>71</v>
+      </c>
+      <c r="B116">
+        <v>3</v>
+      </c>
+      <c r="C116" t="s">
+        <v>88</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
+        <v>71</v>
+      </c>
+      <c r="B117">
+        <v>3</v>
+      </c>
+      <c r="C117" t="s">
+        <v>90</v>
+      </c>
+      <c r="D117">
+        <v>3</v>
+      </c>
+      <c r="E117">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
+        <v>71</v>
+      </c>
+      <c r="B118">
+        <v>3</v>
+      </c>
+      <c r="C118" t="s">
+        <v>89</v>
+      </c>
+      <c r="D118">
+        <v>3</v>
+      </c>
+      <c r="E118">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
+        <v>71</v>
+      </c>
+      <c r="B119">
+        <v>4</v>
+      </c>
+      <c r="C119" t="s">
+        <v>88</v>
+      </c>
+      <c r="D119">
+        <v>2</v>
+      </c>
+      <c r="E119">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
+        <v>71</v>
+      </c>
+      <c r="B120">
+        <v>4</v>
+      </c>
+      <c r="C120" t="s">
+        <v>90</v>
+      </c>
+      <c r="D120">
+        <v>2</v>
+      </c>
+      <c r="E120">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
+        <v>71</v>
+      </c>
+      <c r="B121">
+        <v>4</v>
+      </c>
+      <c r="C121" t="s">
+        <v>89</v>
+      </c>
+      <c r="D121">
+        <v>3</v>
+      </c>
+      <c r="E121">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" t="s">
+        <v>71</v>
+      </c>
+      <c r="B122">
+        <v>5</v>
+      </c>
+      <c r="C122" t="s">
+        <v>88</v>
+      </c>
+      <c r="D122">
+        <v>4</v>
+      </c>
+      <c r="E122">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" t="s">
+        <v>71</v>
+      </c>
+      <c r="B123">
+        <v>5</v>
+      </c>
+      <c r="C123" t="s">
+        <v>90</v>
+      </c>
+      <c r="D123">
+        <v>3</v>
+      </c>
+      <c r="E123">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" t="s">
+        <v>71</v>
+      </c>
+      <c r="B124">
+        <v>5</v>
+      </c>
+      <c r="C124" t="s">
+        <v>89</v>
+      </c>
+      <c r="D124">
+        <v>3</v>
+      </c>
+      <c r="E124">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" t="s">
+        <v>71</v>
+      </c>
+      <c r="B125">
+        <v>6</v>
+      </c>
+      <c r="C125" t="s">
+        <v>88</v>
+      </c>
+      <c r="D125">
+        <v>1</v>
+      </c>
+      <c r="E125">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" t="s">
+        <v>71</v>
+      </c>
+      <c r="B126">
+        <v>6</v>
+      </c>
+      <c r="C126" t="s">
+        <v>90</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" t="s">
+        <v>71</v>
+      </c>
+      <c r="B127">
+        <v>6</v>
+      </c>
+      <c r="C127" t="s">
+        <v>89</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" t="s">
+        <v>71</v>
+      </c>
+      <c r="B128">
+        <v>7</v>
+      </c>
+      <c r="C128" t="s">
+        <v>88</v>
+      </c>
+      <c r="D128">
+        <v>6</v>
+      </c>
+      <c r="E128">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" t="s">
+        <v>71</v>
+      </c>
+      <c r="B129">
+        <v>7</v>
+      </c>
+      <c r="C129" t="s">
+        <v>90</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="E129">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" t="s">
+        <v>71</v>
+      </c>
+      <c r="B130">
+        <v>7</v>
+      </c>
+      <c r="C130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="E130">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" t="s">
+        <v>71</v>
+      </c>
+      <c r="B131">
+        <v>8</v>
+      </c>
+      <c r="C131" t="s">
+        <v>88</v>
+      </c>
+      <c r="D131">
+        <v>5</v>
+      </c>
+      <c r="E131">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" t="s">
+        <v>71</v>
+      </c>
+      <c r="B132">
+        <v>8</v>
+      </c>
+      <c r="C132" t="s">
+        <v>90</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" t="s">
+        <v>71</v>
+      </c>
+      <c r="B133">
+        <v>8</v>
+      </c>
+      <c r="C133" t="s">
+        <v>89</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+      <c r="E133">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" t="s">
+        <v>71</v>
+      </c>
+      <c r="B134">
+        <v>9</v>
+      </c>
+      <c r="C134" t="s">
+        <v>88</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" t="s">
+        <v>71</v>
+      </c>
+      <c r="B135">
+        <v>9</v>
+      </c>
+      <c r="C135" t="s">
+        <v>90</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" t="s">
+        <v>71</v>
+      </c>
+      <c r="B136">
+        <v>9</v>
+      </c>
+      <c r="C136" t="s">
+        <v>89</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" t="s">
+        <v>71</v>
+      </c>
+      <c r="B137">
+        <v>10</v>
+      </c>
+      <c r="C137" t="s">
+        <v>88</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" t="s">
+        <v>71</v>
+      </c>
+      <c r="B138">
+        <v>10</v>
+      </c>
+      <c r="C138" t="s">
+        <v>90</v>
+      </c>
+      <c r="D138">
+        <v>2</v>
+      </c>
+      <c r="E138">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" t="s">
+        <v>71</v>
+      </c>
+      <c r="B139">
+        <v>10</v>
+      </c>
+      <c r="C139" t="s">
+        <v>89</v>
+      </c>
+      <c r="D139">
+        <v>1</v>
+      </c>
+      <c r="E139">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" t="s">
+        <v>71</v>
+      </c>
+      <c r="B140">
+        <v>11</v>
+      </c>
+      <c r="C140" t="s">
+        <v>88</v>
+      </c>
+      <c r="D140">
+        <v>1</v>
+      </c>
+      <c r="E140">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" t="s">
+        <v>71</v>
+      </c>
+      <c r="B141">
+        <v>11</v>
+      </c>
+      <c r="C141" t="s">
+        <v>90</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" t="s">
+        <v>71</v>
+      </c>
+      <c r="B142">
+        <v>11</v>
+      </c>
+      <c r="C142" t="s">
+        <v>89</v>
+      </c>
+      <c r="D142">
+        <v>2</v>
+      </c>
+      <c r="E142">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" t="s">
+        <v>71</v>
+      </c>
+      <c r="B143">
+        <v>12</v>
+      </c>
+      <c r="C143" t="s">
+        <v>88</v>
+      </c>
+      <c r="D143">
+        <v>4</v>
+      </c>
+      <c r="E143">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" t="s">
+        <v>71</v>
+      </c>
+      <c r="B144">
+        <v>12</v>
+      </c>
+      <c r="C144" t="s">
+        <v>90</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="E144">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" t="s">
+        <v>71</v>
+      </c>
+      <c r="B145">
+        <v>12</v>
+      </c>
+      <c r="C145" t="s">
+        <v>89</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" t="s">
+        <v>72</v>
+      </c>
+      <c r="B146">
+        <v>1</v>
+      </c>
+      <c r="C146" t="s">
+        <v>90</v>
+      </c>
+      <c r="D146">
+        <v>6</v>
+      </c>
+      <c r="E146">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" t="s">
+        <v>72</v>
+      </c>
+      <c r="B147">
+        <v>1</v>
+      </c>
+      <c r="C147" t="s">
+        <v>89</v>
+      </c>
+      <c r="D147">
+        <v>1</v>
+      </c>
+      <c r="E147">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" t="s">
+        <v>72</v>
+      </c>
+      <c r="B148">
+        <v>1</v>
+      </c>
+      <c r="C148" t="s">
+        <v>88</v>
+      </c>
+      <c r="D148">
+        <v>2</v>
+      </c>
+      <c r="E148">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" t="s">
+        <v>72</v>
+      </c>
+      <c r="B149">
+        <v>2</v>
+      </c>
+      <c r="C149" t="s">
+        <v>90</v>
+      </c>
+      <c r="D149">
+        <v>8</v>
+      </c>
+      <c r="E149">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" t="s">
+        <v>72</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150" t="s">
+        <v>89</v>
+      </c>
+      <c r="D150">
+        <v>2</v>
+      </c>
+      <c r="E150">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" t="s">
+        <v>72</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151" t="s">
+        <v>88</v>
+      </c>
+      <c r="D151">
+        <v>3</v>
+      </c>
+      <c r="E151">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" t="s">
+        <v>72</v>
+      </c>
+      <c r="B152">
+        <v>3</v>
+      </c>
+      <c r="C152" t="s">
+        <v>90</v>
+      </c>
+      <c r="D152">
+        <v>5</v>
+      </c>
+      <c r="E152">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" t="s">
+        <v>72</v>
+      </c>
+      <c r="B153">
+        <v>3</v>
+      </c>
+      <c r="C153" t="s">
+        <v>89</v>
+      </c>
+      <c r="D153">
+        <v>3</v>
+      </c>
+      <c r="E153">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" t="s">
+        <v>72</v>
+      </c>
+      <c r="B154">
+        <v>3</v>
+      </c>
+      <c r="C154" t="s">
+        <v>88</v>
+      </c>
+      <c r="D154">
+        <v>1</v>
+      </c>
+      <c r="E154">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" t="s">
+        <v>72</v>
+      </c>
+      <c r="B155">
+        <v>4</v>
+      </c>
+      <c r="C155" t="s">
+        <v>90</v>
+      </c>
+      <c r="D155">
+        <v>4</v>
+      </c>
+      <c r="E155">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" t="s">
+        <v>72</v>
+      </c>
+      <c r="B156">
+        <v>4</v>
+      </c>
+      <c r="C156" t="s">
+        <v>89</v>
+      </c>
+      <c r="D156">
+        <v>2</v>
+      </c>
+      <c r="E156">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" t="s">
+        <v>72</v>
+      </c>
+      <c r="B157">
+        <v>4</v>
+      </c>
+      <c r="C157" t="s">
+        <v>88</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="E157">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" t="s">
+        <v>72</v>
+      </c>
+      <c r="B158">
+        <v>5</v>
+      </c>
+      <c r="C158" t="s">
+        <v>90</v>
+      </c>
+      <c r="D158">
+        <v>7</v>
+      </c>
+      <c r="E158">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B159">
+        <v>5</v>
+      </c>
+      <c r="C159" t="s">
+        <v>89</v>
+      </c>
+      <c r="D159">
+        <v>6</v>
+      </c>
+      <c r="E159">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" t="s">
+        <v>72</v>
+      </c>
+      <c r="B160">
+        <v>5</v>
+      </c>
+      <c r="C160" t="s">
+        <v>88</v>
+      </c>
+      <c r="D160">
+        <v>2</v>
+      </c>
+      <c r="E160">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" t="s">
+        <v>72</v>
+      </c>
+      <c r="B161">
+        <v>6</v>
+      </c>
+      <c r="C161" t="s">
+        <v>90</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="E161">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" t="s">
+        <v>72</v>
+      </c>
+      <c r="B162">
+        <v>6</v>
+      </c>
+      <c r="C162" t="s">
+        <v>89</v>
+      </c>
+      <c r="D162">
+        <v>2</v>
+      </c>
+      <c r="E162">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" t="s">
+        <v>72</v>
+      </c>
+      <c r="B163">
+        <v>6</v>
+      </c>
+      <c r="C163" t="s">
+        <v>88</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" t="s">
+        <v>72</v>
+      </c>
+      <c r="B164">
+        <v>7</v>
+      </c>
+      <c r="C164" t="s">
+        <v>90</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="E164">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" t="s">
+        <v>72</v>
+      </c>
+      <c r="B165">
+        <v>7</v>
+      </c>
+      <c r="C165" t="s">
+        <v>89</v>
+      </c>
+      <c r="D165">
+        <v>1</v>
+      </c>
+      <c r="E165">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" t="s">
+        <v>72</v>
+      </c>
+      <c r="B166">
+        <v>7</v>
+      </c>
+      <c r="C166" t="s">
+        <v>88</v>
+      </c>
+      <c r="D166">
+        <v>1</v>
+      </c>
+      <c r="E166">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" t="s">
+        <v>72</v>
+      </c>
+      <c r="B167">
+        <v>8</v>
+      </c>
+      <c r="C167" t="s">
+        <v>90</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" t="s">
+        <v>72</v>
+      </c>
+      <c r="B168">
+        <v>8</v>
+      </c>
+      <c r="C168" t="s">
+        <v>89</v>
+      </c>
+      <c r="D168">
+        <v>4</v>
+      </c>
+      <c r="E168">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" t="s">
+        <v>72</v>
+      </c>
+      <c r="B169">
+        <v>8</v>
+      </c>
+      <c r="C169" t="s">
+        <v>88</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="E169">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" t="s">
+        <v>72</v>
+      </c>
+      <c r="B170">
+        <v>9</v>
+      </c>
+      <c r="C170" t="s">
+        <v>90</v>
+      </c>
+      <c r="D170">
+        <v>1</v>
+      </c>
+      <c r="E170">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" t="s">
+        <v>72</v>
+      </c>
+      <c r="B171">
+        <v>9</v>
+      </c>
+      <c r="C171" t="s">
+        <v>89</v>
+      </c>
+      <c r="D171">
+        <v>2</v>
+      </c>
+      <c r="E171">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" t="s">
+        <v>72</v>
+      </c>
+      <c r="B172">
+        <v>9</v>
+      </c>
+      <c r="C172" t="s">
+        <v>88</v>
+      </c>
+      <c r="D172">
+        <v>3</v>
+      </c>
+      <c r="E172">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" t="s">
+        <v>72</v>
+      </c>
+      <c r="B173">
+        <v>10</v>
+      </c>
+      <c r="C173" t="s">
+        <v>90</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="E173">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" t="s">
+        <v>72</v>
+      </c>
+      <c r="B174">
+        <v>10</v>
+      </c>
+      <c r="C174" t="s">
+        <v>89</v>
+      </c>
+      <c r="D174">
+        <v>4</v>
+      </c>
+      <c r="E174">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" t="s">
+        <v>72</v>
+      </c>
+      <c r="B175">
+        <v>10</v>
+      </c>
+      <c r="C175" t="s">
+        <v>88</v>
+      </c>
+      <c r="D175">
+        <v>2</v>
+      </c>
+      <c r="E175">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" t="s">
+        <v>72</v>
+      </c>
+      <c r="B176">
+        <v>11</v>
+      </c>
+      <c r="C176" t="s">
+        <v>90</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="E176">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" t="s">
+        <v>72</v>
+      </c>
+      <c r="B177">
+        <v>11</v>
+      </c>
+      <c r="C177" t="s">
+        <v>89</v>
+      </c>
+      <c r="D177">
+        <v>3</v>
+      </c>
+      <c r="E177">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" t="s">
+        <v>72</v>
+      </c>
+      <c r="B178">
+        <v>11</v>
+      </c>
+      <c r="C178" t="s">
+        <v>88</v>
+      </c>
+      <c r="D178">
+        <v>3</v>
+      </c>
+      <c r="E178">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" t="s">
+        <v>72</v>
+      </c>
+      <c r="B179">
+        <v>12</v>
+      </c>
+      <c r="C179" t="s">
+        <v>90</v>
+      </c>
+      <c r="D179">
+        <v>1</v>
+      </c>
+      <c r="E179">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" t="s">
+        <v>72</v>
+      </c>
+      <c r="B180">
+        <v>12</v>
+      </c>
+      <c r="C180" t="s">
+        <v>89</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="E180">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" t="s">
+        <v>72</v>
+      </c>
+      <c r="B181">
+        <v>12</v>
+      </c>
+      <c r="C181" t="s">
+        <v>88</v>
+      </c>
+      <c r="D181">
+        <v>3</v>
+      </c>
+      <c r="E181">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" t="s">
+        <v>73</v>
+      </c>
+      <c r="B182">
+        <v>1</v>
+      </c>
+      <c r="C182" t="s">
+        <v>91</v>
+      </c>
+      <c r="D182">
+        <v>16</v>
+      </c>
+      <c r="E182">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" t="s">
+        <v>73</v>
+      </c>
+      <c r="B183">
+        <v>1</v>
+      </c>
+      <c r="C183" t="s">
+        <v>95</v>
+      </c>
+      <c r="D183">
+        <v>23</v>
+      </c>
+      <c r="E183">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" t="s">
+        <v>73</v>
+      </c>
+      <c r="B184">
+        <v>1</v>
+      </c>
+      <c r="C184" t="s">
+        <v>89</v>
+      </c>
+      <c r="D184">
+        <v>6</v>
+      </c>
+      <c r="E184">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" t="s">
+        <v>73</v>
+      </c>
+      <c r="B185">
+        <v>2</v>
+      </c>
+      <c r="C185" t="s">
+        <v>91</v>
+      </c>
+      <c r="D185">
+        <v>34</v>
+      </c>
+      <c r="E185">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" t="s">
+        <v>73</v>
+      </c>
+      <c r="B186">
+        <v>2</v>
+      </c>
+      <c r="C186" t="s">
+        <v>95</v>
+      </c>
+      <c r="D186">
+        <v>19</v>
+      </c>
+      <c r="E186">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" t="s">
+        <v>73</v>
+      </c>
+      <c r="B187">
+        <v>2</v>
+      </c>
+      <c r="C187" t="s">
+        <v>89</v>
+      </c>
+      <c r="D187">
+        <v>5</v>
+      </c>
+      <c r="E187">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" t="s">
+        <v>73</v>
+      </c>
+      <c r="B188">
+        <v>3</v>
+      </c>
+      <c r="C188" t="s">
+        <v>91</v>
+      </c>
+      <c r="D188">
+        <v>12</v>
+      </c>
+      <c r="E188">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" t="s">
+        <v>73</v>
+      </c>
+      <c r="B189">
+        <v>3</v>
+      </c>
+      <c r="C189" t="s">
+        <v>95</v>
+      </c>
+      <c r="D189">
+        <v>7</v>
+      </c>
+      <c r="E189">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" t="s">
+        <v>73</v>
+      </c>
+      <c r="B190">
+        <v>3</v>
+      </c>
+      <c r="C190" t="s">
+        <v>89</v>
+      </c>
+      <c r="D190">
+        <v>11</v>
+      </c>
+      <c r="E190">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" t="s">
+        <v>73</v>
+      </c>
+      <c r="B191">
+        <v>4</v>
+      </c>
+      <c r="C191" t="s">
+        <v>91</v>
+      </c>
+      <c r="D191">
+        <v>28</v>
+      </c>
+      <c r="E191">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" t="s">
+        <v>73</v>
+      </c>
+      <c r="B192">
+        <v>4</v>
+      </c>
+      <c r="C192" t="s">
+        <v>95</v>
+      </c>
+      <c r="D192">
+        <v>11</v>
+      </c>
+      <c r="E192">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" t="s">
+        <v>73</v>
+      </c>
+      <c r="B193">
+        <v>4</v>
+      </c>
+      <c r="C193" t="s">
+        <v>89</v>
+      </c>
+      <c r="D193">
+        <v>8</v>
+      </c>
+      <c r="E193">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" t="s">
+        <v>73</v>
+      </c>
+      <c r="B194">
+        <v>5</v>
+      </c>
+      <c r="C194" t="s">
+        <v>91</v>
+      </c>
+      <c r="D194">
+        <v>16</v>
+      </c>
+      <c r="E194">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" t="s">
+        <v>73</v>
+      </c>
+      <c r="B195">
+        <v>5</v>
+      </c>
+      <c r="C195" t="s">
+        <v>95</v>
+      </c>
+      <c r="D195">
+        <v>11</v>
+      </c>
+      <c r="E195">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" t="s">
+        <v>73</v>
+      </c>
+      <c r="B196">
+        <v>5</v>
+      </c>
+      <c r="C196" t="s">
+        <v>89</v>
+      </c>
+      <c r="D196">
+        <v>11</v>
+      </c>
+      <c r="E196">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" t="s">
+        <v>73</v>
+      </c>
+      <c r="B197">
+        <v>6</v>
+      </c>
+      <c r="C197" t="s">
+        <v>91</v>
+      </c>
+      <c r="D197">
+        <v>9</v>
+      </c>
+      <c r="E197">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" t="s">
+        <v>73</v>
+      </c>
+      <c r="B198">
+        <v>6</v>
+      </c>
+      <c r="C198" t="s">
+        <v>95</v>
+      </c>
+      <c r="D198">
+        <v>12</v>
+      </c>
+      <c r="E198">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" t="s">
+        <v>73</v>
+      </c>
+      <c r="B199">
+        <v>6</v>
+      </c>
+      <c r="C199" t="s">
+        <v>89</v>
+      </c>
+      <c r="D199">
+        <v>3</v>
+      </c>
+      <c r="E199">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" t="s">
+        <v>73</v>
+      </c>
+      <c r="B200">
+        <v>7</v>
+      </c>
+      <c r="C200" t="s">
+        <v>91</v>
+      </c>
+      <c r="D200">
+        <v>19</v>
+      </c>
+      <c r="E200">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" t="s">
+        <v>73</v>
+      </c>
+      <c r="B201">
+        <v>7</v>
+      </c>
+      <c r="C201" t="s">
+        <v>95</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" t="s">
+        <v>73</v>
+      </c>
+      <c r="B202">
+        <v>7</v>
+      </c>
+      <c r="C202" t="s">
+        <v>89</v>
+      </c>
+      <c r="D202">
+        <v>3</v>
+      </c>
+      <c r="E202">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" t="s">
+        <v>73</v>
+      </c>
+      <c r="B203">
+        <v>8</v>
+      </c>
+      <c r="C203" t="s">
+        <v>91</v>
+      </c>
+      <c r="D203">
+        <v>21</v>
+      </c>
+      <c r="E203">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" t="s">
+        <v>73</v>
+      </c>
+      <c r="B204">
+        <v>8</v>
+      </c>
+      <c r="C204" t="s">
+        <v>95</v>
+      </c>
+      <c r="D204">
+        <v>10</v>
+      </c>
+      <c r="E204">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" t="s">
+        <v>73</v>
+      </c>
+      <c r="B205">
+        <v>8</v>
+      </c>
+      <c r="C205" t="s">
+        <v>89</v>
+      </c>
+      <c r="D205">
+        <v>6</v>
+      </c>
+      <c r="E205">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" t="s">
+        <v>73</v>
+      </c>
+      <c r="B206">
+        <v>9</v>
+      </c>
+      <c r="C206" t="s">
+        <v>91</v>
+      </c>
+      <c r="D206">
+        <v>5</v>
+      </c>
+      <c r="E206">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" t="s">
+        <v>73</v>
+      </c>
+      <c r="B207">
+        <v>9</v>
+      </c>
+      <c r="C207" t="s">
+        <v>95</v>
+      </c>
+      <c r="D207">
+        <v>11</v>
+      </c>
+      <c r="E207">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" t="s">
+        <v>73</v>
+      </c>
+      <c r="B208">
+        <v>9</v>
+      </c>
+      <c r="C208" t="s">
+        <v>89</v>
+      </c>
+      <c r="D208">
+        <v>2</v>
+      </c>
+      <c r="E208">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" t="s">
+        <v>73</v>
+      </c>
+      <c r="B209">
+        <v>10</v>
+      </c>
+      <c r="C209" t="s">
+        <v>91</v>
+      </c>
+      <c r="D209">
+        <v>23</v>
+      </c>
+      <c r="E209">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" t="s">
+        <v>73</v>
+      </c>
+      <c r="B210">
+        <v>10</v>
+      </c>
+      <c r="C210" t="s">
+        <v>95</v>
+      </c>
+      <c r="D210">
+        <v>37</v>
+      </c>
+      <c r="E210">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" t="s">
+        <v>73</v>
+      </c>
+      <c r="B211">
+        <v>10</v>
+      </c>
+      <c r="C211" t="s">
+        <v>89</v>
+      </c>
+      <c r="D211">
+        <v>19</v>
+      </c>
+      <c r="E211">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" t="s">
+        <v>73</v>
+      </c>
+      <c r="B212">
+        <v>11</v>
+      </c>
+      <c r="C212" t="s">
+        <v>91</v>
+      </c>
+      <c r="D212">
+        <v>6</v>
+      </c>
+      <c r="E212">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" t="s">
+        <v>73</v>
+      </c>
+      <c r="B213">
+        <v>11</v>
+      </c>
+      <c r="C213" t="s">
+        <v>95</v>
+      </c>
+      <c r="D213">
+        <v>5</v>
+      </c>
+      <c r="E213">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" t="s">
+        <v>73</v>
+      </c>
+      <c r="B214">
+        <v>11</v>
+      </c>
+      <c r="C214" t="s">
+        <v>89</v>
+      </c>
+      <c r="D214">
+        <v>7</v>
+      </c>
+      <c r="E214">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" t="s">
+        <v>73</v>
+      </c>
+      <c r="B215">
+        <v>12</v>
+      </c>
+      <c r="C215" t="s">
+        <v>91</v>
+      </c>
+      <c r="D215">
+        <v>23</v>
+      </c>
+      <c r="E215">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" t="s">
+        <v>73</v>
+      </c>
+      <c r="B216">
+        <v>12</v>
+      </c>
+      <c r="C216" t="s">
+        <v>95</v>
+      </c>
+      <c r="D216">
+        <v>13</v>
+      </c>
+      <c r="E216">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" t="s">
+        <v>73</v>
+      </c>
+      <c r="B217">
+        <v>12</v>
+      </c>
+      <c r="C217" t="s">
+        <v>89</v>
+      </c>
+      <c r="D217">
+        <v>8</v>
+      </c>
+      <c r="E217">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E218">
+    <sortCondition ref="A2:A218"/>
+    <sortCondition ref="B2:B218"/>
+    <sortCondition descending="1" ref="E2:E218"/>
+    <sortCondition ref="C2:C218"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6482E56F-AAD0-45DD-AED2-1DDF0978065A}">
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -19765,3708 +23476,6 @@
       </c>
       <c r="B12">
         <v>125</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{292D24D9-B7AF-4404-B87D-6D3347D4D37D}">
-  <dimension ref="A1:E217"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="5" width="21.81640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E1" s="27" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
-      </c>
-      <c r="E8">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10">
-        <v>4</v>
-      </c>
-      <c r="E10">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11">
-        <v>6</v>
-      </c>
-      <c r="E11">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13">
-        <v>5</v>
-      </c>
-      <c r="E13">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14">
-        <v>5</v>
-      </c>
-      <c r="E14">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16">
-        <v>9</v>
-      </c>
-      <c r="E16">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17">
-        <v>4</v>
-      </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17">
-        <v>7</v>
-      </c>
-      <c r="E17">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18">
-        <v>5</v>
-      </c>
-      <c r="C18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18">
-        <v>4</v>
-      </c>
-      <c r="E18">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19">
-        <v>6</v>
-      </c>
-      <c r="C19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19">
-        <v>5</v>
-      </c>
-      <c r="E19">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20">
-        <v>7</v>
-      </c>
-      <c r="C20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20">
-        <v>4</v>
-      </c>
-      <c r="E20">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21">
-        <v>4</v>
-      </c>
-      <c r="E21">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22">
-        <v>7</v>
-      </c>
-      <c r="E22">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23">
-        <v>10</v>
-      </c>
-      <c r="C23" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23">
-        <v>3</v>
-      </c>
-      <c r="E23">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24">
-        <v>11</v>
-      </c>
-      <c r="C24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25">
-        <v>12</v>
-      </c>
-      <c r="C25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26">
-        <v>13</v>
-      </c>
-      <c r="E26">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27">
-        <v>13</v>
-      </c>
-      <c r="E27">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28">
-        <v>3</v>
-      </c>
-      <c r="C28" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28">
-        <v>12</v>
-      </c>
-      <c r="E28">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29">
-        <v>4</v>
-      </c>
-      <c r="C29" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29">
-        <v>5</v>
-      </c>
-      <c r="E29">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30">
-        <v>5</v>
-      </c>
-      <c r="C30" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-      <c r="E30">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31">
-        <v>6</v>
-      </c>
-      <c r="C31" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31">
-        <v>2</v>
-      </c>
-      <c r="E31">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32">
-        <v>7</v>
-      </c>
-      <c r="C32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33">
-        <v>8</v>
-      </c>
-      <c r="C33" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33">
-        <v>3</v>
-      </c>
-      <c r="E33">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" t="s">
-        <v>61</v>
-      </c>
-      <c r="B34">
-        <v>9</v>
-      </c>
-      <c r="C34" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35">
-        <v>10</v>
-      </c>
-      <c r="C35" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" t="s">
-        <v>61</v>
-      </c>
-      <c r="B36">
-        <v>11</v>
-      </c>
-      <c r="C36" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37">
-        <v>12</v>
-      </c>
-      <c r="C37" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38">
-        <v>6</v>
-      </c>
-      <c r="E38">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" t="s">
-        <v>69</v>
-      </c>
-      <c r="B39">
-        <v>2</v>
-      </c>
-      <c r="C39" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39">
-        <v>3</v>
-      </c>
-      <c r="E39">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" t="s">
-        <v>69</v>
-      </c>
-      <c r="B40">
-        <v>3</v>
-      </c>
-      <c r="C40" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40">
-        <v>5</v>
-      </c>
-      <c r="E40">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" t="s">
-        <v>69</v>
-      </c>
-      <c r="B41">
-        <v>4</v>
-      </c>
-      <c r="C41" t="s">
-        <v>88</v>
-      </c>
-      <c r="D41">
-        <v>6</v>
-      </c>
-      <c r="E41">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" t="s">
-        <v>69</v>
-      </c>
-      <c r="B42">
-        <v>5</v>
-      </c>
-      <c r="C42" t="s">
-        <v>88</v>
-      </c>
-      <c r="D42">
-        <v>7</v>
-      </c>
-      <c r="E42">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" t="s">
-        <v>69</v>
-      </c>
-      <c r="B43">
-        <v>6</v>
-      </c>
-      <c r="C43" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43">
-        <v>2</v>
-      </c>
-      <c r="E43">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" t="s">
-        <v>69</v>
-      </c>
-      <c r="B44">
-        <v>7</v>
-      </c>
-      <c r="C44" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44">
-        <v>6</v>
-      </c>
-      <c r="E44">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" t="s">
-        <v>69</v>
-      </c>
-      <c r="B45">
-        <v>8</v>
-      </c>
-      <c r="C45" t="s">
-        <v>88</v>
-      </c>
-      <c r="D45">
-        <v>3</v>
-      </c>
-      <c r="E45">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46">
-        <v>9</v>
-      </c>
-      <c r="C46" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-      <c r="E46">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" t="s">
-        <v>69</v>
-      </c>
-      <c r="B47">
-        <v>10</v>
-      </c>
-      <c r="C47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D47">
-        <v>4</v>
-      </c>
-      <c r="E47">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" t="s">
-        <v>69</v>
-      </c>
-      <c r="B48">
-        <v>11</v>
-      </c>
-      <c r="C48" t="s">
-        <v>88</v>
-      </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" t="s">
-        <v>69</v>
-      </c>
-      <c r="B49">
-        <v>12</v>
-      </c>
-      <c r="C49" t="s">
-        <v>88</v>
-      </c>
-      <c r="D49">
-        <v>3</v>
-      </c>
-      <c r="E49">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" t="s">
-        <v>69</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="C50" t="s">
-        <v>89</v>
-      </c>
-      <c r="D50">
-        <v>6</v>
-      </c>
-      <c r="E50">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" t="s">
-        <v>69</v>
-      </c>
-      <c r="B51">
-        <v>2</v>
-      </c>
-      <c r="C51" t="s">
-        <v>89</v>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" t="s">
-        <v>69</v>
-      </c>
-      <c r="B52">
-        <v>3</v>
-      </c>
-      <c r="C52" t="s">
-        <v>89</v>
-      </c>
-      <c r="D52">
-        <v>10</v>
-      </c>
-      <c r="E52">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" t="s">
-        <v>69</v>
-      </c>
-      <c r="B53">
-        <v>4</v>
-      </c>
-      <c r="C53" t="s">
-        <v>89</v>
-      </c>
-      <c r="D53">
-        <v>3</v>
-      </c>
-      <c r="E53">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" t="s">
-        <v>69</v>
-      </c>
-      <c r="B54">
-        <v>5</v>
-      </c>
-      <c r="C54" t="s">
-        <v>89</v>
-      </c>
-      <c r="D54">
-        <v>2</v>
-      </c>
-      <c r="E54">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" t="s">
-        <v>69</v>
-      </c>
-      <c r="B55">
-        <v>6</v>
-      </c>
-      <c r="C55" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55">
-        <v>3</v>
-      </c>
-      <c r="E55">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" t="s">
-        <v>69</v>
-      </c>
-      <c r="B56">
-        <v>7</v>
-      </c>
-      <c r="C56" t="s">
-        <v>89</v>
-      </c>
-      <c r="D56">
-        <v>2</v>
-      </c>
-      <c r="E56">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57">
-        <v>8</v>
-      </c>
-      <c r="C57" t="s">
-        <v>89</v>
-      </c>
-      <c r="D57">
-        <v>5</v>
-      </c>
-      <c r="E57">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" t="s">
-        <v>69</v>
-      </c>
-      <c r="B58">
-        <v>9</v>
-      </c>
-      <c r="C58" t="s">
-        <v>89</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59">
-        <v>10</v>
-      </c>
-      <c r="C59" t="s">
-        <v>89</v>
-      </c>
-      <c r="D59">
-        <v>4</v>
-      </c>
-      <c r="E59">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" t="s">
-        <v>69</v>
-      </c>
-      <c r="B60">
-        <v>11</v>
-      </c>
-      <c r="C60" t="s">
-        <v>89</v>
-      </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" t="s">
-        <v>69</v>
-      </c>
-      <c r="B61">
-        <v>12</v>
-      </c>
-      <c r="C61" t="s">
-        <v>89</v>
-      </c>
-      <c r="D61">
-        <v>6</v>
-      </c>
-      <c r="E61">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62" t="s">
-        <v>91</v>
-      </c>
-      <c r="D62">
-        <v>5</v>
-      </c>
-      <c r="E62">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
-      <c r="C63" t="s">
-        <v>91</v>
-      </c>
-      <c r="D63">
-        <v>7</v>
-      </c>
-      <c r="E63">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" t="s">
-        <v>69</v>
-      </c>
-      <c r="B64">
-        <v>3</v>
-      </c>
-      <c r="C64" t="s">
-        <v>91</v>
-      </c>
-      <c r="D64">
-        <v>3</v>
-      </c>
-      <c r="E64">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" t="s">
-        <v>69</v>
-      </c>
-      <c r="B65">
-        <v>4</v>
-      </c>
-      <c r="C65" t="s">
-        <v>91</v>
-      </c>
-      <c r="D65">
-        <v>5</v>
-      </c>
-      <c r="E65">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66">
-        <v>5</v>
-      </c>
-      <c r="C66" t="s">
-        <v>91</v>
-      </c>
-      <c r="D66">
-        <v>6</v>
-      </c>
-      <c r="E66">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" t="s">
-        <v>69</v>
-      </c>
-      <c r="B67">
-        <v>6</v>
-      </c>
-      <c r="C67" t="s">
-        <v>91</v>
-      </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" t="s">
-        <v>69</v>
-      </c>
-      <c r="B68">
-        <v>7</v>
-      </c>
-      <c r="C68" t="s">
-        <v>91</v>
-      </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-      <c r="E68">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" t="s">
-        <v>69</v>
-      </c>
-      <c r="B69">
-        <v>8</v>
-      </c>
-      <c r="C69" t="s">
-        <v>91</v>
-      </c>
-      <c r="D69">
-        <v>4</v>
-      </c>
-      <c r="E69">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" t="s">
-        <v>69</v>
-      </c>
-      <c r="B70">
-        <v>9</v>
-      </c>
-      <c r="C70" t="s">
-        <v>91</v>
-      </c>
-      <c r="D70">
-        <v>3</v>
-      </c>
-      <c r="E70">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" t="s">
-        <v>69</v>
-      </c>
-      <c r="B71">
-        <v>10</v>
-      </c>
-      <c r="C71" t="s">
-        <v>91</v>
-      </c>
-      <c r="D71">
-        <v>4</v>
-      </c>
-      <c r="E71">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" t="s">
-        <v>69</v>
-      </c>
-      <c r="B72">
-        <v>11</v>
-      </c>
-      <c r="C72" t="s">
-        <v>91</v>
-      </c>
-      <c r="D72">
-        <v>5</v>
-      </c>
-      <c r="E72">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" t="s">
-        <v>69</v>
-      </c>
-      <c r="B73">
-        <v>12</v>
-      </c>
-      <c r="C73" t="s">
-        <v>91</v>
-      </c>
-      <c r="D73">
-        <v>2</v>
-      </c>
-      <c r="E73">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" t="s">
-        <v>70</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
-      <c r="C74" t="s">
-        <v>95</v>
-      </c>
-      <c r="D74">
-        <v>11</v>
-      </c>
-      <c r="E74">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" t="s">
-        <v>70</v>
-      </c>
-      <c r="B75">
-        <v>2</v>
-      </c>
-      <c r="C75" t="s">
-        <v>95</v>
-      </c>
-      <c r="D75">
-        <v>8</v>
-      </c>
-      <c r="E75">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" t="s">
-        <v>70</v>
-      </c>
-      <c r="B76">
-        <v>3</v>
-      </c>
-      <c r="C76" t="s">
-        <v>95</v>
-      </c>
-      <c r="D76">
-        <v>2</v>
-      </c>
-      <c r="E76">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" t="s">
-        <v>70</v>
-      </c>
-      <c r="B77">
-        <v>4</v>
-      </c>
-      <c r="C77" t="s">
-        <v>95</v>
-      </c>
-      <c r="D77">
-        <v>3</v>
-      </c>
-      <c r="E77">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" t="s">
-        <v>70</v>
-      </c>
-      <c r="B78">
-        <v>5</v>
-      </c>
-      <c r="C78" t="s">
-        <v>95</v>
-      </c>
-      <c r="D78">
-        <v>5</v>
-      </c>
-      <c r="E78">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" t="s">
-        <v>70</v>
-      </c>
-      <c r="B79">
-        <v>6</v>
-      </c>
-      <c r="C79" t="s">
-        <v>95</v>
-      </c>
-      <c r="D79">
-        <v>2</v>
-      </c>
-      <c r="E79">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" t="s">
-        <v>70</v>
-      </c>
-      <c r="B80">
-        <v>7</v>
-      </c>
-      <c r="C80" t="s">
-        <v>95</v>
-      </c>
-      <c r="D80">
-        <v>5</v>
-      </c>
-      <c r="E80">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" t="s">
-        <v>70</v>
-      </c>
-      <c r="B81">
-        <v>8</v>
-      </c>
-      <c r="C81" t="s">
-        <v>95</v>
-      </c>
-      <c r="D81">
-        <v>2</v>
-      </c>
-      <c r="E81">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" t="s">
-        <v>70</v>
-      </c>
-      <c r="B82">
-        <v>9</v>
-      </c>
-      <c r="C82" t="s">
-        <v>95</v>
-      </c>
-      <c r="D82">
-        <v>5</v>
-      </c>
-      <c r="E82">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" t="s">
-        <v>70</v>
-      </c>
-      <c r="B83">
-        <v>10</v>
-      </c>
-      <c r="C83" t="s">
-        <v>95</v>
-      </c>
-      <c r="D83">
-        <v>0</v>
-      </c>
-      <c r="E83">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" t="s">
-        <v>70</v>
-      </c>
-      <c r="B84">
-        <v>11</v>
-      </c>
-      <c r="C84" t="s">
-        <v>95</v>
-      </c>
-      <c r="D84">
-        <v>3</v>
-      </c>
-      <c r="E84">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" t="s">
-        <v>70</v>
-      </c>
-      <c r="B85">
-        <v>12</v>
-      </c>
-      <c r="C85" t="s">
-        <v>95</v>
-      </c>
-      <c r="D85">
-        <v>1</v>
-      </c>
-      <c r="E85">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" t="s">
-        <v>70</v>
-      </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="C86" t="s">
-        <v>91</v>
-      </c>
-      <c r="D86">
-        <v>17</v>
-      </c>
-      <c r="E86">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" t="s">
-        <v>70</v>
-      </c>
-      <c r="B87">
-        <v>2</v>
-      </c>
-      <c r="C87" t="s">
-        <v>91</v>
-      </c>
-      <c r="D87">
-        <v>13</v>
-      </c>
-      <c r="E87">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" t="s">
-        <v>70</v>
-      </c>
-      <c r="B88">
-        <v>3</v>
-      </c>
-      <c r="C88" t="s">
-        <v>91</v>
-      </c>
-      <c r="D88">
-        <v>14</v>
-      </c>
-      <c r="E88">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" t="s">
-        <v>70</v>
-      </c>
-      <c r="B89">
-        <v>4</v>
-      </c>
-      <c r="C89" t="s">
-        <v>91</v>
-      </c>
-      <c r="D89">
-        <v>8</v>
-      </c>
-      <c r="E89">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" t="s">
-        <v>70</v>
-      </c>
-      <c r="B90">
-        <v>5</v>
-      </c>
-      <c r="C90" t="s">
-        <v>91</v>
-      </c>
-      <c r="D90">
-        <v>3</v>
-      </c>
-      <c r="E90">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" t="s">
-        <v>70</v>
-      </c>
-      <c r="B91">
-        <v>6</v>
-      </c>
-      <c r="C91" t="s">
-        <v>91</v>
-      </c>
-      <c r="D91">
-        <v>3</v>
-      </c>
-      <c r="E91">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" t="s">
-        <v>70</v>
-      </c>
-      <c r="B92">
-        <v>7</v>
-      </c>
-      <c r="C92" t="s">
-        <v>91</v>
-      </c>
-      <c r="D92">
-        <v>6</v>
-      </c>
-      <c r="E92">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" t="s">
-        <v>70</v>
-      </c>
-      <c r="B93">
-        <v>8</v>
-      </c>
-      <c r="C93" t="s">
-        <v>91</v>
-      </c>
-      <c r="D93">
-        <v>8</v>
-      </c>
-      <c r="E93">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" t="s">
-        <v>70</v>
-      </c>
-      <c r="B94">
-        <v>9</v>
-      </c>
-      <c r="C94" t="s">
-        <v>91</v>
-      </c>
-      <c r="D94">
-        <v>8</v>
-      </c>
-      <c r="E94">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" t="s">
-        <v>70</v>
-      </c>
-      <c r="B95">
-        <v>10</v>
-      </c>
-      <c r="C95" t="s">
-        <v>91</v>
-      </c>
-      <c r="D95">
-        <v>3</v>
-      </c>
-      <c r="E95">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" t="s">
-        <v>70</v>
-      </c>
-      <c r="B96">
-        <v>11</v>
-      </c>
-      <c r="C96" t="s">
-        <v>91</v>
-      </c>
-      <c r="D96">
-        <v>5</v>
-      </c>
-      <c r="E96">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" t="s">
-        <v>70</v>
-      </c>
-      <c r="B97">
-        <v>12</v>
-      </c>
-      <c r="C97" t="s">
-        <v>91</v>
-      </c>
-      <c r="D97">
-        <v>5</v>
-      </c>
-      <c r="E97">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" t="s">
-        <v>70</v>
-      </c>
-      <c r="B98">
-        <v>1</v>
-      </c>
-      <c r="C98" t="s">
-        <v>97</v>
-      </c>
-      <c r="D98">
-        <v>4</v>
-      </c>
-      <c r="E98">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" t="s">
-        <v>70</v>
-      </c>
-      <c r="B99">
-        <v>2</v>
-      </c>
-      <c r="C99" t="s">
-        <v>97</v>
-      </c>
-      <c r="D99">
-        <v>2</v>
-      </c>
-      <c r="E99">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" t="s">
-        <v>70</v>
-      </c>
-      <c r="B100">
-        <v>3</v>
-      </c>
-      <c r="C100" t="s">
-        <v>97</v>
-      </c>
-      <c r="D100">
-        <v>4</v>
-      </c>
-      <c r="E100">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" t="s">
-        <v>70</v>
-      </c>
-      <c r="B101">
-        <v>4</v>
-      </c>
-      <c r="C101" t="s">
-        <v>97</v>
-      </c>
-      <c r="D101">
-        <v>2</v>
-      </c>
-      <c r="E101">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" t="s">
-        <v>70</v>
-      </c>
-      <c r="B102">
-        <v>5</v>
-      </c>
-      <c r="C102" t="s">
-        <v>97</v>
-      </c>
-      <c r="D102">
-        <v>1</v>
-      </c>
-      <c r="E102">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" t="s">
-        <v>70</v>
-      </c>
-      <c r="B103">
-        <v>6</v>
-      </c>
-      <c r="C103" t="s">
-        <v>97</v>
-      </c>
-      <c r="D103">
-        <v>2</v>
-      </c>
-      <c r="E103">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" t="s">
-        <v>70</v>
-      </c>
-      <c r="B104">
-        <v>7</v>
-      </c>
-      <c r="C104" t="s">
-        <v>97</v>
-      </c>
-      <c r="D104">
-        <v>56</v>
-      </c>
-      <c r="E104">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" t="s">
-        <v>70</v>
-      </c>
-      <c r="B105">
-        <v>8</v>
-      </c>
-      <c r="C105" t="s">
-        <v>97</v>
-      </c>
-      <c r="D105">
-        <v>71</v>
-      </c>
-      <c r="E105">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" t="s">
-        <v>70</v>
-      </c>
-      <c r="B106">
-        <v>9</v>
-      </c>
-      <c r="C106" t="s">
-        <v>97</v>
-      </c>
-      <c r="D106">
-        <v>97</v>
-      </c>
-      <c r="E106">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" t="s">
-        <v>70</v>
-      </c>
-      <c r="B107">
-        <v>10</v>
-      </c>
-      <c r="C107" t="s">
-        <v>97</v>
-      </c>
-      <c r="D107">
-        <v>50</v>
-      </c>
-      <c r="E107">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" t="s">
-        <v>70</v>
-      </c>
-      <c r="B108">
-        <v>11</v>
-      </c>
-      <c r="C108" t="s">
-        <v>97</v>
-      </c>
-      <c r="D108">
-        <v>52</v>
-      </c>
-      <c r="E108">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" t="s">
-        <v>70</v>
-      </c>
-      <c r="B109">
-        <v>12</v>
-      </c>
-      <c r="C109" t="s">
-        <v>97</v>
-      </c>
-      <c r="D109">
-        <v>54</v>
-      </c>
-      <c r="E109">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" t="s">
-        <v>71</v>
-      </c>
-      <c r="B110">
-        <v>1</v>
-      </c>
-      <c r="C110" t="s">
-        <v>88</v>
-      </c>
-      <c r="D110">
-        <v>1</v>
-      </c>
-      <c r="E110">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" t="s">
-        <v>71</v>
-      </c>
-      <c r="B111">
-        <v>2</v>
-      </c>
-      <c r="C111" t="s">
-        <v>88</v>
-      </c>
-      <c r="D111">
-        <v>5</v>
-      </c>
-      <c r="E111">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" t="s">
-        <v>71</v>
-      </c>
-      <c r="B112">
-        <v>3</v>
-      </c>
-      <c r="C112" t="s">
-        <v>88</v>
-      </c>
-      <c r="D112">
-        <v>0</v>
-      </c>
-      <c r="E112">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" t="s">
-        <v>71</v>
-      </c>
-      <c r="B113">
-        <v>4</v>
-      </c>
-      <c r="C113" t="s">
-        <v>88</v>
-      </c>
-      <c r="D113">
-        <v>2</v>
-      </c>
-      <c r="E113">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" t="s">
-        <v>71</v>
-      </c>
-      <c r="B114">
-        <v>5</v>
-      </c>
-      <c r="C114" t="s">
-        <v>88</v>
-      </c>
-      <c r="D114">
-        <v>4</v>
-      </c>
-      <c r="E114">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" t="s">
-        <v>71</v>
-      </c>
-      <c r="B115">
-        <v>6</v>
-      </c>
-      <c r="C115" t="s">
-        <v>88</v>
-      </c>
-      <c r="D115">
-        <v>1</v>
-      </c>
-      <c r="E115">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" t="s">
-        <v>71</v>
-      </c>
-      <c r="B116">
-        <v>7</v>
-      </c>
-      <c r="C116" t="s">
-        <v>88</v>
-      </c>
-      <c r="D116">
-        <v>6</v>
-      </c>
-      <c r="E116">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="A117" t="s">
-        <v>71</v>
-      </c>
-      <c r="B117">
-        <v>8</v>
-      </c>
-      <c r="C117" t="s">
-        <v>88</v>
-      </c>
-      <c r="D117">
-        <v>5</v>
-      </c>
-      <c r="E117">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="A118" t="s">
-        <v>71</v>
-      </c>
-      <c r="B118">
-        <v>9</v>
-      </c>
-      <c r="C118" t="s">
-        <v>88</v>
-      </c>
-      <c r="D118">
-        <v>1</v>
-      </c>
-      <c r="E118">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
-      <c r="A119" t="s">
-        <v>71</v>
-      </c>
-      <c r="B119">
-        <v>10</v>
-      </c>
-      <c r="C119" t="s">
-        <v>88</v>
-      </c>
-      <c r="D119">
-        <v>1</v>
-      </c>
-      <c r="E119">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
-      <c r="A120" t="s">
-        <v>71</v>
-      </c>
-      <c r="B120">
-        <v>11</v>
-      </c>
-      <c r="C120" t="s">
-        <v>88</v>
-      </c>
-      <c r="D120">
-        <v>1</v>
-      </c>
-      <c r="E120">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="A121" t="s">
-        <v>71</v>
-      </c>
-      <c r="B121">
-        <v>12</v>
-      </c>
-      <c r="C121" t="s">
-        <v>88</v>
-      </c>
-      <c r="D121">
-        <v>4</v>
-      </c>
-      <c r="E121">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122" t="s">
-        <v>71</v>
-      </c>
-      <c r="B122">
-        <v>1</v>
-      </c>
-      <c r="C122" t="s">
-        <v>89</v>
-      </c>
-      <c r="D122">
-        <v>2</v>
-      </c>
-      <c r="E122">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123" t="s">
-        <v>71</v>
-      </c>
-      <c r="B123">
-        <v>2</v>
-      </c>
-      <c r="C123" t="s">
-        <v>89</v>
-      </c>
-      <c r="D123">
-        <v>1</v>
-      </c>
-      <c r="E123">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="A124" t="s">
-        <v>71</v>
-      </c>
-      <c r="B124">
-        <v>3</v>
-      </c>
-      <c r="C124" t="s">
-        <v>89</v>
-      </c>
-      <c r="D124">
-        <v>3</v>
-      </c>
-      <c r="E124">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125" t="s">
-        <v>71</v>
-      </c>
-      <c r="B125">
-        <v>4</v>
-      </c>
-      <c r="C125" t="s">
-        <v>89</v>
-      </c>
-      <c r="D125">
-        <v>3</v>
-      </c>
-      <c r="E125">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
-      <c r="A126" t="s">
-        <v>71</v>
-      </c>
-      <c r="B126">
-        <v>5</v>
-      </c>
-      <c r="C126" t="s">
-        <v>89</v>
-      </c>
-      <c r="D126">
-        <v>3</v>
-      </c>
-      <c r="E126">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
-      <c r="A127" t="s">
-        <v>71</v>
-      </c>
-      <c r="B127">
-        <v>6</v>
-      </c>
-      <c r="C127" t="s">
-        <v>89</v>
-      </c>
-      <c r="D127">
-        <v>0</v>
-      </c>
-      <c r="E127">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
-      <c r="A128" t="s">
-        <v>71</v>
-      </c>
-      <c r="B128">
-        <v>7</v>
-      </c>
-      <c r="C128" t="s">
-        <v>89</v>
-      </c>
-      <c r="D128">
-        <v>1</v>
-      </c>
-      <c r="E128">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
-      <c r="A129" t="s">
-        <v>71</v>
-      </c>
-      <c r="B129">
-        <v>8</v>
-      </c>
-      <c r="C129" t="s">
-        <v>89</v>
-      </c>
-      <c r="D129">
-        <v>1</v>
-      </c>
-      <c r="E129">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
-      <c r="A130" t="s">
-        <v>71</v>
-      </c>
-      <c r="B130">
-        <v>9</v>
-      </c>
-      <c r="C130" t="s">
-        <v>89</v>
-      </c>
-      <c r="D130">
-        <v>1</v>
-      </c>
-      <c r="E130">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="A131" t="s">
-        <v>71</v>
-      </c>
-      <c r="B131">
-        <v>10</v>
-      </c>
-      <c r="C131" t="s">
-        <v>89</v>
-      </c>
-      <c r="D131">
-        <v>1</v>
-      </c>
-      <c r="E131">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
-      <c r="A132" t="s">
-        <v>71</v>
-      </c>
-      <c r="B132">
-        <v>11</v>
-      </c>
-      <c r="C132" t="s">
-        <v>89</v>
-      </c>
-      <c r="D132">
-        <v>2</v>
-      </c>
-      <c r="E132">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
-      <c r="A133" t="s">
-        <v>71</v>
-      </c>
-      <c r="B133">
-        <v>12</v>
-      </c>
-      <c r="C133" t="s">
-        <v>89</v>
-      </c>
-      <c r="D133">
-        <v>0</v>
-      </c>
-      <c r="E133">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
-      <c r="A134" t="s">
-        <v>71</v>
-      </c>
-      <c r="B134">
-        <v>1</v>
-      </c>
-      <c r="C134" t="s">
-        <v>90</v>
-      </c>
-      <c r="D134">
-        <v>6</v>
-      </c>
-      <c r="E134">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
-      <c r="A135" t="s">
-        <v>71</v>
-      </c>
-      <c r="B135">
-        <v>2</v>
-      </c>
-      <c r="C135" t="s">
-        <v>90</v>
-      </c>
-      <c r="D135">
-        <v>3</v>
-      </c>
-      <c r="E135">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
-      <c r="A136" t="s">
-        <v>71</v>
-      </c>
-      <c r="B136">
-        <v>3</v>
-      </c>
-      <c r="C136" t="s">
-        <v>90</v>
-      </c>
-      <c r="D136">
-        <v>3</v>
-      </c>
-      <c r="E136">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" t="s">
-        <v>71</v>
-      </c>
-      <c r="B137">
-        <v>4</v>
-      </c>
-      <c r="C137" t="s">
-        <v>90</v>
-      </c>
-      <c r="D137">
-        <v>2</v>
-      </c>
-      <c r="E137">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138" t="s">
-        <v>71</v>
-      </c>
-      <c r="B138">
-        <v>5</v>
-      </c>
-      <c r="C138" t="s">
-        <v>90</v>
-      </c>
-      <c r="D138">
-        <v>3</v>
-      </c>
-      <c r="E138">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
-      <c r="A139" t="s">
-        <v>71</v>
-      </c>
-      <c r="B139">
-        <v>6</v>
-      </c>
-      <c r="C139" t="s">
-        <v>90</v>
-      </c>
-      <c r="D139">
-        <v>0</v>
-      </c>
-      <c r="E139">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="A140" t="s">
-        <v>71</v>
-      </c>
-      <c r="B140">
-        <v>7</v>
-      </c>
-      <c r="C140" t="s">
-        <v>90</v>
-      </c>
-      <c r="D140">
-        <v>1</v>
-      </c>
-      <c r="E140">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
-      <c r="A141" t="s">
-        <v>71</v>
-      </c>
-      <c r="B141">
-        <v>8</v>
-      </c>
-      <c r="C141" t="s">
-        <v>90</v>
-      </c>
-      <c r="D141">
-        <v>0</v>
-      </c>
-      <c r="E141">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
-      <c r="A142" t="s">
-        <v>71</v>
-      </c>
-      <c r="B142">
-        <v>9</v>
-      </c>
-      <c r="C142" t="s">
-        <v>90</v>
-      </c>
-      <c r="D142">
-        <v>0</v>
-      </c>
-      <c r="E142">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" t="s">
-        <v>71</v>
-      </c>
-      <c r="B143">
-        <v>10</v>
-      </c>
-      <c r="C143" t="s">
-        <v>90</v>
-      </c>
-      <c r="D143">
-        <v>2</v>
-      </c>
-      <c r="E143">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="A144" t="s">
-        <v>71</v>
-      </c>
-      <c r="B144">
-        <v>11</v>
-      </c>
-      <c r="C144" t="s">
-        <v>90</v>
-      </c>
-      <c r="D144">
-        <v>0</v>
-      </c>
-      <c r="E144">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="A145" t="s">
-        <v>71</v>
-      </c>
-      <c r="B145">
-        <v>12</v>
-      </c>
-      <c r="C145" t="s">
-        <v>90</v>
-      </c>
-      <c r="D145">
-        <v>0</v>
-      </c>
-      <c r="E145">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
-      <c r="A146" t="s">
-        <v>72</v>
-      </c>
-      <c r="B146">
-        <v>1</v>
-      </c>
-      <c r="C146" t="s">
-        <v>88</v>
-      </c>
-      <c r="D146">
-        <v>2</v>
-      </c>
-      <c r="E146">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
-      <c r="A147" t="s">
-        <v>72</v>
-      </c>
-      <c r="B147">
-        <v>2</v>
-      </c>
-      <c r="C147" t="s">
-        <v>88</v>
-      </c>
-      <c r="D147">
-        <v>3</v>
-      </c>
-      <c r="E147">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
-      <c r="A148" t="s">
-        <v>72</v>
-      </c>
-      <c r="B148">
-        <v>3</v>
-      </c>
-      <c r="C148" t="s">
-        <v>88</v>
-      </c>
-      <c r="D148">
-        <v>1</v>
-      </c>
-      <c r="E148">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
-      <c r="A149" t="s">
-        <v>72</v>
-      </c>
-      <c r="B149">
-        <v>4</v>
-      </c>
-      <c r="C149" t="s">
-        <v>88</v>
-      </c>
-      <c r="D149">
-        <v>0</v>
-      </c>
-      <c r="E149">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
-      <c r="A150" t="s">
-        <v>72</v>
-      </c>
-      <c r="B150">
-        <v>5</v>
-      </c>
-      <c r="C150" t="s">
-        <v>88</v>
-      </c>
-      <c r="D150">
-        <v>2</v>
-      </c>
-      <c r="E150">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
-      <c r="A151" t="s">
-        <v>72</v>
-      </c>
-      <c r="B151">
-        <v>6</v>
-      </c>
-      <c r="C151" t="s">
-        <v>88</v>
-      </c>
-      <c r="D151">
-        <v>0</v>
-      </c>
-      <c r="E151">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
-      <c r="A152" t="s">
-        <v>72</v>
-      </c>
-      <c r="B152">
-        <v>7</v>
-      </c>
-      <c r="C152" t="s">
-        <v>88</v>
-      </c>
-      <c r="D152">
-        <v>1</v>
-      </c>
-      <c r="E152">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
-      <c r="A153" t="s">
-        <v>72</v>
-      </c>
-      <c r="B153">
-        <v>8</v>
-      </c>
-      <c r="C153" t="s">
-        <v>88</v>
-      </c>
-      <c r="D153">
-        <v>0</v>
-      </c>
-      <c r="E153">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
-      <c r="A154" t="s">
-        <v>72</v>
-      </c>
-      <c r="B154">
-        <v>9</v>
-      </c>
-      <c r="C154" t="s">
-        <v>88</v>
-      </c>
-      <c r="D154">
-        <v>3</v>
-      </c>
-      <c r="E154">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
-      <c r="A155" t="s">
-        <v>72</v>
-      </c>
-      <c r="B155">
-        <v>10</v>
-      </c>
-      <c r="C155" t="s">
-        <v>88</v>
-      </c>
-      <c r="D155">
-        <v>2</v>
-      </c>
-      <c r="E155">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
-      <c r="A156" t="s">
-        <v>72</v>
-      </c>
-      <c r="B156">
-        <v>11</v>
-      </c>
-      <c r="C156" t="s">
-        <v>88</v>
-      </c>
-      <c r="D156">
-        <v>3</v>
-      </c>
-      <c r="E156">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
-      <c r="A157" t="s">
-        <v>72</v>
-      </c>
-      <c r="B157">
-        <v>12</v>
-      </c>
-      <c r="C157" t="s">
-        <v>88</v>
-      </c>
-      <c r="D157">
-        <v>3</v>
-      </c>
-      <c r="E157">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
-      <c r="A158" t="s">
-        <v>72</v>
-      </c>
-      <c r="B158">
-        <v>1</v>
-      </c>
-      <c r="C158" t="s">
-        <v>89</v>
-      </c>
-      <c r="D158">
-        <v>1</v>
-      </c>
-      <c r="E158">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5">
-      <c r="A159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B159">
-        <v>2</v>
-      </c>
-      <c r="C159" t="s">
-        <v>89</v>
-      </c>
-      <c r="D159">
-        <v>2</v>
-      </c>
-      <c r="E159">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5">
-      <c r="A160" t="s">
-        <v>72</v>
-      </c>
-      <c r="B160">
-        <v>3</v>
-      </c>
-      <c r="C160" t="s">
-        <v>89</v>
-      </c>
-      <c r="D160">
-        <v>3</v>
-      </c>
-      <c r="E160">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
-      <c r="A161" t="s">
-        <v>72</v>
-      </c>
-      <c r="B161">
-        <v>4</v>
-      </c>
-      <c r="C161" t="s">
-        <v>89</v>
-      </c>
-      <c r="D161">
-        <v>2</v>
-      </c>
-      <c r="E161">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5">
-      <c r="A162" t="s">
-        <v>72</v>
-      </c>
-      <c r="B162">
-        <v>5</v>
-      </c>
-      <c r="C162" t="s">
-        <v>89</v>
-      </c>
-      <c r="D162">
-        <v>6</v>
-      </c>
-      <c r="E162">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5">
-      <c r="A163" t="s">
-        <v>72</v>
-      </c>
-      <c r="B163">
-        <v>6</v>
-      </c>
-      <c r="C163" t="s">
-        <v>89</v>
-      </c>
-      <c r="D163">
-        <v>2</v>
-      </c>
-      <c r="E163">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
-      <c r="A164" t="s">
-        <v>72</v>
-      </c>
-      <c r="B164">
-        <v>7</v>
-      </c>
-      <c r="C164" t="s">
-        <v>89</v>
-      </c>
-      <c r="D164">
-        <v>1</v>
-      </c>
-      <c r="E164">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5">
-      <c r="A165" t="s">
-        <v>72</v>
-      </c>
-      <c r="B165">
-        <v>8</v>
-      </c>
-      <c r="C165" t="s">
-        <v>89</v>
-      </c>
-      <c r="D165">
-        <v>4</v>
-      </c>
-      <c r="E165">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5">
-      <c r="A166" t="s">
-        <v>72</v>
-      </c>
-      <c r="B166">
-        <v>9</v>
-      </c>
-      <c r="C166" t="s">
-        <v>89</v>
-      </c>
-      <c r="D166">
-        <v>2</v>
-      </c>
-      <c r="E166">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5">
-      <c r="A167" t="s">
-        <v>72</v>
-      </c>
-      <c r="B167">
-        <v>10</v>
-      </c>
-      <c r="C167" t="s">
-        <v>89</v>
-      </c>
-      <c r="D167">
-        <v>4</v>
-      </c>
-      <c r="E167">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
-      <c r="A168" t="s">
-        <v>72</v>
-      </c>
-      <c r="B168">
-        <v>11</v>
-      </c>
-      <c r="C168" t="s">
-        <v>89</v>
-      </c>
-      <c r="D168">
-        <v>3</v>
-      </c>
-      <c r="E168">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5">
-      <c r="A169" t="s">
-        <v>72</v>
-      </c>
-      <c r="B169">
-        <v>12</v>
-      </c>
-      <c r="C169" t="s">
-        <v>89</v>
-      </c>
-      <c r="D169">
-        <v>0</v>
-      </c>
-      <c r="E169">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
-      <c r="A170" t="s">
-        <v>72</v>
-      </c>
-      <c r="B170">
-        <v>1</v>
-      </c>
-      <c r="C170" t="s">
-        <v>90</v>
-      </c>
-      <c r="D170">
-        <v>6</v>
-      </c>
-      <c r="E170">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5">
-      <c r="A171" t="s">
-        <v>72</v>
-      </c>
-      <c r="B171">
-        <v>2</v>
-      </c>
-      <c r="C171" t="s">
-        <v>90</v>
-      </c>
-      <c r="D171">
-        <v>8</v>
-      </c>
-      <c r="E171">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5">
-      <c r="A172" t="s">
-        <v>72</v>
-      </c>
-      <c r="B172">
-        <v>3</v>
-      </c>
-      <c r="C172" t="s">
-        <v>90</v>
-      </c>
-      <c r="D172">
-        <v>5</v>
-      </c>
-      <c r="E172">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
-      <c r="A173" t="s">
-        <v>72</v>
-      </c>
-      <c r="B173">
-        <v>4</v>
-      </c>
-      <c r="C173" t="s">
-        <v>90</v>
-      </c>
-      <c r="D173">
-        <v>4</v>
-      </c>
-      <c r="E173">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
-      <c r="A174" t="s">
-        <v>72</v>
-      </c>
-      <c r="B174">
-        <v>5</v>
-      </c>
-      <c r="C174" t="s">
-        <v>90</v>
-      </c>
-      <c r="D174">
-        <v>7</v>
-      </c>
-      <c r="E174">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
-      <c r="A175" t="s">
-        <v>72</v>
-      </c>
-      <c r="B175">
-        <v>6</v>
-      </c>
-      <c r="C175" t="s">
-        <v>90</v>
-      </c>
-      <c r="D175">
-        <v>0</v>
-      </c>
-      <c r="E175">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
-      <c r="A176" t="s">
-        <v>72</v>
-      </c>
-      <c r="B176">
-        <v>7</v>
-      </c>
-      <c r="C176" t="s">
-        <v>90</v>
-      </c>
-      <c r="D176">
-        <v>0</v>
-      </c>
-      <c r="E176">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
-      <c r="A177" t="s">
-        <v>72</v>
-      </c>
-      <c r="B177">
-        <v>8</v>
-      </c>
-      <c r="C177" t="s">
-        <v>90</v>
-      </c>
-      <c r="D177">
-        <v>0</v>
-      </c>
-      <c r="E177">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
-      <c r="A178" t="s">
-        <v>72</v>
-      </c>
-      <c r="B178">
-        <v>9</v>
-      </c>
-      <c r="C178" t="s">
-        <v>90</v>
-      </c>
-      <c r="D178">
-        <v>1</v>
-      </c>
-      <c r="E178">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
-      <c r="A179" t="s">
-        <v>72</v>
-      </c>
-      <c r="B179">
-        <v>10</v>
-      </c>
-      <c r="C179" t="s">
-        <v>90</v>
-      </c>
-      <c r="D179">
-        <v>0</v>
-      </c>
-      <c r="E179">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
-      <c r="A180" t="s">
-        <v>72</v>
-      </c>
-      <c r="B180">
-        <v>11</v>
-      </c>
-      <c r="C180" t="s">
-        <v>90</v>
-      </c>
-      <c r="D180">
-        <v>0</v>
-      </c>
-      <c r="E180">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
-      <c r="A181" t="s">
-        <v>72</v>
-      </c>
-      <c r="B181">
-        <v>12</v>
-      </c>
-      <c r="C181" t="s">
-        <v>90</v>
-      </c>
-      <c r="D181">
-        <v>1</v>
-      </c>
-      <c r="E181">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
-      <c r="A182" t="s">
-        <v>73</v>
-      </c>
-      <c r="B182">
-        <v>1</v>
-      </c>
-      <c r="C182" t="s">
-        <v>95</v>
-      </c>
-      <c r="D182">
-        <v>23</v>
-      </c>
-      <c r="E182">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
-      <c r="A183" t="s">
-        <v>73</v>
-      </c>
-      <c r="B183">
-        <v>2</v>
-      </c>
-      <c r="C183" t="s">
-        <v>95</v>
-      </c>
-      <c r="D183">
-        <v>19</v>
-      </c>
-      <c r="E183">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5">
-      <c r="A184" t="s">
-        <v>73</v>
-      </c>
-      <c r="B184">
-        <v>3</v>
-      </c>
-      <c r="C184" t="s">
-        <v>95</v>
-      </c>
-      <c r="D184">
-        <v>7</v>
-      </c>
-      <c r="E184">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
-      <c r="A185" t="s">
-        <v>73</v>
-      </c>
-      <c r="B185">
-        <v>4</v>
-      </c>
-      <c r="C185" t="s">
-        <v>95</v>
-      </c>
-      <c r="D185">
-        <v>11</v>
-      </c>
-      <c r="E185">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
-      <c r="A186" t="s">
-        <v>73</v>
-      </c>
-      <c r="B186">
-        <v>5</v>
-      </c>
-      <c r="C186" t="s">
-        <v>95</v>
-      </c>
-      <c r="D186">
-        <v>11</v>
-      </c>
-      <c r="E186">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
-      <c r="A187" t="s">
-        <v>73</v>
-      </c>
-      <c r="B187">
-        <v>6</v>
-      </c>
-      <c r="C187" t="s">
-        <v>95</v>
-      </c>
-      <c r="D187">
-        <v>12</v>
-      </c>
-      <c r="E187">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
-      <c r="A188" t="s">
-        <v>73</v>
-      </c>
-      <c r="B188">
-        <v>7</v>
-      </c>
-      <c r="C188" t="s">
-        <v>95</v>
-      </c>
-      <c r="D188">
-        <v>8</v>
-      </c>
-      <c r="E188">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
-      <c r="A189" t="s">
-        <v>73</v>
-      </c>
-      <c r="B189">
-        <v>8</v>
-      </c>
-      <c r="C189" t="s">
-        <v>95</v>
-      </c>
-      <c r="D189">
-        <v>10</v>
-      </c>
-      <c r="E189">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
-      <c r="A190" t="s">
-        <v>73</v>
-      </c>
-      <c r="B190">
-        <v>9</v>
-      </c>
-      <c r="C190" t="s">
-        <v>95</v>
-      </c>
-      <c r="D190">
-        <v>11</v>
-      </c>
-      <c r="E190">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5">
-      <c r="A191" t="s">
-        <v>73</v>
-      </c>
-      <c r="B191">
-        <v>10</v>
-      </c>
-      <c r="C191" t="s">
-        <v>95</v>
-      </c>
-      <c r="D191">
-        <v>37</v>
-      </c>
-      <c r="E191">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
-      <c r="A192" t="s">
-        <v>73</v>
-      </c>
-      <c r="B192">
-        <v>11</v>
-      </c>
-      <c r="C192" t="s">
-        <v>95</v>
-      </c>
-      <c r="D192">
-        <v>5</v>
-      </c>
-      <c r="E192">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5">
-      <c r="A193" t="s">
-        <v>73</v>
-      </c>
-      <c r="B193">
-        <v>12</v>
-      </c>
-      <c r="C193" t="s">
-        <v>95</v>
-      </c>
-      <c r="D193">
-        <v>13</v>
-      </c>
-      <c r="E193">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5">
-      <c r="A194" t="s">
-        <v>73</v>
-      </c>
-      <c r="B194">
-        <v>1</v>
-      </c>
-      <c r="C194" t="s">
-        <v>89</v>
-      </c>
-      <c r="D194">
-        <v>6</v>
-      </c>
-      <c r="E194">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5">
-      <c r="A195" t="s">
-        <v>73</v>
-      </c>
-      <c r="B195">
-        <v>2</v>
-      </c>
-      <c r="C195" t="s">
-        <v>89</v>
-      </c>
-      <c r="D195">
-        <v>5</v>
-      </c>
-      <c r="E195">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5">
-      <c r="A196" t="s">
-        <v>73</v>
-      </c>
-      <c r="B196">
-        <v>3</v>
-      </c>
-      <c r="C196" t="s">
-        <v>89</v>
-      </c>
-      <c r="D196">
-        <v>11</v>
-      </c>
-      <c r="E196">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5">
-      <c r="A197" t="s">
-        <v>73</v>
-      </c>
-      <c r="B197">
-        <v>4</v>
-      </c>
-      <c r="C197" t="s">
-        <v>89</v>
-      </c>
-      <c r="D197">
-        <v>8</v>
-      </c>
-      <c r="E197">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5">
-      <c r="A198" t="s">
-        <v>73</v>
-      </c>
-      <c r="B198">
-        <v>5</v>
-      </c>
-      <c r="C198" t="s">
-        <v>89</v>
-      </c>
-      <c r="D198">
-        <v>11</v>
-      </c>
-      <c r="E198">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5">
-      <c r="A199" t="s">
-        <v>73</v>
-      </c>
-      <c r="B199">
-        <v>6</v>
-      </c>
-      <c r="C199" t="s">
-        <v>89</v>
-      </c>
-      <c r="D199">
-        <v>3</v>
-      </c>
-      <c r="E199">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5">
-      <c r="A200" t="s">
-        <v>73</v>
-      </c>
-      <c r="B200">
-        <v>7</v>
-      </c>
-      <c r="C200" t="s">
-        <v>89</v>
-      </c>
-      <c r="D200">
-        <v>3</v>
-      </c>
-      <c r="E200">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5">
-      <c r="A201" t="s">
-        <v>73</v>
-      </c>
-      <c r="B201">
-        <v>8</v>
-      </c>
-      <c r="C201" t="s">
-        <v>89</v>
-      </c>
-      <c r="D201">
-        <v>6</v>
-      </c>
-      <c r="E201">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5">
-      <c r="A202" t="s">
-        <v>73</v>
-      </c>
-      <c r="B202">
-        <v>9</v>
-      </c>
-      <c r="C202" t="s">
-        <v>89</v>
-      </c>
-      <c r="D202">
-        <v>2</v>
-      </c>
-      <c r="E202">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5">
-      <c r="A203" t="s">
-        <v>73</v>
-      </c>
-      <c r="B203">
-        <v>10</v>
-      </c>
-      <c r="C203" t="s">
-        <v>89</v>
-      </c>
-      <c r="D203">
-        <v>19</v>
-      </c>
-      <c r="E203">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5">
-      <c r="A204" t="s">
-        <v>73</v>
-      </c>
-      <c r="B204">
-        <v>11</v>
-      </c>
-      <c r="C204" t="s">
-        <v>89</v>
-      </c>
-      <c r="D204">
-        <v>7</v>
-      </c>
-      <c r="E204">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5">
-      <c r="A205" t="s">
-        <v>73</v>
-      </c>
-      <c r="B205">
-        <v>12</v>
-      </c>
-      <c r="C205" t="s">
-        <v>89</v>
-      </c>
-      <c r="D205">
-        <v>8</v>
-      </c>
-      <c r="E205">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5">
-      <c r="A206" t="s">
-        <v>73</v>
-      </c>
-      <c r="B206">
-        <v>1</v>
-      </c>
-      <c r="C206" t="s">
-        <v>91</v>
-      </c>
-      <c r="D206">
-        <v>16</v>
-      </c>
-      <c r="E206">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5">
-      <c r="A207" t="s">
-        <v>73</v>
-      </c>
-      <c r="B207">
-        <v>2</v>
-      </c>
-      <c r="C207" t="s">
-        <v>91</v>
-      </c>
-      <c r="D207">
-        <v>34</v>
-      </c>
-      <c r="E207">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5">
-      <c r="A208" t="s">
-        <v>73</v>
-      </c>
-      <c r="B208">
-        <v>3</v>
-      </c>
-      <c r="C208" t="s">
-        <v>91</v>
-      </c>
-      <c r="D208">
-        <v>12</v>
-      </c>
-      <c r="E208">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5">
-      <c r="A209" t="s">
-        <v>73</v>
-      </c>
-      <c r="B209">
-        <v>4</v>
-      </c>
-      <c r="C209" t="s">
-        <v>91</v>
-      </c>
-      <c r="D209">
-        <v>28</v>
-      </c>
-      <c r="E209">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5">
-      <c r="A210" t="s">
-        <v>73</v>
-      </c>
-      <c r="B210">
-        <v>5</v>
-      </c>
-      <c r="C210" t="s">
-        <v>91</v>
-      </c>
-      <c r="D210">
-        <v>16</v>
-      </c>
-      <c r="E210">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5">
-      <c r="A211" t="s">
-        <v>73</v>
-      </c>
-      <c r="B211">
-        <v>6</v>
-      </c>
-      <c r="C211" t="s">
-        <v>91</v>
-      </c>
-      <c r="D211">
-        <v>9</v>
-      </c>
-      <c r="E211">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5">
-      <c r="A212" t="s">
-        <v>73</v>
-      </c>
-      <c r="B212">
-        <v>7</v>
-      </c>
-      <c r="C212" t="s">
-        <v>91</v>
-      </c>
-      <c r="D212">
-        <v>19</v>
-      </c>
-      <c r="E212">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5">
-      <c r="A213" t="s">
-        <v>73</v>
-      </c>
-      <c r="B213">
-        <v>8</v>
-      </c>
-      <c r="C213" t="s">
-        <v>91</v>
-      </c>
-      <c r="D213">
-        <v>21</v>
-      </c>
-      <c r="E213">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5">
-      <c r="A214" t="s">
-        <v>73</v>
-      </c>
-      <c r="B214">
-        <v>9</v>
-      </c>
-      <c r="C214" t="s">
-        <v>91</v>
-      </c>
-      <c r="D214">
-        <v>5</v>
-      </c>
-      <c r="E214">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5">
-      <c r="A215" t="s">
-        <v>73</v>
-      </c>
-      <c r="B215">
-        <v>10</v>
-      </c>
-      <c r="C215" t="s">
-        <v>91</v>
-      </c>
-      <c r="D215">
-        <v>23</v>
-      </c>
-      <c r="E215">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5">
-      <c r="A216" t="s">
-        <v>73</v>
-      </c>
-      <c r="B216">
-        <v>11</v>
-      </c>
-      <c r="C216" t="s">
-        <v>91</v>
-      </c>
-      <c r="D216">
-        <v>6</v>
-      </c>
-      <c r="E216">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5">
-      <c r="A217" t="s">
-        <v>73</v>
-      </c>
-      <c r="B217">
-        <v>12</v>
-      </c>
-      <c r="C217" t="s">
-        <v>91</v>
-      </c>
-      <c r="D217">
-        <v>23</v>
-      </c>
-      <c r="E217">
-        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/2022_04_29 PWC Challenge 1 - Hotel Analytics/PWC Dashboard.xlsx
+++ b/2022_04_29 PWC Challenge 1 - Hotel Analytics/PWC Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seoul\Dropbox\00 technical\github\kimep-data-science-lab\2022_04_29 PWC Challenge 1 - Hotel Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF621287-69B4-4783-8982-5553D9A1A387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E2FB87-3E44-4FCE-AFD2-82AFF104B7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="4" activeTab="6" xr2:uid="{AACBAEBD-F012-4269-A3B9-168C8D706687}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="3" xr2:uid="{AACBAEBD-F012-4269-A3B9-168C8D706687}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="5" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="109">
   <si>
     <t>Month</t>
   </si>
@@ -157,12 +157,6 @@
   </si>
   <si>
     <t>Executive, Superior</t>
-  </si>
-  <si>
-    <t>Food &amp; Bar - after March</t>
-  </si>
-  <si>
-    <t>Food - January thru June</t>
   </si>
   <si>
     <t>Months &amp; Year</t>
@@ -309,9 +303,6 @@
     <t>Room type</t>
   </si>
   <si>
-    <t>Concern description</t>
-  </si>
-  <si>
     <t>Doesn’t match the website/brochure</t>
   </si>
   <si>
@@ -348,10 +339,40 @@
     <t>Concerns</t>
   </si>
   <si>
-    <t>Count_x</t>
+    <t>Concern description 1</t>
   </si>
   <si>
-    <t>Count_y</t>
+    <t>Concern description 2</t>
+  </si>
+  <si>
+    <t>Concern description 3</t>
+  </si>
+  <si>
+    <t>Count_x 1</t>
+  </si>
+  <si>
+    <t>Count_x 2</t>
+  </si>
+  <si>
+    <t>Count_x 3</t>
+  </si>
+  <si>
+    <t>Label 1</t>
+  </si>
+  <si>
+    <t>Label 2</t>
+  </si>
+  <si>
+    <t>Label 3</t>
+  </si>
+  <si>
+    <t>Problem #1 - Food &amp; Bar - after March</t>
+  </si>
+  <si>
+    <t>Problem # 2 - Food - January thru June</t>
+  </si>
+  <si>
+    <t>Problem #3 - Faulty electronics in all rooms</t>
   </si>
 </sst>
 </file>
@@ -361,7 +382,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,6 +485,20 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -587,7 +622,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -630,6 +665,12 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="13" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -815,40 +856,40 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.96875</c:v>
+                  <c:v>1.0811688311688312</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0119047619047619</c:v>
+                  <c:v>1.1353305785123966</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.89583333333333337</c:v>
+                  <c:v>1.0537190082644627</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.68888888888888888</c:v>
+                  <c:v>1.0088383838383839</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.95333333333333337</c:v>
+                  <c:v>0.97443181818181823</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.87037037037037035</c:v>
+                  <c:v>0.79242424242424248</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.94</c:v>
+                  <c:v>0.43039772727272729</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.1933333333333334</c:v>
+                  <c:v>0.37926136363636365</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.92361111111111116</c:v>
+                  <c:v>0.36969696969696969</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.93181818181818177</c:v>
+                  <c:v>0.25852272727272729</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.9907407407407407</c:v>
+                  <c:v>0.22727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.86842105263157898</c:v>
+                  <c:v>0.18545454545454546</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -996,40 +1037,40 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.4055121527777778</c:v>
+                  <c:v>1.6474837662337662</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.29181547619047621</c:v>
+                  <c:v>1.4303891184573003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.21289682539682539</c:v>
+                  <c:v>0.93027872305947168</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11037037037037037</c:v>
+                  <c:v>0.77790156466627058</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.18450793650793651</c:v>
+                  <c:v>0.52562388591800357</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.4104938271604937E-2</c:v>
+                  <c:v>0.61328282828282832</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.88180555555555551</c:v>
+                  <c:v>9.8697916666666663E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.4589722222222221</c:v>
+                  <c:v>6.5364583333333337E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0264219576719578</c:v>
+                  <c:v>9.0136660724896026E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.67572601010101008</c:v>
+                  <c:v>3.7026515151515151E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0784336419753087</c:v>
+                  <c:v>3.928872053872054E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.68479532163742685</c:v>
+                  <c:v>3.6942148760330577E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1177,40 +1218,40 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.79166666666666663</c:v>
+                  <c:v>1.6248308982683983</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.52802579365079361</c:v>
+                  <c:v>1.3619146005509641</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.54389880952380953</c:v>
+                  <c:v>0.95186272524802595</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.31732804232804235</c:v>
+                  <c:v>0.79917017587317318</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.96047619047619048</c:v>
+                  <c:v>0.5418293363078639</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.59924768518518523</c:v>
+                  <c:v>0.66029040404040407</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.86236111111111113</c:v>
+                  <c:v>0.10292376893939394</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.153125</c:v>
+                  <c:v>6.8714488636363633E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.85945767195767198</c:v>
+                  <c:v>8.3333333333333329E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.77541035353535348</c:v>
+                  <c:v>3.7109375E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.99807098765432101</c:v>
+                  <c:v>3.8457491582491579E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.70175438596491224</c:v>
+                  <c:v>3.8223140495867766E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2077,7 +2118,67 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Top 3 Concerns</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> by Room Type and Month</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -2088,11 +2189,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Revenue Dash'!$B$5</c:f>
+              <c:f>'Concerns Dash'!$B$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Room Revenue</c:v>
+                  <c:v>#1 Temperature of their room</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2100,7 +2201,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent6"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2109,150 +2210,47 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'Revenue Dash'!$E$6:$E$17</c:f>
+              <c:f>'Concerns Dash'!$B$6:$B$17</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>97</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Revenue Dash'!$B$6:$B$17</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>0.96875</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0119047619047619</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.89583333333333337</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.68888888888888888</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.95333333333333337</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.87037037037037035</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.94</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.1933333333333334</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.92361111111111116</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.93181818181818177</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.9907407407407407</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.86842105263157898</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2260,7 +2258,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0600-42E3-ADDF-5AF8218284DB}"/>
+              <c16:uniqueId val="{00000000-9164-4427-AEB9-FC14E48A8528}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2269,11 +2267,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Revenue Dash'!$C$5</c:f>
+              <c:f>'Concerns Dash'!$C$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Food Revenue</c:v>
+                  <c:v>#2 Noisy neighbors</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2281,7 +2279,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2290,150 +2288,47 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'Revenue Dash'!$E$6:$E$17</c:f>
+              <c:f>'Concerns Dash'!$C$6:$C$17</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
                 <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Revenue Dash'!$C$6:$C$17</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>0.4055121527777778</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.29181547619047621</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.21289682539682539</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.11037037037037037</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.18450793650793651</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>8.4104938271604937E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.88180555555555551</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.4589722222222221</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.0264219576719578</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.67572601010101008</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.0784336419753087</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.68479532163742685</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2441,7 +2336,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0600-42E3-ADDF-5AF8218284DB}"/>
+              <c16:uniqueId val="{00000001-9164-4427-AEB9-FC14E48A8528}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2450,11 +2345,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Revenue Dash'!$D$5</c:f>
+              <c:f>'Concerns Dash'!$D$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Bar Revenue</c:v>
+                  <c:v>#3 Bad smells</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2462,7 +2357,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:schemeClr val="accent3"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2471,150 +2366,47 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'Revenue Dash'!$E$6:$E$17</c:f>
+              <c:f>'Concerns Dash'!$D$6:$D$17</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Revenue Dash'!$D$6:$D$17</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>0.79166666666666663</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.52802579365079361</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.54389880952380953</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.31732804232804235</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.96047619047619048</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.59924768518518523</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.86236111111111113</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.153125</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.85945767195767198</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.77541035353535348</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.99807098765432101</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.70175438596491224</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2622,147 +2414,21 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-0600-42E3-ADDF-5AF8218284DB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>'Revenue Dash'!$J$6:$J$17</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.9</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-0600-42E3-ADDF-5AF8218284DB}"/>
+              <c16:uniqueId val="{00000002-9164-4427-AEB9-FC14E48A8528}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="589614264"/>
-        <c:axId val="589614904"/>
+        <c:axId val="523003536"/>
+        <c:axId val="523003856"/>
         <c:extLst>
           <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
             <c15:filteredLineSeries>
@@ -2774,7 +2440,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Revenue Dash'!$E$5</c15:sqref>
+                          <c15:sqref>'Concerns Dash'!$E$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2789,9 +2455,7 @@
                 <c:spPr>
                   <a:ln w="28575" cap="rnd">
                     <a:solidFill>
-                      <a:schemeClr val="accent6">
-                        <a:lumMod val="60000"/>
-                      </a:schemeClr>
+                      <a:schemeClr val="accent4"/>
                     </a:solidFill>
                     <a:round/>
                   </a:ln>
@@ -2800,121 +2464,12 @@
                 <c:marker>
                   <c:symbol val="none"/>
                 </c:marker>
-                <c:dLbls>
-                  <c:spPr>
-                    <a:noFill/>
-                    <a:ln>
-                      <a:noFill/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                  <c:txPr>
-                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                      <a:spAutoFit/>
-                    </a:bodyPr>
-                    <a:lstStyle/>
-                    <a:p>
-                      <a:pPr>
-                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                          <a:solidFill>
-                            <a:schemeClr val="tx1">
-                              <a:lumMod val="75000"/>
-                              <a:lumOff val="25000"/>
-                            </a:schemeClr>
-                          </a:solidFill>
-                          <a:latin typeface="+mn-lt"/>
-                          <a:ea typeface="+mn-ea"/>
-                          <a:cs typeface="+mn-cs"/>
-                        </a:defRPr>
-                      </a:pPr>
-                      <a:endParaRPr lang="en-US"/>
-                    </a:p>
-                  </c:txPr>
-                  <c:dLblPos val="ctr"/>
-                  <c:showLegendKey val="0"/>
-                  <c:showVal val="1"/>
-                  <c:showCatName val="0"/>
-                  <c:showSerName val="0"/>
-                  <c:showPercent val="0"/>
-                  <c:showBubbleSize val="0"/>
-                  <c:showLeaderLines val="0"/>
-                  <c:extLst>
-                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                      <c15:showLeaderLines val="1"/>
-                      <c15:leaderLines>
-                        <c:spPr>
-                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                            <a:solidFill>
-                              <a:schemeClr val="tx1">
-                                <a:lumMod val="35000"/>
-                                <a:lumOff val="65000"/>
-                              </a:schemeClr>
-                            </a:solidFill>
-                            <a:round/>
-                          </a:ln>
-                          <a:effectLst/>
-                        </c:spPr>
-                      </c15:leaderLines>
-                    </c:ext>
-                  </c:extLst>
-                </c:dLbls>
-                <c:cat>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Revenue Dash'!$E$6:$E$17</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="12"/>
-                      <c:pt idx="0">
-                        <c:v>1</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>2</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>3</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>4</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>5</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>6</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>7</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>8</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>9</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>10</c:v>
-                      </c:pt>
-                      <c:pt idx="10">
-                        <c:v>11</c:v>
-                      </c:pt>
-                      <c:pt idx="11">
-                        <c:v>12</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:cat>
                 <c:val>
                   <c:numRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Revenue Dash'!$E$6:$E$17</c15:sqref>
+                          <c15:sqref>'Concerns Dash'!$E$6:$E$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2963,7 +2518,7 @@
                 <c:smooth val="0"/>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000004-0600-42E3-ADDF-5AF8218284DB}"/>
+                    <c16:uniqueId val="{00000003-9164-4427-AEB9-FC14E48A8528}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -2972,13 +2527,12 @@
         </c:extLst>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="589614264"/>
+        <c:axId val="523003536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3015,7 +2569,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="589614904"/>
+        <c:crossAx val="523003856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3023,7 +2577,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="589614904"/>
+        <c:axId val="523003856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3043,7 +2597,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3074,7 +2628,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="589614264"/>
+        <c:crossAx val="523003536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6283,10 +5837,13 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent6"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent4"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -11343,28 +10900,26 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>336550</xdr:colOff>
+      <xdr:colOff>219074</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:rowOff>82550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>260349</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="차트 5">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A982CA32-023A-40E5-8CBB-9DAC946D9F57}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2BA64F7-F7D1-102E-923A-6F7F25D6B59A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -12737,16 +12292,16 @@
   <sheetData>
     <row r="6" spans="3:9">
       <c r="C6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="3:9">
@@ -12754,7 +12309,7 @@
         <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="3:9">
@@ -12762,7 +12317,7 @@
         <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="3:9">
@@ -12770,7 +12325,7 @@
         <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="3:9">
@@ -12807,56 +12362,56 @@
   <sheetData>
     <row r="1" spans="2:15" s="10" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B1" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="2:15">
       <c r="B3" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="E3" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="J3" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="K3" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="N3" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="O3" s="11" t="s">
         <v>58</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -12874,7 +12429,7 @@
     </row>
     <row r="5" spans="2:15">
       <c r="B5" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C5">
         <v>28</v>
@@ -12915,7 +12470,7 @@
     </row>
     <row r="6" spans="2:15">
       <c r="B6" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2">
         <v>304164</v>
@@ -12959,7 +12514,7 @@
     </row>
     <row r="7" spans="2:15">
       <c r="B7" s="15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2">
         <v>214200</v>
@@ -13003,7 +12558,7 @@
     </row>
     <row r="8" spans="2:15">
       <c r="B8" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C8" s="2">
         <v>64260</v>
@@ -13047,7 +12602,7 @@
     </row>
     <row r="9" spans="2:15">
       <c r="B9" s="15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C9" s="2">
         <v>25704</v>
@@ -13091,7 +12646,7 @@
     </row>
     <row r="10" spans="2:15" s="20" customFormat="1">
       <c r="B10" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C10" s="18">
         <v>31</v>
@@ -13133,7 +12688,7 @@
     </row>
     <row r="11" spans="2:15" s="20" customFormat="1">
       <c r="B11" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C11" s="18">
         <f>C6/C10/C5</f>
@@ -13187,7 +12742,7 @@
     </row>
     <row r="12" spans="2:15">
       <c r="B12" s="12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
@@ -13205,7 +12760,7 @@
     </row>
     <row r="13" spans="2:15">
       <c r="B13" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C13">
         <v>36</v>
@@ -13249,7 +12804,7 @@
     </row>
     <row r="14" spans="2:15">
       <c r="B14" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2">
         <v>383400</v>
@@ -13293,7 +12848,7 @@
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C15" s="2">
         <v>270000</v>
@@ -13337,7 +12892,7 @@
     </row>
     <row r="16" spans="2:15">
       <c r="B16" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C16" s="2">
         <v>81000</v>
@@ -13381,7 +12936,7 @@
     </row>
     <row r="17" spans="2:15">
       <c r="B17" s="15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C17" s="2">
         <v>32400</v>
@@ -13425,7 +12980,7 @@
     </row>
     <row r="18" spans="2:15" s="20" customFormat="1">
       <c r="B18" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C18" s="18">
         <v>31</v>
@@ -13467,7 +13022,7 @@
     </row>
     <row r="19" spans="2:15" s="20" customFormat="1">
       <c r="B19" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C19" s="18">
         <f>C14/C18/C13</f>
@@ -13521,7 +13076,7 @@
     </row>
     <row r="20" spans="2:15">
       <c r="B20" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -13539,7 +13094,7 @@
     </row>
     <row r="21" spans="2:15">
       <c r="B21" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C21">
         <v>44</v>
@@ -13583,7 +13138,7 @@
     </row>
     <row r="22" spans="2:15">
       <c r="B22" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C22" s="2">
         <v>349888</v>
@@ -13627,7 +13182,7 @@
     </row>
     <row r="23" spans="2:15">
       <c r="B23" s="15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C23" s="2">
         <v>246400</v>
@@ -13671,7 +13226,7 @@
     </row>
     <row r="24" spans="2:15">
       <c r="B24" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C24" s="2">
         <v>73920</v>
@@ -13715,7 +13270,7 @@
     </row>
     <row r="25" spans="2:15">
       <c r="B25" s="15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C25" s="2">
         <v>29568</v>
@@ -13759,7 +13314,7 @@
     </row>
     <row r="26" spans="2:15" s="20" customFormat="1">
       <c r="B26" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C26" s="18">
         <v>31</v>
@@ -13801,7 +13356,7 @@
     </row>
     <row r="27" spans="2:15" s="20" customFormat="1">
       <c r="B27" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C27" s="18">
         <f>C22/C26/C21</f>
@@ -13855,7 +13410,7 @@
     </row>
     <row r="28" spans="2:15">
       <c r="B28" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -13873,7 +13428,7 @@
     </row>
     <row r="29" spans="2:15">
       <c r="B29" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -13917,7 +13472,7 @@
     </row>
     <row r="30" spans="2:15">
       <c r="B30" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2">
         <v>144840</v>
@@ -13961,7 +13516,7 @@
     </row>
     <row r="31" spans="2:15">
       <c r="B31" s="15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2">
         <v>102000</v>
@@ -14005,7 +13560,7 @@
     </row>
     <row r="32" spans="2:15">
       <c r="B32" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C32" s="2">
         <v>30600</v>
@@ -14049,7 +13604,7 @@
     </row>
     <row r="33" spans="2:15">
       <c r="B33" s="15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C33" s="2">
         <v>12240</v>
@@ -14093,7 +13648,7 @@
     </row>
     <row r="34" spans="2:15" s="20" customFormat="1">
       <c r="B34" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C34" s="18">
         <v>31</v>
@@ -14135,7 +13690,7 @@
     </row>
     <row r="35" spans="2:15" s="20" customFormat="1">
       <c r="B35" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C35" s="18">
         <f>C30/C34/C29</f>
@@ -14189,7 +13744,7 @@
     </row>
     <row r="36" spans="2:15">
       <c r="B36" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -14207,7 +13762,7 @@
     </row>
     <row r="37" spans="2:15">
       <c r="B37" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C37">
         <v>6</v>
@@ -14251,7 +13806,7 @@
     </row>
     <row r="38" spans="2:15">
       <c r="B38" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C38" s="2">
         <v>109056</v>
@@ -14295,7 +13850,7 @@
     </row>
     <row r="39" spans="2:15">
       <c r="B39" s="15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C39" s="2">
         <v>76800</v>
@@ -14339,7 +13894,7 @@
     </row>
     <row r="40" spans="2:15">
       <c r="B40" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C40" s="2">
         <v>23040</v>
@@ -14383,7 +13938,7 @@
     </row>
     <row r="41" spans="2:15">
       <c r="B41" s="15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C41" s="2">
         <v>9216</v>
@@ -14427,7 +13982,7 @@
     </row>
     <row r="42" spans="2:15" s="20" customFormat="1">
       <c r="B42" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C42" s="18">
         <v>31</v>
@@ -14469,7 +14024,7 @@
     </row>
     <row r="43" spans="2:15" s="20" customFormat="1">
       <c r="B43" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C43" s="18">
         <f>C38/C42/C37</f>
@@ -14523,7 +14078,7 @@
     </row>
     <row r="44" spans="2:15">
       <c r="B44" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
@@ -14541,7 +14096,7 @@
     </row>
     <row r="45" spans="2:15">
       <c r="B45" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C45">
         <v>76</v>
@@ -14585,7 +14140,7 @@
     </row>
     <row r="46" spans="2:15">
       <c r="B46" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C46" s="2">
         <v>307572</v>
@@ -14629,7 +14184,7 @@
     </row>
     <row r="47" spans="2:15">
       <c r="B47" s="15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C47" s="2">
         <v>216600</v>
@@ -14673,7 +14228,7 @@
     </row>
     <row r="48" spans="2:15">
       <c r="B48" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C48" s="2">
         <v>64980</v>
@@ -14717,7 +14272,7 @@
     </row>
     <row r="49" spans="2:15">
       <c r="B49" s="15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C49" s="2">
         <v>25992</v>
@@ -14761,7 +14316,7 @@
     </row>
     <row r="50" spans="2:15" s="20" customFormat="1">
       <c r="B50" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C50" s="18">
         <v>31</v>
@@ -14803,7 +14358,7 @@
     </row>
     <row r="51" spans="2:15" s="20" customFormat="1">
       <c r="B51" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C51" s="18">
         <f>C46/C50/C45</f>
@@ -14857,7 +14412,7 @@
     </row>
     <row r="52" spans="2:15">
       <c r="B52" s="21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C52" s="22">
         <v>200</v>
@@ -14901,7 +14456,7 @@
     </row>
     <row r="53" spans="2:15">
       <c r="B53" s="23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C53" s="16">
         <v>1598920</v>
@@ -14945,7 +14500,7 @@
     </row>
     <row r="54" spans="2:15">
       <c r="B54" s="23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C54" s="16">
         <v>1126000</v>
@@ -14989,7 +14544,7 @@
     </row>
     <row r="55" spans="2:15">
       <c r="B55" s="23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C55" s="16">
         <v>337800</v>
@@ -15033,7 +14588,7 @@
     </row>
     <row r="56" spans="2:15">
       <c r="B56" s="23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C56" s="16">
         <v>135120</v>
@@ -15077,7 +14632,7 @@
     </row>
     <row r="57" spans="2:15">
       <c r="B57" s="23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C57" s="24">
         <v>31</v>
@@ -15121,7 +14676,7 @@
     </row>
     <row r="58" spans="2:15" ht="15" thickBot="1">
       <c r="B58" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C58" s="26">
         <v>386.24</v>
@@ -15170,7 +14725,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73523379-831F-41E0-B5B2-536D4959CE04}">
-  <dimension ref="B2:J22"/>
+  <dimension ref="B2:J21"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="4.6328125" customWidth="1"/>
@@ -15188,12 +14743,12 @@
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="2:10" ht="29" thickBot="1">
-      <c r="B3" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
+      <c r="B3" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="34"/>
     </row>
     <row r="5" spans="2:10" ht="18.5">
       <c r="B5" s="8" t="s">
@@ -15213,15 +14768,15 @@
     <row r="6" spans="2:10" ht="15.5">
       <c r="B6" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M2,IF($B$3="King",'Revenue - Data'!M14,IF($B$3="Superior King",'Revenue - Data'!M26,IF($B$3="Executive",'Revenue - Data'!M38,IF($B$3="One Club",'Revenue - Data'!M50,'Revenue - Data'!M62)))))</f>
-        <v>0.96875</v>
+        <v>1.0811688311688312</v>
       </c>
       <c r="C6" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N2,IF($B$3="King",'Revenue - Data'!N14,IF($B$3="Superior King",'Revenue - Data'!N26,IF($B$3="Executive",'Revenue - Data'!N38,IF($B$3="One Club",'Revenue - Data'!N50,'Revenue - Data'!N62)))))</f>
-        <v>0.4055121527777778</v>
+        <v>1.6474837662337662</v>
       </c>
       <c r="D6" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O2,IF($B$3="King",'Revenue - Data'!O14,IF($B$3="Superior King",'Revenue - Data'!O26,IF($B$3="Executive",'Revenue - Data'!O38,IF($B$3="One Club",'Revenue - Data'!O50,'Revenue - Data'!O62)))))</f>
-        <v>0.79166666666666663</v>
+        <v>1.6248308982683983</v>
       </c>
       <c r="E6" s="7">
         <v>1</v>
@@ -15233,15 +14788,15 @@
     <row r="7" spans="2:10" ht="15.5">
       <c r="B7" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M3,IF($B$3="King",'Revenue - Data'!M15,IF($B$3="Superior King",'Revenue - Data'!M27,IF($B$3="Executive",'Revenue - Data'!M39,IF($B$3="One Club",'Revenue - Data'!M51,'Revenue - Data'!M63)))))</f>
-        <v>1.0119047619047619</v>
+        <v>1.1353305785123966</v>
       </c>
       <c r="C7" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N3,IF($B$3="King",'Revenue - Data'!N15,IF($B$3="Superior King",'Revenue - Data'!N27,IF($B$3="Executive",'Revenue - Data'!N39,IF($B$3="One Club",'Revenue - Data'!N51,'Revenue - Data'!N63)))))</f>
-        <v>0.29181547619047621</v>
+        <v>1.4303891184573003</v>
       </c>
       <c r="D7" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O3,IF($B$3="King",'Revenue - Data'!O15,IF($B$3="Superior King",'Revenue - Data'!O27,IF($B$3="Executive",'Revenue - Data'!O39,IF($B$3="One Club",'Revenue - Data'!O51,'Revenue - Data'!O63)))))</f>
-        <v>0.52802579365079361</v>
+        <v>1.3619146005509641</v>
       </c>
       <c r="E7" s="7">
         <v>2</v>
@@ -15253,15 +14808,15 @@
     <row r="8" spans="2:10" ht="15.5">
       <c r="B8" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M4,IF($B$3="King",'Revenue - Data'!M16,IF($B$3="Superior King",'Revenue - Data'!M28,IF($B$3="Executive",'Revenue - Data'!M40,IF($B$3="One Club",'Revenue - Data'!M52,'Revenue - Data'!M64)))))</f>
-        <v>0.89583333333333337</v>
+        <v>1.0537190082644627</v>
       </c>
       <c r="C8" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N4,IF($B$3="King",'Revenue - Data'!N16,IF($B$3="Superior King",'Revenue - Data'!N28,IF($B$3="Executive",'Revenue - Data'!N40,IF($B$3="One Club",'Revenue - Data'!N52,'Revenue - Data'!N64)))))</f>
-        <v>0.21289682539682539</v>
+        <v>0.93027872305947168</v>
       </c>
       <c r="D8" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O4,IF($B$3="King",'Revenue - Data'!O16,IF($B$3="Superior King",'Revenue - Data'!O28,IF($B$3="Executive",'Revenue - Data'!O40,IF($B$3="One Club",'Revenue - Data'!O52,'Revenue - Data'!O64)))))</f>
-        <v>0.54389880952380953</v>
+        <v>0.95186272524802595</v>
       </c>
       <c r="E8" s="7">
         <v>3</v>
@@ -15273,15 +14828,15 @@
     <row r="9" spans="2:10" ht="15.5">
       <c r="B9" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M5,IF($B$3="King",'Revenue - Data'!M17,IF($B$3="Superior King",'Revenue - Data'!M29,IF($B$3="Executive",'Revenue - Data'!M41,IF($B$3="One Club",'Revenue - Data'!M53,'Revenue - Data'!M65)))))</f>
-        <v>0.68888888888888888</v>
+        <v>1.0088383838383839</v>
       </c>
       <c r="C9" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N5,IF($B$3="King",'Revenue - Data'!N17,IF($B$3="Superior King",'Revenue - Data'!N29,IF($B$3="Executive",'Revenue - Data'!N41,IF($B$3="One Club",'Revenue - Data'!N53,'Revenue - Data'!N65)))))</f>
-        <v>0.11037037037037037</v>
+        <v>0.77790156466627058</v>
       </c>
       <c r="D9" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O5,IF($B$3="King",'Revenue - Data'!O17,IF($B$3="Superior King",'Revenue - Data'!O29,IF($B$3="Executive",'Revenue - Data'!O41,IF($B$3="One Club",'Revenue - Data'!O53,'Revenue - Data'!O65)))))</f>
-        <v>0.31732804232804235</v>
+        <v>0.79917017587317318</v>
       </c>
       <c r="E9" s="7">
         <v>4</v>
@@ -15293,15 +14848,15 @@
     <row r="10" spans="2:10" ht="15.5">
       <c r="B10" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M6,IF($B$3="King",'Revenue - Data'!M18,IF($B$3="Superior King",'Revenue - Data'!M30,IF($B$3="Executive",'Revenue - Data'!M42,IF($B$3="One Club",'Revenue - Data'!M54,'Revenue - Data'!M66)))))</f>
-        <v>0.95333333333333337</v>
+        <v>0.97443181818181823</v>
       </c>
       <c r="C10" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N6,IF($B$3="King",'Revenue - Data'!N18,IF($B$3="Superior King",'Revenue - Data'!N30,IF($B$3="Executive",'Revenue - Data'!N42,IF($B$3="One Club",'Revenue - Data'!N54,'Revenue - Data'!N66)))))</f>
-        <v>0.18450793650793651</v>
+        <v>0.52562388591800357</v>
       </c>
       <c r="D10" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O6,IF($B$3="King",'Revenue - Data'!O18,IF($B$3="Superior King",'Revenue - Data'!O30,IF($B$3="Executive",'Revenue - Data'!O42,IF($B$3="One Club",'Revenue - Data'!O54,'Revenue - Data'!O66)))))</f>
-        <v>0.96047619047619048</v>
+        <v>0.5418293363078639</v>
       </c>
       <c r="E10" s="7">
         <v>5</v>
@@ -15313,15 +14868,15 @@
     <row r="11" spans="2:10" ht="15.5">
       <c r="B11" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M7,IF($B$3="King",'Revenue - Data'!M19,IF($B$3="Superior King",'Revenue - Data'!M31,IF($B$3="Executive",'Revenue - Data'!M43,IF($B$3="One Club",'Revenue - Data'!M55,'Revenue - Data'!M67)))))</f>
-        <v>0.87037037037037035</v>
+        <v>0.79242424242424248</v>
       </c>
       <c r="C11" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N7,IF($B$3="King",'Revenue - Data'!N19,IF($B$3="Superior King",'Revenue - Data'!N31,IF($B$3="Executive",'Revenue - Data'!N43,IF($B$3="One Club",'Revenue - Data'!N55,'Revenue - Data'!N67)))))</f>
-        <v>8.4104938271604937E-2</v>
+        <v>0.61328282828282832</v>
       </c>
       <c r="D11" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O7,IF($B$3="King",'Revenue - Data'!O19,IF($B$3="Superior King",'Revenue - Data'!O31,IF($B$3="Executive",'Revenue - Data'!O43,IF($B$3="One Club",'Revenue - Data'!O55,'Revenue - Data'!O67)))))</f>
-        <v>0.59924768518518523</v>
+        <v>0.66029040404040407</v>
       </c>
       <c r="E11" s="7">
         <v>6</v>
@@ -15333,15 +14888,15 @@
     <row r="12" spans="2:10" ht="15.5">
       <c r="B12" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M8,IF($B$3="King",'Revenue - Data'!M20,IF($B$3="Superior King",'Revenue - Data'!M32,IF($B$3="Executive",'Revenue - Data'!M44,IF($B$3="One Club",'Revenue - Data'!M56,'Revenue - Data'!M68)))))</f>
-        <v>0.94</v>
+        <v>0.43039772727272729</v>
       </c>
       <c r="C12" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N8,IF($B$3="King",'Revenue - Data'!N20,IF($B$3="Superior King",'Revenue - Data'!N32,IF($B$3="Executive",'Revenue - Data'!N44,IF($B$3="One Club",'Revenue - Data'!N56,'Revenue - Data'!N68)))))</f>
-        <v>0.88180555555555551</v>
+        <v>9.8697916666666663E-2</v>
       </c>
       <c r="D12" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O8,IF($B$3="King",'Revenue - Data'!O20,IF($B$3="Superior King",'Revenue - Data'!O32,IF($B$3="Executive",'Revenue - Data'!O44,IF($B$3="One Club",'Revenue - Data'!O56,'Revenue - Data'!O68)))))</f>
-        <v>0.86236111111111113</v>
+        <v>0.10292376893939394</v>
       </c>
       <c r="E12" s="7">
         <v>7</v>
@@ -15353,15 +14908,15 @@
     <row r="13" spans="2:10" ht="15.5">
       <c r="B13" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M9,IF($B$3="King",'Revenue - Data'!M21,IF($B$3="Superior King",'Revenue - Data'!M33,IF($B$3="Executive",'Revenue - Data'!M45,IF($B$3="One Club",'Revenue - Data'!M57,'Revenue - Data'!M69)))))</f>
-        <v>1.1933333333333334</v>
+        <v>0.37926136363636365</v>
       </c>
       <c r="C13" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N9,IF($B$3="King",'Revenue - Data'!N21,IF($B$3="Superior King",'Revenue - Data'!N33,IF($B$3="Executive",'Revenue - Data'!N45,IF($B$3="One Club",'Revenue - Data'!N57,'Revenue - Data'!N69)))))</f>
-        <v>1.4589722222222221</v>
+        <v>6.5364583333333337E-2</v>
       </c>
       <c r="D13" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O9,IF($B$3="King",'Revenue - Data'!O21,IF($B$3="Superior King",'Revenue - Data'!O33,IF($B$3="Executive",'Revenue - Data'!O45,IF($B$3="One Club",'Revenue - Data'!O57,'Revenue - Data'!O69)))))</f>
-        <v>1.153125</v>
+        <v>6.8714488636363633E-2</v>
       </c>
       <c r="E13" s="7">
         <v>8</v>
@@ -15373,15 +14928,15 @@
     <row r="14" spans="2:10" ht="15.5">
       <c r="B14" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M10,IF($B$3="King",'Revenue - Data'!M22,IF($B$3="Superior King",'Revenue - Data'!M34,IF($B$3="Executive",'Revenue - Data'!M46,IF($B$3="One Club",'Revenue - Data'!M58,'Revenue - Data'!M70)))))</f>
-        <v>0.92361111111111116</v>
+        <v>0.36969696969696969</v>
       </c>
       <c r="C14" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N10,IF($B$3="King",'Revenue - Data'!N22,IF($B$3="Superior King",'Revenue - Data'!N34,IF($B$3="Executive",'Revenue - Data'!N46,IF($B$3="One Club",'Revenue - Data'!N58,'Revenue - Data'!N70)))))</f>
-        <v>1.0264219576719578</v>
+        <v>9.0136660724896026E-2</v>
       </c>
       <c r="D14" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O10,IF($B$3="King",'Revenue - Data'!O22,IF($B$3="Superior King",'Revenue - Data'!O34,IF($B$3="Executive",'Revenue - Data'!O46,IF($B$3="One Club",'Revenue - Data'!O58,'Revenue - Data'!O70)))))</f>
-        <v>0.85945767195767198</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="E14" s="7">
         <v>9</v>
@@ -15393,15 +14948,15 @@
     <row r="15" spans="2:10" ht="15.5">
       <c r="B15" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M11,IF($B$3="King",'Revenue - Data'!M23,IF($B$3="Superior King",'Revenue - Data'!M35,IF($B$3="Executive",'Revenue - Data'!M47,IF($B$3="One Club",'Revenue - Data'!M59,'Revenue - Data'!M71)))))</f>
-        <v>0.93181818181818177</v>
+        <v>0.25852272727272729</v>
       </c>
       <c r="C15" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N11,IF($B$3="King",'Revenue - Data'!N23,IF($B$3="Superior King",'Revenue - Data'!N35,IF($B$3="Executive",'Revenue - Data'!N47,IF($B$3="One Club",'Revenue - Data'!N59,'Revenue - Data'!N71)))))</f>
-        <v>0.67572601010101008</v>
+        <v>3.7026515151515151E-2</v>
       </c>
       <c r="D15" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O11,IF($B$3="King",'Revenue - Data'!O23,IF($B$3="Superior King",'Revenue - Data'!O35,IF($B$3="Executive",'Revenue - Data'!O47,IF($B$3="One Club",'Revenue - Data'!O59,'Revenue - Data'!O71)))))</f>
-        <v>0.77541035353535348</v>
+        <v>3.7109375E-2</v>
       </c>
       <c r="E15" s="7">
         <v>10</v>
@@ -15413,15 +14968,15 @@
     <row r="16" spans="2:10" ht="15.5">
       <c r="B16" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M12,IF($B$3="King",'Revenue - Data'!M24,IF($B$3="Superior King",'Revenue - Data'!M36,IF($B$3="Executive",'Revenue - Data'!M48,IF($B$3="One Club",'Revenue - Data'!M60,'Revenue - Data'!M72)))))</f>
-        <v>0.9907407407407407</v>
+        <v>0.22727272727272727</v>
       </c>
       <c r="C16" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N12,IF($B$3="King",'Revenue - Data'!N24,IF($B$3="Superior King",'Revenue - Data'!N36,IF($B$3="Executive",'Revenue - Data'!N48,IF($B$3="One Club",'Revenue - Data'!N60,'Revenue - Data'!N72)))))</f>
-        <v>1.0784336419753087</v>
+        <v>3.928872053872054E-2</v>
       </c>
       <c r="D16" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O12,IF($B$3="King",'Revenue - Data'!O24,IF($B$3="Superior King",'Revenue - Data'!O36,IF($B$3="Executive",'Revenue - Data'!O48,IF($B$3="One Club",'Revenue - Data'!O60,'Revenue - Data'!O72)))))</f>
-        <v>0.99807098765432101</v>
+        <v>3.8457491582491579E-2</v>
       </c>
       <c r="E16" s="7">
         <v>11</v>
@@ -15433,15 +14988,15 @@
     <row r="17" spans="2:10" ht="15.5">
       <c r="B17" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!M13,IF($B$3="King",'Revenue - Data'!M25,IF($B$3="Superior King",'Revenue - Data'!M37,IF($B$3="Executive",'Revenue - Data'!M49,IF($B$3="One Club",'Revenue - Data'!M61,'Revenue - Data'!M73)))))</f>
-        <v>0.86842105263157898</v>
+        <v>0.18545454545454546</v>
       </c>
       <c r="C17" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!N13,IF($B$3="King",'Revenue - Data'!N25,IF($B$3="Superior King",'Revenue - Data'!N37,IF($B$3="Executive",'Revenue - Data'!N49,IF($B$3="One Club",'Revenue - Data'!N61,'Revenue - Data'!N73)))))</f>
-        <v>0.68479532163742685</v>
+        <v>3.6942148760330577E-2</v>
       </c>
       <c r="D17" s="6">
         <f>IF($B$3="Club Deluxe",'Revenue - Data'!O13,IF($B$3="King",'Revenue - Data'!O25,IF($B$3="Superior King",'Revenue - Data'!O37,IF($B$3="Executive",'Revenue - Data'!O49,IF($B$3="One Club",'Revenue - Data'!O61,'Revenue - Data'!O73)))))</f>
-        <v>0.70175438596491224</v>
+        <v>3.8223140495867766E-2</v>
       </c>
       <c r="E17" s="7">
         <v>12</v>
@@ -15450,27 +15005,27 @@
         <v>0.9</v>
       </c>
     </row>
+    <row r="19" spans="2:10">
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+    </row>
     <row r="20" spans="2:10">
       <c r="B20" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="2:10">
       <c r="B21" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" t="s">
         <v>35</v>
       </c>
     </row>
@@ -15503,7 +15058,7 @@
   <sheetData>
     <row r="4" spans="3:4">
       <c r="C4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -15511,7 +15066,7 @@
     </row>
     <row r="5" spans="3:4">
       <c r="C5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -15535,7 +15090,7 @@
     </row>
     <row r="8" spans="3:4">
       <c r="C8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D8">
         <v>70</v>
@@ -15543,7 +15098,7 @@
     </row>
     <row r="9" spans="3:4">
       <c r="C9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -15551,7 +15106,7 @@
     </row>
     <row r="10" spans="3:4">
       <c r="C10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D10">
         <v>50</v>
@@ -15565,16 +15120,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA41081-7588-469A-AFDA-DD303C470471}">
-  <dimension ref="B2:J22"/>
+  <dimension ref="B2:E22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="4.6328125" customWidth="1"/>
-    <col min="2" max="4" width="17.54296875" customWidth="1"/>
-    <col min="5" max="5" width="11.36328125" customWidth="1"/>
+    <col min="2" max="4" width="21.1796875" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" customWidth="1"/>
     <col min="7" max="7" width="17.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="16" thickBot="1">
+    <row r="2" spans="2:5" ht="16" thickBot="1">
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
@@ -15582,294 +15137,262 @@
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="2:10" ht="29" thickBot="1">
-      <c r="B3" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-    </row>
-    <row r="5" spans="2:10" ht="18.5">
-      <c r="B5" s="6" t="str">
-        <f>IF($B$3="Club Deluxe",'Concerns dash data'!C2,IF($B$3="King",'Revenue - Data'!M13,IF($B$3="Superior King",'Revenue - Data'!M25,IF($B$3="Executive",'Revenue - Data'!M37,IF($B$3="One Club",'Revenue - Data'!M49,'Revenue - Data'!M61)))))</f>
-        <v>Faulty electronics</v>
-      </c>
-      <c r="C5" s="6" t="str">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N1,IF($B$3="King",'Revenue - Data'!N13,IF($B$3="Superior King",'Revenue - Data'!N25,IF($B$3="Executive",'Revenue - Data'!N37,IF($B$3="One Club",'Revenue - Data'!N49,'Revenue - Data'!N61)))))</f>
-        <v>PercentFood</v>
-      </c>
-      <c r="D5" s="6" t="str">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O1,IF($B$3="King",'Revenue - Data'!O13,IF($B$3="Superior King",'Revenue - Data'!O25,IF($B$3="Executive",'Revenue - Data'!O37,IF($B$3="One Club",'Revenue - Data'!O49,'Revenue - Data'!O61)))))</f>
-        <v>PercentBar</v>
-      </c>
-      <c r="E5" s="8" t="s">
+    <row r="3" spans="2:5" ht="29" thickBot="1">
+      <c r="B3" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="34"/>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5" s="29" t="str">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!F2,IF($B$3="King",'Concerns dash data'!F26,IF($B$3="Superior King",'Concerns dash data'!F62,IF($B$3="Executive",'Concerns dash data'!F14,IF($B$3="One Club",'Concerns dash data'!F38,'Concerns dash data'!F50)))))</f>
+        <v>#1 Temperature of their room</v>
+      </c>
+      <c r="C5" s="29" t="str">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!G2,IF($B$3="King",'Concerns dash data'!G26,IF($B$3="Superior King",'Concerns dash data'!G62,IF($B$3="Executive",'Concerns dash data'!G14,IF($B$3="One Club",'Concerns dash data'!G38,'Concerns dash data'!G50)))))</f>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="D5" s="29" t="str">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!H2,IF($B$3="King",'Concerns dash data'!H26,IF($B$3="Superior King",'Concerns dash data'!H62,IF($B$3="Executive",'Concerns dash data'!H14,IF($B$3="One Club",'Concerns dash data'!H38,'Concerns dash data'!H50)))))</f>
+        <v>#3 Bad smells</v>
+      </c>
+      <c r="E5" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="2:10" ht="15.5">
-      <c r="B6" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M2,IF($B$3="King",'Revenue - Data'!M14,IF($B$3="Superior King",'Revenue - Data'!M26,IF($B$3="Executive",'Revenue - Data'!M38,IF($B$3="One Club",'Revenue - Data'!M50,'Revenue - Data'!M62)))))</f>
-        <v>0.95798319327731096</v>
-      </c>
-      <c r="C6" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N2,IF($B$3="King",'Revenue - Data'!N14,IF($B$3="Superior King",'Revenue - Data'!N26,IF($B$3="Executive",'Revenue - Data'!N38,IF($B$3="One Club",'Revenue - Data'!N50,'Revenue - Data'!N62)))))</f>
-        <v>0.4710706504824152</v>
-      </c>
-      <c r="D6" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O2,IF($B$3="King",'Revenue - Data'!O14,IF($B$3="Superior King",'Revenue - Data'!O26,IF($B$3="Executive",'Revenue - Data'!O38,IF($B$3="One Club",'Revenue - Data'!O50,'Revenue - Data'!O62)))))</f>
-        <v>0.85154061624649857</v>
+    </row>
+    <row r="6" spans="2:5" ht="15.5">
+      <c r="B6" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!I2,IF($B$3="King",'Concerns dash data'!I26,IF($B$3="Superior King",'Concerns dash data'!I62,IF($B$3="Executive",'Concerns dash data'!I14,IF($B$3="One Club",'Concerns dash data'!I38,'Concerns dash data'!I50)))))</f>
+        <v>4</v>
+      </c>
+      <c r="C6" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!J2,IF($B$3="King",'Concerns dash data'!J26,IF($B$3="Superior King",'Concerns dash data'!J62,IF($B$3="Executive",'Concerns dash data'!J14,IF($B$3="One Club",'Concerns dash data'!J38,'Concerns dash data'!J50)))))</f>
+        <v>17</v>
+      </c>
+      <c r="D6" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!K2,IF($B$3="King",'Concerns dash data'!K26,IF($B$3="Superior King",'Concerns dash data'!K62,IF($B$3="Executive",'Concerns dash data'!K14,IF($B$3="One Club",'Concerns dash data'!K38,'Concerns dash data'!K50)))))</f>
+        <v>11</v>
       </c>
       <c r="E6" s="7">
         <v>1</v>
       </c>
-      <c r="J6" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" ht="15.5">
-      <c r="B7" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M3,IF($B$3="King",'Revenue - Data'!M15,IF($B$3="Superior King",'Revenue - Data'!M27,IF($B$3="Executive",'Revenue - Data'!M39,IF($B$3="One Club",'Revenue - Data'!M51,'Revenue - Data'!M63)))))</f>
-        <v>0.9732142857142857</v>
-      </c>
-      <c r="C7" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N3,IF($B$3="King",'Revenue - Data'!N15,IF($B$3="Superior King",'Revenue - Data'!N27,IF($B$3="Executive",'Revenue - Data'!N39,IF($B$3="One Club",'Revenue - Data'!N51,'Revenue - Data'!N63)))))</f>
-        <v>0.42544973544973547</v>
-      </c>
-      <c r="D7" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O3,IF($B$3="King",'Revenue - Data'!O15,IF($B$3="Superior King",'Revenue - Data'!O27,IF($B$3="Executive",'Revenue - Data'!O39,IF($B$3="One Club",'Revenue - Data'!O51,'Revenue - Data'!O63)))))</f>
-        <v>0.86908068783068781</v>
+    </row>
+    <row r="7" spans="2:5" ht="15.5">
+      <c r="B7" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!I3,IF($B$3="King",'Concerns dash data'!I27,IF($B$3="Superior King",'Concerns dash data'!I63,IF($B$3="Executive",'Concerns dash data'!I15,IF($B$3="One Club",'Concerns dash data'!I39,'Concerns dash data'!I51)))))</f>
+        <v>2</v>
+      </c>
+      <c r="C7" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!J3,IF($B$3="King",'Concerns dash data'!J27,IF($B$3="Superior King",'Concerns dash data'!J63,IF($B$3="Executive",'Concerns dash data'!J15,IF($B$3="One Club",'Concerns dash data'!J39,'Concerns dash data'!J51)))))</f>
+        <v>13</v>
+      </c>
+      <c r="D7" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!K3,IF($B$3="King",'Concerns dash data'!K27,IF($B$3="Superior King",'Concerns dash data'!K63,IF($B$3="Executive",'Concerns dash data'!K15,IF($B$3="One Club",'Concerns dash data'!K39,'Concerns dash data'!K51)))))</f>
+        <v>8</v>
       </c>
       <c r="E7" s="7">
         <v>2</v>
       </c>
-      <c r="J7" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" ht="15.5">
-      <c r="B8" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M4,IF($B$3="King",'Revenue - Data'!M16,IF($B$3="Superior King",'Revenue - Data'!M28,IF($B$3="Executive",'Revenue - Data'!M40,IF($B$3="One Club",'Revenue - Data'!M52,'Revenue - Data'!M64)))))</f>
-        <v>0.92729591836734693</v>
-      </c>
-      <c r="C8" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N4,IF($B$3="King",'Revenue - Data'!N16,IF($B$3="Superior King",'Revenue - Data'!N28,IF($B$3="Executive",'Revenue - Data'!N40,IF($B$3="One Club",'Revenue - Data'!N52,'Revenue - Data'!N64)))))</f>
-        <v>0.43664965986394561</v>
-      </c>
-      <c r="D8" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O4,IF($B$3="King",'Revenue - Data'!O16,IF($B$3="Superior King",'Revenue - Data'!O28,IF($B$3="Executive",'Revenue - Data'!O40,IF($B$3="One Club",'Revenue - Data'!O52,'Revenue - Data'!O64)))))</f>
-        <v>1.0997555272108843</v>
+    </row>
+    <row r="8" spans="2:5" ht="15.5">
+      <c r="B8" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!I4,IF($B$3="King",'Concerns dash data'!I28,IF($B$3="Superior King",'Concerns dash data'!I64,IF($B$3="Executive",'Concerns dash data'!I16,IF($B$3="One Club",'Concerns dash data'!I40,'Concerns dash data'!I52)))))</f>
+        <v>4</v>
+      </c>
+      <c r="C8" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!J4,IF($B$3="King",'Concerns dash data'!J28,IF($B$3="Superior King",'Concerns dash data'!J64,IF($B$3="Executive",'Concerns dash data'!J16,IF($B$3="One Club",'Concerns dash data'!J40,'Concerns dash data'!J52)))))</f>
+        <v>14</v>
+      </c>
+      <c r="D8" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!K4,IF($B$3="King",'Concerns dash data'!K28,IF($B$3="Superior King",'Concerns dash data'!K64,IF($B$3="Executive",'Concerns dash data'!K16,IF($B$3="One Club",'Concerns dash data'!K40,'Concerns dash data'!K52)))))</f>
+        <v>2</v>
       </c>
       <c r="E8" s="7">
         <v>3</v>
       </c>
-      <c r="J8" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" ht="15.5">
-      <c r="B9" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M5,IF($B$3="King",'Revenue - Data'!M17,IF($B$3="Superior King",'Revenue - Data'!M29,IF($B$3="Executive",'Revenue - Data'!M41,IF($B$3="One Club",'Revenue - Data'!M53,'Revenue - Data'!M65)))))</f>
-        <v>0.99068322981366463</v>
-      </c>
-      <c r="C9" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N5,IF($B$3="King",'Revenue - Data'!N17,IF($B$3="Superior King",'Revenue - Data'!N29,IF($B$3="Executive",'Revenue - Data'!N41,IF($B$3="One Club",'Revenue - Data'!N53,'Revenue - Data'!N65)))))</f>
-        <v>0.32637163561076604</v>
-      </c>
-      <c r="D9" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O5,IF($B$3="King",'Revenue - Data'!O17,IF($B$3="Superior King",'Revenue - Data'!O29,IF($B$3="Executive",'Revenue - Data'!O41,IF($B$3="One Club",'Revenue - Data'!O53,'Revenue - Data'!O65)))))</f>
-        <v>1.132214026915114</v>
+    </row>
+    <row r="9" spans="2:5" ht="15.5">
+      <c r="B9" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!I5,IF($B$3="King",'Concerns dash data'!I29,IF($B$3="Superior King",'Concerns dash data'!I65,IF($B$3="Executive",'Concerns dash data'!I17,IF($B$3="One Club",'Concerns dash data'!I41,'Concerns dash data'!I53)))))</f>
+        <v>2</v>
+      </c>
+      <c r="C9" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!J5,IF($B$3="King",'Concerns dash data'!J29,IF($B$3="Superior King",'Concerns dash data'!J65,IF($B$3="Executive",'Concerns dash data'!J17,IF($B$3="One Club",'Concerns dash data'!J41,'Concerns dash data'!J53)))))</f>
+        <v>8</v>
+      </c>
+      <c r="D9" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!K5,IF($B$3="King",'Concerns dash data'!K29,IF($B$3="Superior King",'Concerns dash data'!K65,IF($B$3="Executive",'Concerns dash data'!K17,IF($B$3="One Club",'Concerns dash data'!K41,'Concerns dash data'!K53)))))</f>
+        <v>3</v>
       </c>
       <c r="E9" s="7">
         <v>4</v>
       </c>
-      <c r="J9" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" ht="15.5">
-      <c r="B10" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M6,IF($B$3="King",'Revenue - Data'!M18,IF($B$3="Superior King",'Revenue - Data'!M30,IF($B$3="Executive",'Revenue - Data'!M42,IF($B$3="One Club",'Revenue - Data'!M54,'Revenue - Data'!M66)))))</f>
-        <v>1.0285714285714285</v>
-      </c>
-      <c r="C10" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N6,IF($B$3="King",'Revenue - Data'!N18,IF($B$3="Superior King",'Revenue - Data'!N30,IF($B$3="Executive",'Revenue - Data'!N42,IF($B$3="One Club",'Revenue - Data'!N54,'Revenue - Data'!N66)))))</f>
-        <v>0.19396428571428573</v>
-      </c>
-      <c r="D10" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O6,IF($B$3="King",'Revenue - Data'!O18,IF($B$3="Superior King",'Revenue - Data'!O30,IF($B$3="Executive",'Revenue - Data'!O42,IF($B$3="One Club",'Revenue - Data'!O54,'Revenue - Data'!O66)))))</f>
-        <v>0.93348214285714282</v>
+    </row>
+    <row r="10" spans="2:5" ht="15.5">
+      <c r="B10" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!I6,IF($B$3="King",'Concerns dash data'!I30,IF($B$3="Superior King",'Concerns dash data'!I66,IF($B$3="Executive",'Concerns dash data'!I18,IF($B$3="One Club",'Concerns dash data'!I42,'Concerns dash data'!I54)))))</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!J6,IF($B$3="King",'Concerns dash data'!J30,IF($B$3="Superior King",'Concerns dash data'!J66,IF($B$3="Executive",'Concerns dash data'!J18,IF($B$3="One Club",'Concerns dash data'!J42,'Concerns dash data'!J54)))))</f>
+        <v>3</v>
+      </c>
+      <c r="D10" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!K6,IF($B$3="King",'Concerns dash data'!K30,IF($B$3="Superior King",'Concerns dash data'!K66,IF($B$3="Executive",'Concerns dash data'!K18,IF($B$3="One Club",'Concerns dash data'!K42,'Concerns dash data'!K54)))))</f>
+        <v>5</v>
       </c>
       <c r="E10" s="7">
         <v>5</v>
       </c>
-      <c r="J10" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" ht="15.5">
-      <c r="B11" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M7,IF($B$3="King",'Revenue - Data'!M19,IF($B$3="Superior King",'Revenue - Data'!M31,IF($B$3="Executive",'Revenue - Data'!M43,IF($B$3="One Club",'Revenue - Data'!M55,'Revenue - Data'!M67)))))</f>
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="C11" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N7,IF($B$3="King",'Revenue - Data'!N19,IF($B$3="Superior King",'Revenue - Data'!N31,IF($B$3="Executive",'Revenue - Data'!N43,IF($B$3="One Club",'Revenue - Data'!N55,'Revenue - Data'!N67)))))</f>
-        <v>9.9029982363315699E-2</v>
-      </c>
-      <c r="D11" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O7,IF($B$3="King",'Revenue - Data'!O19,IF($B$3="Superior King",'Revenue - Data'!O31,IF($B$3="Executive",'Revenue - Data'!O43,IF($B$3="One Club",'Revenue - Data'!O55,'Revenue - Data'!O67)))))</f>
-        <v>0.79574514991181655</v>
+    </row>
+    <row r="11" spans="2:5" ht="15.5">
+      <c r="B11" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!I7,IF($B$3="King",'Concerns dash data'!I31,IF($B$3="Superior King",'Concerns dash data'!I67,IF($B$3="Executive",'Concerns dash data'!I19,IF($B$3="One Club",'Concerns dash data'!I43,'Concerns dash data'!I55)))))</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!J7,IF($B$3="King",'Concerns dash data'!J31,IF($B$3="Superior King",'Concerns dash data'!J67,IF($B$3="Executive",'Concerns dash data'!J19,IF($B$3="One Club",'Concerns dash data'!J43,'Concerns dash data'!J55)))))</f>
+        <v>3</v>
+      </c>
+      <c r="D11" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!K7,IF($B$3="King",'Concerns dash data'!K31,IF($B$3="Superior King",'Concerns dash data'!K67,IF($B$3="Executive",'Concerns dash data'!K19,IF($B$3="One Club",'Concerns dash data'!K43,'Concerns dash data'!K55)))))</f>
+        <v>2</v>
       </c>
       <c r="E11" s="7">
         <v>6</v>
       </c>
-      <c r="J11" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" ht="15.5">
-      <c r="B12" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M8,IF($B$3="King",'Revenue - Data'!M20,IF($B$3="Superior King",'Revenue - Data'!M32,IF($B$3="Executive",'Revenue - Data'!M44,IF($B$3="One Club",'Revenue - Data'!M56,'Revenue - Data'!M68)))))</f>
-        <v>1.0012755102040816</v>
-      </c>
-      <c r="C12" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N8,IF($B$3="King",'Revenue - Data'!N20,IF($B$3="Superior King",'Revenue - Data'!N32,IF($B$3="Executive",'Revenue - Data'!N44,IF($B$3="One Club",'Revenue - Data'!N56,'Revenue - Data'!N68)))))</f>
-        <v>1.1167044595616025</v>
-      </c>
-      <c r="D12" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O8,IF($B$3="King",'Revenue - Data'!O20,IF($B$3="Superior King",'Revenue - Data'!O32,IF($B$3="Executive",'Revenue - Data'!O44,IF($B$3="One Club",'Revenue - Data'!O56,'Revenue - Data'!O68)))))</f>
-        <v>1.1552343159486016</v>
+    </row>
+    <row r="12" spans="2:5" ht="15.5">
+      <c r="B12" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!I8,IF($B$3="King",'Concerns dash data'!I32,IF($B$3="Superior King",'Concerns dash data'!I68,IF($B$3="Executive",'Concerns dash data'!I20,IF($B$3="One Club",'Concerns dash data'!I44,'Concerns dash data'!I56)))))</f>
+        <v>56</v>
+      </c>
+      <c r="C12" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!J8,IF($B$3="King",'Concerns dash data'!J32,IF($B$3="Superior King",'Concerns dash data'!J68,IF($B$3="Executive",'Concerns dash data'!J20,IF($B$3="One Club",'Concerns dash data'!J44,'Concerns dash data'!J56)))))</f>
+        <v>6</v>
+      </c>
+      <c r="D12" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!K8,IF($B$3="King",'Concerns dash data'!K32,IF($B$3="Superior King",'Concerns dash data'!K68,IF($B$3="Executive",'Concerns dash data'!K20,IF($B$3="One Club",'Concerns dash data'!K44,'Concerns dash data'!K56)))))</f>
+        <v>5</v>
       </c>
       <c r="E12" s="7">
         <v>7</v>
       </c>
-      <c r="J12" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" ht="15.5">
-      <c r="B13" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M9,IF($B$3="King",'Revenue - Data'!M21,IF($B$3="Superior King",'Revenue - Data'!M33,IF($B$3="Executive",'Revenue - Data'!M45,IF($B$3="One Club",'Revenue - Data'!M57,'Revenue - Data'!M69)))))</f>
-        <v>1.0127551020408163</v>
-      </c>
-      <c r="C13" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N9,IF($B$3="King",'Revenue - Data'!N21,IF($B$3="Superior King",'Revenue - Data'!N33,IF($B$3="Executive",'Revenue - Data'!N45,IF($B$3="One Club",'Revenue - Data'!N57,'Revenue - Data'!N69)))))</f>
-        <v>1.0267668178382463</v>
-      </c>
-      <c r="D13" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O9,IF($B$3="King",'Revenue - Data'!O21,IF($B$3="Superior King",'Revenue - Data'!O33,IF($B$3="Executive",'Revenue - Data'!O45,IF($B$3="One Club",'Revenue - Data'!O57,'Revenue - Data'!O69)))))</f>
-        <v>1.0101568405139834</v>
+    </row>
+    <row r="13" spans="2:5" ht="15.5">
+      <c r="B13" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!I9,IF($B$3="King",'Concerns dash data'!I33,IF($B$3="Superior King",'Concerns dash data'!I69,IF($B$3="Executive",'Concerns dash data'!I21,IF($B$3="One Club",'Concerns dash data'!I45,'Concerns dash data'!I57)))))</f>
+        <v>71</v>
+      </c>
+      <c r="C13" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!J9,IF($B$3="King",'Concerns dash data'!J33,IF($B$3="Superior King",'Concerns dash data'!J69,IF($B$3="Executive",'Concerns dash data'!J21,IF($B$3="One Club",'Concerns dash data'!J45,'Concerns dash data'!J57)))))</f>
+        <v>8</v>
+      </c>
+      <c r="D13" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!K9,IF($B$3="King",'Concerns dash data'!K33,IF($B$3="Superior King",'Concerns dash data'!K69,IF($B$3="Executive",'Concerns dash data'!K21,IF($B$3="One Club",'Concerns dash data'!K45,'Concerns dash data'!K57)))))</f>
+        <v>2</v>
       </c>
       <c r="E13" s="7">
         <v>8</v>
       </c>
-      <c r="J13" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" ht="15.5">
-      <c r="B14" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M10,IF($B$3="King",'Revenue - Data'!M22,IF($B$3="Superior King",'Revenue - Data'!M34,IF($B$3="Executive",'Revenue - Data'!M46,IF($B$3="One Club",'Revenue - Data'!M58,'Revenue - Data'!M70)))))</f>
-        <v>0.96768707482993199</v>
-      </c>
-      <c r="C14" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N10,IF($B$3="King",'Revenue - Data'!N22,IF($B$3="Superior King",'Revenue - Data'!N34,IF($B$3="Executive",'Revenue - Data'!N46,IF($B$3="One Club",'Revenue - Data'!N58,'Revenue - Data'!N70)))))</f>
-        <v>0.99092970521541945</v>
-      </c>
-      <c r="D14" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O10,IF($B$3="King",'Revenue - Data'!O22,IF($B$3="Superior King",'Revenue - Data'!O34,IF($B$3="Executive",'Revenue - Data'!O46,IF($B$3="One Club",'Revenue - Data'!O58,'Revenue - Data'!O70)))))</f>
-        <v>0.87673611111111116</v>
+    </row>
+    <row r="14" spans="2:5" ht="15.5">
+      <c r="B14" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!I10,IF($B$3="King",'Concerns dash data'!I34,IF($B$3="Superior King",'Concerns dash data'!I70,IF($B$3="Executive",'Concerns dash data'!I22,IF($B$3="One Club",'Concerns dash data'!I46,'Concerns dash data'!I58)))))</f>
+        <v>97</v>
+      </c>
+      <c r="C14" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!J10,IF($B$3="King",'Concerns dash data'!J34,IF($B$3="Superior King",'Concerns dash data'!J70,IF($B$3="Executive",'Concerns dash data'!J22,IF($B$3="One Club",'Concerns dash data'!J46,'Concerns dash data'!J58)))))</f>
+        <v>8</v>
+      </c>
+      <c r="D14" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!K10,IF($B$3="King",'Concerns dash data'!K34,IF($B$3="Superior King",'Concerns dash data'!K70,IF($B$3="Executive",'Concerns dash data'!K22,IF($B$3="One Club",'Concerns dash data'!K46,'Concerns dash data'!K58)))))</f>
+        <v>5</v>
       </c>
       <c r="E14" s="7">
         <v>9</v>
       </c>
-      <c r="J14" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" ht="15.5">
-      <c r="B15" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M11,IF($B$3="King",'Revenue - Data'!M23,IF($B$3="Superior King",'Revenue - Data'!M35,IF($B$3="Executive",'Revenue - Data'!M47,IF($B$3="One Club",'Revenue - Data'!M59,'Revenue - Data'!M71)))))</f>
-        <v>0.98913043478260865</v>
-      </c>
-      <c r="C15" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N11,IF($B$3="King",'Revenue - Data'!N23,IF($B$3="Superior King",'Revenue - Data'!N35,IF($B$3="Executive",'Revenue - Data'!N47,IF($B$3="One Club",'Revenue - Data'!N59,'Revenue - Data'!N71)))))</f>
-        <v>0.99608925695882222</v>
-      </c>
-      <c r="D15" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O11,IF($B$3="King",'Revenue - Data'!O23,IF($B$3="Superior King",'Revenue - Data'!O35,IF($B$3="Executive",'Revenue - Data'!O47,IF($B$3="One Club",'Revenue - Data'!O59,'Revenue - Data'!O71)))))</f>
-        <v>0.9511732229123534</v>
+    </row>
+    <row r="15" spans="2:5" ht="15.5">
+      <c r="B15" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!I11,IF($B$3="King",'Concerns dash data'!I35,IF($B$3="Superior King",'Concerns dash data'!I71,IF($B$3="Executive",'Concerns dash data'!I23,IF($B$3="One Club",'Concerns dash data'!I47,'Concerns dash data'!I59)))))</f>
+        <v>50</v>
+      </c>
+      <c r="C15" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!J11,IF($B$3="King",'Concerns dash data'!J35,IF($B$3="Superior King",'Concerns dash data'!J71,IF($B$3="Executive",'Concerns dash data'!J23,IF($B$3="One Club",'Concerns dash data'!J47,'Concerns dash data'!J59)))))</f>
+        <v>3</v>
+      </c>
+      <c r="D15" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!K11,IF($B$3="King",'Concerns dash data'!K35,IF($B$3="Superior King",'Concerns dash data'!K71,IF($B$3="Executive",'Concerns dash data'!K23,IF($B$3="One Club",'Concerns dash data'!K47,'Concerns dash data'!K59)))))</f>
+        <v>0</v>
       </c>
       <c r="E15" s="7">
         <v>10</v>
       </c>
-      <c r="J15" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" ht="15.5">
-      <c r="B16" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M12,IF($B$3="King",'Revenue - Data'!M24,IF($B$3="Superior King",'Revenue - Data'!M36,IF($B$3="Executive",'Revenue - Data'!M48,IF($B$3="One Club",'Revenue - Data'!M60,'Revenue - Data'!M72)))))</f>
-        <v>1</v>
-      </c>
-      <c r="C16" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N12,IF($B$3="King",'Revenue - Data'!N24,IF($B$3="Superior King",'Revenue - Data'!N36,IF($B$3="Executive",'Revenue - Data'!N48,IF($B$3="One Club",'Revenue - Data'!N60,'Revenue - Data'!N72)))))</f>
-        <v>0.96484126984126983</v>
-      </c>
-      <c r="D16" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O12,IF($B$3="King",'Revenue - Data'!O24,IF($B$3="Superior King",'Revenue - Data'!O36,IF($B$3="Executive",'Revenue - Data'!O48,IF($B$3="One Club",'Revenue - Data'!O60,'Revenue - Data'!O72)))))</f>
-        <v>0.92685185185185182</v>
+    </row>
+    <row r="16" spans="2:5" ht="15.5">
+      <c r="B16" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!I12,IF($B$3="King",'Concerns dash data'!I36,IF($B$3="Superior King",'Concerns dash data'!I72,IF($B$3="Executive",'Concerns dash data'!I24,IF($B$3="One Club",'Concerns dash data'!I48,'Concerns dash data'!I60)))))</f>
+        <v>52</v>
+      </c>
+      <c r="C16" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!J12,IF($B$3="King",'Concerns dash data'!J36,IF($B$3="Superior King",'Concerns dash data'!J72,IF($B$3="Executive",'Concerns dash data'!J24,IF($B$3="One Club",'Concerns dash data'!J48,'Concerns dash data'!J60)))))</f>
+        <v>5</v>
+      </c>
+      <c r="D16" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!K12,IF($B$3="King",'Concerns dash data'!K36,IF($B$3="Superior King",'Concerns dash data'!K72,IF($B$3="Executive",'Concerns dash data'!K24,IF($B$3="One Club",'Concerns dash data'!K48,'Concerns dash data'!K60)))))</f>
+        <v>3</v>
       </c>
       <c r="E16" s="7">
         <v>11</v>
       </c>
-      <c r="J16" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" ht="15.5">
-      <c r="B17" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!M13,IF($B$3="King",'Revenue - Data'!M25,IF($B$3="Superior King",'Revenue - Data'!M37,IF($B$3="Executive",'Revenue - Data'!M49,IF($B$3="One Club",'Revenue - Data'!M61,'Revenue - Data'!M73)))))</f>
-        <v>0.95676691729323304</v>
-      </c>
-      <c r="C17" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!N13,IF($B$3="King",'Revenue - Data'!N25,IF($B$3="Superior King",'Revenue - Data'!N37,IF($B$3="Executive",'Revenue - Data'!N49,IF($B$3="One Club",'Revenue - Data'!N61,'Revenue - Data'!N73)))))</f>
-        <v>0.78618740729374459</v>
-      </c>
-      <c r="D17" s="6">
-        <f>IF($B$3="Club Deluxe",'Revenue - Data'!O13,IF($B$3="King",'Revenue - Data'!O25,IF($B$3="Superior King",'Revenue - Data'!O37,IF($B$3="Executive",'Revenue - Data'!O49,IF($B$3="One Club",'Revenue - Data'!O61,'Revenue - Data'!O73)))))</f>
-        <v>0.80911881314746126</v>
+    </row>
+    <row r="17" spans="2:5" ht="15.5">
+      <c r="B17" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!I13,IF($B$3="King",'Concerns dash data'!I37,IF($B$3="Superior King",'Concerns dash data'!I73,IF($B$3="Executive",'Concerns dash data'!I25,IF($B$3="One Club",'Concerns dash data'!I49,'Concerns dash data'!I61)))))</f>
+        <v>54</v>
+      </c>
+      <c r="C17" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!J13,IF($B$3="King",'Concerns dash data'!J37,IF($B$3="Superior King",'Concerns dash data'!J73,IF($B$3="Executive",'Concerns dash data'!J25,IF($B$3="One Club",'Concerns dash data'!J49,'Concerns dash data'!J61)))))</f>
+        <v>5</v>
+      </c>
+      <c r="D17" s="28">
+        <f>IF($B$3="Club Deluxe",'Concerns dash data'!K13,IF($B$3="King",'Concerns dash data'!K37,IF($B$3="Superior King",'Concerns dash data'!K73,IF($B$3="Executive",'Concerns dash data'!K25,IF($B$3="One Club",'Concerns dash data'!K49,'Concerns dash data'!K61)))))</f>
+        <v>1</v>
       </c>
       <c r="E17" s="7">
         <v>12</v>
       </c>
-      <c r="J17" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10">
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
       <c r="B20" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
       <c r="B21" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
       <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -15877,7 +15400,8 @@
     <mergeCell ref="B3:E3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -19668,642 +19192,1416 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{292D24D9-B7AF-4404-B87D-6D3347D4D37D}">
-  <dimension ref="A1:E217"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="5" width="21.81640625" customWidth="1"/>
+    <col min="1" max="8" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:11">
       <c r="A1" s="27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D1" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="J1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="K1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" t="str">
+        <f>"#1 "&amp;C2</f>
+        <v>#1 Faulty electronics</v>
+      </c>
+      <c r="G2" t="str">
+        <f>"#2 "&amp;D2</f>
+        <v>#2 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="H2" t="str">
+        <f>"#3 "&amp;E2</f>
+        <v>#3 Low-quality food</v>
+      </c>
+      <c r="I2">
         <v>5</v>
       </c>
-      <c r="E2">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F66" si="0">"#1 "&amp;C3</f>
+        <v>#1 Faulty electronics</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G66" si="1">"#2 "&amp;D3</f>
+        <v>#2 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H66" si="2">"#3 "&amp;E3</f>
+        <v>#3 Low-quality food</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Faulty electronics</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Low-quality food</v>
+      </c>
+      <c r="I4">
+        <v>9</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Faulty electronics</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Low-quality food</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Faulty electronics</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Low-quality food</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Faulty electronics</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Low-quality food</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Faulty electronics</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Low-quality food</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Faulty electronics</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Low-quality food</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Faulty electronics</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Low-quality food</v>
+      </c>
+      <c r="I10">
+        <v>7</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Faulty electronics</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Low-quality food</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>6</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Faulty electronics</v>
+      </c>
+      <c r="G12" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Low-quality food</v>
+      </c>
+      <c r="I12">
+        <v>3</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Faulty electronics</v>
+      </c>
+      <c r="G13" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Low-quality food</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>5</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" t="s">
         <v>88</v>
       </c>
-      <c r="D3">
+      <c r="E14" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G14" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I14">
+        <v>6</v>
+      </c>
+      <c r="J14">
+        <v>5</v>
+      </c>
+      <c r="K14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G15" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+      <c r="J15">
+        <v>7</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G16" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17">
         <v>4</v>
       </c>
-      <c r="E3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4">
-        <v>13</v>
-      </c>
-      <c r="E4">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5">
+      <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G17" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I17">
+        <v>6</v>
+      </c>
+      <c r="J17">
+        <v>5</v>
+      </c>
+      <c r="K17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G18" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I18">
+        <v>7</v>
+      </c>
+      <c r="J18">
+        <v>6</v>
+      </c>
+      <c r="K18">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8">
-        <v>9</v>
-      </c>
-      <c r="E8">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="C9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-      <c r="E9">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10">
-        <v>12</v>
-      </c>
-      <c r="E10">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11">
-        <v>7</v>
-      </c>
-      <c r="E11">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12">
-        <v>4</v>
-      </c>
-      <c r="C12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12">
-        <v>5</v>
-      </c>
-      <c r="E12">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13">
-        <v>5</v>
-      </c>
-      <c r="E13">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-      <c r="E14">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15">
-        <v>5</v>
-      </c>
-      <c r="E15">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16">
-        <v>5</v>
-      </c>
-      <c r="C16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17">
-        <v>5</v>
-      </c>
-      <c r="E17">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B19">
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19">
+        <v>85</v>
+      </c>
+      <c r="D19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G19" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I19">
         <v>2</v>
       </c>
-      <c r="E19">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B20">
         <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20">
+        <v>85</v>
+      </c>
+      <c r="D20" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G20" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I20">
+        <v>6</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G21" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
+      </c>
+      <c r="J21">
         <v>4</v>
       </c>
-      <c r="E20">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21">
+      <c r="K21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G22" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>3</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G23" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I23">
+        <v>4</v>
+      </c>
+      <c r="J23">
+        <v>4</v>
+      </c>
+      <c r="K23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G24" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>5</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G25" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I25">
+        <v>3</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Temperature of their room</v>
+      </c>
+      <c r="G26" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Bad smells</v>
+      </c>
+      <c r="I26">
+        <v>4</v>
+      </c>
+      <c r="J26">
+        <v>17</v>
+      </c>
+      <c r="K26">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Temperature of their room</v>
+      </c>
+      <c r="G27" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Bad smells</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27">
+        <v>13</v>
+      </c>
+      <c r="K27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Temperature of their room</v>
+      </c>
+      <c r="G28" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Bad smells</v>
+      </c>
+      <c r="I28">
+        <v>4</v>
+      </c>
+      <c r="J28">
+        <v>14</v>
+      </c>
+      <c r="K28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Temperature of their room</v>
+      </c>
+      <c r="G29" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Bad smells</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29">
+        <v>8</v>
+      </c>
+      <c r="K29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Temperature of their room</v>
+      </c>
+      <c r="G30" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Bad smells</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>3</v>
+      </c>
+      <c r="K30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Temperature of their room</v>
+      </c>
+      <c r="G31" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Bad smells</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>3</v>
+      </c>
+      <c r="K31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32">
         <v>7</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" t="s">
         <v>88</v>
       </c>
-      <c r="D21">
-        <v>7</v>
-      </c>
-      <c r="E21">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22">
-        <v>7</v>
-      </c>
-      <c r="C22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22">
+      <c r="E32" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Temperature of their room</v>
+      </c>
+      <c r="G32" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Bad smells</v>
+      </c>
+      <c r="I32">
+        <v>56</v>
+      </c>
+      <c r="J32">
+        <v>6</v>
+      </c>
+      <c r="K32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Temperature of their room</v>
+      </c>
+      <c r="G33" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Bad smells</v>
+      </c>
+      <c r="I33">
+        <v>71</v>
+      </c>
+      <c r="J33">
+        <v>8</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Temperature of their room</v>
+      </c>
+      <c r="G34" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Bad smells</v>
+      </c>
+      <c r="I34">
+        <v>97</v>
+      </c>
+      <c r="J34">
+        <v>8</v>
+      </c>
+      <c r="K34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" t="s">
+        <v>88</v>
+      </c>
+      <c r="E35" t="s">
+        <v>92</v>
+      </c>
+      <c r="F35" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Temperature of their room</v>
+      </c>
+      <c r="G35" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Bad smells</v>
+      </c>
+      <c r="I35">
+        <v>50</v>
+      </c>
+      <c r="J35">
+        <v>3</v>
+      </c>
+      <c r="K35">
         <v>0</v>
       </c>
-      <c r="E22">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23">
-        <v>4</v>
-      </c>
-      <c r="E23">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24">
-        <v>8</v>
-      </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" t="s">
         <v>88</v>
       </c>
-      <c r="D24">
+      <c r="E36" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Temperature of their room</v>
+      </c>
+      <c r="G36" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H36" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Bad smells</v>
+      </c>
+      <c r="I36">
+        <v>52</v>
+      </c>
+      <c r="J36">
+        <v>5</v>
+      </c>
+      <c r="K36">
         <v>3</v>
       </c>
-      <c r="E24">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25">
-        <v>8</v>
-      </c>
-      <c r="C25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-      <c r="E25">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26">
-        <v>7</v>
-      </c>
-      <c r="E26">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27">
-        <v>9</v>
-      </c>
-      <c r="C27" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27">
-        <v>4</v>
-      </c>
-      <c r="E27">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29">
-        <v>10</v>
-      </c>
-      <c r="C29" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
-      <c r="E29">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30">
-        <v>10</v>
-      </c>
-      <c r="C30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30">
-        <v>6</v>
-      </c>
-      <c r="E30">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31">
-        <v>10</v>
-      </c>
-      <c r="C31" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32">
-        <v>11</v>
-      </c>
-      <c r="C32" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32">
-        <v>3</v>
-      </c>
-      <c r="E32">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33">
-        <v>11</v>
-      </c>
-      <c r="C33" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33">
-        <v>2</v>
-      </c>
-      <c r="E33">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" t="s">
-        <v>61</v>
-      </c>
-      <c r="B34">
-        <v>11</v>
-      </c>
-      <c r="C34" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35">
-        <v>12</v>
-      </c>
-      <c r="C35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" t="s">
-        <v>61</v>
-      </c>
-      <c r="B36">
-        <v>12</v>
-      </c>
-      <c r="C36" t="s">
-        <v>88</v>
-      </c>
-      <c r="D36">
-        <v>5</v>
-      </c>
-      <c r="E36">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B37">
         <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37">
+        <v>94</v>
+      </c>
+      <c r="D37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" t="s">
+        <v>92</v>
+      </c>
+      <c r="F37" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Temperature of their room</v>
+      </c>
+      <c r="G37" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Noisy neighbors</v>
+      </c>
+      <c r="H37" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Bad smells</v>
+      </c>
+      <c r="I37">
+        <v>54</v>
+      </c>
+      <c r="J37">
+        <v>5</v>
+      </c>
+      <c r="K37">
         <v>1</v>
       </c>
-      <c r="E37">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" t="s">
         <v>69</v>
       </c>
@@ -20311,3056 +20609,1364 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38">
+        <v>85</v>
+      </c>
+      <c r="D38" t="s">
+        <v>87</v>
+      </c>
+      <c r="E38" t="s">
+        <v>86</v>
+      </c>
+      <c r="F38" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G38" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Low-quality food</v>
+      </c>
+      <c r="H38" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
         <v>6</v>
       </c>
-      <c r="E38">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="K38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
         <v>69</v>
       </c>
       <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" t="s">
+        <v>87</v>
+      </c>
+      <c r="E39" t="s">
+        <v>86</v>
+      </c>
+      <c r="F39" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G39" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Low-quality food</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I39">
+        <v>5</v>
+      </c>
+      <c r="J39">
+        <v>3</v>
+      </c>
+      <c r="K39">
         <v>1</v>
       </c>
-      <c r="C39" t="s">
-        <v>91</v>
-      </c>
-      <c r="D39">
-        <v>5</v>
-      </c>
-      <c r="E39">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
         <v>69</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
-      </c>
-      <c r="D40">
-        <v>6</v>
-      </c>
-      <c r="E40">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>85</v>
+      </c>
+      <c r="D40" t="s">
+        <v>87</v>
+      </c>
+      <c r="E40" t="s">
+        <v>86</v>
+      </c>
+      <c r="F40" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G40" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Low-quality food</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3</v>
+      </c>
+      <c r="K40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
         <v>69</v>
       </c>
       <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" t="s">
+        <v>87</v>
+      </c>
+      <c r="E41" t="s">
+        <v>86</v>
+      </c>
+      <c r="F41" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G41" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Low-quality food</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I41">
         <v>2</v>
       </c>
-      <c r="C41" t="s">
-        <v>88</v>
-      </c>
-      <c r="D41">
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41">
         <v>3</v>
       </c>
-      <c r="E41">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
         <v>69</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>91</v>
-      </c>
-      <c r="D42">
-        <v>7</v>
-      </c>
-      <c r="E42">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>85</v>
+      </c>
+      <c r="D42" t="s">
+        <v>87</v>
+      </c>
+      <c r="E42" t="s">
+        <v>86</v>
+      </c>
+      <c r="F42" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G42" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Low-quality food</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I42">
+        <v>4</v>
+      </c>
+      <c r="J42">
+        <v>3</v>
+      </c>
+      <c r="K42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
         <v>69</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>89</v>
-      </c>
-      <c r="D43">
+        <v>85</v>
+      </c>
+      <c r="D43" t="s">
+        <v>87</v>
+      </c>
+      <c r="E43" t="s">
+        <v>86</v>
+      </c>
+      <c r="F43" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G43" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Low-quality food</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I43">
         <v>1</v>
       </c>
-      <c r="E43">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
         <v>69</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44">
-        <v>5</v>
-      </c>
-      <c r="E44">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>85</v>
+      </c>
+      <c r="D44" t="s">
+        <v>87</v>
+      </c>
+      <c r="E44" t="s">
+        <v>86</v>
+      </c>
+      <c r="F44" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G44" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Low-quality food</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I44">
+        <v>6</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
         <v>69</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45">
-        <v>3</v>
-      </c>
-      <c r="E45">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>85</v>
+      </c>
+      <c r="D45" t="s">
+        <v>87</v>
+      </c>
+      <c r="E45" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G45" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Low-quality food</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I45">
+        <v>5</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
         <v>69</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
-      </c>
-      <c r="D46">
-        <v>10</v>
-      </c>
-      <c r="E46">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>85</v>
+      </c>
+      <c r="D46" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" t="s">
+        <v>86</v>
+      </c>
+      <c r="F46" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G46" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Low-quality food</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
         <v>69</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D47">
-        <v>6</v>
-      </c>
-      <c r="E47">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>85</v>
+      </c>
+      <c r="D47" t="s">
+        <v>87</v>
+      </c>
+      <c r="E47" t="s">
+        <v>86</v>
+      </c>
+      <c r="F47" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G47" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Low-quality food</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>2</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
         <v>69</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>91</v>
-      </c>
-      <c r="D48">
-        <v>5</v>
-      </c>
-      <c r="E48">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>85</v>
+      </c>
+      <c r="D48" t="s">
+        <v>87</v>
+      </c>
+      <c r="E48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F48" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Low-quality food</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" t="s">
         <v>69</v>
       </c>
       <c r="B49">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>85</v>
+      </c>
+      <c r="D49" t="s">
+        <v>87</v>
+      </c>
+      <c r="E49" t="s">
+        <v>86</v>
+      </c>
+      <c r="F49" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Low-quality food</v>
+      </c>
+      <c r="H49" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I49">
         <v>4</v>
       </c>
-      <c r="C49" t="s">
-        <v>89</v>
-      </c>
-      <c r="D49">
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>87</v>
+      </c>
+      <c r="D50" t="s">
+        <v>86</v>
+      </c>
+      <c r="E50" t="s">
+        <v>85</v>
+      </c>
+      <c r="F50" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Low-quality food</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Faulty electronics</v>
+      </c>
+      <c r="H50" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="I50">
+        <v>6</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>87</v>
+      </c>
+      <c r="D51" t="s">
+        <v>86</v>
+      </c>
+      <c r="E51" t="s">
+        <v>85</v>
+      </c>
+      <c r="F51" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Low-quality food</v>
+      </c>
+      <c r="G51" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Faulty electronics</v>
+      </c>
+      <c r="H51" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="I51">
+        <v>8</v>
+      </c>
+      <c r="J51">
+        <v>2</v>
+      </c>
+      <c r="K51">
         <v>3</v>
       </c>
-      <c r="E49">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" t="s">
-        <v>69</v>
-      </c>
-      <c r="B50">
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52">
+        <v>3</v>
+      </c>
+      <c r="C52" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" t="s">
+        <v>86</v>
+      </c>
+      <c r="E52" t="s">
+        <v>85</v>
+      </c>
+      <c r="F52" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Low-quality food</v>
+      </c>
+      <c r="G52" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Faulty electronics</v>
+      </c>
+      <c r="H52" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="I52">
         <v>5</v>
       </c>
-      <c r="C50" t="s">
-        <v>88</v>
-      </c>
-      <c r="D50">
+      <c r="J52">
+        <v>3</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>87</v>
+      </c>
+      <c r="D53" t="s">
+        <v>86</v>
+      </c>
+      <c r="E53" t="s">
+        <v>85</v>
+      </c>
+      <c r="F53" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Low-quality food</v>
+      </c>
+      <c r="G53" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Faulty electronics</v>
+      </c>
+      <c r="H53" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="I53">
+        <v>4</v>
+      </c>
+      <c r="J53">
+        <v>2</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54">
+        <v>5</v>
+      </c>
+      <c r="C54" t="s">
+        <v>87</v>
+      </c>
+      <c r="D54" t="s">
+        <v>86</v>
+      </c>
+      <c r="E54" t="s">
+        <v>85</v>
+      </c>
+      <c r="F54" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Low-quality food</v>
+      </c>
+      <c r="G54" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Faulty electronics</v>
+      </c>
+      <c r="H54" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="I54">
         <v>7</v>
       </c>
-      <c r="E50">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" t="s">
-        <v>69</v>
-      </c>
-      <c r="B51">
-        <v>5</v>
-      </c>
-      <c r="C51" t="s">
-        <v>91</v>
-      </c>
-      <c r="D51">
+      <c r="J54">
         <v>6</v>
       </c>
-      <c r="E51">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" t="s">
-        <v>69</v>
-      </c>
-      <c r="B52">
-        <v>5</v>
-      </c>
-      <c r="C52" t="s">
-        <v>89</v>
-      </c>
-      <c r="D52">
+      <c r="K54">
         <v>2</v>
       </c>
-      <c r="E52">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" t="s">
-        <v>69</v>
-      </c>
-      <c r="B53">
-        <v>6</v>
-      </c>
-      <c r="C53" t="s">
-        <v>88</v>
-      </c>
-      <c r="D53">
-        <v>2</v>
-      </c>
-      <c r="E53">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" t="s">
-        <v>69</v>
-      </c>
-      <c r="B54">
-        <v>6</v>
-      </c>
-      <c r="C54" t="s">
-        <v>91</v>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B55">
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55">
-        <v>3</v>
-      </c>
-      <c r="E55">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>87</v>
+      </c>
+      <c r="D55" t="s">
+        <v>86</v>
+      </c>
+      <c r="E55" t="s">
+        <v>85</v>
+      </c>
+      <c r="F55" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Low-quality food</v>
+      </c>
+      <c r="G55" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Faulty electronics</v>
+      </c>
+      <c r="H55" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>2</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B56">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>88</v>
-      </c>
-      <c r="D56">
-        <v>6</v>
-      </c>
-      <c r="E56">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>87</v>
+      </c>
+      <c r="D56" t="s">
+        <v>86</v>
+      </c>
+      <c r="E56" t="s">
+        <v>85</v>
+      </c>
+      <c r="F56" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Low-quality food</v>
+      </c>
+      <c r="G56" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Faulty electronics</v>
+      </c>
+      <c r="H56" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B57">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>91</v>
-      </c>
-      <c r="D57">
+        <v>87</v>
+      </c>
+      <c r="D57" t="s">
+        <v>86</v>
+      </c>
+      <c r="E57" t="s">
+        <v>85</v>
+      </c>
+      <c r="F57" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Low-quality food</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Faulty electronics</v>
+      </c>
+      <c r="H57" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="I57">
         <v>0</v>
       </c>
-      <c r="E57">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="J57">
+        <v>4</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B58">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>89</v>
-      </c>
-      <c r="D58">
+        <v>87</v>
+      </c>
+      <c r="D58" t="s">
+        <v>86</v>
+      </c>
+      <c r="E58" t="s">
+        <v>85</v>
+      </c>
+      <c r="F58" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Low-quality food</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Faulty electronics</v>
+      </c>
+      <c r="H58" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58">
         <v>2</v>
       </c>
-      <c r="E58">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="K58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B59">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C59" t="s">
-        <v>88</v>
-      </c>
-      <c r="D59">
+        <v>87</v>
+      </c>
+      <c r="D59" t="s">
+        <v>86</v>
+      </c>
+      <c r="E59" t="s">
+        <v>85</v>
+      </c>
+      <c r="F59" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Low-quality food</v>
+      </c>
+      <c r="G59" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Faulty electronics</v>
+      </c>
+      <c r="H59" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>4</v>
+      </c>
+      <c r="K59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" t="s">
+        <v>70</v>
+      </c>
+      <c r="B60">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>87</v>
+      </c>
+      <c r="D60" t="s">
+        <v>86</v>
+      </c>
+      <c r="E60" t="s">
+        <v>85</v>
+      </c>
+      <c r="F60" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Low-quality food</v>
+      </c>
+      <c r="G60" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Faulty electronics</v>
+      </c>
+      <c r="H60" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
         <v>3</v>
       </c>
-      <c r="E59">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" t="s">
-        <v>69</v>
-      </c>
-      <c r="B60">
-        <v>8</v>
-      </c>
-      <c r="C60" t="s">
-        <v>91</v>
-      </c>
-      <c r="D60">
-        <v>4</v>
-      </c>
-      <c r="E60">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="K60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B61">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>89</v>
-      </c>
-      <c r="D61">
-        <v>5</v>
-      </c>
-      <c r="E61">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>87</v>
+      </c>
+      <c r="D61" t="s">
+        <v>86</v>
+      </c>
+      <c r="E61" t="s">
+        <v>85</v>
+      </c>
+      <c r="F61" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Low-quality food</v>
+      </c>
+      <c r="G61" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Faulty electronics</v>
+      </c>
+      <c r="H61" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Doesn’t match the website/brochure</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B62">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C62" t="s">
         <v>88</v>
       </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="E62">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="D62" t="s">
+        <v>92</v>
+      </c>
+      <c r="E62" t="s">
+        <v>86</v>
+      </c>
+      <c r="F62" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Noisy neighbors</v>
+      </c>
+      <c r="G62" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Bad smells</v>
+      </c>
+      <c r="H62" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I62">
+        <v>16</v>
+      </c>
+      <c r="J62">
+        <v>23</v>
+      </c>
+      <c r="K62">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B63">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>91</v>
-      </c>
-      <c r="D63">
+        <v>88</v>
+      </c>
+      <c r="D63" t="s">
+        <v>92</v>
+      </c>
+      <c r="E63" t="s">
+        <v>86</v>
+      </c>
+      <c r="F63" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Noisy neighbors</v>
+      </c>
+      <c r="G63" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Bad smells</v>
+      </c>
+      <c r="H63" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I63">
+        <v>34</v>
+      </c>
+      <c r="J63">
+        <v>19</v>
+      </c>
+      <c r="K63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64">
         <v>3</v>
       </c>
-      <c r="E63">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" t="s">
-        <v>69</v>
-      </c>
-      <c r="B64">
-        <v>9</v>
-      </c>
       <c r="C64" t="s">
-        <v>89</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>88</v>
+      </c>
+      <c r="D64" t="s">
+        <v>92</v>
+      </c>
+      <c r="E64" t="s">
+        <v>86</v>
+      </c>
+      <c r="F64" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Noisy neighbors</v>
+      </c>
+      <c r="G64" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Bad smells</v>
+      </c>
+      <c r="H64" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I64">
+        <v>12</v>
+      </c>
+      <c r="J64">
+        <v>7</v>
+      </c>
+      <c r="K64">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B65">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C65" t="s">
         <v>88</v>
       </c>
-      <c r="D65">
-        <v>4</v>
-      </c>
-      <c r="E65">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="D65" t="s">
+        <v>92</v>
+      </c>
+      <c r="E65" t="s">
+        <v>86</v>
+      </c>
+      <c r="F65" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Noisy neighbors</v>
+      </c>
+      <c r="G65" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Bad smells</v>
+      </c>
+      <c r="H65" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I65">
+        <v>28</v>
+      </c>
+      <c r="J65">
+        <v>11</v>
+      </c>
+      <c r="K65">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B66">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>91</v>
-      </c>
-      <c r="D66">
-        <v>4</v>
-      </c>
-      <c r="E66">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>88</v>
+      </c>
+      <c r="D66" t="s">
+        <v>92</v>
+      </c>
+      <c r="E66" t="s">
+        <v>86</v>
+      </c>
+      <c r="F66" t="str">
+        <f t="shared" si="0"/>
+        <v>#1 Noisy neighbors</v>
+      </c>
+      <c r="G66" t="str">
+        <f t="shared" si="1"/>
+        <v>#2 Bad smells</v>
+      </c>
+      <c r="H66" t="str">
+        <f t="shared" si="2"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I66">
+        <v>16</v>
+      </c>
+      <c r="J66">
+        <v>11</v>
+      </c>
+      <c r="K66">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B67">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>89</v>
-      </c>
-      <c r="D67">
-        <v>4</v>
-      </c>
-      <c r="E67">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>88</v>
+      </c>
+      <c r="D67" t="s">
+        <v>92</v>
+      </c>
+      <c r="E67" t="s">
+        <v>86</v>
+      </c>
+      <c r="F67" t="str">
+        <f t="shared" ref="F67:F73" si="3">"#1 "&amp;C67</f>
+        <v>#1 Noisy neighbors</v>
+      </c>
+      <c r="G67" t="str">
+        <f t="shared" ref="G67:G73" si="4">"#2 "&amp;D67</f>
+        <v>#2 Bad smells</v>
+      </c>
+      <c r="H67" t="str">
+        <f t="shared" ref="H67:H73" si="5">"#3 "&amp;E67</f>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I67">
+        <v>9</v>
+      </c>
+      <c r="J67">
+        <v>12</v>
+      </c>
+      <c r="K67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B68">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C68" t="s">
         <v>88</v>
       </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+      <c r="D68" t="s">
+        <v>92</v>
+      </c>
+      <c r="E68" t="s">
+        <v>86</v>
+      </c>
+      <c r="F68" t="str">
+        <f t="shared" si="3"/>
+        <v>#1 Noisy neighbors</v>
+      </c>
+      <c r="G68" t="str">
+        <f t="shared" si="4"/>
+        <v>#2 Bad smells</v>
+      </c>
+      <c r="H68" t="str">
+        <f t="shared" si="5"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I68">
+        <v>19</v>
+      </c>
+      <c r="J68">
+        <v>8</v>
+      </c>
+      <c r="K68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>88</v>
+      </c>
+      <c r="D69" t="s">
+        <v>92</v>
+      </c>
+      <c r="E69" t="s">
+        <v>86</v>
+      </c>
+      <c r="F69" t="str">
+        <f t="shared" si="3"/>
+        <v>#1 Noisy neighbors</v>
+      </c>
+      <c r="G69" t="str">
+        <f t="shared" si="4"/>
+        <v>#2 Bad smells</v>
+      </c>
+      <c r="H69" t="str">
+        <f t="shared" si="5"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I69">
+        <v>21</v>
+      </c>
+      <c r="J69">
+        <v>10</v>
+      </c>
+      <c r="K69">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>88</v>
+      </c>
+      <c r="D70" t="s">
+        <v>92</v>
+      </c>
+      <c r="E70" t="s">
+        <v>86</v>
+      </c>
+      <c r="F70" t="str">
+        <f t="shared" si="3"/>
+        <v>#1 Noisy neighbors</v>
+      </c>
+      <c r="G70" t="str">
+        <f t="shared" si="4"/>
+        <v>#2 Bad smells</v>
+      </c>
+      <c r="H70" t="str">
+        <f t="shared" si="5"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I70">
+        <v>5</v>
+      </c>
+      <c r="J70">
         <v>11</v>
       </c>
-      <c r="C69" t="s">
-        <v>91</v>
-      </c>
-      <c r="D69">
-        <v>5</v>
-      </c>
-      <c r="E69">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" t="s">
-        <v>69</v>
-      </c>
-      <c r="B70">
-        <v>11</v>
-      </c>
-      <c r="C70" t="s">
-        <v>89</v>
-      </c>
-      <c r="D70">
-        <v>1</v>
-      </c>
-      <c r="E70">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+      <c r="K70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B71">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C71" t="s">
         <v>88</v>
       </c>
-      <c r="D71">
-        <v>3</v>
-      </c>
-      <c r="E71">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="D71" t="s">
+        <v>92</v>
+      </c>
+      <c r="E71" t="s">
+        <v>86</v>
+      </c>
+      <c r="F71" t="str">
+        <f t="shared" si="3"/>
+        <v>#1 Noisy neighbors</v>
+      </c>
+      <c r="G71" t="str">
+        <f t="shared" si="4"/>
+        <v>#2 Bad smells</v>
+      </c>
+      <c r="H71" t="str">
+        <f t="shared" si="5"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I71">
+        <v>23</v>
+      </c>
+      <c r="J71">
+        <v>37</v>
+      </c>
+      <c r="K71">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B72">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>91</v>
-      </c>
-      <c r="D72">
-        <v>2</v>
-      </c>
-      <c r="E72">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>88</v>
+      </c>
+      <c r="D72" t="s">
+        <v>92</v>
+      </c>
+      <c r="E72" t="s">
+        <v>86</v>
+      </c>
+      <c r="F72" t="str">
+        <f t="shared" si="3"/>
+        <v>#1 Noisy neighbors</v>
+      </c>
+      <c r="G72" t="str">
+        <f t="shared" si="4"/>
+        <v>#2 Bad smells</v>
+      </c>
+      <c r="H72" t="str">
+        <f t="shared" si="5"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I72">
+        <v>6</v>
+      </c>
+      <c r="J72">
+        <v>5</v>
+      </c>
+      <c r="K72">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B73">
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>89</v>
-      </c>
-      <c r="D73">
-        <v>6</v>
-      </c>
-      <c r="E73">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" t="s">
-        <v>70</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
-      <c r="C74" t="s">
-        <v>97</v>
-      </c>
-      <c r="D74">
-        <v>4</v>
-      </c>
-      <c r="E74">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" t="s">
-        <v>70</v>
-      </c>
-      <c r="B75">
-        <v>1</v>
-      </c>
-      <c r="C75" t="s">
-        <v>91</v>
-      </c>
-      <c r="D75">
-        <v>17</v>
-      </c>
-      <c r="E75">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" t="s">
-        <v>70</v>
-      </c>
-      <c r="B76">
-        <v>1</v>
-      </c>
-      <c r="C76" t="s">
-        <v>95</v>
-      </c>
-      <c r="D76">
-        <v>11</v>
-      </c>
-      <c r="E76">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" t="s">
-        <v>70</v>
-      </c>
-      <c r="B77">
-        <v>2</v>
-      </c>
-      <c r="C77" t="s">
-        <v>97</v>
-      </c>
-      <c r="D77">
-        <v>2</v>
-      </c>
-      <c r="E77">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" t="s">
-        <v>70</v>
-      </c>
-      <c r="B78">
-        <v>2</v>
-      </c>
-      <c r="C78" t="s">
-        <v>91</v>
-      </c>
-      <c r="D78">
+        <v>88</v>
+      </c>
+      <c r="D73" t="s">
+        <v>92</v>
+      </c>
+      <c r="E73" t="s">
+        <v>86</v>
+      </c>
+      <c r="F73" t="str">
+        <f t="shared" si="3"/>
+        <v>#1 Noisy neighbors</v>
+      </c>
+      <c r="G73" t="str">
+        <f t="shared" si="4"/>
+        <v>#2 Bad smells</v>
+      </c>
+      <c r="H73" t="str">
+        <f t="shared" si="5"/>
+        <v>#3 Faulty electronics</v>
+      </c>
+      <c r="I73">
+        <v>23</v>
+      </c>
+      <c r="J73">
         <v>13</v>
       </c>
-      <c r="E78">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" t="s">
-        <v>70</v>
-      </c>
-      <c r="B79">
-        <v>2</v>
-      </c>
-      <c r="C79" t="s">
-        <v>95</v>
-      </c>
-      <c r="D79">
+      <c r="K73">
         <v>8</v>
-      </c>
-      <c r="E79">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" t="s">
-        <v>70</v>
-      </c>
-      <c r="B80">
-        <v>3</v>
-      </c>
-      <c r="C80" t="s">
-        <v>97</v>
-      </c>
-      <c r="D80">
-        <v>4</v>
-      </c>
-      <c r="E80">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" t="s">
-        <v>70</v>
-      </c>
-      <c r="B81">
-        <v>3</v>
-      </c>
-      <c r="C81" t="s">
-        <v>91</v>
-      </c>
-      <c r="D81">
-        <v>14</v>
-      </c>
-      <c r="E81">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" t="s">
-        <v>70</v>
-      </c>
-      <c r="B82">
-        <v>3</v>
-      </c>
-      <c r="C82" t="s">
-        <v>95</v>
-      </c>
-      <c r="D82">
-        <v>2</v>
-      </c>
-      <c r="E82">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" t="s">
-        <v>70</v>
-      </c>
-      <c r="B83">
-        <v>4</v>
-      </c>
-      <c r="C83" t="s">
-        <v>97</v>
-      </c>
-      <c r="D83">
-        <v>2</v>
-      </c>
-      <c r="E83">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" t="s">
-        <v>70</v>
-      </c>
-      <c r="B84">
-        <v>4</v>
-      </c>
-      <c r="C84" t="s">
-        <v>91</v>
-      </c>
-      <c r="D84">
-        <v>8</v>
-      </c>
-      <c r="E84">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" t="s">
-        <v>70</v>
-      </c>
-      <c r="B85">
-        <v>4</v>
-      </c>
-      <c r="C85" t="s">
-        <v>95</v>
-      </c>
-      <c r="D85">
-        <v>3</v>
-      </c>
-      <c r="E85">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" t="s">
-        <v>70</v>
-      </c>
-      <c r="B86">
-        <v>5</v>
-      </c>
-      <c r="C86" t="s">
-        <v>97</v>
-      </c>
-      <c r="D86">
-        <v>1</v>
-      </c>
-      <c r="E86">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" t="s">
-        <v>70</v>
-      </c>
-      <c r="B87">
-        <v>5</v>
-      </c>
-      <c r="C87" t="s">
-        <v>91</v>
-      </c>
-      <c r="D87">
-        <v>3</v>
-      </c>
-      <c r="E87">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" t="s">
-        <v>70</v>
-      </c>
-      <c r="B88">
-        <v>5</v>
-      </c>
-      <c r="C88" t="s">
-        <v>95</v>
-      </c>
-      <c r="D88">
-        <v>5</v>
-      </c>
-      <c r="E88">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" t="s">
-        <v>70</v>
-      </c>
-      <c r="B89">
-        <v>6</v>
-      </c>
-      <c r="C89" t="s">
-        <v>97</v>
-      </c>
-      <c r="D89">
-        <v>2</v>
-      </c>
-      <c r="E89">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" t="s">
-        <v>70</v>
-      </c>
-      <c r="B90">
-        <v>6</v>
-      </c>
-      <c r="C90" t="s">
-        <v>91</v>
-      </c>
-      <c r="D90">
-        <v>3</v>
-      </c>
-      <c r="E90">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" t="s">
-        <v>70</v>
-      </c>
-      <c r="B91">
-        <v>6</v>
-      </c>
-      <c r="C91" t="s">
-        <v>95</v>
-      </c>
-      <c r="D91">
-        <v>2</v>
-      </c>
-      <c r="E91">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" t="s">
-        <v>70</v>
-      </c>
-      <c r="B92">
-        <v>7</v>
-      </c>
-      <c r="C92" t="s">
-        <v>97</v>
-      </c>
-      <c r="D92">
-        <v>56</v>
-      </c>
-      <c r="E92">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" t="s">
-        <v>70</v>
-      </c>
-      <c r="B93">
-        <v>7</v>
-      </c>
-      <c r="C93" t="s">
-        <v>91</v>
-      </c>
-      <c r="D93">
-        <v>6</v>
-      </c>
-      <c r="E93">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" t="s">
-        <v>70</v>
-      </c>
-      <c r="B94">
-        <v>7</v>
-      </c>
-      <c r="C94" t="s">
-        <v>95</v>
-      </c>
-      <c r="D94">
-        <v>5</v>
-      </c>
-      <c r="E94">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" t="s">
-        <v>70</v>
-      </c>
-      <c r="B95">
-        <v>8</v>
-      </c>
-      <c r="C95" t="s">
-        <v>97</v>
-      </c>
-      <c r="D95">
-        <v>71</v>
-      </c>
-      <c r="E95">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" t="s">
-        <v>70</v>
-      </c>
-      <c r="B96">
-        <v>8</v>
-      </c>
-      <c r="C96" t="s">
-        <v>91</v>
-      </c>
-      <c r="D96">
-        <v>8</v>
-      </c>
-      <c r="E96">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" t="s">
-        <v>70</v>
-      </c>
-      <c r="B97">
-        <v>8</v>
-      </c>
-      <c r="C97" t="s">
-        <v>95</v>
-      </c>
-      <c r="D97">
-        <v>2</v>
-      </c>
-      <c r="E97">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" t="s">
-        <v>70</v>
-      </c>
-      <c r="B98">
-        <v>9</v>
-      </c>
-      <c r="C98" t="s">
-        <v>97</v>
-      </c>
-      <c r="D98">
-        <v>97</v>
-      </c>
-      <c r="E98">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" t="s">
-        <v>70</v>
-      </c>
-      <c r="B99">
-        <v>9</v>
-      </c>
-      <c r="C99" t="s">
-        <v>91</v>
-      </c>
-      <c r="D99">
-        <v>8</v>
-      </c>
-      <c r="E99">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" t="s">
-        <v>70</v>
-      </c>
-      <c r="B100">
-        <v>9</v>
-      </c>
-      <c r="C100" t="s">
-        <v>95</v>
-      </c>
-      <c r="D100">
-        <v>5</v>
-      </c>
-      <c r="E100">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" t="s">
-        <v>70</v>
-      </c>
-      <c r="B101">
-        <v>10</v>
-      </c>
-      <c r="C101" t="s">
-        <v>97</v>
-      </c>
-      <c r="D101">
-        <v>50</v>
-      </c>
-      <c r="E101">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" t="s">
-        <v>70</v>
-      </c>
-      <c r="B102">
-        <v>10</v>
-      </c>
-      <c r="C102" t="s">
-        <v>91</v>
-      </c>
-      <c r="D102">
-        <v>3</v>
-      </c>
-      <c r="E102">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" t="s">
-        <v>70</v>
-      </c>
-      <c r="B103">
-        <v>10</v>
-      </c>
-      <c r="C103" t="s">
-        <v>95</v>
-      </c>
-      <c r="D103">
-        <v>0</v>
-      </c>
-      <c r="E103">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" t="s">
-        <v>70</v>
-      </c>
-      <c r="B104">
-        <v>11</v>
-      </c>
-      <c r="C104" t="s">
-        <v>97</v>
-      </c>
-      <c r="D104">
-        <v>52</v>
-      </c>
-      <c r="E104">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" t="s">
-        <v>70</v>
-      </c>
-      <c r="B105">
-        <v>11</v>
-      </c>
-      <c r="C105" t="s">
-        <v>91</v>
-      </c>
-      <c r="D105">
-        <v>5</v>
-      </c>
-      <c r="E105">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" t="s">
-        <v>70</v>
-      </c>
-      <c r="B106">
-        <v>11</v>
-      </c>
-      <c r="C106" t="s">
-        <v>95</v>
-      </c>
-      <c r="D106">
-        <v>3</v>
-      </c>
-      <c r="E106">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" t="s">
-        <v>70</v>
-      </c>
-      <c r="B107">
-        <v>12</v>
-      </c>
-      <c r="C107" t="s">
-        <v>97</v>
-      </c>
-      <c r="D107">
-        <v>54</v>
-      </c>
-      <c r="E107">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" t="s">
-        <v>70</v>
-      </c>
-      <c r="B108">
-        <v>12</v>
-      </c>
-      <c r="C108" t="s">
-        <v>91</v>
-      </c>
-      <c r="D108">
-        <v>5</v>
-      </c>
-      <c r="E108">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" t="s">
-        <v>70</v>
-      </c>
-      <c r="B109">
-        <v>12</v>
-      </c>
-      <c r="C109" t="s">
-        <v>95</v>
-      </c>
-      <c r="D109">
-        <v>1</v>
-      </c>
-      <c r="E109">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" t="s">
-        <v>71</v>
-      </c>
-      <c r="B110">
-        <v>1</v>
-      </c>
-      <c r="C110" t="s">
-        <v>88</v>
-      </c>
-      <c r="D110">
-        <v>1</v>
-      </c>
-      <c r="E110">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" t="s">
-        <v>71</v>
-      </c>
-      <c r="B111">
-        <v>1</v>
-      </c>
-      <c r="C111" t="s">
-        <v>90</v>
-      </c>
-      <c r="D111">
-        <v>6</v>
-      </c>
-      <c r="E111">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" t="s">
-        <v>71</v>
-      </c>
-      <c r="B112">
-        <v>1</v>
-      </c>
-      <c r="C112" t="s">
-        <v>89</v>
-      </c>
-      <c r="D112">
-        <v>2</v>
-      </c>
-      <c r="E112">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" t="s">
-        <v>71</v>
-      </c>
-      <c r="B113">
-        <v>2</v>
-      </c>
-      <c r="C113" t="s">
-        <v>88</v>
-      </c>
-      <c r="D113">
-        <v>5</v>
-      </c>
-      <c r="E113">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" t="s">
-        <v>71</v>
-      </c>
-      <c r="B114">
-        <v>2</v>
-      </c>
-      <c r="C114" t="s">
-        <v>90</v>
-      </c>
-      <c r="D114">
-        <v>3</v>
-      </c>
-      <c r="E114">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" t="s">
-        <v>71</v>
-      </c>
-      <c r="B115">
-        <v>2</v>
-      </c>
-      <c r="C115" t="s">
-        <v>89</v>
-      </c>
-      <c r="D115">
-        <v>1</v>
-      </c>
-      <c r="E115">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" t="s">
-        <v>71</v>
-      </c>
-      <c r="B116">
-        <v>3</v>
-      </c>
-      <c r="C116" t="s">
-        <v>88</v>
-      </c>
-      <c r="D116">
-        <v>0</v>
-      </c>
-      <c r="E116">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="A117" t="s">
-        <v>71</v>
-      </c>
-      <c r="B117">
-        <v>3</v>
-      </c>
-      <c r="C117" t="s">
-        <v>90</v>
-      </c>
-      <c r="D117">
-        <v>3</v>
-      </c>
-      <c r="E117">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="A118" t="s">
-        <v>71</v>
-      </c>
-      <c r="B118">
-        <v>3</v>
-      </c>
-      <c r="C118" t="s">
-        <v>89</v>
-      </c>
-      <c r="D118">
-        <v>3</v>
-      </c>
-      <c r="E118">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
-      <c r="A119" t="s">
-        <v>71</v>
-      </c>
-      <c r="B119">
-        <v>4</v>
-      </c>
-      <c r="C119" t="s">
-        <v>88</v>
-      </c>
-      <c r="D119">
-        <v>2</v>
-      </c>
-      <c r="E119">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
-      <c r="A120" t="s">
-        <v>71</v>
-      </c>
-      <c r="B120">
-        <v>4</v>
-      </c>
-      <c r="C120" t="s">
-        <v>90</v>
-      </c>
-      <c r="D120">
-        <v>2</v>
-      </c>
-      <c r="E120">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="A121" t="s">
-        <v>71</v>
-      </c>
-      <c r="B121">
-        <v>4</v>
-      </c>
-      <c r="C121" t="s">
-        <v>89</v>
-      </c>
-      <c r="D121">
-        <v>3</v>
-      </c>
-      <c r="E121">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122" t="s">
-        <v>71</v>
-      </c>
-      <c r="B122">
-        <v>5</v>
-      </c>
-      <c r="C122" t="s">
-        <v>88</v>
-      </c>
-      <c r="D122">
-        <v>4</v>
-      </c>
-      <c r="E122">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123" t="s">
-        <v>71</v>
-      </c>
-      <c r="B123">
-        <v>5</v>
-      </c>
-      <c r="C123" t="s">
-        <v>90</v>
-      </c>
-      <c r="D123">
-        <v>3</v>
-      </c>
-      <c r="E123">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="A124" t="s">
-        <v>71</v>
-      </c>
-      <c r="B124">
-        <v>5</v>
-      </c>
-      <c r="C124" t="s">
-        <v>89</v>
-      </c>
-      <c r="D124">
-        <v>3</v>
-      </c>
-      <c r="E124">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125" t="s">
-        <v>71</v>
-      </c>
-      <c r="B125">
-        <v>6</v>
-      </c>
-      <c r="C125" t="s">
-        <v>88</v>
-      </c>
-      <c r="D125">
-        <v>1</v>
-      </c>
-      <c r="E125">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
-      <c r="A126" t="s">
-        <v>71</v>
-      </c>
-      <c r="B126">
-        <v>6</v>
-      </c>
-      <c r="C126" t="s">
-        <v>90</v>
-      </c>
-      <c r="D126">
-        <v>0</v>
-      </c>
-      <c r="E126">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
-      <c r="A127" t="s">
-        <v>71</v>
-      </c>
-      <c r="B127">
-        <v>6</v>
-      </c>
-      <c r="C127" t="s">
-        <v>89</v>
-      </c>
-      <c r="D127">
-        <v>0</v>
-      </c>
-      <c r="E127">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
-      <c r="A128" t="s">
-        <v>71</v>
-      </c>
-      <c r="B128">
-        <v>7</v>
-      </c>
-      <c r="C128" t="s">
-        <v>88</v>
-      </c>
-      <c r="D128">
-        <v>6</v>
-      </c>
-      <c r="E128">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
-      <c r="A129" t="s">
-        <v>71</v>
-      </c>
-      <c r="B129">
-        <v>7</v>
-      </c>
-      <c r="C129" t="s">
-        <v>90</v>
-      </c>
-      <c r="D129">
-        <v>1</v>
-      </c>
-      <c r="E129">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
-      <c r="A130" t="s">
-        <v>71</v>
-      </c>
-      <c r="B130">
-        <v>7</v>
-      </c>
-      <c r="C130" t="s">
-        <v>89</v>
-      </c>
-      <c r="D130">
-        <v>1</v>
-      </c>
-      <c r="E130">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="A131" t="s">
-        <v>71</v>
-      </c>
-      <c r="B131">
-        <v>8</v>
-      </c>
-      <c r="C131" t="s">
-        <v>88</v>
-      </c>
-      <c r="D131">
-        <v>5</v>
-      </c>
-      <c r="E131">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
-      <c r="A132" t="s">
-        <v>71</v>
-      </c>
-      <c r="B132">
-        <v>8</v>
-      </c>
-      <c r="C132" t="s">
-        <v>90</v>
-      </c>
-      <c r="D132">
-        <v>0</v>
-      </c>
-      <c r="E132">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
-      <c r="A133" t="s">
-        <v>71</v>
-      </c>
-      <c r="B133">
-        <v>8</v>
-      </c>
-      <c r="C133" t="s">
-        <v>89</v>
-      </c>
-      <c r="D133">
-        <v>1</v>
-      </c>
-      <c r="E133">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
-      <c r="A134" t="s">
-        <v>71</v>
-      </c>
-      <c r="B134">
-        <v>9</v>
-      </c>
-      <c r="C134" t="s">
-        <v>88</v>
-      </c>
-      <c r="D134">
-        <v>1</v>
-      </c>
-      <c r="E134">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
-      <c r="A135" t="s">
-        <v>71</v>
-      </c>
-      <c r="B135">
-        <v>9</v>
-      </c>
-      <c r="C135" t="s">
-        <v>90</v>
-      </c>
-      <c r="D135">
-        <v>0</v>
-      </c>
-      <c r="E135">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
-      <c r="A136" t="s">
-        <v>71</v>
-      </c>
-      <c r="B136">
-        <v>9</v>
-      </c>
-      <c r="C136" t="s">
-        <v>89</v>
-      </c>
-      <c r="D136">
-        <v>1</v>
-      </c>
-      <c r="E136">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" t="s">
-        <v>71</v>
-      </c>
-      <c r="B137">
-        <v>10</v>
-      </c>
-      <c r="C137" t="s">
-        <v>88</v>
-      </c>
-      <c r="D137">
-        <v>1</v>
-      </c>
-      <c r="E137">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138" t="s">
-        <v>71</v>
-      </c>
-      <c r="B138">
-        <v>10</v>
-      </c>
-      <c r="C138" t="s">
-        <v>90</v>
-      </c>
-      <c r="D138">
-        <v>2</v>
-      </c>
-      <c r="E138">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
-      <c r="A139" t="s">
-        <v>71</v>
-      </c>
-      <c r="B139">
-        <v>10</v>
-      </c>
-      <c r="C139" t="s">
-        <v>89</v>
-      </c>
-      <c r="D139">
-        <v>1</v>
-      </c>
-      <c r="E139">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="A140" t="s">
-        <v>71</v>
-      </c>
-      <c r="B140">
-        <v>11</v>
-      </c>
-      <c r="C140" t="s">
-        <v>88</v>
-      </c>
-      <c r="D140">
-        <v>1</v>
-      </c>
-      <c r="E140">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
-      <c r="A141" t="s">
-        <v>71</v>
-      </c>
-      <c r="B141">
-        <v>11</v>
-      </c>
-      <c r="C141" t="s">
-        <v>90</v>
-      </c>
-      <c r="D141">
-        <v>0</v>
-      </c>
-      <c r="E141">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
-      <c r="A142" t="s">
-        <v>71</v>
-      </c>
-      <c r="B142">
-        <v>11</v>
-      </c>
-      <c r="C142" t="s">
-        <v>89</v>
-      </c>
-      <c r="D142">
-        <v>2</v>
-      </c>
-      <c r="E142">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" t="s">
-        <v>71</v>
-      </c>
-      <c r="B143">
-        <v>12</v>
-      </c>
-      <c r="C143" t="s">
-        <v>88</v>
-      </c>
-      <c r="D143">
-        <v>4</v>
-      </c>
-      <c r="E143">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="A144" t="s">
-        <v>71</v>
-      </c>
-      <c r="B144">
-        <v>12</v>
-      </c>
-      <c r="C144" t="s">
-        <v>90</v>
-      </c>
-      <c r="D144">
-        <v>0</v>
-      </c>
-      <c r="E144">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="A145" t="s">
-        <v>71</v>
-      </c>
-      <c r="B145">
-        <v>12</v>
-      </c>
-      <c r="C145" t="s">
-        <v>89</v>
-      </c>
-      <c r="D145">
-        <v>0</v>
-      </c>
-      <c r="E145">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
-      <c r="A146" t="s">
-        <v>72</v>
-      </c>
-      <c r="B146">
-        <v>1</v>
-      </c>
-      <c r="C146" t="s">
-        <v>90</v>
-      </c>
-      <c r="D146">
-        <v>6</v>
-      </c>
-      <c r="E146">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
-      <c r="A147" t="s">
-        <v>72</v>
-      </c>
-      <c r="B147">
-        <v>1</v>
-      </c>
-      <c r="C147" t="s">
-        <v>89</v>
-      </c>
-      <c r="D147">
-        <v>1</v>
-      </c>
-      <c r="E147">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
-      <c r="A148" t="s">
-        <v>72</v>
-      </c>
-      <c r="B148">
-        <v>1</v>
-      </c>
-      <c r="C148" t="s">
-        <v>88</v>
-      </c>
-      <c r="D148">
-        <v>2</v>
-      </c>
-      <c r="E148">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
-      <c r="A149" t="s">
-        <v>72</v>
-      </c>
-      <c r="B149">
-        <v>2</v>
-      </c>
-      <c r="C149" t="s">
-        <v>90</v>
-      </c>
-      <c r="D149">
-        <v>8</v>
-      </c>
-      <c r="E149">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
-      <c r="A150" t="s">
-        <v>72</v>
-      </c>
-      <c r="B150">
-        <v>2</v>
-      </c>
-      <c r="C150" t="s">
-        <v>89</v>
-      </c>
-      <c r="D150">
-        <v>2</v>
-      </c>
-      <c r="E150">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
-      <c r="A151" t="s">
-        <v>72</v>
-      </c>
-      <c r="B151">
-        <v>2</v>
-      </c>
-      <c r="C151" t="s">
-        <v>88</v>
-      </c>
-      <c r="D151">
-        <v>3</v>
-      </c>
-      <c r="E151">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
-      <c r="A152" t="s">
-        <v>72</v>
-      </c>
-      <c r="B152">
-        <v>3</v>
-      </c>
-      <c r="C152" t="s">
-        <v>90</v>
-      </c>
-      <c r="D152">
-        <v>5</v>
-      </c>
-      <c r="E152">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
-      <c r="A153" t="s">
-        <v>72</v>
-      </c>
-      <c r="B153">
-        <v>3</v>
-      </c>
-      <c r="C153" t="s">
-        <v>89</v>
-      </c>
-      <c r="D153">
-        <v>3</v>
-      </c>
-      <c r="E153">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
-      <c r="A154" t="s">
-        <v>72</v>
-      </c>
-      <c r="B154">
-        <v>3</v>
-      </c>
-      <c r="C154" t="s">
-        <v>88</v>
-      </c>
-      <c r="D154">
-        <v>1</v>
-      </c>
-      <c r="E154">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
-      <c r="A155" t="s">
-        <v>72</v>
-      </c>
-      <c r="B155">
-        <v>4</v>
-      </c>
-      <c r="C155" t="s">
-        <v>90</v>
-      </c>
-      <c r="D155">
-        <v>4</v>
-      </c>
-      <c r="E155">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
-      <c r="A156" t="s">
-        <v>72</v>
-      </c>
-      <c r="B156">
-        <v>4</v>
-      </c>
-      <c r="C156" t="s">
-        <v>89</v>
-      </c>
-      <c r="D156">
-        <v>2</v>
-      </c>
-      <c r="E156">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
-      <c r="A157" t="s">
-        <v>72</v>
-      </c>
-      <c r="B157">
-        <v>4</v>
-      </c>
-      <c r="C157" t="s">
-        <v>88</v>
-      </c>
-      <c r="D157">
-        <v>0</v>
-      </c>
-      <c r="E157">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
-      <c r="A158" t="s">
-        <v>72</v>
-      </c>
-      <c r="B158">
-        <v>5</v>
-      </c>
-      <c r="C158" t="s">
-        <v>90</v>
-      </c>
-      <c r="D158">
-        <v>7</v>
-      </c>
-      <c r="E158">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5">
-      <c r="A159" t="s">
-        <v>72</v>
-      </c>
-      <c r="B159">
-        <v>5</v>
-      </c>
-      <c r="C159" t="s">
-        <v>89</v>
-      </c>
-      <c r="D159">
-        <v>6</v>
-      </c>
-      <c r="E159">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5">
-      <c r="A160" t="s">
-        <v>72</v>
-      </c>
-      <c r="B160">
-        <v>5</v>
-      </c>
-      <c r="C160" t="s">
-        <v>88</v>
-      </c>
-      <c r="D160">
-        <v>2</v>
-      </c>
-      <c r="E160">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
-      <c r="A161" t="s">
-        <v>72</v>
-      </c>
-      <c r="B161">
-        <v>6</v>
-      </c>
-      <c r="C161" t="s">
-        <v>90</v>
-      </c>
-      <c r="D161">
-        <v>0</v>
-      </c>
-      <c r="E161">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5">
-      <c r="A162" t="s">
-        <v>72</v>
-      </c>
-      <c r="B162">
-        <v>6</v>
-      </c>
-      <c r="C162" t="s">
-        <v>89</v>
-      </c>
-      <c r="D162">
-        <v>2</v>
-      </c>
-      <c r="E162">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5">
-      <c r="A163" t="s">
-        <v>72</v>
-      </c>
-      <c r="B163">
-        <v>6</v>
-      </c>
-      <c r="C163" t="s">
-        <v>88</v>
-      </c>
-      <c r="D163">
-        <v>0</v>
-      </c>
-      <c r="E163">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
-      <c r="A164" t="s">
-        <v>72</v>
-      </c>
-      <c r="B164">
-        <v>7</v>
-      </c>
-      <c r="C164" t="s">
-        <v>90</v>
-      </c>
-      <c r="D164">
-        <v>0</v>
-      </c>
-      <c r="E164">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5">
-      <c r="A165" t="s">
-        <v>72</v>
-      </c>
-      <c r="B165">
-        <v>7</v>
-      </c>
-      <c r="C165" t="s">
-        <v>89</v>
-      </c>
-      <c r="D165">
-        <v>1</v>
-      </c>
-      <c r="E165">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5">
-      <c r="A166" t="s">
-        <v>72</v>
-      </c>
-      <c r="B166">
-        <v>7</v>
-      </c>
-      <c r="C166" t="s">
-        <v>88</v>
-      </c>
-      <c r="D166">
-        <v>1</v>
-      </c>
-      <c r="E166">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5">
-      <c r="A167" t="s">
-        <v>72</v>
-      </c>
-      <c r="B167">
-        <v>8</v>
-      </c>
-      <c r="C167" t="s">
-        <v>90</v>
-      </c>
-      <c r="D167">
-        <v>0</v>
-      </c>
-      <c r="E167">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
-      <c r="A168" t="s">
-        <v>72</v>
-      </c>
-      <c r="B168">
-        <v>8</v>
-      </c>
-      <c r="C168" t="s">
-        <v>89</v>
-      </c>
-      <c r="D168">
-        <v>4</v>
-      </c>
-      <c r="E168">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5">
-      <c r="A169" t="s">
-        <v>72</v>
-      </c>
-      <c r="B169">
-        <v>8</v>
-      </c>
-      <c r="C169" t="s">
-        <v>88</v>
-      </c>
-      <c r="D169">
-        <v>0</v>
-      </c>
-      <c r="E169">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
-      <c r="A170" t="s">
-        <v>72</v>
-      </c>
-      <c r="B170">
-        <v>9</v>
-      </c>
-      <c r="C170" t="s">
-        <v>90</v>
-      </c>
-      <c r="D170">
-        <v>1</v>
-      </c>
-      <c r="E170">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5">
-      <c r="A171" t="s">
-        <v>72</v>
-      </c>
-      <c r="B171">
-        <v>9</v>
-      </c>
-      <c r="C171" t="s">
-        <v>89</v>
-      </c>
-      <c r="D171">
-        <v>2</v>
-      </c>
-      <c r="E171">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5">
-      <c r="A172" t="s">
-        <v>72</v>
-      </c>
-      <c r="B172">
-        <v>9</v>
-      </c>
-      <c r="C172" t="s">
-        <v>88</v>
-      </c>
-      <c r="D172">
-        <v>3</v>
-      </c>
-      <c r="E172">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
-      <c r="A173" t="s">
-        <v>72</v>
-      </c>
-      <c r="B173">
-        <v>10</v>
-      </c>
-      <c r="C173" t="s">
-        <v>90</v>
-      </c>
-      <c r="D173">
-        <v>0</v>
-      </c>
-      <c r="E173">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
-      <c r="A174" t="s">
-        <v>72</v>
-      </c>
-      <c r="B174">
-        <v>10</v>
-      </c>
-      <c r="C174" t="s">
-        <v>89</v>
-      </c>
-      <c r="D174">
-        <v>4</v>
-      </c>
-      <c r="E174">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
-      <c r="A175" t="s">
-        <v>72</v>
-      </c>
-      <c r="B175">
-        <v>10</v>
-      </c>
-      <c r="C175" t="s">
-        <v>88</v>
-      </c>
-      <c r="D175">
-        <v>2</v>
-      </c>
-      <c r="E175">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
-      <c r="A176" t="s">
-        <v>72</v>
-      </c>
-      <c r="B176">
-        <v>11</v>
-      </c>
-      <c r="C176" t="s">
-        <v>90</v>
-      </c>
-      <c r="D176">
-        <v>0</v>
-      </c>
-      <c r="E176">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
-      <c r="A177" t="s">
-        <v>72</v>
-      </c>
-      <c r="B177">
-        <v>11</v>
-      </c>
-      <c r="C177" t="s">
-        <v>89</v>
-      </c>
-      <c r="D177">
-        <v>3</v>
-      </c>
-      <c r="E177">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
-      <c r="A178" t="s">
-        <v>72</v>
-      </c>
-      <c r="B178">
-        <v>11</v>
-      </c>
-      <c r="C178" t="s">
-        <v>88</v>
-      </c>
-      <c r="D178">
-        <v>3</v>
-      </c>
-      <c r="E178">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
-      <c r="A179" t="s">
-        <v>72</v>
-      </c>
-      <c r="B179">
-        <v>12</v>
-      </c>
-      <c r="C179" t="s">
-        <v>90</v>
-      </c>
-      <c r="D179">
-        <v>1</v>
-      </c>
-      <c r="E179">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
-      <c r="A180" t="s">
-        <v>72</v>
-      </c>
-      <c r="B180">
-        <v>12</v>
-      </c>
-      <c r="C180" t="s">
-        <v>89</v>
-      </c>
-      <c r="D180">
-        <v>0</v>
-      </c>
-      <c r="E180">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
-      <c r="A181" t="s">
-        <v>72</v>
-      </c>
-      <c r="B181">
-        <v>12</v>
-      </c>
-      <c r="C181" t="s">
-        <v>88</v>
-      </c>
-      <c r="D181">
-        <v>3</v>
-      </c>
-      <c r="E181">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
-      <c r="A182" t="s">
-        <v>73</v>
-      </c>
-      <c r="B182">
-        <v>1</v>
-      </c>
-      <c r="C182" t="s">
-        <v>91</v>
-      </c>
-      <c r="D182">
-        <v>16</v>
-      </c>
-      <c r="E182">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
-      <c r="A183" t="s">
-        <v>73</v>
-      </c>
-      <c r="B183">
-        <v>1</v>
-      </c>
-      <c r="C183" t="s">
-        <v>95</v>
-      </c>
-      <c r="D183">
-        <v>23</v>
-      </c>
-      <c r="E183">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5">
-      <c r="A184" t="s">
-        <v>73</v>
-      </c>
-      <c r="B184">
-        <v>1</v>
-      </c>
-      <c r="C184" t="s">
-        <v>89</v>
-      </c>
-      <c r="D184">
-        <v>6</v>
-      </c>
-      <c r="E184">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
-      <c r="A185" t="s">
-        <v>73</v>
-      </c>
-      <c r="B185">
-        <v>2</v>
-      </c>
-      <c r="C185" t="s">
-        <v>91</v>
-      </c>
-      <c r="D185">
-        <v>34</v>
-      </c>
-      <c r="E185">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
-      <c r="A186" t="s">
-        <v>73</v>
-      </c>
-      <c r="B186">
-        <v>2</v>
-      </c>
-      <c r="C186" t="s">
-        <v>95</v>
-      </c>
-      <c r="D186">
-        <v>19</v>
-      </c>
-      <c r="E186">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
-      <c r="A187" t="s">
-        <v>73</v>
-      </c>
-      <c r="B187">
-        <v>2</v>
-      </c>
-      <c r="C187" t="s">
-        <v>89</v>
-      </c>
-      <c r="D187">
-        <v>5</v>
-      </c>
-      <c r="E187">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
-      <c r="A188" t="s">
-        <v>73</v>
-      </c>
-      <c r="B188">
-        <v>3</v>
-      </c>
-      <c r="C188" t="s">
-        <v>91</v>
-      </c>
-      <c r="D188">
-        <v>12</v>
-      </c>
-      <c r="E188">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
-      <c r="A189" t="s">
-        <v>73</v>
-      </c>
-      <c r="B189">
-        <v>3</v>
-      </c>
-      <c r="C189" t="s">
-        <v>95</v>
-      </c>
-      <c r="D189">
-        <v>7</v>
-      </c>
-      <c r="E189">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
-      <c r="A190" t="s">
-        <v>73</v>
-      </c>
-      <c r="B190">
-        <v>3</v>
-      </c>
-      <c r="C190" t="s">
-        <v>89</v>
-      </c>
-      <c r="D190">
-        <v>11</v>
-      </c>
-      <c r="E190">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5">
-      <c r="A191" t="s">
-        <v>73</v>
-      </c>
-      <c r="B191">
-        <v>4</v>
-      </c>
-      <c r="C191" t="s">
-        <v>91</v>
-      </c>
-      <c r="D191">
-        <v>28</v>
-      </c>
-      <c r="E191">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
-      <c r="A192" t="s">
-        <v>73</v>
-      </c>
-      <c r="B192">
-        <v>4</v>
-      </c>
-      <c r="C192" t="s">
-        <v>95</v>
-      </c>
-      <c r="D192">
-        <v>11</v>
-      </c>
-      <c r="E192">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5">
-      <c r="A193" t="s">
-        <v>73</v>
-      </c>
-      <c r="B193">
-        <v>4</v>
-      </c>
-      <c r="C193" t="s">
-        <v>89</v>
-      </c>
-      <c r="D193">
-        <v>8</v>
-      </c>
-      <c r="E193">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5">
-      <c r="A194" t="s">
-        <v>73</v>
-      </c>
-      <c r="B194">
-        <v>5</v>
-      </c>
-      <c r="C194" t="s">
-        <v>91</v>
-      </c>
-      <c r="D194">
-        <v>16</v>
-      </c>
-      <c r="E194">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5">
-      <c r="A195" t="s">
-        <v>73</v>
-      </c>
-      <c r="B195">
-        <v>5</v>
-      </c>
-      <c r="C195" t="s">
-        <v>95</v>
-      </c>
-      <c r="D195">
-        <v>11</v>
-      </c>
-      <c r="E195">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5">
-      <c r="A196" t="s">
-        <v>73</v>
-      </c>
-      <c r="B196">
-        <v>5</v>
-      </c>
-      <c r="C196" t="s">
-        <v>89</v>
-      </c>
-      <c r="D196">
-        <v>11</v>
-      </c>
-      <c r="E196">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5">
-      <c r="A197" t="s">
-        <v>73</v>
-      </c>
-      <c r="B197">
-        <v>6</v>
-      </c>
-      <c r="C197" t="s">
-        <v>91</v>
-      </c>
-      <c r="D197">
-        <v>9</v>
-      </c>
-      <c r="E197">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5">
-      <c r="A198" t="s">
-        <v>73</v>
-      </c>
-      <c r="B198">
-        <v>6</v>
-      </c>
-      <c r="C198" t="s">
-        <v>95</v>
-      </c>
-      <c r="D198">
-        <v>12</v>
-      </c>
-      <c r="E198">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5">
-      <c r="A199" t="s">
-        <v>73</v>
-      </c>
-      <c r="B199">
-        <v>6</v>
-      </c>
-      <c r="C199" t="s">
-        <v>89</v>
-      </c>
-      <c r="D199">
-        <v>3</v>
-      </c>
-      <c r="E199">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5">
-      <c r="A200" t="s">
-        <v>73</v>
-      </c>
-      <c r="B200">
-        <v>7</v>
-      </c>
-      <c r="C200" t="s">
-        <v>91</v>
-      </c>
-      <c r="D200">
-        <v>19</v>
-      </c>
-      <c r="E200">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5">
-      <c r="A201" t="s">
-        <v>73</v>
-      </c>
-      <c r="B201">
-        <v>7</v>
-      </c>
-      <c r="C201" t="s">
-        <v>95</v>
-      </c>
-      <c r="D201">
-        <v>8</v>
-      </c>
-      <c r="E201">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5">
-      <c r="A202" t="s">
-        <v>73</v>
-      </c>
-      <c r="B202">
-        <v>7</v>
-      </c>
-      <c r="C202" t="s">
-        <v>89</v>
-      </c>
-      <c r="D202">
-        <v>3</v>
-      </c>
-      <c r="E202">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5">
-      <c r="A203" t="s">
-        <v>73</v>
-      </c>
-      <c r="B203">
-        <v>8</v>
-      </c>
-      <c r="C203" t="s">
-        <v>91</v>
-      </c>
-      <c r="D203">
-        <v>21</v>
-      </c>
-      <c r="E203">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5">
-      <c r="A204" t="s">
-        <v>73</v>
-      </c>
-      <c r="B204">
-        <v>8</v>
-      </c>
-      <c r="C204" t="s">
-        <v>95</v>
-      </c>
-      <c r="D204">
-        <v>10</v>
-      </c>
-      <c r="E204">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5">
-      <c r="A205" t="s">
-        <v>73</v>
-      </c>
-      <c r="B205">
-        <v>8</v>
-      </c>
-      <c r="C205" t="s">
-        <v>89</v>
-      </c>
-      <c r="D205">
-        <v>6</v>
-      </c>
-      <c r="E205">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5">
-      <c r="A206" t="s">
-        <v>73</v>
-      </c>
-      <c r="B206">
-        <v>9</v>
-      </c>
-      <c r="C206" t="s">
-        <v>91</v>
-      </c>
-      <c r="D206">
-        <v>5</v>
-      </c>
-      <c r="E206">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5">
-      <c r="A207" t="s">
-        <v>73</v>
-      </c>
-      <c r="B207">
-        <v>9</v>
-      </c>
-      <c r="C207" t="s">
-        <v>95</v>
-      </c>
-      <c r="D207">
-        <v>11</v>
-      </c>
-      <c r="E207">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5">
-      <c r="A208" t="s">
-        <v>73</v>
-      </c>
-      <c r="B208">
-        <v>9</v>
-      </c>
-      <c r="C208" t="s">
-        <v>89</v>
-      </c>
-      <c r="D208">
-        <v>2</v>
-      </c>
-      <c r="E208">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5">
-      <c r="A209" t="s">
-        <v>73</v>
-      </c>
-      <c r="B209">
-        <v>10</v>
-      </c>
-      <c r="C209" t="s">
-        <v>91</v>
-      </c>
-      <c r="D209">
-        <v>23</v>
-      </c>
-      <c r="E209">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5">
-      <c r="A210" t="s">
-        <v>73</v>
-      </c>
-      <c r="B210">
-        <v>10</v>
-      </c>
-      <c r="C210" t="s">
-        <v>95</v>
-      </c>
-      <c r="D210">
-        <v>37</v>
-      </c>
-      <c r="E210">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5">
-      <c r="A211" t="s">
-        <v>73</v>
-      </c>
-      <c r="B211">
-        <v>10</v>
-      </c>
-      <c r="C211" t="s">
-        <v>89</v>
-      </c>
-      <c r="D211">
-        <v>19</v>
-      </c>
-      <c r="E211">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5">
-      <c r="A212" t="s">
-        <v>73</v>
-      </c>
-      <c r="B212">
-        <v>11</v>
-      </c>
-      <c r="C212" t="s">
-        <v>91</v>
-      </c>
-      <c r="D212">
-        <v>6</v>
-      </c>
-      <c r="E212">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5">
-      <c r="A213" t="s">
-        <v>73</v>
-      </c>
-      <c r="B213">
-        <v>11</v>
-      </c>
-      <c r="C213" t="s">
-        <v>95</v>
-      </c>
-      <c r="D213">
-        <v>5</v>
-      </c>
-      <c r="E213">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5">
-      <c r="A214" t="s">
-        <v>73</v>
-      </c>
-      <c r="B214">
-        <v>11</v>
-      </c>
-      <c r="C214" t="s">
-        <v>89</v>
-      </c>
-      <c r="D214">
-        <v>7</v>
-      </c>
-      <c r="E214">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5">
-      <c r="A215" t="s">
-        <v>73</v>
-      </c>
-      <c r="B215">
-        <v>12</v>
-      </c>
-      <c r="C215" t="s">
-        <v>91</v>
-      </c>
-      <c r="D215">
-        <v>23</v>
-      </c>
-      <c r="E215">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5">
-      <c r="A216" t="s">
-        <v>73</v>
-      </c>
-      <c r="B216">
-        <v>12</v>
-      </c>
-      <c r="C216" t="s">
-        <v>95</v>
-      </c>
-      <c r="D216">
-        <v>13</v>
-      </c>
-      <c r="E216">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5">
-      <c r="A217" t="s">
-        <v>73</v>
-      </c>
-      <c r="B217">
-        <v>12</v>
-      </c>
-      <c r="C217" t="s">
-        <v>89</v>
-      </c>
-      <c r="D217">
-        <v>8</v>
-      </c>
-      <c r="E217">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -23384,7 +21990,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="27" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B1" s="27" t="s">
         <v>33</v>
@@ -23392,7 +21998,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B2">
         <v>485</v>
@@ -23400,7 +22006,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B3">
         <v>399</v>
@@ -23408,7 +22014,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B4">
         <v>283</v>
@@ -23416,7 +22022,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B5">
         <v>278</v>
@@ -23424,7 +22030,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B6">
         <v>221</v>
@@ -23432,7 +22038,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B7">
         <v>189</v>
@@ -23440,7 +22046,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B8">
         <v>182</v>
@@ -23448,7 +22054,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B9">
         <v>178</v>
@@ -23456,7 +22062,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B10">
         <v>146</v>
@@ -23464,7 +22070,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B11">
         <v>146</v>
@@ -23472,7 +22078,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B12">
         <v>125</v>
